--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,7 +175,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>53.6 → 45.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>53.6</t>
+  </si>
+  <si>
+    <t>45.6</t>
+  </si>
+  <si>
+    <t>57.0 → 47.5</t>
+  </si>
+  <si>
+    <t>57.0</t>
+  </si>
+  <si>
+    <t>47.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -377,17 +413,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -899,10 +936,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>407.75</v>
+        <v>407.15</v>
       </c>
       <c r="D2">
-        <v>-0.07000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -911,46 +948,46 @@
         <v>268.05</v>
       </c>
       <c r="G2">
-        <v>-3.99</v>
+        <v>-4.13</v>
       </c>
       <c r="H2">
-        <v>52.12</v>
+        <v>51.89</v>
       </c>
       <c r="I2">
-        <v>-3.91</v>
+        <v>-3.06</v>
       </c>
       <c r="J2">
-        <v>-0.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="K2">
-        <v>19.5</v>
+        <v>18.25</v>
       </c>
       <c r="L2">
-        <v>46.44</v>
+        <v>44.38</v>
       </c>
       <c r="M2">
-        <v>28.59</v>
+        <v>28.77</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>416.4</v>
+        <v>413.83</v>
       </c>
       <c r="Q2">
-        <v>404.79</v>
+        <v>405.18</v>
       </c>
       <c r="R2">
-        <v>387.82</v>
+        <v>388.95</v>
       </c>
       <c r="S2">
-        <v>353</v>
+        <v>353.51</v>
       </c>
       <c r="T2">
-        <v>15.51</v>
+        <v>15.17</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -965,34 +1002,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>53.23</v>
+        <v>52.87</v>
       </c>
       <c r="Z2">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="AA2">
-        <v>6.94</v>
+        <v>6.79</v>
       </c>
       <c r="AB2">
-        <v>-0.04</v>
+        <v>-0.59</v>
       </c>
       <c r="AC2">
-        <v>43.9</v>
+        <v>25.01</v>
       </c>
       <c r="AD2">
-        <v>65.23</v>
+        <v>45.19</v>
       </c>
       <c r="AE2">
-        <v>11.56</v>
+        <v>11.22</v>
       </c>
       <c r="AF2">
-        <v>-46.81</v>
+        <v>4.31</v>
       </c>
       <c r="AG2">
-        <v>425.66</v>
+        <v>425.91</v>
       </c>
       <c r="AH2">
-        <v>383.92</v>
+        <v>384.46</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1001,7 +1038,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>25.77</v>
+        <v>23.83</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1012,10 +1049,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>61.04</v>
+        <v>58.63</v>
       </c>
       <c r="D3">
-        <v>-3.62</v>
+        <v>-3.95</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1024,46 +1061,46 @@
         <v>53.89</v>
       </c>
       <c r="G3">
-        <v>-34.7</v>
+        <v>-37.28</v>
       </c>
       <c r="H3">
-        <v>13.27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
-        <v>-2.2</v>
+        <v>-3.89</v>
       </c>
       <c r="J3">
-        <v>1.7</v>
+        <v>-3.11</v>
       </c>
       <c r="K3">
-        <v>-2.18</v>
+        <v>-7.8</v>
       </c>
       <c r="L3">
-        <v>-19.53</v>
+        <v>-22</v>
       </c>
       <c r="M3">
-        <v>-21.62</v>
+        <v>-22.37</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="P3">
-        <v>62.15</v>
+        <v>61.67</v>
       </c>
       <c r="Q3">
-        <v>59.14</v>
+        <v>59.13</v>
       </c>
       <c r="R3">
-        <v>59.86</v>
+        <v>59.78</v>
       </c>
       <c r="S3">
-        <v>67.31</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="T3">
-        <v>-9.31</v>
+        <v>-12.73</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1078,34 +1115,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>53.64</v>
+        <v>45.59</v>
       </c>
       <c r="Z3">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="AA3">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="AB3">
-        <v>0.59</v>
+        <v>0.3</v>
       </c>
       <c r="AC3">
-        <v>88.02</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="AD3">
-        <v>90.98</v>
+        <v>83.55</v>
       </c>
       <c r="AE3">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="AF3">
-        <v>526.15</v>
+        <v>147.97</v>
       </c>
       <c r="AG3">
-        <v>63.84</v>
+        <v>63.83</v>
       </c>
       <c r="AH3">
-        <v>54.45</v>
+        <v>54.43</v>
       </c>
       <c r="AI3">
         <v>57.07</v>
@@ -1114,7 +1151,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>40.55</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1125,10 +1162,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3380.5</v>
+        <v>3322.2</v>
       </c>
       <c r="D4">
-        <v>1.73</v>
+        <v>-1.72</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1137,46 +1174,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>-1.72</v>
       </c>
       <c r="H4">
-        <v>33.56</v>
+        <v>31.26</v>
       </c>
       <c r="I4">
-        <v>3.7</v>
+        <v>5.87</v>
       </c>
       <c r="J4">
-        <v>5.19</v>
+        <v>5.66</v>
       </c>
       <c r="K4">
-        <v>16.45</v>
+        <v>12.79</v>
       </c>
       <c r="L4">
-        <v>21.7</v>
+        <v>19.2</v>
       </c>
       <c r="M4">
-        <v>18.49</v>
+        <v>17.89</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P4">
-        <v>3257.1</v>
+        <v>3293.94</v>
       </c>
       <c r="Q4">
-        <v>3158.35</v>
+        <v>3168.79</v>
       </c>
       <c r="R4">
-        <v>3143.1</v>
+        <v>3147.49</v>
       </c>
       <c r="S4">
-        <v>2893.27</v>
+        <v>2895.53</v>
       </c>
       <c r="T4">
-        <v>16.84</v>
+        <v>14.74</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1191,34 +1228,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>67.53</v>
+        <v>61.48</v>
       </c>
       <c r="Z4">
-        <v>42.48</v>
+        <v>47.7</v>
       </c>
       <c r="AA4">
-        <v>18.73</v>
+        <v>24.53</v>
       </c>
       <c r="AB4">
-        <v>23.75</v>
+        <v>23.17</v>
       </c>
       <c r="AC4">
-        <v>86.05</v>
+        <v>89.94</v>
       </c>
       <c r="AD4">
-        <v>70.83</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="AE4">
-        <v>76.88</v>
+        <v>78.59</v>
       </c>
       <c r="AF4">
-        <v>388.02</v>
+        <v>21.13</v>
       </c>
       <c r="AG4">
-        <v>3324.99</v>
+        <v>3349.17</v>
       </c>
       <c r="AH4">
-        <v>2991.71</v>
+        <v>2988.42</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1227,7 +1264,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>40.63</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1238,10 +1275,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1054.05</v>
+        <v>1049.1</v>
       </c>
       <c r="D5">
-        <v>-0.52</v>
+        <v>-0.47</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1250,46 +1287,46 @@
         <v>667.05</v>
       </c>
       <c r="G5">
-        <v>-8.32</v>
+        <v>-8.75</v>
       </c>
       <c r="H5">
-        <v>58.02</v>
+        <v>57.27</v>
       </c>
       <c r="I5">
-        <v>5.95</v>
+        <v>2.85</v>
       </c>
       <c r="J5">
-        <v>8.949999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="K5">
-        <v>1.21</v>
+        <v>-2.24</v>
       </c>
       <c r="L5">
-        <v>54.4</v>
+        <v>53.8</v>
       </c>
       <c r="M5">
-        <v>20.67</v>
+        <v>20.01</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P5">
-        <v>1040.13</v>
+        <v>1045.95</v>
       </c>
       <c r="Q5">
-        <v>978.29</v>
+        <v>982.03</v>
       </c>
       <c r="R5">
-        <v>999.4</v>
+        <v>997.5599999999999</v>
       </c>
       <c r="S5">
-        <v>944.78</v>
+        <v>946.11</v>
       </c>
       <c r="T5">
-        <v>11.57</v>
+        <v>10.89</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1304,43 +1341,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>67.83</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="Z5">
-        <v>15.66</v>
+        <v>17.71</v>
       </c>
       <c r="AA5">
-        <v>1.93</v>
+        <v>5.08</v>
       </c>
       <c r="AB5">
-        <v>13.73</v>
+        <v>12.63</v>
       </c>
       <c r="AC5">
-        <v>92.61</v>
+        <v>93.94</v>
       </c>
       <c r="AD5">
-        <v>94</v>
+        <v>93.75</v>
       </c>
       <c r="AE5">
-        <v>23.37</v>
+        <v>23.11</v>
       </c>
       <c r="AF5">
-        <v>40.1</v>
+        <v>-5.13</v>
       </c>
       <c r="AG5">
-        <v>1057.75</v>
+        <v>1067.51</v>
       </c>
       <c r="AH5">
-        <v>898.8200000000001</v>
+        <v>896.54</v>
       </c>
       <c r="AI5">
-        <v>984.28</v>
+        <v>989.6</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>48.92</v>
+        <v>52.88</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1351,10 +1388,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.92</v>
+        <v>12.89</v>
       </c>
       <c r="D6">
-        <v>1.49</v>
+        <v>-0.23</v>
       </c>
       <c r="E6">
         <v>15.01</v>
@@ -1363,46 +1400,46 @@
         <v>6.15</v>
       </c>
       <c r="G6">
-        <v>-13.92</v>
+        <v>-14.12</v>
       </c>
       <c r="H6">
-        <v>110.08</v>
+        <v>109.59</v>
       </c>
       <c r="I6">
+        <v>-0.08</v>
+      </c>
+      <c r="J6">
+        <v>-7.66</v>
+      </c>
+      <c r="K6">
         <v>0.47</v>
       </c>
-      <c r="J6">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="K6">
-        <v>8.66</v>
-      </c>
       <c r="L6">
-        <v>88.89</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="M6">
-        <v>14.21</v>
+        <v>14.15</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P6">
-        <v>12.8</v>
+        <v>12.79</v>
       </c>
       <c r="Q6">
-        <v>13.19</v>
+        <v>13.14</v>
       </c>
       <c r="R6">
-        <v>13.93</v>
+        <v>13.91</v>
       </c>
       <c r="S6">
-        <v>11.47</v>
+        <v>11.49</v>
       </c>
       <c r="T6">
-        <v>12.61</v>
+        <v>12.16</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1417,34 +1454,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>40.41</v>
+        <v>39.79</v>
       </c>
       <c r="Z6">
-        <v>-0.31</v>
+        <v>-0.29</v>
       </c>
       <c r="AA6">
         <v>-0.29</v>
       </c>
       <c r="AB6">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="AC6">
-        <v>40.95</v>
+        <v>72.09</v>
       </c>
       <c r="AD6">
-        <v>22.48</v>
+        <v>42.68</v>
       </c>
       <c r="AE6">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="AF6">
-        <v>45.43</v>
+        <v>128.4</v>
       </c>
       <c r="AG6">
-        <v>13.97</v>
+        <v>13.88</v>
       </c>
       <c r="AH6">
-        <v>12.4</v>
+        <v>12.41</v>
       </c>
       <c r="AI6">
         <v>13.76</v>
@@ -1453,7 +1490,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>61.1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1464,10 +1501,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.6</v>
+        <v>12.35</v>
       </c>
       <c r="D7">
-        <v>-1.1</v>
+        <v>-1.98</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1476,25 +1513,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-9.48</v>
+        <v>-11.28</v>
       </c>
       <c r="H7">
-        <v>168.66</v>
+        <v>163.33</v>
       </c>
       <c r="I7">
-        <v>-4.11</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="J7">
-        <v>21.5</v>
+        <v>16.95</v>
       </c>
       <c r="K7">
-        <v>-2.85</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L7">
-        <v>133.77</v>
+        <v>133.9</v>
       </c>
       <c r="M7">
-        <v>-29.85</v>
+        <v>-30.04</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1503,19 +1540,19 @@
         <v>95</v>
       </c>
       <c r="P7">
-        <v>13.03</v>
+        <v>12.79</v>
       </c>
       <c r="Q7">
-        <v>12.01</v>
+        <v>12.09</v>
       </c>
       <c r="R7">
         <v>11.58</v>
       </c>
       <c r="S7">
-        <v>9.710000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="T7">
-        <v>29.7</v>
+        <v>26.66</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1530,34 +1567,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>57.52</v>
+        <v>54.04</v>
       </c>
       <c r="Z7">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AA7">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="AB7">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="AC7">
-        <v>56.77</v>
+        <v>45.16</v>
       </c>
       <c r="AD7">
-        <v>69.98</v>
+        <v>56.98</v>
       </c>
       <c r="AE7">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="AF7">
-        <v>25.97</v>
+        <v>-84.22</v>
       </c>
       <c r="AG7">
-        <v>13.65</v>
+        <v>13.63</v>
       </c>
       <c r="AH7">
-        <v>10.36</v>
+        <v>10.54</v>
       </c>
       <c r="AI7">
         <v>11.82</v>
@@ -1566,7 +1603,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>18.83</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1577,10 +1614,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4364.2</v>
+        <v>4390.3</v>
       </c>
       <c r="D8">
-        <v>-0.15</v>
+        <v>0.6</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1589,46 +1626,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-24.88</v>
+        <v>-24.43</v>
       </c>
       <c r="H8">
-        <v>5.03</v>
+        <v>5.66</v>
       </c>
       <c r="I8">
-        <v>0.4</v>
+        <v>1.06</v>
       </c>
       <c r="J8">
-        <v>-1.59</v>
+        <v>-1.55</v>
       </c>
       <c r="K8">
-        <v>-4.37</v>
+        <v>-0.25</v>
       </c>
       <c r="L8">
-        <v>-13.66</v>
+        <v>-13.25</v>
       </c>
       <c r="M8">
-        <v>18.94</v>
+        <v>19.22</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P8">
-        <v>4346.54</v>
+        <v>4355.74</v>
       </c>
       <c r="Q8">
-        <v>4344.42</v>
+        <v>4345.81</v>
       </c>
       <c r="R8">
-        <v>4350.89</v>
+        <v>4351.53</v>
       </c>
       <c r="S8">
-        <v>4724.73</v>
+        <v>4717.63</v>
       </c>
       <c r="T8">
-        <v>-7.63</v>
+        <v>-6.94</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1643,34 +1680,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>51.03</v>
+        <v>53.61</v>
       </c>
       <c r="Z8">
-        <v>-11.42</v>
+        <v>-6.72</v>
       </c>
       <c r="AA8">
-        <v>-17.55</v>
+        <v>-15.39</v>
       </c>
       <c r="AB8">
-        <v>6.14</v>
+        <v>8.67</v>
       </c>
       <c r="AC8">
-        <v>76.65000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="AD8">
-        <v>67.45999999999999</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AE8">
-        <v>82.15000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AF8">
-        <v>3.6</v>
+        <v>294.08</v>
       </c>
       <c r="AG8">
-        <v>4430.79</v>
+        <v>4434.28</v>
       </c>
       <c r="AH8">
-        <v>4258.04</v>
+        <v>4257.34</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1679,7 +1716,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>22.24</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1690,10 +1727,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>12038</v>
+        <v>11780</v>
       </c>
       <c r="D9">
-        <v>-0.55</v>
+        <v>-2.14</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1702,46 +1739,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-7.77</v>
+        <v>-9.75</v>
       </c>
       <c r="H9">
-        <v>16.17</v>
+        <v>13.68</v>
       </c>
       <c r="I9">
-        <v>-0.13</v>
+        <v>-2.24</v>
       </c>
       <c r="J9">
-        <v>2.79</v>
+        <v>1.81</v>
       </c>
       <c r="K9">
-        <v>4.53</v>
+        <v>1.79</v>
       </c>
       <c r="L9">
-        <v>-1.79</v>
+        <v>-4.21</v>
       </c>
       <c r="M9">
-        <v>10.5</v>
+        <v>10.09</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="P9">
-        <v>12091.6</v>
+        <v>12037.6</v>
       </c>
       <c r="Q9">
-        <v>11927.35</v>
+        <v>11941.55</v>
       </c>
       <c r="R9">
-        <v>11558.02</v>
+        <v>11568.98</v>
       </c>
       <c r="S9">
-        <v>11801.13</v>
+        <v>11798.32</v>
       </c>
       <c r="T9">
-        <v>2.01</v>
+        <v>-0.16</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1753,37 +1790,37 @@
         <v>47</v>
       </c>
       <c r="X9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>57</v>
+        <v>47.51</v>
       </c>
       <c r="Z9">
-        <v>136.08</v>
+        <v>108.34</v>
       </c>
       <c r="AA9">
-        <v>135.1</v>
+        <v>129.75</v>
       </c>
       <c r="AB9">
-        <v>0.98</v>
+        <v>-21.4</v>
       </c>
       <c r="AC9">
-        <v>41.94</v>
+        <v>26.88</v>
       </c>
       <c r="AD9">
-        <v>57.05</v>
+        <v>44.31</v>
       </c>
       <c r="AE9">
-        <v>209</v>
+        <v>218.43</v>
       </c>
       <c r="AF9">
-        <v>-53.48</v>
+        <v>-38.06</v>
       </c>
       <c r="AG9">
-        <v>12245.63</v>
+        <v>12198.16</v>
       </c>
       <c r="AH9">
-        <v>11609.07</v>
+        <v>11684.94</v>
       </c>
       <c r="AI9">
         <v>11461.94</v>
@@ -1792,7 +1829,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>19.92</v>
+        <v>19.58</v>
       </c>
     </row>
   </sheetData>
@@ -1953,1144 +1990,1182 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>56</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>2.69</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-0.13</v>
       </c>
-      <c r="E7" s="6">
-        <v>-2.82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>8.16</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>1.7</v>
       </c>
-      <c r="E8" s="6">
-        <v>-6.46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-3.11</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-4.81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>4.11</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>5.19</v>
       </c>
-      <c r="E9" s="7">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>5.66</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>9.98</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>8.949999999999999</v>
       </c>
-      <c r="E10" s="6">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>8.51</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-9.33</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-8.949999999999999</v>
       </c>
-      <c r="E11" s="7">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-7.66</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>25.27</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>21.5</v>
       </c>
-      <c r="E12" s="6">
-        <v>-3.77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>16.95</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-0.3</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-1.59</v>
       </c>
-      <c r="E13" s="6">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-1.55</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5">
-        <v>5.04</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>2.79</v>
       </c>
-      <c r="E14" s="6">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>1.81</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>0.93</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-3.91</v>
       </c>
-      <c r="E15" s="6">
-        <v>-4.84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-3.06</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>5.13</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-2.2</v>
       </c>
-      <c r="E16" s="6">
-        <v>-7.33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-3.89</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>7.17</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>3.7</v>
       </c>
-      <c r="E17" s="6">
-        <v>-3.47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>5.87</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>8.74</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>5.95</v>
       </c>
-      <c r="E18" s="6">
-        <v>-2.79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>2.85</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
-        <v>-2.15</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>0.47</v>
       </c>
-      <c r="E19" s="7">
-        <v>2.62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-0.08</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="5">
-        <v>1.76</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>-4.11</v>
       </c>
-      <c r="E20" s="6">
-        <v>-5.87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="6">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-4.61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>0.4</v>
       </c>
-      <c r="E21" s="6">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="5">
-        <v>1.7</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>-0.13</v>
       </c>
-      <c r="E22" s="6">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>-2.24</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
-        <v>62.28</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>46.44</v>
       </c>
-      <c r="E23" s="6">
-        <v>-15.84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="6">
+        <v>44.38</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-2.06</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="5">
-        <v>-14.16</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="6">
         <v>-19.53</v>
       </c>
-      <c r="E24" s="6">
-        <v>-5.37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="6">
+        <v>-22</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="5">
-        <v>22.51</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="6">
         <v>21.7</v>
       </c>
-      <c r="E25" s="6">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="6">
+        <v>19.2</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="5">
-        <v>58.73</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="6">
         <v>54.4</v>
       </c>
-      <c r="E26" s="6">
-        <v>-4.33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="6">
+        <v>53.8</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="5">
-        <v>92.88</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="6">
         <v>88.89</v>
       </c>
-      <c r="E27" s="6">
+      <c r="D28" s="6">
+        <v>86.54000000000001</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>133.77</v>
+      </c>
+      <c r="D29" s="6">
+        <v>133.9</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-13.66</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-13.25</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-1.79</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-4.21</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-2.42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>19.5</v>
+      </c>
+      <c r="D32" s="6">
+        <v>18.25</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-2.18</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-7.8</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-5.62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>16.45</v>
+      </c>
+      <c r="D34" s="6">
+        <v>12.79</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1.21</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-2.24</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>8.66</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0.47</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-8.19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-2.85</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-6.27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-4.37</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-0.25</v>
+      </c>
+      <c r="E38" s="7">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>4.53</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1.79</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-2.74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
         <v>-3.99</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D40" s="6">
+        <v>-4.13</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-34.7</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-37.28</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-1.72</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-8.32</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-8.75</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-13.92</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-14.12</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>131.64</v>
-      </c>
-      <c r="D28" s="5">
-        <v>133.77</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-9.48</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-11.28</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-13.1</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-13.66</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-24.88</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-24.43</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-1.79</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-7.77</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-9.75</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>15.61</v>
-      </c>
-      <c r="D31" s="5">
-        <v>19.5</v>
-      </c>
-      <c r="E31" s="7">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>407.75</v>
+      </c>
+      <c r="D48" s="6">
+        <v>407.15</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-2.55</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-2.18</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>61.04</v>
+      </c>
+      <c r="D49" s="6">
+        <v>58.63</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>11.35</v>
-      </c>
-      <c r="D33" s="5">
-        <v>16.45</v>
-      </c>
-      <c r="E33" s="7">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>3380.5</v>
+      </c>
+      <c r="D50" s="6">
+        <v>3322.2</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-58.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>3.53</v>
-      </c>
-      <c r="D34" s="5">
-        <v>1.21</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>1054.05</v>
+      </c>
+      <c r="D51" s="6">
+        <v>1049.1</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-4.95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>4.52</v>
-      </c>
-      <c r="D35" s="5">
-        <v>8.66</v>
-      </c>
-      <c r="E35" s="7">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>12.92</v>
+      </c>
+      <c r="D52" s="6">
+        <v>12.89</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2.41</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-2.85</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-5.26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>12.6</v>
+      </c>
+      <c r="D53" s="6">
+        <v>12.35</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-7.66</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-4.37</v>
-      </c>
-      <c r="E37" s="7">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>4364.2</v>
+      </c>
+      <c r="D54" s="6">
+        <v>4390.3</v>
+      </c>
+      <c r="E54" s="7">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>2.01</v>
-      </c>
-      <c r="D38" s="5">
-        <v>4.53</v>
-      </c>
-      <c r="E38" s="7">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>12038</v>
+      </c>
+      <c r="D55" s="6">
+        <v>11780</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-258</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-3.92</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-3.99</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>53.23</v>
+      </c>
+      <c r="D56" s="6">
+        <v>52.87</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-32.25</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-34.7</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-2.45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>53.64</v>
+      </c>
+      <c r="D57" s="6">
+        <v>45.59</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-8.050000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>67.53</v>
+      </c>
+      <c r="D58" s="6">
+        <v>61.48</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-6.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-7.84</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-8.32</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>67.83</v>
+      </c>
+      <c r="D59" s="6">
+        <v>65.93000000000001</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-15.19</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-13.92</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>40.41</v>
+      </c>
+      <c r="D60" s="6">
+        <v>39.79</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-8.48</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-9.48</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>57.52</v>
+      </c>
+      <c r="D61" s="6">
+        <v>54.04</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-3.48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-24.77</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-24.88</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>51.03</v>
+      </c>
+      <c r="D62" s="6">
+        <v>53.61</v>
+      </c>
+      <c r="E62" s="7">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-7.26</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-7.77</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>57</v>
+      </c>
+      <c r="D63" s="6">
+        <v>47.51</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-9.49</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>408.05</v>
-      </c>
-      <c r="D46" s="5">
-        <v>407.75</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-46.81</v>
+      </c>
+      <c r="D64" s="6">
+        <v>4.31</v>
+      </c>
+      <c r="E64" s="7">
+        <v>51.12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>63.33</v>
-      </c>
-      <c r="D47" s="5">
-        <v>61.04</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>526.15</v>
+      </c>
+      <c r="D65" s="6">
+        <v>147.97</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-378.18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>3323</v>
-      </c>
-      <c r="D48" s="5">
-        <v>3380.5</v>
-      </c>
-      <c r="E48" s="7">
-        <v>57.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>388.02</v>
+      </c>
+      <c r="D66" s="6">
+        <v>21.13</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-366.89</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>1059.6</v>
-      </c>
-      <c r="D49" s="5">
-        <v>1054.05</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-5.55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>40.1</v>
+      </c>
+      <c r="D67" s="6">
+        <v>-5.13</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-45.23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>12.73</v>
-      </c>
-      <c r="D50" s="5">
-        <v>12.92</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>45.43</v>
+      </c>
+      <c r="D68" s="6">
+        <v>128.4</v>
+      </c>
+      <c r="E68" s="7">
+        <v>82.97</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>12.74</v>
-      </c>
-      <c r="D51" s="5">
-        <v>12.6</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>25.97</v>
+      </c>
+      <c r="D69" s="6">
+        <v>-84.22</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-110.19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>4370.7</v>
-      </c>
-      <c r="D52" s="5">
-        <v>4364.2</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-6.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="D70" s="6">
+        <v>294.08</v>
+      </c>
+      <c r="E70" s="7">
+        <v>290.48</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>12105</v>
-      </c>
-      <c r="D53" s="5">
-        <v>12038</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-67</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="5">
-        <v>26</v>
-      </c>
-      <c r="D54" s="5">
-        <v>13</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="5">
-        <v>13</v>
-      </c>
-      <c r="D55" s="5">
-        <v>26</v>
-      </c>
-      <c r="E55" s="7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>53.4</v>
-      </c>
-      <c r="D56" s="5">
-        <v>53.23</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>63.53</v>
-      </c>
-      <c r="D57" s="5">
-        <v>53.64</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-9.890000000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>64.31</v>
-      </c>
-      <c r="D58" s="5">
-        <v>67.53</v>
-      </c>
-      <c r="E58" s="7">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>69.94</v>
-      </c>
-      <c r="D59" s="5">
-        <v>67.83</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>34.41</v>
-      </c>
-      <c r="D60" s="5">
-        <v>40.41</v>
-      </c>
-      <c r="E60" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>59.52</v>
-      </c>
-      <c r="D61" s="5">
-        <v>57.52</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>51.69</v>
-      </c>
-      <c r="D62" s="5">
-        <v>51.03</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>59.89</v>
-      </c>
-      <c r="D63" s="5">
-        <v>57</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="3" t="s">
+      <c r="B71" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C64" s="5">
-        <v>24.66</v>
-      </c>
-      <c r="D64" s="5">
-        <v>-46.81</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-71.47</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>32.86</v>
-      </c>
-      <c r="D65" s="5">
-        <v>526.15</v>
-      </c>
-      <c r="E65" s="7">
-        <v>493.29</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>105.98</v>
-      </c>
-      <c r="D66" s="5">
-        <v>388.02</v>
-      </c>
-      <c r="E66" s="7">
-        <v>282.04</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>90.14</v>
-      </c>
-      <c r="D67" s="5">
-        <v>40.1</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-50.04</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>-27.35</v>
-      </c>
-      <c r="D68" s="5">
-        <v>45.43</v>
-      </c>
-      <c r="E68" s="7">
-        <v>72.78</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
-        <v>42.21</v>
-      </c>
-      <c r="D69" s="5">
-        <v>25.97</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-16.24</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="5">
-        <v>51.6</v>
-      </c>
-      <c r="D70" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="E70" s="6">
-        <v>-48</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="5">
-        <v>-42.48</v>
-      </c>
-      <c r="D71" s="5">
+      <c r="C71" s="6">
         <v>-53.48</v>
       </c>
-      <c r="E71" s="6">
-        <v>-11</v>
+      <c r="D71" s="6">
+        <v>-38.06</v>
+      </c>
+      <c r="E71" s="7">
+        <v>15.42</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3110,60 +3185,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="11">
+        <v>56.44</v>
+      </c>
+      <c r="C2" s="12">
+        <v>8</v>
+      </c>
+      <c r="D2" s="11">
+        <v>52.6</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="10">
-        <v>64.44</v>
-      </c>
-      <c r="C2" s="11">
-        <v>8</v>
-      </c>
-      <c r="D2" s="10">
-        <v>56</v>
-      </c>
-      <c r="E2" s="10">
-        <v>80</v>
-      </c>
-      <c r="F2" s="10">
-        <v>3.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>5.1</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>2.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -3265,55 +3340,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.2859</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2067</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1894</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1849</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1421</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.105</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2162</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.2985</v>
+      <c r="A2" s="14">
+        <v>0.2877</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2001</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1922</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1789</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1415</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1009</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2237</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.3004</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="87">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,25 +193,55 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>53.6 → 45.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.6</t>
-  </si>
-  <si>
-    <t>45.6</t>
-  </si>
-  <si>
-    <t>57.0 → 47.5</t>
-  </si>
-  <si>
-    <t>57.0</t>
+    <t>39.8 → 54.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>39.8</t>
+  </si>
+  <si>
+    <t>54.9</t>
+  </si>
+  <si>
+    <t>47.5 → 51.3</t>
   </si>
   <si>
     <t>47.5</t>
+  </si>
+  <si>
+    <t>51.3</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.7% → -2.1%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.7%</t>
+  </si>
+  <si>
+    <t>-2.1%</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>65.9 → 71.1</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>65.9</t>
+  </si>
+  <si>
+    <t>71.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -263,7 +293,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,20 +327,34 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,13 +381,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -421,14 +477,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -437,7 +495,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -795,15 +853,14 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -936,10 +993,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>407.15</v>
+        <v>410.95</v>
       </c>
       <c r="D2">
-        <v>-0.15</v>
+        <v>0.93</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -948,46 +1005,46 @@
         <v>268.05</v>
       </c>
       <c r="G2">
-        <v>-4.13</v>
+        <v>-3.24</v>
       </c>
       <c r="H2">
-        <v>51.89</v>
+        <v>53.31</v>
       </c>
       <c r="I2">
-        <v>-3.06</v>
+        <v>-3.24</v>
       </c>
       <c r="J2">
-        <v>-0.07000000000000001</v>
+        <v>2.93</v>
       </c>
       <c r="K2">
-        <v>18.25</v>
+        <v>17.53</v>
       </c>
       <c r="L2">
-        <v>44.38</v>
+        <v>48.28</v>
       </c>
       <c r="M2">
-        <v>28.77</v>
+        <v>28.68</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P2">
-        <v>413.83</v>
+        <v>411.08</v>
       </c>
       <c r="Q2">
-        <v>405.18</v>
+        <v>405.52</v>
       </c>
       <c r="R2">
-        <v>388.95</v>
+        <v>390.15</v>
       </c>
       <c r="S2">
-        <v>353.51</v>
+        <v>354.03</v>
       </c>
       <c r="T2">
-        <v>15.17</v>
+        <v>16.08</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1002,34 +1059,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>52.87</v>
+        <v>54.95</v>
       </c>
       <c r="Z2">
-        <v>6.2</v>
+        <v>5.89</v>
       </c>
       <c r="AA2">
-        <v>6.79</v>
+        <v>6.61</v>
       </c>
       <c r="AB2">
-        <v>-0.59</v>
+        <v>-0.72</v>
       </c>
       <c r="AC2">
-        <v>25.01</v>
+        <v>28.4</v>
       </c>
       <c r="AD2">
-        <v>45.19</v>
+        <v>32.44</v>
       </c>
       <c r="AE2">
-        <v>11.22</v>
+        <v>10.99</v>
       </c>
       <c r="AF2">
-        <v>4.31</v>
+        <v>-41.98</v>
       </c>
       <c r="AG2">
-        <v>425.91</v>
+        <v>426.4</v>
       </c>
       <c r="AH2">
-        <v>384.46</v>
+        <v>384.64</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1038,7 +1095,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>23.83</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1049,10 +1106,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>58.63</v>
+        <v>57.16</v>
       </c>
       <c r="D3">
-        <v>-3.95</v>
+        <v>-2.51</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1061,46 +1118,46 @@
         <v>53.89</v>
       </c>
       <c r="G3">
-        <v>-37.28</v>
+        <v>-38.85</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>6.07</v>
       </c>
       <c r="I3">
-        <v>-3.89</v>
+        <v>-7.95</v>
       </c>
       <c r="J3">
-        <v>-3.11</v>
+        <v>-3</v>
       </c>
       <c r="K3">
-        <v>-7.8</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="L3">
-        <v>-22</v>
+        <v>-25.24</v>
       </c>
       <c r="M3">
-        <v>-22.37</v>
+        <v>-22.89</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="P3">
-        <v>61.67</v>
+        <v>60.68</v>
       </c>
       <c r="Q3">
-        <v>59.13</v>
+        <v>59.02</v>
       </c>
       <c r="R3">
-        <v>59.78</v>
+        <v>59.68</v>
       </c>
       <c r="S3">
-        <v>67.18000000000001</v>
+        <v>67.05</v>
       </c>
       <c r="T3">
-        <v>-12.73</v>
+        <v>-14.75</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1115,34 +1172,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>45.59</v>
+        <v>41.51</v>
       </c>
       <c r="Z3">
-        <v>0.46</v>
+        <v>0.17</v>
       </c>
       <c r="AA3">
         <v>0.16</v>
       </c>
       <c r="AB3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>66.29000000000001</v>
+        <v>38.41</v>
       </c>
       <c r="AD3">
-        <v>83.55</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AE3">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AF3">
-        <v>147.97</v>
+        <v>-26.13</v>
       </c>
       <c r="AG3">
-        <v>63.83</v>
+        <v>63.8</v>
       </c>
       <c r="AH3">
-        <v>54.43</v>
+        <v>54.25</v>
       </c>
       <c r="AI3">
         <v>57.07</v>
@@ -1151,7 +1208,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>37.22</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1162,10 +1219,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3322.2</v>
+        <v>3307.8</v>
       </c>
       <c r="D4">
-        <v>-1.72</v>
+        <v>-0.43</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1174,46 +1231,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-1.72</v>
+        <v>-2.15</v>
       </c>
       <c r="H4">
-        <v>31.26</v>
+        <v>30.69</v>
       </c>
       <c r="I4">
-        <v>5.87</v>
+        <v>2.6</v>
       </c>
       <c r="J4">
-        <v>5.66</v>
+        <v>6.25</v>
       </c>
       <c r="K4">
-        <v>12.79</v>
+        <v>12.56</v>
       </c>
       <c r="L4">
-        <v>19.2</v>
+        <v>20.03</v>
       </c>
       <c r="M4">
-        <v>17.89</v>
+        <v>17.8</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P4">
-        <v>3293.94</v>
+        <v>3310.7</v>
       </c>
       <c r="Q4">
-        <v>3168.79</v>
+        <v>3179.88</v>
       </c>
       <c r="R4">
-        <v>3147.49</v>
+        <v>3151.69</v>
       </c>
       <c r="S4">
-        <v>2895.53</v>
+        <v>2897.74</v>
       </c>
       <c r="T4">
-        <v>14.74</v>
+        <v>14.15</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1228,34 +1285,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>61.48</v>
+        <v>60.05</v>
       </c>
       <c r="Z4">
-        <v>47.7</v>
+        <v>50.1</v>
       </c>
       <c r="AA4">
-        <v>24.53</v>
+        <v>29.64</v>
       </c>
       <c r="AB4">
-        <v>23.17</v>
+        <v>20.46</v>
       </c>
       <c r="AC4">
-        <v>89.94</v>
+        <v>79.69</v>
       </c>
       <c r="AD4">
-        <v>83.26000000000001</v>
+        <v>85.23</v>
       </c>
       <c r="AE4">
-        <v>78.59</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="AF4">
-        <v>21.13</v>
+        <v>267.12</v>
       </c>
       <c r="AG4">
-        <v>3349.17</v>
+        <v>3366.01</v>
       </c>
       <c r="AH4">
-        <v>2988.42</v>
+        <v>2993.75</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1264,7 +1321,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>45.51</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1275,10 +1332,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1049.1</v>
+        <v>1078.5</v>
       </c>
       <c r="D5">
-        <v>-0.47</v>
+        <v>2.8</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1287,46 +1344,46 @@
         <v>667.05</v>
       </c>
       <c r="G5">
-        <v>-8.75</v>
+        <v>-6.19</v>
       </c>
       <c r="H5">
-        <v>57.27</v>
+        <v>61.68</v>
       </c>
       <c r="I5">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="J5">
-        <v>8.51</v>
+        <v>10.69</v>
       </c>
       <c r="K5">
-        <v>-2.24</v>
+        <v>-2.25</v>
       </c>
       <c r="L5">
-        <v>53.8</v>
+        <v>58.64</v>
       </c>
       <c r="M5">
-        <v>20.01</v>
+        <v>20.48</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P5">
-        <v>1045.95</v>
+        <v>1053.65</v>
       </c>
       <c r="Q5">
-        <v>982.03</v>
+        <v>988.16</v>
       </c>
       <c r="R5">
-        <v>997.5599999999999</v>
+        <v>996.2</v>
       </c>
       <c r="S5">
-        <v>946.11</v>
+        <v>947.54</v>
       </c>
       <c r="T5">
-        <v>10.89</v>
+        <v>13.82</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1341,43 +1398,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>65.93000000000001</v>
+        <v>71.12</v>
       </c>
       <c r="Z5">
-        <v>17.71</v>
+        <v>21.46</v>
       </c>
       <c r="AA5">
-        <v>5.08</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AB5">
-        <v>12.63</v>
+        <v>13.1</v>
       </c>
       <c r="AC5">
         <v>93.94</v>
       </c>
       <c r="AD5">
-        <v>93.75</v>
+        <v>93.5</v>
       </c>
       <c r="AE5">
-        <v>23.11</v>
+        <v>24.23</v>
       </c>
       <c r="AF5">
-        <v>-5.13</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="AG5">
-        <v>1067.51</v>
+        <v>1082.84</v>
       </c>
       <c r="AH5">
-        <v>896.54</v>
+        <v>893.48</v>
       </c>
       <c r="AI5">
-        <v>989.6</v>
+        <v>999.73</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>52.88</v>
+        <v>56.98</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1388,10 +1445,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.89</v>
+        <v>13.5</v>
       </c>
       <c r="D6">
-        <v>-0.23</v>
+        <v>4.73</v>
       </c>
       <c r="E6">
         <v>15.01</v>
@@ -1400,46 +1457,46 @@
         <v>6.15</v>
       </c>
       <c r="G6">
-        <v>-14.12</v>
+        <v>-10.06</v>
       </c>
       <c r="H6">
-        <v>109.59</v>
+        <v>119.51</v>
       </c>
       <c r="I6">
-        <v>-0.08</v>
+        <v>5.47</v>
       </c>
       <c r="J6">
-        <v>-7.66</v>
+        <v>-2.39</v>
       </c>
       <c r="K6">
-        <v>0.47</v>
+        <v>4.09</v>
       </c>
       <c r="L6">
-        <v>86.54000000000001</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="M6">
-        <v>14.15</v>
+        <v>15.74</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P6">
-        <v>12.79</v>
+        <v>12.93</v>
       </c>
       <c r="Q6">
-        <v>13.14</v>
+        <v>13.13</v>
       </c>
       <c r="R6">
-        <v>13.91</v>
+        <v>13.9</v>
       </c>
       <c r="S6">
-        <v>11.49</v>
+        <v>11.51</v>
       </c>
       <c r="T6">
-        <v>12.16</v>
+        <v>17.27</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1454,34 +1511,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>39.79</v>
+        <v>54.93</v>
       </c>
       <c r="Z6">
-        <v>-0.29</v>
+        <v>-0.22</v>
       </c>
       <c r="AA6">
-        <v>-0.29</v>
+        <v>-0.27</v>
       </c>
       <c r="AB6">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="AC6">
-        <v>72.09</v>
+        <v>94.55</v>
       </c>
       <c r="AD6">
-        <v>42.68</v>
+        <v>69.2</v>
       </c>
       <c r="AE6">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="AF6">
-        <v>128.4</v>
+        <v>148.82</v>
       </c>
       <c r="AG6">
-        <v>13.88</v>
+        <v>13.85</v>
       </c>
       <c r="AH6">
-        <v>12.41</v>
+        <v>12.42</v>
       </c>
       <c r="AI6">
         <v>13.76</v>
@@ -1490,7 +1547,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>53</v>
+        <v>50.36</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1501,10 +1558,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.35</v>
+        <v>12.11</v>
       </c>
       <c r="D7">
-        <v>-1.98</v>
+        <v>-1.94</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1513,25 +1570,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-11.28</v>
+        <v>-13</v>
       </c>
       <c r="H7">
-        <v>163.33</v>
+        <v>158.21</v>
       </c>
       <c r="I7">
-        <v>-8.720000000000001</v>
+        <v>-8.67</v>
       </c>
       <c r="J7">
-        <v>16.95</v>
+        <v>12.44</v>
       </c>
       <c r="K7">
-        <v>-9.119999999999999</v>
+        <v>-6.41</v>
       </c>
       <c r="L7">
-        <v>133.9</v>
+        <v>134.24</v>
       </c>
       <c r="M7">
-        <v>-30.04</v>
+        <v>-30.84</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1540,19 +1597,19 @@
         <v>95</v>
       </c>
       <c r="P7">
-        <v>12.79</v>
+        <v>12.56</v>
       </c>
       <c r="Q7">
-        <v>12.09</v>
+        <v>12.14</v>
       </c>
       <c r="R7">
         <v>11.58</v>
       </c>
       <c r="S7">
-        <v>9.75</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="T7">
-        <v>26.66</v>
+        <v>23.76</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1567,34 +1624,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>54.04</v>
+        <v>50.86</v>
       </c>
       <c r="Z7">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="AA7">
         <v>0.35</v>
       </c>
       <c r="AB7">
-        <v>0.05</v>
+        <v>-0</v>
       </c>
       <c r="AC7">
-        <v>45.16</v>
+        <v>34.31</v>
       </c>
       <c r="AD7">
-        <v>56.98</v>
+        <v>45.41</v>
       </c>
       <c r="AE7">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AF7">
-        <v>-84.22</v>
+        <v>-71.38</v>
       </c>
       <c r="AG7">
-        <v>13.63</v>
+        <v>13.6</v>
       </c>
       <c r="AH7">
-        <v>10.54</v>
+        <v>10.69</v>
       </c>
       <c r="AI7">
         <v>11.82</v>
@@ -1603,7 +1660,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>20</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1614,10 +1671,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4390.3</v>
+        <v>4365</v>
       </c>
       <c r="D8">
-        <v>0.6</v>
+        <v>-0.58</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1626,46 +1683,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-24.43</v>
+        <v>-24.86</v>
       </c>
       <c r="H8">
-        <v>5.66</v>
+        <v>5.05</v>
       </c>
       <c r="I8">
-        <v>1.06</v>
+        <v>0.61</v>
       </c>
       <c r="J8">
-        <v>-1.55</v>
+        <v>0.06</v>
       </c>
       <c r="K8">
-        <v>-0.25</v>
+        <v>-1.38</v>
       </c>
       <c r="L8">
-        <v>-13.25</v>
+        <v>-13.28</v>
       </c>
       <c r="M8">
-        <v>19.22</v>
+        <v>18.73</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P8">
-        <v>4355.74</v>
+        <v>4361.04</v>
       </c>
       <c r="Q8">
-        <v>4345.81</v>
+        <v>4345.99</v>
       </c>
       <c r="R8">
-        <v>4351.53</v>
+        <v>4351.59</v>
       </c>
       <c r="S8">
-        <v>4717.63</v>
+        <v>4710.56</v>
       </c>
       <c r="T8">
-        <v>-6.94</v>
+        <v>-7.34</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1680,34 +1737,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>53.61</v>
+        <v>50.81</v>
       </c>
       <c r="Z8">
-        <v>-6.72</v>
+        <v>-4.98</v>
       </c>
       <c r="AA8">
-        <v>-15.39</v>
+        <v>-13.31</v>
       </c>
       <c r="AB8">
-        <v>8.67</v>
+        <v>8.33</v>
       </c>
       <c r="AC8">
-        <v>93.98999999999999</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="AD8">
-        <v>78.95999999999999</v>
+        <v>87.45</v>
       </c>
       <c r="AE8">
-        <v>84.09999999999999</v>
+        <v>84.45</v>
       </c>
       <c r="AF8">
-        <v>294.08</v>
+        <v>-23.84</v>
       </c>
       <c r="AG8">
-        <v>4434.28</v>
+        <v>4434.61</v>
       </c>
       <c r="AH8">
-        <v>4257.34</v>
+        <v>4257.37</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1716,7 +1773,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>19.62</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1727,10 +1784,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11780</v>
+        <v>11891</v>
       </c>
       <c r="D9">
-        <v>-2.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1739,46 +1796,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-9.75</v>
+        <v>-8.9</v>
       </c>
       <c r="H9">
-        <v>13.68</v>
+        <v>14.76</v>
       </c>
       <c r="I9">
-        <v>-2.24</v>
+        <v>-2.45</v>
       </c>
       <c r="J9">
-        <v>1.81</v>
+        <v>3.44</v>
       </c>
       <c r="K9">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="L9">
-        <v>-4.21</v>
+        <v>-2.74</v>
       </c>
       <c r="M9">
-        <v>10.09</v>
+        <v>10.24</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P9">
-        <v>12037.6</v>
+        <v>11977.8</v>
       </c>
       <c r="Q9">
-        <v>11941.55</v>
+        <v>11945.5</v>
       </c>
       <c r="R9">
-        <v>11568.98</v>
+        <v>11583.5</v>
       </c>
       <c r="S9">
-        <v>11798.32</v>
+        <v>11797.05</v>
       </c>
       <c r="T9">
-        <v>-0.16</v>
+        <v>0.8</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1790,37 +1847,37 @@
         <v>47</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9">
-        <v>47.51</v>
+        <v>51.27</v>
       </c>
       <c r="Z9">
-        <v>108.34</v>
+        <v>94.23</v>
       </c>
       <c r="AA9">
-        <v>129.75</v>
+        <v>122.64</v>
       </c>
       <c r="AB9">
-        <v>-21.4</v>
+        <v>-28.41</v>
       </c>
       <c r="AC9">
-        <v>26.88</v>
+        <v>16.62</v>
       </c>
       <c r="AD9">
-        <v>44.31</v>
+        <v>28.48</v>
       </c>
       <c r="AE9">
-        <v>218.43</v>
+        <v>220.04</v>
       </c>
       <c r="AF9">
-        <v>-38.06</v>
+        <v>8.82</v>
       </c>
       <c r="AG9">
-        <v>12198.16</v>
+        <v>12196.08</v>
       </c>
       <c r="AH9">
-        <v>11684.94</v>
+        <v>11694.92</v>
       </c>
       <c r="AI9">
         <v>11461.94</v>
@@ -1829,7 +1886,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>19.58</v>
+        <v>20.39</v>
       </c>
     </row>
   </sheetData>
@@ -1970,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2010,7 +2067,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2048,1124 +2105,1164 @@
         <v>63</v>
       </c>
     </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-0.13</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C10" s="8">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="E8" s="7">
+      <c r="D10" s="8">
+        <v>2.93</v>
+      </c>
+      <c r="E10" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="8">
+        <v>-3.11</v>
+      </c>
+      <c r="D11" s="8">
+        <v>-3</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="8">
+        <v>5.66</v>
+      </c>
+      <c r="D12" s="8">
+        <v>6.25</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="8">
+        <v>8.51</v>
+      </c>
+      <c r="D13" s="8">
+        <v>10.69</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="8">
+        <v>-7.66</v>
+      </c>
+      <c r="D14" s="8">
+        <v>-2.39</v>
+      </c>
+      <c r="E14" s="9">
+        <v>5.27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="8">
+        <v>16.95</v>
+      </c>
+      <c r="D15" s="8">
+        <v>12.44</v>
+      </c>
+      <c r="E15" s="10">
+        <v>-4.51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="8">
+        <v>-1.55</v>
+      </c>
+      <c r="D16" s="8">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="E16" s="9">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="8">
+        <v>1.81</v>
+      </c>
+      <c r="D17" s="8">
+        <v>3.44</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="8">
+        <v>-3.06</v>
+      </c>
+      <c r="D18" s="8">
+        <v>-3.24</v>
+      </c>
+      <c r="E18" s="10">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
+      <c r="B19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="8">
+        <v>-3.89</v>
+      </c>
+      <c r="D19" s="8">
+        <v>-7.95</v>
+      </c>
+      <c r="E19" s="10">
+        <v>-4.06</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="8">
+        <v>5.87</v>
+      </c>
+      <c r="D20" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="E20" s="10">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2.85</v>
+      </c>
+      <c r="D21" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="8">
+        <v>-0.08</v>
+      </c>
+      <c r="D22" s="8">
+        <v>5.47</v>
+      </c>
+      <c r="E22" s="9">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="8">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="D23" s="8">
+        <v>-8.67</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="8">
+        <v>1.06</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0.61</v>
+      </c>
+      <c r="E24" s="10">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="8">
+        <v>-2.24</v>
+      </c>
+      <c r="D25" s="8">
+        <v>-2.45</v>
+      </c>
+      <c r="E25" s="10">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="8">
+        <v>44.38</v>
+      </c>
+      <c r="D26" s="8">
+        <v>48.28</v>
+      </c>
+      <c r="E26" s="9">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="8">
+        <v>-22</v>
+      </c>
+      <c r="D27" s="8">
+        <v>-25.24</v>
+      </c>
+      <c r="E27" s="10">
+        <v>-3.24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="8">
+        <v>19.2</v>
+      </c>
+      <c r="D28" s="8">
+        <v>20.03</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="8">
+        <v>53.8</v>
+      </c>
+      <c r="D29" s="8">
+        <v>58.64</v>
+      </c>
+      <c r="E29" s="9">
+        <v>4.84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="8">
+        <v>86.54000000000001</v>
+      </c>
+      <c r="D30" s="8">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="E30" s="9">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="8">
+        <v>133.9</v>
+      </c>
+      <c r="D31" s="8">
+        <v>134.24</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="8">
+        <v>-13.25</v>
+      </c>
+      <c r="D32" s="8">
+        <v>-13.28</v>
+      </c>
+      <c r="E32" s="10">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="8">
+        <v>-4.21</v>
+      </c>
+      <c r="D33" s="8">
+        <v>-2.74</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="8">
+        <v>18.25</v>
+      </c>
+      <c r="D34" s="8">
+        <v>17.53</v>
+      </c>
+      <c r="E34" s="10">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="8">
+        <v>-7.8</v>
+      </c>
+      <c r="D35" s="8">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="E35" s="10">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="8">
+        <v>12.79</v>
+      </c>
+      <c r="D36" s="8">
+        <v>12.56</v>
+      </c>
+      <c r="E36" s="10">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="8">
+        <v>-2.24</v>
+      </c>
+      <c r="D37" s="8">
+        <v>-2.25</v>
+      </c>
+      <c r="E37" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="8">
+        <v>0.47</v>
+      </c>
+      <c r="D38" s="8">
+        <v>4.09</v>
+      </c>
+      <c r="E38" s="9">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="8">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="D39" s="8">
+        <v>-6.41</v>
+      </c>
+      <c r="E39" s="9">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="8">
+        <v>-0.25</v>
+      </c>
+      <c r="D40" s="8">
+        <v>-1.38</v>
+      </c>
+      <c r="E40" s="10">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="8">
+        <v>1.79</v>
+      </c>
+      <c r="D41" s="8">
         <v>1.7</v>
       </c>
-      <c r="D9" s="6">
-        <v>-3.11</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-4.81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="E41" s="10">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="8">
+        <v>-4.13</v>
+      </c>
+      <c r="D42" s="8">
+        <v>-3.24</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="8">
+        <v>-37.28</v>
+      </c>
+      <c r="D43" s="8">
+        <v>-38.85</v>
+      </c>
+      <c r="E43" s="10">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
+      <c r="B44" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="8">
+        <v>-1.72</v>
+      </c>
+      <c r="D44" s="8">
+        <v>-2.15</v>
+      </c>
+      <c r="E44" s="10">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="8">
+        <v>-8.75</v>
+      </c>
+      <c r="D45" s="8">
+        <v>-6.19</v>
+      </c>
+      <c r="E45" s="9">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="8">
+        <v>-14.12</v>
+      </c>
+      <c r="D46" s="8">
+        <v>-10.06</v>
+      </c>
+      <c r="E46" s="9">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="8">
+        <v>-11.28</v>
+      </c>
+      <c r="D47" s="8">
+        <v>-13</v>
+      </c>
+      <c r="E47" s="10">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="8">
+        <v>-24.43</v>
+      </c>
+      <c r="D48" s="8">
+        <v>-24.86</v>
+      </c>
+      <c r="E48" s="10">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="8">
+        <v>-9.75</v>
+      </c>
+      <c r="D49" s="8">
+        <v>-8.9</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="8">
+        <v>407.15</v>
+      </c>
+      <c r="D50" s="8">
+        <v>410.95</v>
+      </c>
+      <c r="E50" s="9">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="8">
+        <v>58.63</v>
+      </c>
+      <c r="D51" s="8">
+        <v>57.16</v>
+      </c>
+      <c r="E51" s="10">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="8">
+        <v>3322.2</v>
+      </c>
+      <c r="D52" s="8">
+        <v>3307.8</v>
+      </c>
+      <c r="E52" s="10">
+        <v>-14.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="8">
+        <v>1049.1</v>
+      </c>
+      <c r="D53" s="8">
+        <v>1078.5</v>
+      </c>
+      <c r="E53" s="9">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="8">
+        <v>12.89</v>
+      </c>
+      <c r="D54" s="8">
+        <v>13.5</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="8">
+        <v>12.35</v>
+      </c>
+      <c r="D55" s="8">
+        <v>12.11</v>
+      </c>
+      <c r="E55" s="10">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="8">
+        <v>4390.3</v>
+      </c>
+      <c r="D56" s="8">
+        <v>4365</v>
+      </c>
+      <c r="E56" s="10">
+        <v>-25.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="8">
+        <v>11780</v>
+      </c>
+      <c r="D57" s="8">
+        <v>11891</v>
+      </c>
+      <c r="E57" s="9">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="8">
+        <v>52.87</v>
+      </c>
+      <c r="D58" s="8">
+        <v>54.95</v>
+      </c>
+      <c r="E58" s="9">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="8">
+        <v>45.59</v>
+      </c>
+      <c r="D59" s="8">
+        <v>41.51</v>
+      </c>
+      <c r="E59" s="10">
+        <v>-4.08</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="8">
+        <v>61.48</v>
+      </c>
+      <c r="D60" s="8">
+        <v>60.05</v>
+      </c>
+      <c r="E60" s="10">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="8">
+        <v>65.93000000000001</v>
+      </c>
+      <c r="D61" s="8">
+        <v>71.12</v>
+      </c>
+      <c r="E61" s="9">
         <v>5.19</v>
       </c>
-      <c r="D10" s="6">
-        <v>5.66</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="8">
+        <v>39.79</v>
+      </c>
+      <c r="D62" s="8">
+        <v>54.93</v>
+      </c>
+      <c r="E62" s="9">
+        <v>15.14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="8">
+        <v>54.04</v>
+      </c>
+      <c r="D63" s="8">
+        <v>50.86</v>
+      </c>
+      <c r="E63" s="10">
+        <v>-3.18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="8">
+        <v>53.61</v>
+      </c>
+      <c r="D64" s="8">
+        <v>50.81</v>
+      </c>
+      <c r="E64" s="10">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="8">
+        <v>47.51</v>
+      </c>
+      <c r="D65" s="8">
+        <v>51.27</v>
+      </c>
+      <c r="E65" s="9">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="8">
+        <v>4.31</v>
+      </c>
+      <c r="D66" s="8">
+        <v>-41.98</v>
+      </c>
+      <c r="E66" s="10">
+        <v>-46.29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="8">
+        <v>147.97</v>
+      </c>
+      <c r="D67" s="8">
+        <v>-26.13</v>
+      </c>
+      <c r="E67" s="10">
+        <v>-174.1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="8">
+        <v>21.13</v>
+      </c>
+      <c r="D68" s="8">
+        <v>267.12</v>
+      </c>
+      <c r="E68" s="9">
+        <v>245.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="D11" s="6">
-        <v>8.51</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B69" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="8">
+        <v>-5.13</v>
+      </c>
+      <c r="D69" s="8">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="E69" s="9">
+        <v>76.28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-7.66</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B70" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="8">
+        <v>128.4</v>
+      </c>
+      <c r="D70" s="8">
+        <v>148.82</v>
+      </c>
+      <c r="E70" s="9">
+        <v>20.42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>21.5</v>
-      </c>
-      <c r="D13" s="6">
-        <v>16.95</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-4.55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B71" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="8">
+        <v>-84.22</v>
+      </c>
+      <c r="D71" s="8">
+        <v>-71.38</v>
+      </c>
+      <c r="E71" s="9">
+        <v>12.84</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-1.59</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-1.55</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B72" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="8">
+        <v>294.08</v>
+      </c>
+      <c r="D72" s="8">
+        <v>-23.84</v>
+      </c>
+      <c r="E72" s="10">
+        <v>-317.92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>2.79</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1.81</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-3.91</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.06</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-2.2</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-3.89</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>3.7</v>
-      </c>
-      <c r="D18" s="6">
-        <v>5.87</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>5.95</v>
-      </c>
-      <c r="D19" s="6">
-        <v>2.85</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.47</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-0.08</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-4.11</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-4.61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1.06</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-0.13</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-2.24</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>46.44</v>
-      </c>
-      <c r="D24" s="6">
-        <v>44.38</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-19.53</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-22</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>21.7</v>
-      </c>
-      <c r="D26" s="6">
-        <v>19.2</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>54.4</v>
-      </c>
-      <c r="D27" s="6">
-        <v>53.8</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>88.89</v>
-      </c>
-      <c r="D28" s="6">
-        <v>86.54000000000001</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-2.35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>133.77</v>
-      </c>
-      <c r="D29" s="6">
-        <v>133.9</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-13.66</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-13.25</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-1.79</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-4.21</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-2.42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>19.5</v>
-      </c>
-      <c r="D32" s="6">
-        <v>18.25</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-2.18</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-7.8</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-5.62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>16.45</v>
-      </c>
-      <c r="D34" s="6">
-        <v>12.79</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-3.66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1.21</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-2.24</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>8.66</v>
-      </c>
-      <c r="D36" s="6">
-        <v>0.47</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-8.19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-2.85</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-9.119999999999999</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-6.27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-4.37</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-0.25</v>
-      </c>
-      <c r="E38" s="7">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>4.53</v>
-      </c>
-      <c r="D39" s="6">
-        <v>1.79</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-3.99</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-4.13</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-34.7</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-37.28</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>0</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-1.72</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-8.32</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-8.75</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-13.92</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-14.12</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-9.48</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-11.28</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-24.88</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-24.43</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-7.77</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-9.75</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>407.75</v>
-      </c>
-      <c r="D48" s="6">
-        <v>407.15</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>61.04</v>
-      </c>
-      <c r="D49" s="6">
-        <v>58.63</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>3380.5</v>
-      </c>
-      <c r="D50" s="6">
-        <v>3322.2</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-58.3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>1054.05</v>
-      </c>
-      <c r="D51" s="6">
-        <v>1049.1</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-4.95</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>12.92</v>
-      </c>
-      <c r="D52" s="6">
-        <v>12.89</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>12.6</v>
-      </c>
-      <c r="D53" s="6">
-        <v>12.35</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>4364.2</v>
-      </c>
-      <c r="D54" s="6">
-        <v>4390.3</v>
-      </c>
-      <c r="E54" s="7">
-        <v>26.1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>12038</v>
-      </c>
-      <c r="D55" s="6">
-        <v>11780</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-258</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>53.23</v>
-      </c>
-      <c r="D56" s="6">
-        <v>52.87</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>53.64</v>
-      </c>
-      <c r="D57" s="6">
-        <v>45.59</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-8.050000000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>67.53</v>
-      </c>
-      <c r="D58" s="6">
-        <v>61.48</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-6.05</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>67.83</v>
-      </c>
-      <c r="D59" s="6">
-        <v>65.93000000000001</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>40.41</v>
-      </c>
-      <c r="D60" s="6">
-        <v>39.79</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>57.52</v>
-      </c>
-      <c r="D61" s="6">
-        <v>54.04</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-3.48</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>51.03</v>
-      </c>
-      <c r="D62" s="6">
-        <v>53.61</v>
-      </c>
-      <c r="E62" s="7">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>57</v>
-      </c>
-      <c r="D63" s="6">
-        <v>47.51</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-9.49</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="5" t="s">
+      <c r="B73" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C64" s="6">
-        <v>-46.81</v>
-      </c>
-      <c r="D64" s="6">
-        <v>4.31</v>
-      </c>
-      <c r="E64" s="7">
-        <v>51.12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>526.15</v>
-      </c>
-      <c r="D65" s="6">
-        <v>147.97</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-378.18</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>388.02</v>
-      </c>
-      <c r="D66" s="6">
-        <v>21.13</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-366.89</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>40.1</v>
-      </c>
-      <c r="D67" s="6">
-        <v>-5.13</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-45.23</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>45.43</v>
-      </c>
-      <c r="D68" s="6">
-        <v>128.4</v>
-      </c>
-      <c r="E68" s="7">
-        <v>82.97</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>25.97</v>
-      </c>
-      <c r="D69" s="6">
-        <v>-84.22</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-110.19</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>3.6</v>
-      </c>
-      <c r="D70" s="6">
-        <v>294.08</v>
-      </c>
-      <c r="E70" s="7">
-        <v>290.48</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>-53.48</v>
-      </c>
-      <c r="D71" s="6">
+      <c r="C73" s="8">
         <v>-38.06</v>
       </c>
-      <c r="E71" s="7">
-        <v>15.42</v>
+      <c r="D73" s="8">
+        <v>8.82</v>
+      </c>
+      <c r="E73" s="9">
+        <v>46.88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3185,60 +3282,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>76</v>
+      <c r="B1" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
-        <v>56.44</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="13">
+        <v>64.44</v>
+      </c>
+      <c r="C2" s="14">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>52.6</v>
-      </c>
-      <c r="E2" s="11">
-        <v>60</v>
-      </c>
-      <c r="F2" s="11">
-        <v>2.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>1.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="13">
+        <v>54.4</v>
+      </c>
+      <c r="E2" s="13">
+        <v>80</v>
+      </c>
+      <c r="F2" s="13">
+        <v>3.8</v>
+      </c>
+      <c r="G2" s="13">
+        <v>2</v>
+      </c>
+      <c r="H2" s="13">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="13">
         <v>40</v>
       </c>
     </row>
@@ -3340,55 +3437,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="15" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.2877</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2001</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1922</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1789</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1415</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1009</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2237</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.3004</v>
+      <c r="A2" s="16">
+        <v>0.2868</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.2048</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.1873</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.178</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.1574</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.1024</v>
+      </c>
+      <c r="G2" s="16">
+        <v>-0.2289</v>
+      </c>
+      <c r="H2" s="16">
+        <v>-0.3084</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,58 +190,43 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>71.1 → 60.3</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>71.1</t>
+  </si>
+  <si>
+    <t>60.3</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>39.8 → 54.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>39.8</t>
-  </si>
-  <si>
-    <t>54.9</t>
-  </si>
-  <si>
-    <t>47.5 → 51.3</t>
-  </si>
-  <si>
-    <t>47.5</t>
+    <t>50.9 → 47.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.9</t>
+  </si>
+  <si>
+    <t>47.8</t>
+  </si>
+  <si>
+    <t>51.3 → 45.4</t>
   </si>
   <si>
     <t>51.3</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.7% → -2.1%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.7%</t>
-  </si>
-  <si>
-    <t>-2.1%</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>65.9 → 71.1</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>65.9</t>
-  </si>
-  <si>
-    <t>71.1</t>
+    <t>45.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -293,7 +278,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,21 +312,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -353,8 +324,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,25 +359,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -469,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -478,15 +450,14 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -495,7 +466,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -853,7 +824,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="18" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" customWidth="1"/>
     <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
@@ -993,10 +966,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>410.95</v>
+        <v>407.7</v>
       </c>
       <c r="D2">
-        <v>0.93</v>
+        <v>-0.79</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -1005,46 +978,46 @@
         <v>268.05</v>
       </c>
       <c r="G2">
-        <v>-3.24</v>
+        <v>-4</v>
       </c>
       <c r="H2">
-        <v>53.31</v>
+        <v>52.1</v>
       </c>
       <c r="I2">
-        <v>-3.24</v>
+        <v>-3.27</v>
       </c>
       <c r="J2">
-        <v>2.93</v>
+        <v>0.84</v>
       </c>
       <c r="K2">
-        <v>17.53</v>
+        <v>14.15</v>
       </c>
       <c r="L2">
-        <v>48.28</v>
+        <v>46.58</v>
       </c>
       <c r="M2">
-        <v>28.68</v>
+        <v>28.41</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>411.08</v>
+        <v>408.32</v>
       </c>
       <c r="Q2">
-        <v>405.52</v>
+        <v>405.92</v>
       </c>
       <c r="R2">
-        <v>390.15</v>
+        <v>391.33</v>
       </c>
       <c r="S2">
-        <v>354.03</v>
+        <v>354.54</v>
       </c>
       <c r="T2">
-        <v>16.08</v>
+        <v>15</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1059,34 +1032,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>54.95</v>
+        <v>52.8</v>
       </c>
       <c r="Z2">
-        <v>5.89</v>
+        <v>5.32</v>
       </c>
       <c r="AA2">
-        <v>6.61</v>
+        <v>6.35</v>
       </c>
       <c r="AB2">
-        <v>-0.72</v>
+        <v>-1.03</v>
       </c>
       <c r="AC2">
-        <v>28.4</v>
+        <v>27.46</v>
       </c>
       <c r="AD2">
-        <v>32.44</v>
+        <v>26.96</v>
       </c>
       <c r="AE2">
-        <v>10.99</v>
+        <v>10.94</v>
       </c>
       <c r="AF2">
-        <v>-41.98</v>
+        <v>-39.58</v>
       </c>
       <c r="AG2">
-        <v>426.4</v>
+        <v>426.63</v>
       </c>
       <c r="AH2">
-        <v>384.64</v>
+        <v>385.2</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1095,7 +1068,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>21.68</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1106,10 +1079,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>57.16</v>
+        <v>56.73</v>
       </c>
       <c r="D3">
-        <v>-2.51</v>
+        <v>-0.75</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1118,25 +1091,25 @@
         <v>53.89</v>
       </c>
       <c r="G3">
-        <v>-38.85</v>
+        <v>-39.31</v>
       </c>
       <c r="H3">
-        <v>6.07</v>
+        <v>5.27</v>
       </c>
       <c r="I3">
-        <v>-7.95</v>
+        <v>-10.32</v>
       </c>
       <c r="J3">
-        <v>-3</v>
+        <v>-4.27</v>
       </c>
       <c r="K3">
-        <v>-9.960000000000001</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L3">
-        <v>-25.24</v>
+        <v>-25.47</v>
       </c>
       <c r="M3">
-        <v>-22.89</v>
+        <v>-22.78</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1145,19 +1118,19 @@
         <v>18</v>
       </c>
       <c r="P3">
-        <v>60.68</v>
+        <v>59.38</v>
       </c>
       <c r="Q3">
-        <v>59.02</v>
+        <v>58.93</v>
       </c>
       <c r="R3">
-        <v>59.68</v>
+        <v>59.61</v>
       </c>
       <c r="S3">
-        <v>67.05</v>
+        <v>66.92</v>
       </c>
       <c r="T3">
-        <v>-14.75</v>
+        <v>-15.23</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1172,43 +1145,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.51</v>
+        <v>40.36</v>
       </c>
       <c r="Z3">
-        <v>0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="AA3">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="AC3">
-        <v>38.41</v>
+        <v>17.34</v>
       </c>
       <c r="AD3">
-        <v>64.23999999999999</v>
+        <v>40.68</v>
       </c>
       <c r="AE3">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="AF3">
-        <v>-26.13</v>
+        <v>-50.5</v>
       </c>
       <c r="AG3">
-        <v>63.8</v>
+        <v>63.81</v>
       </c>
       <c r="AH3">
-        <v>54.25</v>
+        <v>54.04</v>
       </c>
       <c r="AI3">
-        <v>57.07</v>
+        <v>63.88</v>
       </c>
       <c r="AJ3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK3">
-        <v>35.78</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1219,10 +1192,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3307.8</v>
+        <v>3257</v>
       </c>
       <c r="D4">
-        <v>-0.43</v>
+        <v>-1.54</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1231,46 +1204,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.15</v>
+        <v>-3.65</v>
       </c>
       <c r="H4">
-        <v>30.69</v>
+        <v>28.68</v>
       </c>
       <c r="I4">
-        <v>2.6</v>
+        <v>1.15</v>
       </c>
       <c r="J4">
-        <v>6.25</v>
+        <v>5.54</v>
       </c>
       <c r="K4">
-        <v>12.56</v>
+        <v>11.02</v>
       </c>
       <c r="L4">
-        <v>20.03</v>
+        <v>19.14</v>
       </c>
       <c r="M4">
-        <v>17.8</v>
+        <v>17.37</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P4">
-        <v>3310.7</v>
+        <v>3318.1</v>
       </c>
       <c r="Q4">
-        <v>3179.88</v>
+        <v>3189.08</v>
       </c>
       <c r="R4">
-        <v>3151.69</v>
+        <v>3154.8</v>
       </c>
       <c r="S4">
-        <v>2897.74</v>
+        <v>2899.82</v>
       </c>
       <c r="T4">
-        <v>14.15</v>
+        <v>12.32</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1285,34 +1258,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>60.05</v>
+        <v>55.17</v>
       </c>
       <c r="Z4">
-        <v>50.1</v>
+        <v>47.35</v>
       </c>
       <c r="AA4">
-        <v>29.64</v>
+        <v>33.18</v>
       </c>
       <c r="AB4">
-        <v>20.46</v>
+        <v>14.17</v>
       </c>
       <c r="AC4">
-        <v>79.69</v>
+        <v>59.94</v>
       </c>
       <c r="AD4">
-        <v>85.23</v>
+        <v>76.52</v>
       </c>
       <c r="AE4">
-        <v>81.79000000000001</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="AF4">
-        <v>267.12</v>
+        <v>51.29</v>
       </c>
       <c r="AG4">
-        <v>3366.01</v>
+        <v>3371.11</v>
       </c>
       <c r="AH4">
-        <v>2993.75</v>
+        <v>3007.06</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1321,7 +1294,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>46.91</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1332,10 +1305,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1078.5</v>
+        <v>1046.25</v>
       </c>
       <c r="D5">
-        <v>2.8</v>
+        <v>-2.99</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1344,46 +1317,46 @@
         <v>667.05</v>
       </c>
       <c r="G5">
-        <v>-6.19</v>
+        <v>-9</v>
       </c>
       <c r="H5">
-        <v>61.68</v>
+        <v>56.85</v>
       </c>
       <c r="I5">
-        <v>3.7</v>
+        <v>1.87</v>
       </c>
       <c r="J5">
-        <v>10.69</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="K5">
-        <v>-2.25</v>
+        <v>-1.99</v>
       </c>
       <c r="L5">
-        <v>58.64</v>
+        <v>53.45</v>
       </c>
       <c r="M5">
-        <v>20.48</v>
+        <v>19.49</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P5">
-        <v>1053.65</v>
+        <v>1057.5</v>
       </c>
       <c r="Q5">
-        <v>988.16</v>
+        <v>992.51</v>
       </c>
       <c r="R5">
-        <v>996.2</v>
+        <v>994.35</v>
       </c>
       <c r="S5">
-        <v>947.54</v>
+        <v>948.65</v>
       </c>
       <c r="T5">
-        <v>13.82</v>
+        <v>10.29</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1398,34 +1371,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>71.12</v>
+        <v>60.27</v>
       </c>
       <c r="Z5">
-        <v>21.46</v>
+        <v>21.59</v>
       </c>
       <c r="AA5">
-        <v>8.359999999999999</v>
+        <v>11.01</v>
       </c>
       <c r="AB5">
-        <v>13.1</v>
+        <v>10.58</v>
       </c>
       <c r="AC5">
-        <v>93.94</v>
+        <v>85.64</v>
       </c>
       <c r="AD5">
-        <v>93.5</v>
+        <v>91.17</v>
       </c>
       <c r="AE5">
-        <v>24.23</v>
+        <v>25.25</v>
       </c>
       <c r="AF5">
-        <v>71.15000000000001</v>
+        <v>-3.48</v>
       </c>
       <c r="AG5">
-        <v>1082.84</v>
+        <v>1089.56</v>
       </c>
       <c r="AH5">
-        <v>893.48</v>
+        <v>895.45</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1434,7 +1407,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>56.98</v>
+        <v>55.87</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1445,10 +1418,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>13.5</v>
+        <v>13.51</v>
       </c>
       <c r="D6">
-        <v>4.73</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6">
         <v>15.01</v>
@@ -1457,25 +1430,25 @@
         <v>6.15</v>
       </c>
       <c r="G6">
-        <v>-10.06</v>
+        <v>-9.99</v>
       </c>
       <c r="H6">
-        <v>119.51</v>
+        <v>119.67</v>
       </c>
       <c r="I6">
-        <v>5.47</v>
+        <v>6.97</v>
       </c>
       <c r="J6">
-        <v>-2.39</v>
+        <v>-1.17</v>
       </c>
       <c r="K6">
-        <v>4.09</v>
+        <v>4.32</v>
       </c>
       <c r="L6">
-        <v>98.81999999999999</v>
+        <v>101.04</v>
       </c>
       <c r="M6">
-        <v>15.74</v>
+        <v>16.49</v>
       </c>
       <c r="N6">
         <v>87</v>
@@ -1484,19 +1457,19 @@
         <v>91</v>
       </c>
       <c r="P6">
-        <v>12.93</v>
+        <v>13.11</v>
       </c>
       <c r="Q6">
-        <v>13.13</v>
+        <v>13.11</v>
       </c>
       <c r="R6">
-        <v>13.9</v>
+        <v>13.87</v>
       </c>
       <c r="S6">
-        <v>11.51</v>
+        <v>11.53</v>
       </c>
       <c r="T6">
-        <v>17.27</v>
+        <v>17.16</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1511,34 +1484,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>54.93</v>
+        <v>55.13</v>
       </c>
       <c r="Z6">
-        <v>-0.22</v>
+        <v>-0.17</v>
       </c>
       <c r="AA6">
-        <v>-0.27</v>
+        <v>-0.25</v>
       </c>
       <c r="AB6">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="AC6">
-        <v>94.55</v>
+        <v>97.8</v>
       </c>
       <c r="AD6">
-        <v>69.2</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="AE6">
         <v>0.39</v>
       </c>
       <c r="AF6">
-        <v>148.82</v>
+        <v>64.16</v>
       </c>
       <c r="AG6">
-        <v>13.85</v>
+        <v>13.76</v>
       </c>
       <c r="AH6">
-        <v>12.42</v>
+        <v>12.47</v>
       </c>
       <c r="AI6">
         <v>13.76</v>
@@ -1547,7 +1520,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>50.36</v>
+        <v>49.46</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1558,10 +1531,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.11</v>
+        <v>11.87</v>
       </c>
       <c r="D7">
-        <v>-1.94</v>
+        <v>-1.98</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1570,46 +1543,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-13</v>
+        <v>-14.73</v>
       </c>
       <c r="H7">
-        <v>158.21</v>
+        <v>153.09</v>
       </c>
       <c r="I7">
-        <v>-8.67</v>
+        <v>-8.69</v>
       </c>
       <c r="J7">
-        <v>12.44</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="K7">
-        <v>-6.41</v>
+        <v>-3.5</v>
       </c>
       <c r="L7">
-        <v>134.24</v>
+        <v>134.58</v>
       </c>
       <c r="M7">
-        <v>-30.84</v>
+        <v>-30.55</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P7">
-        <v>12.56</v>
+        <v>12.33</v>
       </c>
       <c r="Q7">
-        <v>12.14</v>
+        <v>12.18</v>
       </c>
       <c r="R7">
         <v>11.58</v>
       </c>
       <c r="S7">
-        <v>9.779999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="T7">
-        <v>23.76</v>
+        <v>20.9</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1624,34 +1597,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>50.86</v>
+        <v>47.82</v>
       </c>
       <c r="Z7">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="AA7">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="AB7">
-        <v>-0</v>
+        <v>-0.06</v>
       </c>
       <c r="AC7">
-        <v>34.31</v>
+        <v>22.15</v>
       </c>
       <c r="AD7">
-        <v>45.41</v>
+        <v>33.87</v>
       </c>
       <c r="AE7">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="AF7">
-        <v>-71.38</v>
+        <v>-77.45999999999999</v>
       </c>
       <c r="AG7">
-        <v>13.6</v>
+        <v>13.57</v>
       </c>
       <c r="AH7">
-        <v>10.69</v>
+        <v>10.79</v>
       </c>
       <c r="AI7">
         <v>11.82</v>
@@ -1660,7 +1633,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>22.1</v>
+        <v>24.91</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1671,10 +1644,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4365</v>
+        <v>4533.5</v>
       </c>
       <c r="D8">
-        <v>-0.58</v>
+        <v>3.86</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1683,46 +1656,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-24.86</v>
+        <v>-21.96</v>
       </c>
       <c r="H8">
-        <v>5.05</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I8">
-        <v>0.61</v>
+        <v>5.06</v>
       </c>
       <c r="J8">
-        <v>0.06</v>
+        <v>3.95</v>
       </c>
       <c r="K8">
-        <v>-1.38</v>
+        <v>1.76</v>
       </c>
       <c r="L8">
-        <v>-13.28</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="M8">
-        <v>18.73</v>
+        <v>19.75</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="P8">
-        <v>4361.04</v>
+        <v>4404.74</v>
       </c>
       <c r="Q8">
-        <v>4345.99</v>
+        <v>4352.09</v>
       </c>
       <c r="R8">
-        <v>4351.59</v>
+        <v>4355.81</v>
       </c>
       <c r="S8">
-        <v>4710.56</v>
+        <v>4705.09</v>
       </c>
       <c r="T8">
-        <v>-7.34</v>
+        <v>-3.65</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1737,34 +1710,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>50.81</v>
+        <v>64.22</v>
       </c>
       <c r="Z8">
-        <v>-4.98</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AA8">
-        <v>-13.31</v>
+        <v>-8.67</v>
       </c>
       <c r="AB8">
-        <v>8.33</v>
+        <v>18.55</v>
       </c>
       <c r="AC8">
-        <v>91.70999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AD8">
-        <v>87.45</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="AE8">
-        <v>84.45</v>
+        <v>105.92</v>
       </c>
       <c r="AF8">
-        <v>-23.84</v>
+        <v>1129.83</v>
       </c>
       <c r="AG8">
-        <v>4434.61</v>
+        <v>4471.24</v>
       </c>
       <c r="AH8">
-        <v>4257.37</v>
+        <v>4232.94</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1773,7 +1746,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>17.35</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1784,10 +1757,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11891</v>
+        <v>11706</v>
       </c>
       <c r="D9">
-        <v>0.9399999999999999</v>
+        <v>-1.56</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1796,46 +1769,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-8.9</v>
+        <v>-10.31</v>
       </c>
       <c r="H9">
-        <v>14.76</v>
+        <v>12.97</v>
       </c>
       <c r="I9">
-        <v>-2.45</v>
+        <v>-3.06</v>
       </c>
       <c r="J9">
-        <v>3.44</v>
+        <v>-0.9</v>
       </c>
       <c r="K9">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="L9">
-        <v>-2.74</v>
+        <v>-4.62</v>
       </c>
       <c r="M9">
-        <v>10.24</v>
+        <v>9.92</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>11977.8</v>
+        <v>11904</v>
       </c>
       <c r="Q9">
-        <v>11945.5</v>
+        <v>11942.25</v>
       </c>
       <c r="R9">
-        <v>11583.5</v>
+        <v>11595.6</v>
       </c>
       <c r="S9">
-        <v>11797.05</v>
+        <v>11795.99</v>
       </c>
       <c r="T9">
-        <v>0.8</v>
+        <v>-0.76</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1847,37 +1820,37 @@
         <v>47</v>
       </c>
       <c r="X9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>51.27</v>
+        <v>45.43</v>
       </c>
       <c r="Z9">
-        <v>94.23</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="AA9">
-        <v>122.64</v>
+        <v>111.58</v>
       </c>
       <c r="AB9">
-        <v>-28.41</v>
+        <v>-44.24</v>
       </c>
       <c r="AC9">
-        <v>16.62</v>
+        <v>7.64</v>
       </c>
       <c r="AD9">
-        <v>28.48</v>
+        <v>17.05</v>
       </c>
       <c r="AE9">
-        <v>220.04</v>
+        <v>228.25</v>
       </c>
       <c r="AF9">
-        <v>8.82</v>
+        <v>4</v>
       </c>
       <c r="AG9">
-        <v>12196.08</v>
+        <v>12203.8</v>
       </c>
       <c r="AH9">
-        <v>11694.92</v>
+        <v>11680.7</v>
       </c>
       <c r="AI9">
         <v>11461.94</v>
@@ -1886,7 +1859,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>20.39</v>
+        <v>22.26</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2067,7 +2040,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2086,37 +2059,37 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>63</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>67</v>
@@ -2125,1144 +2098,1124 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="6" t="s">
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2.93</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.84</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-3</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-4.27</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>6.25</v>
+      </c>
+      <c r="D11" s="7">
+        <v>5.54</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>10.69</v>
+      </c>
+      <c r="D12" s="7">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-2.39</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-1.17</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>12.44</v>
+      </c>
+      <c r="D14" s="7">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-4.33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="D15" s="7">
+        <v>3.95</v>
+      </c>
+      <c r="E15" s="9">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>3.44</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-0.9</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-4.34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="D10" s="8">
-        <v>2.93</v>
-      </c>
-      <c r="E10" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-3.24</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-3.27</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="8">
-        <v>-3.11</v>
-      </c>
-      <c r="D11" s="8">
-        <v>-3</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-7.95</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-10.32</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-2.37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8">
-        <v>5.66</v>
-      </c>
-      <c r="D12" s="8">
-        <v>6.25</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>8.51</v>
-      </c>
-      <c r="D13" s="8">
-        <v>10.69</v>
-      </c>
-      <c r="E13" s="9">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>3.7</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1.87</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>-7.66</v>
-      </c>
-      <c r="D14" s="8">
-        <v>-2.39</v>
-      </c>
-      <c r="E14" s="9">
-        <v>5.27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>5.47</v>
+      </c>
+      <c r="D21" s="7">
+        <v>6.97</v>
+      </c>
+      <c r="E21" s="9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>16.95</v>
-      </c>
-      <c r="D15" s="8">
-        <v>12.44</v>
-      </c>
-      <c r="E15" s="10">
-        <v>-4.51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-8.67</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-8.69</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8">
-        <v>-1.55</v>
-      </c>
-      <c r="D16" s="8">
-        <v>0.06</v>
-      </c>
-      <c r="E16" s="9">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>0.61</v>
+      </c>
+      <c r="D23" s="7">
+        <v>5.06</v>
+      </c>
+      <c r="E23" s="9">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="8">
-        <v>1.81</v>
-      </c>
-      <c r="D17" s="8">
-        <v>3.44</v>
-      </c>
-      <c r="E17" s="9">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-2.45</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-3.06</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="8">
-        <v>-3.06</v>
-      </c>
-      <c r="D18" s="8">
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>48.28</v>
+      </c>
+      <c r="D25" s="7">
+        <v>46.58</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-25.24</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-25.47</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>20.03</v>
+      </c>
+      <c r="D27" s="7">
+        <v>19.14</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>58.64</v>
+      </c>
+      <c r="D28" s="7">
+        <v>53.45</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-5.19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="D29" s="7">
+        <v>101.04</v>
+      </c>
+      <c r="E29" s="9">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>134.24</v>
+      </c>
+      <c r="D30" s="7">
+        <v>134.58</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-13.28</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="E31" s="9">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-2.74</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-4.62</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>17.53</v>
+      </c>
+      <c r="D33" s="7">
+        <v>14.15</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-3.38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>12.56</v>
+      </c>
+      <c r="D35" s="7">
+        <v>11.02</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-2.25</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-1.99</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>4.09</v>
+      </c>
+      <c r="D37" s="7">
+        <v>4.32</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-6.41</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-3.5</v>
+      </c>
+      <c r="E38" s="9">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-1.38</v>
+      </c>
+      <c r="D39" s="7">
+        <v>1.76</v>
+      </c>
+      <c r="E39" s="9">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>1.7</v>
+      </c>
+      <c r="D40" s="7">
+        <v>1.91</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
         <v>-3.24</v>
       </c>
-      <c r="E18" s="10">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="D41" s="7">
+        <v>-4</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-3.89</v>
-      </c>
-      <c r="D19" s="8">
-        <v>-7.95</v>
-      </c>
-      <c r="E19" s="10">
-        <v>-4.06</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-38.85</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-39.31</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="8">
-        <v>5.87</v>
-      </c>
-      <c r="D20" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="E20" s="10">
-        <v>-3.27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-2.15</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-3.65</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="8">
-        <v>2.85</v>
-      </c>
-      <c r="D21" s="8">
-        <v>3.7</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-6.19</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-9</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>-0.08</v>
-      </c>
-      <c r="D22" s="8">
-        <v>5.47</v>
-      </c>
-      <c r="E22" s="9">
-        <v>5.55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-10.06</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-9.99</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="D23" s="8">
-        <v>-8.67</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-13</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-14.73</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="8">
-        <v>1.06</v>
-      </c>
-      <c r="D24" s="8">
-        <v>0.61</v>
-      </c>
-      <c r="E24" s="10">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-24.86</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-21.96</v>
+      </c>
+      <c r="E47" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="8">
-        <v>-2.24</v>
-      </c>
-      <c r="D25" s="8">
-        <v>-2.45</v>
-      </c>
-      <c r="E25" s="10">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-8.9</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-10.31</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="8">
-        <v>44.38</v>
-      </c>
-      <c r="D26" s="8">
-        <v>48.28</v>
-      </c>
-      <c r="E26" s="9">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>410.95</v>
+      </c>
+      <c r="D49" s="7">
+        <v>407.7</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-3.25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="8">
-        <v>-22</v>
-      </c>
-      <c r="D27" s="8">
-        <v>-25.24</v>
-      </c>
-      <c r="E27" s="10">
-        <v>-3.24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>57.16</v>
+      </c>
+      <c r="D50" s="7">
+        <v>56.73</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="8">
-        <v>19.2</v>
-      </c>
-      <c r="D28" s="8">
-        <v>20.03</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
+      <c r="B51" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7">
+        <v>3307.8</v>
+      </c>
+      <c r="D51" s="7">
+        <v>3257</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-50.8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="8">
-        <v>53.8</v>
-      </c>
-      <c r="D29" s="8">
-        <v>58.64</v>
-      </c>
-      <c r="E29" s="9">
-        <v>4.84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
+      <c r="B52" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7">
+        <v>1078.5</v>
+      </c>
+      <c r="D52" s="7">
+        <v>1046.25</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-32.25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="8">
-        <v>86.54000000000001</v>
-      </c>
-      <c r="D30" s="8">
-        <v>98.81999999999999</v>
-      </c>
-      <c r="E30" s="9">
-        <v>12.28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="D53" s="7">
+        <v>13.51</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="8">
-        <v>133.9</v>
-      </c>
-      <c r="D31" s="8">
-        <v>134.24</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>12.11</v>
+      </c>
+      <c r="D54" s="7">
+        <v>11.87</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="8">
-        <v>-13.25</v>
-      </c>
-      <c r="D32" s="8">
-        <v>-13.28</v>
-      </c>
-      <c r="E32" s="10">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>4365</v>
+      </c>
+      <c r="D55" s="7">
+        <v>4533.5</v>
+      </c>
+      <c r="E55" s="9">
+        <v>168.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="8">
-        <v>-4.21</v>
-      </c>
-      <c r="D33" s="8">
-        <v>-2.74</v>
-      </c>
-      <c r="E33" s="9">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>11891</v>
+      </c>
+      <c r="D56" s="7">
+        <v>11706</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-185</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="8">
-        <v>18.25</v>
-      </c>
-      <c r="D34" s="8">
-        <v>17.53</v>
-      </c>
-      <c r="E34" s="10">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>54.95</v>
+      </c>
+      <c r="D57" s="7">
+        <v>52.8</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-2.15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="8">
-        <v>-7.8</v>
-      </c>
-      <c r="D35" s="8">
-        <v>-9.960000000000001</v>
-      </c>
-      <c r="E35" s="10">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>41.51</v>
+      </c>
+      <c r="D58" s="7">
+        <v>40.36</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="8">
-        <v>12.79</v>
-      </c>
-      <c r="D36" s="8">
-        <v>12.56</v>
-      </c>
-      <c r="E36" s="10">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>60.05</v>
+      </c>
+      <c r="D59" s="7">
+        <v>55.17</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-4.88</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="8">
-        <v>-2.24</v>
-      </c>
-      <c r="D37" s="8">
-        <v>-2.25</v>
-      </c>
-      <c r="E37" s="10">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
+      <c r="B60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="7">
+        <v>71.12</v>
+      </c>
+      <c r="D60" s="7">
+        <v>60.27</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-10.85</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="8">
-        <v>0.47</v>
-      </c>
-      <c r="D38" s="8">
-        <v>4.09</v>
-      </c>
-      <c r="E38" s="9">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
+      <c r="B61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="7">
+        <v>54.93</v>
+      </c>
+      <c r="D61" s="7">
+        <v>55.13</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="8">
-        <v>-9.119999999999999</v>
-      </c>
-      <c r="D39" s="8">
-        <v>-6.41</v>
-      </c>
-      <c r="E39" s="9">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>50.86</v>
+      </c>
+      <c r="D62" s="7">
+        <v>47.82</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="8">
-        <v>-0.25</v>
-      </c>
-      <c r="D40" s="8">
-        <v>-1.38</v>
-      </c>
-      <c r="E40" s="10">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>50.81</v>
+      </c>
+      <c r="D63" s="7">
+        <v>64.22</v>
+      </c>
+      <c r="E63" s="9">
+        <v>13.41</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="8">
-        <v>1.79</v>
-      </c>
-      <c r="D41" s="8">
-        <v>1.7</v>
-      </c>
-      <c r="E41" s="10">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>51.27</v>
+      </c>
+      <c r="D64" s="7">
+        <v>45.43</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-5.84</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="8">
-        <v>-4.13</v>
-      </c>
-      <c r="D42" s="8">
-        <v>-3.24</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
+      <c r="B65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7">
+        <v>-41.98</v>
+      </c>
+      <c r="D65" s="7">
+        <v>-39.58</v>
+      </c>
+      <c r="E65" s="9">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="8">
-        <v>-37.28</v>
-      </c>
-      <c r="D43" s="8">
-        <v>-38.85</v>
-      </c>
-      <c r="E43" s="10">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
+      <c r="B66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="7">
+        <v>-26.13</v>
+      </c>
+      <c r="D66" s="7">
+        <v>-50.5</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-24.37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="8">
-        <v>-1.72</v>
-      </c>
-      <c r="D44" s="8">
-        <v>-2.15</v>
-      </c>
-      <c r="E44" s="10">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
+      <c r="B67" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="7">
+        <v>267.12</v>
+      </c>
+      <c r="D67" s="7">
+        <v>51.29</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-215.83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="8">
-        <v>-8.75</v>
-      </c>
-      <c r="D45" s="8">
-        <v>-6.19</v>
-      </c>
-      <c r="E45" s="9">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
+      <c r="B68" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="7">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="D68" s="7">
+        <v>-3.48</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-74.63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="8">
-        <v>-14.12</v>
-      </c>
-      <c r="D46" s="8">
-        <v>-10.06</v>
-      </c>
-      <c r="E46" s="9">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
+      <c r="B69" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="7">
+        <v>148.82</v>
+      </c>
+      <c r="D69" s="7">
+        <v>64.16</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-84.66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="8">
-        <v>-11.28</v>
-      </c>
-      <c r="D47" s="8">
-        <v>-13</v>
-      </c>
-      <c r="E47" s="10">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
+      <c r="B70" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="7">
+        <v>-71.38</v>
+      </c>
+      <c r="D70" s="7">
+        <v>-77.45999999999999</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-6.08</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="8">
-        <v>-24.43</v>
-      </c>
-      <c r="D48" s="8">
-        <v>-24.86</v>
-      </c>
-      <c r="E48" s="10">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>-23.84</v>
+      </c>
+      <c r="D71" s="7">
+        <v>1129.83</v>
+      </c>
+      <c r="E71" s="9">
+        <v>1153.67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="8">
-        <v>-9.75</v>
-      </c>
-      <c r="D49" s="8">
-        <v>-8.9</v>
-      </c>
-      <c r="E49" s="9">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="8">
-        <v>407.15</v>
-      </c>
-      <c r="D50" s="8">
-        <v>410.95</v>
-      </c>
-      <c r="E50" s="9">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="8">
-        <v>58.63</v>
-      </c>
-      <c r="D51" s="8">
-        <v>57.16</v>
-      </c>
-      <c r="E51" s="10">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="8">
-        <v>3322.2</v>
-      </c>
-      <c r="D52" s="8">
-        <v>3307.8</v>
-      </c>
-      <c r="E52" s="10">
-        <v>-14.4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="8">
-        <v>1049.1</v>
-      </c>
-      <c r="D53" s="8">
-        <v>1078.5</v>
-      </c>
-      <c r="E53" s="9">
-        <v>29.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="8">
-        <v>12.89</v>
-      </c>
-      <c r="D54" s="8">
-        <v>13.5</v>
-      </c>
-      <c r="E54" s="9">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="8">
-        <v>12.35</v>
-      </c>
-      <c r="D55" s="8">
-        <v>12.11</v>
-      </c>
-      <c r="E55" s="10">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="8">
-        <v>4390.3</v>
-      </c>
-      <c r="D56" s="8">
-        <v>4365</v>
-      </c>
-      <c r="E56" s="10">
-        <v>-25.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="8">
-        <v>11780</v>
-      </c>
-      <c r="D57" s="8">
-        <v>11891</v>
-      </c>
-      <c r="E57" s="9">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="8">
-        <v>52.87</v>
-      </c>
-      <c r="D58" s="8">
-        <v>54.95</v>
-      </c>
-      <c r="E58" s="9">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="8">
-        <v>45.59</v>
-      </c>
-      <c r="D59" s="8">
-        <v>41.51</v>
-      </c>
-      <c r="E59" s="10">
-        <v>-4.08</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="8">
-        <v>61.48</v>
-      </c>
-      <c r="D60" s="8">
-        <v>60.05</v>
-      </c>
-      <c r="E60" s="10">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="8">
-        <v>65.93000000000001</v>
-      </c>
-      <c r="D61" s="8">
-        <v>71.12</v>
-      </c>
-      <c r="E61" s="9">
-        <v>5.19</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="8">
-        <v>39.79</v>
-      </c>
-      <c r="D62" s="8">
-        <v>54.93</v>
-      </c>
-      <c r="E62" s="9">
-        <v>15.14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="8">
-        <v>54.04</v>
-      </c>
-      <c r="D63" s="8">
-        <v>50.86</v>
-      </c>
-      <c r="E63" s="10">
-        <v>-3.18</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="8">
-        <v>53.61</v>
-      </c>
-      <c r="D64" s="8">
-        <v>50.81</v>
-      </c>
-      <c r="E64" s="10">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="8">
-        <v>47.51</v>
-      </c>
-      <c r="D65" s="8">
-        <v>51.27</v>
-      </c>
-      <c r="E65" s="9">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="7" t="s">
+      <c r="B72" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C66" s="8">
-        <v>4.31</v>
-      </c>
-      <c r="D66" s="8">
-        <v>-41.98</v>
-      </c>
-      <c r="E66" s="10">
-        <v>-46.29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="8">
-        <v>147.97</v>
-      </c>
-      <c r="D67" s="8">
-        <v>-26.13</v>
-      </c>
-      <c r="E67" s="10">
-        <v>-174.1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="8">
-        <v>21.13</v>
-      </c>
-      <c r="D68" s="8">
-        <v>267.12</v>
-      </c>
-      <c r="E68" s="9">
-        <v>245.99</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="8">
-        <v>-5.13</v>
-      </c>
-      <c r="D69" s="8">
-        <v>71.15000000000001</v>
-      </c>
-      <c r="E69" s="9">
-        <v>76.28</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="8">
-        <v>128.4</v>
-      </c>
-      <c r="D70" s="8">
-        <v>148.82</v>
-      </c>
-      <c r="E70" s="9">
-        <v>20.42</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="8">
-        <v>-84.22</v>
-      </c>
-      <c r="D71" s="8">
-        <v>-71.38</v>
-      </c>
-      <c r="E71" s="9">
-        <v>12.84</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="8">
-        <v>294.08</v>
-      </c>
-      <c r="D72" s="8">
-        <v>-23.84</v>
-      </c>
-      <c r="E72" s="10">
-        <v>-317.92</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="8">
-        <v>-38.06</v>
-      </c>
-      <c r="D73" s="8">
+      <c r="C72" s="7">
         <v>8.82</v>
       </c>
-      <c r="E73" s="9">
-        <v>46.88</v>
+      <c r="D72" s="7">
+        <v>4</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-4.82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3282,60 +3235,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="13">
-        <v>64.44</v>
-      </c>
-      <c r="C2" s="14">
+      <c r="B2" s="12">
+        <v>56.44</v>
+      </c>
+      <c r="C2" s="13">
         <v>8</v>
       </c>
-      <c r="D2" s="13">
-        <v>54.4</v>
-      </c>
-      <c r="E2" s="13">
-        <v>80</v>
-      </c>
-      <c r="F2" s="13">
-        <v>3.8</v>
-      </c>
-      <c r="G2" s="13">
-        <v>2</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="D2" s="12">
+        <v>52.6</v>
+      </c>
+      <c r="E2" s="12">
+        <v>60</v>
+      </c>
+      <c r="F2" s="12">
+        <v>2.7</v>
+      </c>
+      <c r="G2" s="12">
+        <v>2.3</v>
+      </c>
+      <c r="H2" s="12">
         <v>56.1</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -3437,55 +3390,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="16">
-        <v>0.2868</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.2048</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.1873</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.178</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.1574</v>
-      </c>
-      <c r="F2" s="16">
-        <v>0.1024</v>
-      </c>
-      <c r="G2" s="16">
-        <v>-0.2289</v>
-      </c>
-      <c r="H2" s="16">
-        <v>-0.3084</v>
+      <c r="A2" s="15">
+        <v>0.2841</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1975</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1949</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1737</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1649</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0992</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.2278</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.3055</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,43 +190,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>71.1 → 60.3</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>71.1</t>
-  </si>
-  <si>
-    <t>60.3</t>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.9 → 47.8</t>
+    <t>52.8 → 48.6</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.9</t>
-  </si>
-  <si>
-    <t>47.8</t>
-  </si>
-  <si>
-    <t>51.3 → 45.4</t>
-  </si>
-  <si>
-    <t>51.3</t>
-  </si>
-  <si>
-    <t>45.4</t>
+    <t>52.8</t>
+  </si>
+  <si>
+    <t>48.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -278,7 +263,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,7 +297,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -324,15 +309,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -359,19 +337,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,11 +425,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -466,7 +438,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -825,9 +797,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -966,10 +936,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>407.7</v>
+        <v>401</v>
       </c>
       <c r="D2">
-        <v>-0.79</v>
+        <v>-1.64</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -978,46 +948,46 @@
         <v>268.05</v>
       </c>
       <c r="G2">
-        <v>-4</v>
+        <v>-5.58</v>
       </c>
       <c r="H2">
-        <v>52.1</v>
+        <v>49.6</v>
       </c>
       <c r="I2">
-        <v>-3.27</v>
+        <v>-1.73</v>
       </c>
       <c r="J2">
-        <v>0.84</v>
+        <v>0.33</v>
       </c>
       <c r="K2">
-        <v>14.15</v>
+        <v>14.54</v>
       </c>
       <c r="L2">
-        <v>46.58</v>
+        <v>47.53</v>
       </c>
       <c r="M2">
-        <v>28.41</v>
+        <v>28.61</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P2">
-        <v>408.32</v>
+        <v>406.91</v>
       </c>
       <c r="Q2">
-        <v>405.92</v>
+        <v>405.89</v>
       </c>
       <c r="R2">
-        <v>391.33</v>
+        <v>392.27</v>
       </c>
       <c r="S2">
-        <v>354.54</v>
+        <v>354.99</v>
       </c>
       <c r="T2">
-        <v>15</v>
+        <v>12.96</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1032,34 +1002,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>52.8</v>
+        <v>48.59</v>
       </c>
       <c r="Z2">
-        <v>5.32</v>
+        <v>4.27</v>
       </c>
       <c r="AA2">
-        <v>6.35</v>
+        <v>5.94</v>
       </c>
       <c r="AB2">
-        <v>-1.03</v>
+        <v>-1.66</v>
       </c>
       <c r="AC2">
-        <v>27.46</v>
+        <v>19.77</v>
       </c>
       <c r="AD2">
-        <v>26.96</v>
+        <v>25.21</v>
       </c>
       <c r="AE2">
-        <v>10.94</v>
+        <v>10.68</v>
       </c>
       <c r="AF2">
-        <v>-39.58</v>
+        <v>-67.86</v>
       </c>
       <c r="AG2">
         <v>426.63</v>
       </c>
       <c r="AH2">
-        <v>385.2</v>
+        <v>385.15</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1068,7 +1038,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>20.79</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1079,10 +1049,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>56.73</v>
+        <v>55.98</v>
       </c>
       <c r="D3">
-        <v>-0.75</v>
+        <v>-1.32</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1091,25 +1061,25 @@
         <v>53.89</v>
       </c>
       <c r="G3">
-        <v>-39.31</v>
+        <v>-40.12</v>
       </c>
       <c r="H3">
-        <v>5.27</v>
+        <v>3.88</v>
       </c>
       <c r="I3">
-        <v>-10.32</v>
+        <v>-11.61</v>
       </c>
       <c r="J3">
-        <v>-4.27</v>
+        <v>-4.6</v>
       </c>
       <c r="K3">
-        <v>-9.460000000000001</v>
+        <v>-9.65</v>
       </c>
       <c r="L3">
-        <v>-25.47</v>
+        <v>-24.55</v>
       </c>
       <c r="M3">
-        <v>-22.78</v>
+        <v>-23</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1118,19 +1088,19 @@
         <v>18</v>
       </c>
       <c r="P3">
-        <v>59.38</v>
+        <v>57.91</v>
       </c>
       <c r="Q3">
-        <v>58.93</v>
+        <v>58.83</v>
       </c>
       <c r="R3">
-        <v>59.61</v>
+        <v>59.51</v>
       </c>
       <c r="S3">
-        <v>66.92</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="T3">
-        <v>-15.23</v>
+        <v>-16.19</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1145,43 +1115,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>40.36</v>
+        <v>38.38</v>
       </c>
       <c r="Z3">
-        <v>-0.1</v>
+        <v>-0.36</v>
       </c>
       <c r="AA3">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="AB3">
-        <v>-0.21</v>
+        <v>-0.38</v>
       </c>
       <c r="AC3">
-        <v>17.34</v>
+        <v>5.73</v>
       </c>
       <c r="AD3">
-        <v>40.68</v>
+        <v>20.49</v>
       </c>
       <c r="AE3">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AF3">
-        <v>-50.5</v>
+        <v>-25.59</v>
       </c>
       <c r="AG3">
-        <v>63.81</v>
+        <v>63.87</v>
       </c>
       <c r="AH3">
-        <v>54.04</v>
+        <v>53.79</v>
       </c>
       <c r="AI3">
-        <v>63.88</v>
+        <v>63.09</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>35.09</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1192,10 +1162,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3257</v>
+        <v>3248.7</v>
       </c>
       <c r="D4">
-        <v>-1.54</v>
+        <v>-0.25</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1204,46 +1174,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-3.65</v>
+        <v>-3.9</v>
       </c>
       <c r="H4">
-        <v>28.68</v>
+        <v>28.35</v>
       </c>
       <c r="I4">
-        <v>1.15</v>
+        <v>-2.24</v>
       </c>
       <c r="J4">
-        <v>5.54</v>
+        <v>5.72</v>
       </c>
       <c r="K4">
-        <v>11.02</v>
+        <v>10.36</v>
       </c>
       <c r="L4">
-        <v>19.14</v>
+        <v>21.14</v>
       </c>
       <c r="M4">
-        <v>17.37</v>
+        <v>17.42</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P4">
-        <v>3318.1</v>
+        <v>3303.24</v>
       </c>
       <c r="Q4">
-        <v>3189.08</v>
+        <v>3196.03</v>
       </c>
       <c r="R4">
-        <v>3154.8</v>
+        <v>3157.7</v>
       </c>
       <c r="S4">
-        <v>2899.82</v>
+        <v>2901.45</v>
       </c>
       <c r="T4">
-        <v>12.32</v>
+        <v>11.97</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1258,34 +1228,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>55.17</v>
+        <v>54.39</v>
       </c>
       <c r="Z4">
-        <v>47.35</v>
+        <v>44</v>
       </c>
       <c r="AA4">
-        <v>33.18</v>
+        <v>35.35</v>
       </c>
       <c r="AB4">
-        <v>14.17</v>
+        <v>8.65</v>
       </c>
       <c r="AC4">
-        <v>59.94</v>
+        <v>48.01</v>
       </c>
       <c r="AD4">
-        <v>76.52</v>
+        <v>62.55</v>
       </c>
       <c r="AE4">
-        <v>83.56999999999999</v>
+        <v>80.73</v>
       </c>
       <c r="AF4">
-        <v>51.29</v>
+        <v>-32.32</v>
       </c>
       <c r="AG4">
-        <v>3371.11</v>
+        <v>3375.9</v>
       </c>
       <c r="AH4">
-        <v>3007.06</v>
+        <v>3016.17</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1294,7 +1264,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>43.24</v>
+        <v>40.06</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1305,10 +1275,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1046.25</v>
+        <v>1029.5</v>
       </c>
       <c r="D5">
-        <v>-2.99</v>
+        <v>-1.6</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1317,88 +1287,88 @@
         <v>667.05</v>
       </c>
       <c r="G5">
-        <v>-9</v>
+        <v>-10.45</v>
       </c>
       <c r="H5">
-        <v>56.85</v>
+        <v>54.34</v>
       </c>
       <c r="I5">
-        <v>1.87</v>
+        <v>-2.84</v>
       </c>
       <c r="J5">
-        <v>9.460000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="K5">
-        <v>-1.99</v>
+        <v>-2.24</v>
       </c>
       <c r="L5">
-        <v>53.45</v>
+        <v>53.03</v>
       </c>
       <c r="M5">
-        <v>19.49</v>
+        <v>19.14</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P5">
-        <v>1057.5</v>
+        <v>1051.48</v>
       </c>
       <c r="Q5">
-        <v>992.51</v>
+        <v>996.78</v>
       </c>
       <c r="R5">
-        <v>994.35</v>
+        <v>992.4299999999999</v>
       </c>
       <c r="S5">
-        <v>948.65</v>
+        <v>949.59</v>
       </c>
       <c r="T5">
-        <v>10.29</v>
+        <v>8.42</v>
       </c>
       <c r="U5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V5" t="s">
         <v>46</v>
       </c>
       <c r="W5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5">
-        <v>60.27</v>
+        <v>55.53</v>
       </c>
       <c r="Z5">
-        <v>21.59</v>
+        <v>20.1</v>
       </c>
       <c r="AA5">
-        <v>11.01</v>
+        <v>12.82</v>
       </c>
       <c r="AB5">
-        <v>10.58</v>
+        <v>7.28</v>
       </c>
       <c r="AC5">
-        <v>85.64</v>
+        <v>74.7</v>
       </c>
       <c r="AD5">
-        <v>91.17</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="AE5">
-        <v>25.25</v>
+        <v>25.23</v>
       </c>
       <c r="AF5">
-        <v>-3.48</v>
+        <v>-33.5</v>
       </c>
       <c r="AG5">
-        <v>1089.56</v>
+        <v>1092.37</v>
       </c>
       <c r="AH5">
-        <v>895.45</v>
+        <v>901.1799999999999</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1407,7 +1377,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>55.87</v>
+        <v>51.02</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1418,10 +1388,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>13.51</v>
+        <v>14.11</v>
       </c>
       <c r="D6">
-        <v>0.07000000000000001</v>
+        <v>4.44</v>
       </c>
       <c r="E6">
         <v>15.01</v>
@@ -1430,46 +1400,46 @@
         <v>6.15</v>
       </c>
       <c r="G6">
-        <v>-9.99</v>
+        <v>-6</v>
       </c>
       <c r="H6">
-        <v>119.67</v>
+        <v>129.43</v>
       </c>
       <c r="I6">
-        <v>6.97</v>
+        <v>10.84</v>
       </c>
       <c r="J6">
-        <v>-1.17</v>
+        <v>1.58</v>
       </c>
       <c r="K6">
-        <v>4.32</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L6">
-        <v>101.04</v>
+        <v>116.74</v>
       </c>
       <c r="M6">
-        <v>16.49</v>
+        <v>18.88</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P6">
-        <v>13.11</v>
+        <v>13.39</v>
       </c>
       <c r="Q6">
-        <v>13.11</v>
+        <v>13.13</v>
       </c>
       <c r="R6">
-        <v>13.87</v>
+        <v>13.85</v>
       </c>
       <c r="S6">
-        <v>11.53</v>
+        <v>11.55</v>
       </c>
       <c r="T6">
-        <v>17.16</v>
+        <v>22.14</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1484,43 +1454,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>55.13</v>
+        <v>65.09</v>
       </c>
       <c r="Z6">
-        <v>-0.17</v>
+        <v>-0.08</v>
       </c>
       <c r="AA6">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="AB6">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AC6">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="AD6">
-        <v>88.15000000000001</v>
+        <v>97.45</v>
       </c>
       <c r="AE6">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="AF6">
-        <v>64.16</v>
+        <v>126.24</v>
       </c>
       <c r="AG6">
-        <v>13.76</v>
+        <v>13.87</v>
       </c>
       <c r="AH6">
-        <v>12.47</v>
+        <v>12.4</v>
       </c>
       <c r="AI6">
-        <v>13.76</v>
+        <v>12.61</v>
       </c>
       <c r="AJ6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK6">
-        <v>49.46</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1531,10 +1501,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.87</v>
+        <v>11.7</v>
       </c>
       <c r="D7">
-        <v>-1.98</v>
+        <v>-1.43</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1543,46 +1513,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-14.73</v>
+        <v>-15.95</v>
       </c>
       <c r="H7">
-        <v>153.09</v>
+        <v>149.47</v>
       </c>
       <c r="I7">
-        <v>-8.69</v>
+        <v>-8.16</v>
       </c>
       <c r="J7">
-        <v>8.109999999999999</v>
+        <v>4.56</v>
       </c>
       <c r="K7">
-        <v>-3.5</v>
+        <v>0.09</v>
       </c>
       <c r="L7">
-        <v>134.58</v>
+        <v>134</v>
       </c>
       <c r="M7">
-        <v>-30.55</v>
+        <v>-30.52</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P7">
-        <v>12.33</v>
+        <v>12.13</v>
       </c>
       <c r="Q7">
-        <v>12.18</v>
+        <v>12.19</v>
       </c>
       <c r="R7">
         <v>11.58</v>
       </c>
       <c r="S7">
-        <v>9.82</v>
+        <v>9.85</v>
       </c>
       <c r="T7">
-        <v>20.9</v>
+        <v>18.77</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1597,43 +1567,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>47.82</v>
+        <v>45.74</v>
       </c>
       <c r="Z7">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="AA7">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AB7">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="AC7">
-        <v>22.15</v>
+        <v>11.74</v>
       </c>
       <c r="AD7">
-        <v>33.87</v>
+        <v>22.73</v>
       </c>
       <c r="AE7">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="AF7">
-        <v>-77.45999999999999</v>
+        <v>-50.44</v>
       </c>
       <c r="AG7">
-        <v>13.57</v>
+        <v>13.55</v>
       </c>
       <c r="AH7">
-        <v>10.79</v>
+        <v>10.83</v>
       </c>
       <c r="AI7">
-        <v>11.82</v>
+        <v>12.92</v>
       </c>
       <c r="AJ7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK7">
-        <v>24.91</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1644,10 +1614,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4533.5</v>
+        <v>4547</v>
       </c>
       <c r="D8">
-        <v>3.86</v>
+        <v>0.3</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1656,46 +1626,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-21.96</v>
+        <v>-21.73</v>
       </c>
       <c r="H8">
-        <v>9.109999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="I8">
-        <v>5.06</v>
+        <v>4.03</v>
       </c>
       <c r="J8">
-        <v>3.95</v>
+        <v>3.07</v>
       </c>
       <c r="K8">
-        <v>1.76</v>
+        <v>3.34</v>
       </c>
       <c r="L8">
-        <v>-9.380000000000001</v>
+        <v>-8.66</v>
       </c>
       <c r="M8">
-        <v>19.75</v>
+        <v>20.12</v>
       </c>
       <c r="N8">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="O8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P8">
-        <v>4404.74</v>
+        <v>4440</v>
       </c>
       <c r="Q8">
-        <v>4352.09</v>
+        <v>4360.16</v>
       </c>
       <c r="R8">
-        <v>4355.81</v>
+        <v>4361.23</v>
       </c>
       <c r="S8">
-        <v>4705.09</v>
+        <v>4699.47</v>
       </c>
       <c r="T8">
-        <v>-3.65</v>
+        <v>-3.24</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1710,34 +1680,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>64.22</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="Z8">
-        <v>9.880000000000001</v>
+        <v>22.49</v>
       </c>
       <c r="AA8">
-        <v>-8.67</v>
+        <v>-2.44</v>
       </c>
       <c r="AB8">
-        <v>18.55</v>
+        <v>24.93</v>
       </c>
       <c r="AC8">
         <v>93.5</v>
       </c>
       <c r="AD8">
-        <v>93.06999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AE8">
-        <v>105.92</v>
+        <v>104.53</v>
       </c>
       <c r="AF8">
-        <v>1129.83</v>
+        <v>173.89</v>
       </c>
       <c r="AG8">
-        <v>4471.24</v>
+        <v>4507.41</v>
       </c>
       <c r="AH8">
-        <v>4232.94</v>
+        <v>4212.91</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1746,7 +1716,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>24.22</v>
+        <v>30.18</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1757,10 +1727,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11706</v>
+        <v>11619</v>
       </c>
       <c r="D9">
-        <v>-1.56</v>
+        <v>-0.74</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1769,46 +1739,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-10.31</v>
+        <v>-10.98</v>
       </c>
       <c r="H9">
-        <v>12.97</v>
+        <v>12.13</v>
       </c>
       <c r="I9">
-        <v>-3.06</v>
+        <v>-4.01</v>
       </c>
       <c r="J9">
-        <v>-0.9</v>
+        <v>-1.29</v>
       </c>
       <c r="K9">
-        <v>1.91</v>
+        <v>0.5</v>
       </c>
       <c r="L9">
-        <v>-4.62</v>
+        <v>-4.43</v>
       </c>
       <c r="M9">
-        <v>9.92</v>
+        <v>10.11</v>
       </c>
       <c r="N9">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="O9">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P9">
-        <v>11904</v>
+        <v>11806.8</v>
       </c>
       <c r="Q9">
-        <v>11942.25</v>
+        <v>11936.85</v>
       </c>
       <c r="R9">
-        <v>11595.6</v>
+        <v>11608.04</v>
       </c>
       <c r="S9">
-        <v>11795.99</v>
+        <v>11794.01</v>
       </c>
       <c r="T9">
-        <v>-0.76</v>
+        <v>-1.48</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1823,34 +1793,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>45.43</v>
+        <v>42.95</v>
       </c>
       <c r="Z9">
-        <v>67.34999999999999</v>
+        <v>38.57</v>
       </c>
       <c r="AA9">
-        <v>111.58</v>
+        <v>96.98</v>
       </c>
       <c r="AB9">
-        <v>-44.24</v>
+        <v>-58.41</v>
       </c>
       <c r="AC9">
         <v>7.64</v>
       </c>
       <c r="AD9">
-        <v>17.05</v>
+        <v>10.63</v>
       </c>
       <c r="AE9">
-        <v>228.25</v>
+        <v>220.45</v>
       </c>
       <c r="AF9">
-        <v>4</v>
+        <v>-32.47</v>
       </c>
       <c r="AG9">
-        <v>12203.8</v>
+        <v>12220.63</v>
       </c>
       <c r="AH9">
-        <v>11680.7</v>
+        <v>11653.07</v>
       </c>
       <c r="AI9">
         <v>11461.94</v>
@@ -1859,7 +1829,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>22.26</v>
+        <v>23.87</v>
       </c>
     </row>
   </sheetData>
@@ -2000,7 +1970,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2043,64 +2013,64 @@
         <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>65</v>
+      <c r="C4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2112,16 +2082,16 @@
         <v>0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2132,13 +2102,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>2.93</v>
+        <v>0.84</v>
       </c>
       <c r="D9" s="7">
-        <v>0.84</v>
+        <v>0.33</v>
       </c>
       <c r="E9" s="8">
-        <v>-2.09</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2149,13 +2119,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>-3</v>
+        <v>-4.27</v>
       </c>
       <c r="D10" s="7">
-        <v>-4.27</v>
+        <v>-4.6</v>
       </c>
       <c r="E10" s="8">
-        <v>-1.27</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2166,13 +2136,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>6.25</v>
+        <v>5.54</v>
       </c>
       <c r="D11" s="7">
-        <v>5.54</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.71</v>
+        <v>5.72</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.18</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2183,13 +2153,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>10.69</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="D12" s="7">
-        <v>9.460000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="E12" s="8">
-        <v>-1.23</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2200,13 +2170,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-2.39</v>
+        <v>-1.17</v>
       </c>
       <c r="D13" s="7">
-        <v>-1.17</v>
+        <v>1.58</v>
       </c>
       <c r="E13" s="9">
-        <v>1.22</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2217,13 +2187,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>12.44</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="D14" s="7">
-        <v>8.109999999999999</v>
+        <v>4.56</v>
       </c>
       <c r="E14" s="8">
-        <v>-4.33</v>
+        <v>-3.55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2234,13 +2204,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>0.06</v>
+        <v>3.95</v>
       </c>
       <c r="D15" s="7">
-        <v>3.95</v>
-      </c>
-      <c r="E15" s="9">
-        <v>3.89</v>
+        <v>3.07</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2251,13 +2221,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>3.44</v>
+        <v>-0.9</v>
       </c>
       <c r="D16" s="7">
-        <v>-0.9</v>
+        <v>-1.29</v>
       </c>
       <c r="E16" s="8">
-        <v>-4.34</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2268,13 +2238,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>-3.24</v>
+        <v>-3.27</v>
       </c>
       <c r="D17" s="7">
-        <v>-3.27</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.03</v>
+        <v>-1.73</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1.54</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2285,13 +2255,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>-7.95</v>
+        <v>-10.32</v>
       </c>
       <c r="D18" s="7">
-        <v>-10.32</v>
+        <v>-11.61</v>
       </c>
       <c r="E18" s="8">
-        <v>-2.37</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2302,13 +2272,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>2.6</v>
+        <v>1.15</v>
       </c>
       <c r="D19" s="7">
-        <v>1.15</v>
+        <v>-2.24</v>
       </c>
       <c r="E19" s="8">
-        <v>-1.45</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2319,13 +2289,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>3.7</v>
+        <v>1.87</v>
       </c>
       <c r="D20" s="7">
-        <v>1.87</v>
+        <v>-2.84</v>
       </c>
       <c r="E20" s="8">
-        <v>-1.83</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2336,13 +2306,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>5.47</v>
+        <v>6.97</v>
       </c>
       <c r="D21" s="7">
-        <v>6.97</v>
+        <v>10.84</v>
       </c>
       <c r="E21" s="9">
-        <v>1.5</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2353,13 +2323,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>-8.67</v>
+        <v>-8.69</v>
       </c>
       <c r="D22" s="7">
-        <v>-8.69</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.02</v>
+        <v>-8.16</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.53</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2370,13 +2340,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>0.61</v>
+        <v>5.06</v>
       </c>
       <c r="D23" s="7">
-        <v>5.06</v>
-      </c>
-      <c r="E23" s="9">
-        <v>4.45</v>
+        <v>4.03</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2387,13 +2357,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>-2.45</v>
+        <v>-3.06</v>
       </c>
       <c r="D24" s="7">
-        <v>-3.06</v>
+        <v>-4.01</v>
       </c>
       <c r="E24" s="8">
-        <v>-0.61</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2404,13 +2374,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="7">
-        <v>48.28</v>
+        <v>46.58</v>
       </c>
       <c r="D25" s="7">
-        <v>46.58</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.7</v>
+        <v>47.53</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.95</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2421,13 +2391,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="7">
-        <v>-25.24</v>
+        <v>-25.47</v>
       </c>
       <c r="D26" s="7">
-        <v>-25.47</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.23</v>
+        <v>-24.55</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.92</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2438,13 +2408,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>20.03</v>
+        <v>19.14</v>
       </c>
       <c r="D27" s="7">
-        <v>19.14</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.89</v>
+        <v>21.14</v>
+      </c>
+      <c r="E27" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2455,13 +2425,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>58.64</v>
+        <v>53.45</v>
       </c>
       <c r="D28" s="7">
-        <v>53.45</v>
+        <v>53.03</v>
       </c>
       <c r="E28" s="8">
-        <v>-5.19</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2472,13 +2442,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>98.81999999999999</v>
+        <v>101.04</v>
       </c>
       <c r="D29" s="7">
-        <v>101.04</v>
+        <v>116.74</v>
       </c>
       <c r="E29" s="9">
-        <v>2.22</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2489,13 +2459,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>134.24</v>
+        <v>134.58</v>
       </c>
       <c r="D30" s="7">
-        <v>134.58</v>
-      </c>
-      <c r="E30" s="9">
-        <v>0.34</v>
+        <v>134</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2506,13 +2476,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>-13.28</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="D31" s="7">
-        <v>-9.380000000000001</v>
+        <v>-8.66</v>
       </c>
       <c r="E31" s="9">
-        <v>3.9</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2523,13 +2493,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>-2.74</v>
+        <v>-4.62</v>
       </c>
       <c r="D32" s="7">
-        <v>-4.62</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.88</v>
+        <v>-4.43</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.19</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2540,13 +2510,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="7">
-        <v>17.53</v>
+        <v>14.15</v>
       </c>
       <c r="D33" s="7">
-        <v>14.15</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-3.38</v>
+        <v>14.54</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.39</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2557,13 +2527,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="7">
-        <v>-9.960000000000001</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="D34" s="7">
-        <v>-9.460000000000001</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.5</v>
+        <v>-9.65</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2574,13 +2544,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="7">
-        <v>12.56</v>
+        <v>11.02</v>
       </c>
       <c r="D35" s="7">
-        <v>11.02</v>
+        <v>10.36</v>
       </c>
       <c r="E35" s="8">
-        <v>-1.54</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2591,13 +2561,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>-2.25</v>
+        <v>-1.99</v>
       </c>
       <c r="D36" s="7">
-        <v>-1.99</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0.26</v>
+        <v>-2.24</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2608,13 +2578,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>4.09</v>
+        <v>4.32</v>
       </c>
       <c r="D37" s="7">
-        <v>4.32</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="E37" s="9">
-        <v>0.23</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2625,13 +2595,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>-6.41</v>
+        <v>-3.5</v>
       </c>
       <c r="D38" s="7">
-        <v>-3.5</v>
+        <v>0.09</v>
       </c>
       <c r="E38" s="9">
-        <v>2.91</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2642,13 +2612,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>-1.38</v>
+        <v>1.76</v>
       </c>
       <c r="D39" s="7">
-        <v>1.76</v>
+        <v>3.34</v>
       </c>
       <c r="E39" s="9">
-        <v>3.14</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2659,13 +2629,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="D40" s="7">
-        <v>1.91</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.21</v>
+        <v>0.5</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2676,13 +2646,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="7">
-        <v>-3.24</v>
+        <v>-4</v>
       </c>
       <c r="D41" s="7">
-        <v>-4</v>
+        <v>-5.58</v>
       </c>
       <c r="E41" s="8">
-        <v>-0.76</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2693,13 +2663,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="7">
-        <v>-38.85</v>
+        <v>-39.31</v>
       </c>
       <c r="D42" s="7">
-        <v>-39.31</v>
+        <v>-40.12</v>
       </c>
       <c r="E42" s="8">
-        <v>-0.46</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2710,13 +2680,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="7">
-        <v>-2.15</v>
+        <v>-3.65</v>
       </c>
       <c r="D43" s="7">
-        <v>-3.65</v>
+        <v>-3.9</v>
       </c>
       <c r="E43" s="8">
-        <v>-1.5</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2727,13 +2697,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="7">
-        <v>-6.19</v>
+        <v>-9</v>
       </c>
       <c r="D44" s="7">
-        <v>-9</v>
+        <v>-10.45</v>
       </c>
       <c r="E44" s="8">
-        <v>-2.81</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2744,13 +2714,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>-10.06</v>
+        <v>-9.99</v>
       </c>
       <c r="D45" s="7">
-        <v>-9.99</v>
+        <v>-6</v>
       </c>
       <c r="E45" s="9">
-        <v>0.07000000000000001</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2761,13 +2731,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-13</v>
+        <v>-14.73</v>
       </c>
       <c r="D46" s="7">
-        <v>-14.73</v>
+        <v>-15.95</v>
       </c>
       <c r="E46" s="8">
-        <v>-1.73</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2778,13 +2748,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-24.86</v>
+        <v>-21.96</v>
       </c>
       <c r="D47" s="7">
-        <v>-21.96</v>
+        <v>-21.73</v>
       </c>
       <c r="E47" s="9">
-        <v>2.9</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2795,13 +2765,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-8.9</v>
+        <v>-10.31</v>
       </c>
       <c r="D48" s="7">
-        <v>-10.31</v>
+        <v>-10.98</v>
       </c>
       <c r="E48" s="8">
-        <v>-1.41</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2812,13 +2782,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="7">
-        <v>410.95</v>
+        <v>407.7</v>
       </c>
       <c r="D49" s="7">
-        <v>407.7</v>
+        <v>401</v>
       </c>
       <c r="E49" s="8">
-        <v>-3.25</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2829,13 +2799,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="7">
-        <v>57.16</v>
+        <v>56.73</v>
       </c>
       <c r="D50" s="7">
-        <v>56.73</v>
+        <v>55.98</v>
       </c>
       <c r="E50" s="8">
-        <v>-0.43</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2846,13 +2816,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="7">
-        <v>3307.8</v>
+        <v>3257</v>
       </c>
       <c r="D51" s="7">
-        <v>3257</v>
+        <v>3248.7</v>
       </c>
       <c r="E51" s="8">
-        <v>-50.8</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2863,13 +2833,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="7">
-        <v>1078.5</v>
+        <v>1046.25</v>
       </c>
       <c r="D52" s="7">
-        <v>1046.25</v>
+        <v>1029.5</v>
       </c>
       <c r="E52" s="8">
-        <v>-32.25</v>
+        <v>-16.75</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2880,13 +2850,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="7">
-        <v>13.5</v>
+        <v>13.51</v>
       </c>
       <c r="D53" s="7">
-        <v>13.51</v>
+        <v>14.11</v>
       </c>
       <c r="E53" s="9">
-        <v>0.01</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2897,13 +2867,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="7">
-        <v>12.11</v>
+        <v>11.87</v>
       </c>
       <c r="D54" s="7">
-        <v>11.87</v>
+        <v>11.7</v>
       </c>
       <c r="E54" s="8">
-        <v>-0.24</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2914,13 +2884,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>4365</v>
+        <v>4533.5</v>
       </c>
       <c r="D55" s="7">
-        <v>4533.5</v>
+        <v>4547</v>
       </c>
       <c r="E55" s="9">
-        <v>168.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2931,285 +2901,319 @@
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>11891</v>
+        <v>11706</v>
       </c>
       <c r="D56" s="7">
-        <v>11706</v>
+        <v>11619</v>
       </c>
       <c r="E56" s="8">
-        <v>-185</v>
+        <v>-87</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C57" s="7">
-        <v>54.95</v>
+        <v>26</v>
       </c>
       <c r="D57" s="7">
-        <v>52.8</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-2.15</v>
+        <v>38</v>
+      </c>
+      <c r="E57" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="7">
         <v>38</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>41.51</v>
-      </c>
       <c r="D58" s="7">
-        <v>40.36</v>
+        <v>26</v>
       </c>
       <c r="E58" s="8">
-        <v>-1.15</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="7">
-        <v>60.05</v>
+        <v>52.8</v>
       </c>
       <c r="D59" s="7">
-        <v>55.17</v>
+        <v>48.59</v>
       </c>
       <c r="E59" s="8">
-        <v>-4.88</v>
+        <v>-4.21</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="7">
-        <v>71.12</v>
+        <v>40.36</v>
       </c>
       <c r="D60" s="7">
-        <v>60.27</v>
+        <v>38.38</v>
       </c>
       <c r="E60" s="8">
-        <v>-10.85</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="7">
-        <v>54.93</v>
+        <v>55.17</v>
       </c>
       <c r="D61" s="7">
-        <v>55.13</v>
-      </c>
-      <c r="E61" s="9">
-        <v>0.2</v>
+        <v>54.39</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="7">
-        <v>50.86</v>
+        <v>60.27</v>
       </c>
       <c r="D62" s="7">
-        <v>47.82</v>
+        <v>55.53</v>
       </c>
       <c r="E62" s="8">
-        <v>-3.04</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="7">
-        <v>50.81</v>
+        <v>55.13</v>
       </c>
       <c r="D63" s="7">
-        <v>64.22</v>
+        <v>65.09</v>
       </c>
       <c r="E63" s="9">
-        <v>13.41</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="7">
-        <v>51.27</v>
+        <v>47.82</v>
       </c>
       <c r="D64" s="7">
-        <v>45.43</v>
+        <v>45.74</v>
       </c>
       <c r="E64" s="8">
-        <v>-5.84</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C65" s="7">
-        <v>-41.98</v>
+        <v>64.22</v>
       </c>
       <c r="D65" s="7">
-        <v>-39.58</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="E65" s="9">
-        <v>2.4</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C66" s="7">
-        <v>-26.13</v>
+        <v>45.43</v>
       </c>
       <c r="D66" s="7">
-        <v>-50.5</v>
+        <v>42.95</v>
       </c>
       <c r="E66" s="8">
-        <v>-24.37</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C67" s="7">
-        <v>267.12</v>
+        <v>-39.58</v>
       </c>
       <c r="D67" s="7">
-        <v>51.29</v>
+        <v>-67.86</v>
       </c>
       <c r="E67" s="8">
-        <v>-215.83</v>
+        <v>-28.28</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="7">
-        <v>71.15000000000001</v>
+        <v>-50.5</v>
       </c>
       <c r="D68" s="7">
-        <v>-3.48</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-74.63</v>
+        <v>-25.59</v>
+      </c>
+      <c r="E68" s="9">
+        <v>24.91</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="7">
-        <v>148.82</v>
+        <v>51.29</v>
       </c>
       <c r="D69" s="7">
-        <v>64.16</v>
+        <v>-32.32</v>
       </c>
       <c r="E69" s="8">
-        <v>-84.66</v>
+        <v>-83.61</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C70" s="7">
-        <v>-71.38</v>
+        <v>-3.48</v>
       </c>
       <c r="D70" s="7">
-        <v>-77.45999999999999</v>
+        <v>-33.5</v>
       </c>
       <c r="E70" s="8">
-        <v>-6.08</v>
+        <v>-30.02</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C71" s="7">
-        <v>-23.84</v>
+        <v>64.16</v>
       </c>
       <c r="D71" s="7">
-        <v>1129.83</v>
+        <v>126.24</v>
       </c>
       <c r="E71" s="9">
-        <v>1153.67</v>
+        <v>62.08</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="7">
-        <v>8.82</v>
+        <v>-77.45999999999999</v>
       </c>
       <c r="D72" s="7">
+        <v>-50.44</v>
+      </c>
+      <c r="E72" s="9">
+        <v>27.02</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>1129.83</v>
+      </c>
+      <c r="D73" s="7">
+        <v>173.89</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-955.9400000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
         <v>4</v>
       </c>
-      <c r="E72" s="8">
-        <v>-4.82</v>
+      <c r="D74" s="7">
+        <v>-32.47</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-36.47</v>
       </c>
     </row>
   </sheetData>
@@ -3239,28 +3243,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3274,22 +3278,22 @@
         <v>8</v>
       </c>
       <c r="D2" s="12">
-        <v>52.6</v>
+        <v>52</v>
       </c>
       <c r="E2" s="12">
         <v>60</v>
       </c>
       <c r="F2" s="12">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="G2" s="12">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="H2" s="12">
         <v>56.1</v>
       </c>
       <c r="I2" s="12">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3400,10 +3404,10 @@
         <v>40</v>
       </c>
       <c r="D1" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>41</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>44</v>
@@ -3417,28 +3421,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="15">
-        <v>0.2841</v>
+        <v>0.2861</v>
       </c>
       <c r="B2" s="15">
-        <v>0.1975</v>
+        <v>0.2012</v>
       </c>
       <c r="C2" s="15">
-        <v>0.1949</v>
+        <v>0.1914</v>
       </c>
       <c r="D2" s="15">
-        <v>0.1737</v>
+        <v>0.1888</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1649</v>
+        <v>0.1742</v>
       </c>
       <c r="F2" s="15">
-        <v>0.0992</v>
+        <v>0.1011</v>
       </c>
       <c r="G2" s="15">
-        <v>-0.2278</v>
+        <v>-0.23</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.3055</v>
+        <v>-0.3052</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,28 +190,13 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
     <t>No → Yes</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>52.8 → 48.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.8</t>
-  </si>
-  <si>
-    <t>48.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -413,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -421,7 +406,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -936,10 +920,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>401</v>
+        <v>398.7</v>
       </c>
       <c r="D2">
-        <v>-1.64</v>
+        <v>-0.57</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -948,46 +932,46 @@
         <v>268.05</v>
       </c>
       <c r="G2">
-        <v>-5.58</v>
+        <v>-6.12</v>
       </c>
       <c r="H2">
-        <v>49.6</v>
+        <v>48.74</v>
       </c>
       <c r="I2">
-        <v>-1.73</v>
+        <v>-2.22</v>
       </c>
       <c r="J2">
-        <v>0.33</v>
+        <v>-0.71</v>
       </c>
       <c r="K2">
-        <v>14.54</v>
+        <v>13.53</v>
       </c>
       <c r="L2">
-        <v>47.53</v>
+        <v>47.01</v>
       </c>
       <c r="M2">
-        <v>28.61</v>
+        <v>28.8</v>
       </c>
       <c r="N2">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="O2">
         <v>83</v>
       </c>
       <c r="P2">
-        <v>406.91</v>
+        <v>405.1</v>
       </c>
       <c r="Q2">
-        <v>405.89</v>
+        <v>405.77</v>
       </c>
       <c r="R2">
-        <v>392.27</v>
+        <v>393.1</v>
       </c>
       <c r="S2">
-        <v>354.99</v>
+        <v>355.42</v>
       </c>
       <c r="T2">
-        <v>12.96</v>
+        <v>12.18</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1002,34 +986,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>48.59</v>
+        <v>47.2</v>
       </c>
       <c r="Z2">
-        <v>4.27</v>
+        <v>3.23</v>
       </c>
       <c r="AA2">
-        <v>5.94</v>
+        <v>5.39</v>
       </c>
       <c r="AB2">
-        <v>-1.66</v>
+        <v>-2.17</v>
       </c>
       <c r="AC2">
-        <v>19.77</v>
+        <v>7.55</v>
       </c>
       <c r="AD2">
-        <v>25.21</v>
+        <v>18.26</v>
       </c>
       <c r="AE2">
-        <v>10.68</v>
+        <v>10.38</v>
       </c>
       <c r="AF2">
-        <v>-67.86</v>
+        <v>-49.52</v>
       </c>
       <c r="AG2">
-        <v>426.63</v>
+        <v>426.66</v>
       </c>
       <c r="AH2">
-        <v>385.15</v>
+        <v>384.88</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1038,7 +1022,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>20.03</v>
+        <v>21.81</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1052,7 +1036,7 @@
         <v>55.98</v>
       </c>
       <c r="D3">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1067,40 +1051,40 @@
         <v>3.88</v>
       </c>
       <c r="I3">
-        <v>-11.61</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="J3">
-        <v>-4.6</v>
+        <v>-3.23</v>
       </c>
       <c r="K3">
-        <v>-9.65</v>
+        <v>-10.37</v>
       </c>
       <c r="L3">
-        <v>-24.55</v>
+        <v>-25.01</v>
       </c>
       <c r="M3">
-        <v>-23</v>
+        <v>-22.97</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P3">
-        <v>57.91</v>
+        <v>56.9</v>
       </c>
       <c r="Q3">
-        <v>58.83</v>
+        <v>58.77</v>
       </c>
       <c r="R3">
-        <v>59.51</v>
+        <v>59.42</v>
       </c>
       <c r="S3">
-        <v>66.79000000000001</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="T3">
-        <v>-16.19</v>
+        <v>-16.01</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1118,40 +1102,40 @@
         <v>38.38</v>
       </c>
       <c r="Z3">
-        <v>-0.36</v>
+        <v>-0.57</v>
       </c>
       <c r="AA3">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="AB3">
-        <v>-0.38</v>
+        <v>-0.47</v>
       </c>
       <c r="AC3">
-        <v>5.73</v>
+        <v>0.28</v>
       </c>
       <c r="AD3">
-        <v>20.49</v>
+        <v>7.78</v>
       </c>
       <c r="AE3">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AF3">
-        <v>-25.59</v>
+        <v>-18.86</v>
       </c>
       <c r="AG3">
-        <v>63.87</v>
+        <v>63.93</v>
       </c>
       <c r="AH3">
-        <v>53.79</v>
+        <v>53.61</v>
       </c>
       <c r="AI3">
-        <v>63.09</v>
+        <v>62.97</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>35.61</v>
+        <v>36.07</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1162,10 +1146,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3248.7</v>
+        <v>3250.5</v>
       </c>
       <c r="D4">
-        <v>-0.25</v>
+        <v>0.06</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1174,25 +1158,25 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-3.9</v>
+        <v>-3.85</v>
       </c>
       <c r="H4">
-        <v>28.35</v>
+        <v>28.42</v>
       </c>
       <c r="I4">
-        <v>-2.24</v>
+        <v>-3.85</v>
       </c>
       <c r="J4">
-        <v>5.72</v>
+        <v>4.53</v>
       </c>
       <c r="K4">
-        <v>10.36</v>
+        <v>10.74</v>
       </c>
       <c r="L4">
-        <v>21.14</v>
+        <v>18.25</v>
       </c>
       <c r="M4">
-        <v>17.42</v>
+        <v>17.57</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1201,16 +1185,16 @@
         <v>71</v>
       </c>
       <c r="P4">
-        <v>3303.24</v>
+        <v>3277.24</v>
       </c>
       <c r="Q4">
-        <v>3196.03</v>
+        <v>3201.37</v>
       </c>
       <c r="R4">
-        <v>3157.7</v>
+        <v>3160.96</v>
       </c>
       <c r="S4">
-        <v>2901.45</v>
+        <v>2903.03</v>
       </c>
       <c r="T4">
         <v>11.97</v>
@@ -1228,34 +1212,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>54.39</v>
+        <v>54.54</v>
       </c>
       <c r="Z4">
-        <v>44</v>
+        <v>41.01</v>
       </c>
       <c r="AA4">
-        <v>35.35</v>
+        <v>36.48</v>
       </c>
       <c r="AB4">
-        <v>8.65</v>
+        <v>4.53</v>
       </c>
       <c r="AC4">
-        <v>48.01</v>
+        <v>38.48</v>
       </c>
       <c r="AD4">
-        <v>62.55</v>
+        <v>48.81</v>
       </c>
       <c r="AE4">
-        <v>80.73</v>
+        <v>78.44</v>
       </c>
       <c r="AF4">
-        <v>-32.32</v>
+        <v>89.08</v>
       </c>
       <c r="AG4">
-        <v>3375.9</v>
+        <v>3381.04</v>
       </c>
       <c r="AH4">
-        <v>3016.17</v>
+        <v>3021.7</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1264,7 +1248,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>40.06</v>
+        <v>37.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1275,10 +1259,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1029.5</v>
+        <v>1049.9</v>
       </c>
       <c r="D5">
-        <v>-1.6</v>
+        <v>1.98</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1287,46 +1271,46 @@
         <v>667.05</v>
       </c>
       <c r="G5">
-        <v>-10.45</v>
+        <v>-8.68</v>
       </c>
       <c r="H5">
-        <v>54.34</v>
+        <v>57.39</v>
       </c>
       <c r="I5">
-        <v>-2.84</v>
+        <v>-0.39</v>
       </c>
       <c r="J5">
-        <v>7.32</v>
+        <v>11.2</v>
       </c>
       <c r="K5">
-        <v>-2.24</v>
+        <v>0.15</v>
       </c>
       <c r="L5">
-        <v>53.03</v>
+        <v>56.04</v>
       </c>
       <c r="M5">
-        <v>19.14</v>
+        <v>19.87</v>
       </c>
       <c r="N5">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="O5">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P5">
-        <v>1051.48</v>
+        <v>1050.65</v>
       </c>
       <c r="Q5">
-        <v>996.78</v>
+        <v>1001.88</v>
       </c>
       <c r="R5">
-        <v>992.4299999999999</v>
+        <v>991.5700000000001</v>
       </c>
       <c r="S5">
-        <v>949.59</v>
+        <v>950.59</v>
       </c>
       <c r="T5">
-        <v>8.42</v>
+        <v>10.45</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1341,34 +1325,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>55.53</v>
+        <v>59.69</v>
       </c>
       <c r="Z5">
-        <v>20.1</v>
+        <v>20.33</v>
       </c>
       <c r="AA5">
-        <v>12.82</v>
+        <v>14.33</v>
       </c>
       <c r="AB5">
-        <v>7.28</v>
+        <v>6.01</v>
       </c>
       <c r="AC5">
-        <v>74.7</v>
+        <v>58.5</v>
       </c>
       <c r="AD5">
-        <v>84.76000000000001</v>
+        <v>72.95</v>
       </c>
       <c r="AE5">
-        <v>25.23</v>
+        <v>25.6</v>
       </c>
       <c r="AF5">
-        <v>-33.5</v>
+        <v>-40.52</v>
       </c>
       <c r="AG5">
-        <v>1092.37</v>
+        <v>1097.37</v>
       </c>
       <c r="AH5">
-        <v>901.1799999999999</v>
+        <v>906.39</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1377,7 +1361,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>51.02</v>
+        <v>49.18</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1388,10 +1372,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.11</v>
+        <v>13.71</v>
       </c>
       <c r="D6">
-        <v>4.44</v>
+        <v>-2.83</v>
       </c>
       <c r="E6">
         <v>15.01</v>
@@ -1400,46 +1384,46 @@
         <v>6.15</v>
       </c>
       <c r="G6">
-        <v>-6</v>
+        <v>-8.66</v>
       </c>
       <c r="H6">
-        <v>129.43</v>
+        <v>122.93</v>
       </c>
       <c r="I6">
-        <v>10.84</v>
+        <v>6.11</v>
       </c>
       <c r="J6">
-        <v>1.58</v>
+        <v>-0.22</v>
       </c>
       <c r="K6">
-        <v>9.720000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="L6">
-        <v>116.74</v>
+        <v>107.73</v>
       </c>
       <c r="M6">
-        <v>18.88</v>
+        <v>18.98</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P6">
-        <v>13.39</v>
+        <v>13.54</v>
       </c>
       <c r="Q6">
-        <v>13.13</v>
+        <v>13.14</v>
       </c>
       <c r="R6">
-        <v>13.85</v>
+        <v>13.83</v>
       </c>
       <c r="S6">
-        <v>11.55</v>
+        <v>11.57</v>
       </c>
       <c r="T6">
-        <v>22.14</v>
+        <v>18.46</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1454,43 +1438,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>65.09</v>
+        <v>56.14</v>
       </c>
       <c r="Z6">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="AA6">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="AB6">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="AC6">
-        <v>100</v>
+        <v>91.25</v>
       </c>
       <c r="AD6">
-        <v>97.45</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="AE6">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="AF6">
-        <v>126.24</v>
+        <v>-15.3</v>
       </c>
       <c r="AG6">
-        <v>13.87</v>
+        <v>13.9</v>
       </c>
       <c r="AH6">
-        <v>12.4</v>
+        <v>12.38</v>
       </c>
       <c r="AI6">
-        <v>12.61</v>
+        <v>12.65</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>50.39</v>
+        <v>51.19</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,7 +1488,7 @@
         <v>11.7</v>
       </c>
       <c r="D7">
-        <v>-1.43</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1519,19 +1503,19 @@
         <v>149.47</v>
       </c>
       <c r="I7">
-        <v>-8.16</v>
+        <v>-7.14</v>
       </c>
       <c r="J7">
-        <v>4.56</v>
+        <v>2.54</v>
       </c>
       <c r="K7">
-        <v>0.09</v>
+        <v>-4.49</v>
       </c>
       <c r="L7">
-        <v>134</v>
+        <v>129.41</v>
       </c>
       <c r="M7">
-        <v>-30.52</v>
+        <v>-30.28</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1540,19 +1524,19 @@
         <v>93</v>
       </c>
       <c r="P7">
-        <v>12.13</v>
+        <v>11.95</v>
       </c>
       <c r="Q7">
-        <v>12.19</v>
+        <v>12.2</v>
       </c>
       <c r="R7">
         <v>11.58</v>
       </c>
       <c r="S7">
-        <v>9.85</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="T7">
-        <v>18.77</v>
+        <v>18.38</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1570,40 +1554,40 @@
         <v>45.74</v>
       </c>
       <c r="Z7">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="AA7">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="AB7">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="AC7">
-        <v>11.74</v>
+        <v>4.42</v>
       </c>
       <c r="AD7">
-        <v>22.73</v>
+        <v>12.77</v>
       </c>
       <c r="AE7">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="AF7">
-        <v>-50.44</v>
+        <v>-51.78</v>
       </c>
       <c r="AG7">
         <v>13.55</v>
       </c>
       <c r="AH7">
-        <v>10.83</v>
+        <v>10.84</v>
       </c>
       <c r="AI7">
-        <v>12.92</v>
+        <v>12.88</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>28.2</v>
+        <v>31.05</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,7 +1601,7 @@
         <v>4547</v>
       </c>
       <c r="D8">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1632,19 +1616,19 @@
         <v>9.43</v>
       </c>
       <c r="I8">
-        <v>4.03</v>
+        <v>4.19</v>
       </c>
       <c r="J8">
-        <v>3.07</v>
+        <v>3.68</v>
       </c>
       <c r="K8">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="L8">
-        <v>-8.66</v>
+        <v>-7.01</v>
       </c>
       <c r="M8">
-        <v>20.12</v>
+        <v>20.19</v>
       </c>
       <c r="N8">
         <v>38</v>
@@ -1653,22 +1637,22 @@
         <v>48</v>
       </c>
       <c r="P8">
-        <v>4440</v>
+        <v>4476.56</v>
       </c>
       <c r="Q8">
-        <v>4360.16</v>
+        <v>4369.09</v>
       </c>
       <c r="R8">
-        <v>4361.23</v>
+        <v>4367.67</v>
       </c>
       <c r="S8">
-        <v>4699.47</v>
+        <v>4693.59</v>
       </c>
       <c r="T8">
-        <v>-3.24</v>
+        <v>-3.12</v>
       </c>
       <c r="U8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V8" t="s">
         <v>47</v>
@@ -1677,37 +1661,37 @@
         <v>47</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
         <v>65.04000000000001</v>
       </c>
       <c r="Z8">
-        <v>22.49</v>
+        <v>32.11</v>
       </c>
       <c r="AA8">
-        <v>-2.44</v>
+        <v>4.47</v>
       </c>
       <c r="AB8">
-        <v>24.93</v>
+        <v>27.64</v>
       </c>
       <c r="AC8">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="AD8">
-        <v>92.90000000000001</v>
+        <v>95.67</v>
       </c>
       <c r="AE8">
-        <v>104.53</v>
+        <v>103.21</v>
       </c>
       <c r="AF8">
-        <v>173.89</v>
+        <v>49.61</v>
       </c>
       <c r="AG8">
-        <v>4507.41</v>
+        <v>4538.44</v>
       </c>
       <c r="AH8">
-        <v>4212.91</v>
+        <v>4199.73</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1716,7 +1700,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>30.18</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1730,7 +1714,7 @@
         <v>11619</v>
       </c>
       <c r="D9">
-        <v>-0.74</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1745,40 +1729,40 @@
         <v>12.13</v>
       </c>
       <c r="I9">
-        <v>-4.01</v>
+        <v>-3.48</v>
       </c>
       <c r="J9">
-        <v>-1.29</v>
+        <v>-0.92</v>
       </c>
       <c r="K9">
-        <v>0.5</v>
+        <v>2.21</v>
       </c>
       <c r="L9">
-        <v>-4.43</v>
+        <v>-6.34</v>
       </c>
       <c r="M9">
-        <v>10.11</v>
+        <v>9.91</v>
       </c>
       <c r="N9">
         <v>26</v>
       </c>
       <c r="O9">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P9">
-        <v>11806.8</v>
+        <v>11723</v>
       </c>
       <c r="Q9">
-        <v>11936.85</v>
+        <v>11922.65</v>
       </c>
       <c r="R9">
-        <v>11608.04</v>
+        <v>11622.18</v>
       </c>
       <c r="S9">
-        <v>11794.01</v>
+        <v>11792.45</v>
       </c>
       <c r="T9">
-        <v>-1.48</v>
+        <v>-1.47</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1796,31 +1780,31 @@
         <v>42.95</v>
       </c>
       <c r="Z9">
-        <v>38.57</v>
+        <v>15.59</v>
       </c>
       <c r="AA9">
-        <v>96.98</v>
+        <v>80.7</v>
       </c>
       <c r="AB9">
-        <v>-58.41</v>
+        <v>-65.11</v>
       </c>
       <c r="AC9">
-        <v>7.64</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>10.63</v>
+        <v>5.09</v>
       </c>
       <c r="AE9">
-        <v>220.45</v>
+        <v>212.63</v>
       </c>
       <c r="AF9">
-        <v>-32.47</v>
+        <v>-33.39</v>
       </c>
       <c r="AG9">
-        <v>12220.63</v>
+        <v>12240</v>
       </c>
       <c r="AH9">
-        <v>11653.07</v>
+        <v>11605.3</v>
       </c>
       <c r="AI9">
         <v>11461.94</v>
@@ -1829,7 +1813,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>23.87</v>
+        <v>25.27</v>
       </c>
     </row>
   </sheetData>
@@ -1970,7 +1954,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2010,16 +1994,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>47</v>
@@ -2028,1198 +2012,954 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.33</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-0.71</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-4.6</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-3.23</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>5.72</v>
+      </c>
+      <c r="D9" s="6">
+        <v>4.53</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>7.32</v>
+      </c>
+      <c r="D10" s="6">
+        <v>11.2</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1.58</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-0.22</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>4.56</v>
+      </c>
+      <c r="D12" s="6">
+        <v>2.54</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>3.07</v>
+      </c>
+      <c r="D13" s="6">
+        <v>3.68</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-1.29</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.92</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-1.73</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-2.22</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-11.61</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="E16" s="8">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-2.24</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-3.85</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.84</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.39</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>10.84</v>
+      </c>
+      <c r="D19" s="6">
+        <v>6.11</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-4.73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-8.16</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-7.14</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>4.03</v>
+      </c>
+      <c r="D21" s="6">
+        <v>4.19</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-4.01</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-3.48</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>47.53</v>
+      </c>
+      <c r="D23" s="6">
+        <v>47.01</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-24.55</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-25.01</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>21.14</v>
+      </c>
+      <c r="D25" s="6">
+        <v>18.25</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>53.03</v>
+      </c>
+      <c r="D26" s="6">
+        <v>56.04</v>
+      </c>
+      <c r="E26" s="8">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>116.74</v>
+      </c>
+      <c r="D27" s="6">
+        <v>107.73</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-9.01</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>134</v>
+      </c>
+      <c r="D28" s="6">
+        <v>129.41</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-4.59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-8.66</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-7.01</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-4.43</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-6.34</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>14.54</v>
+      </c>
+      <c r="D31" s="6">
+        <v>13.53</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-9.65</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-10.37</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>10.36</v>
+      </c>
+      <c r="D33" s="6">
+        <v>10.74</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-2.24</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="E34" s="8">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1.41</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-8.31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-4.49</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-4.58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>3.34</v>
+      </c>
+      <c r="D37" s="6">
+        <v>3.14</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D38" s="6">
+        <v>2.21</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-5.58</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-6.12</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-3.9</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-3.85</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-10.45</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-8.68</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-6</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-8.66</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>401</v>
+      </c>
+      <c r="D43" s="6">
+        <v>398.7</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>3248.7</v>
+      </c>
+      <c r="D44" s="6">
+        <v>3250.5</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1029.5</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1049.9</v>
+      </c>
+      <c r="E45" s="8">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>14.11</v>
+      </c>
+      <c r="D46" s="6">
+        <v>13.71</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="6">
+        <v>74</v>
+      </c>
+      <c r="D47" s="6">
         <v>62</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="E47" s="7">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="6">
+        <v>62</v>
+      </c>
+      <c r="D48" s="6">
+        <v>74</v>
+      </c>
+      <c r="E48" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>0.84</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0.33</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>48.59</v>
+      </c>
+      <c r="D49" s="6">
+        <v>47.2</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>54.39</v>
+      </c>
+      <c r="D50" s="6">
+        <v>54.54</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>55.53</v>
+      </c>
+      <c r="D51" s="6">
+        <v>59.69</v>
+      </c>
+      <c r="E51" s="8">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>65.09</v>
+      </c>
+      <c r="D52" s="6">
+        <v>56.14</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-8.949999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-67.86</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-49.52</v>
+      </c>
+      <c r="E53" s="8">
+        <v>18.34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-4.27</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-4.6</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B54" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="6">
+        <v>-25.59</v>
+      </c>
+      <c r="D54" s="6">
+        <v>-18.86</v>
+      </c>
+      <c r="E54" s="8">
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>5.54</v>
-      </c>
-      <c r="D11" s="7">
-        <v>5.72</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B55" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="6">
+        <v>-32.32</v>
+      </c>
+      <c r="D55" s="6">
+        <v>89.08</v>
+      </c>
+      <c r="E55" s="8">
+        <v>121.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="D12" s="7">
-        <v>7.32</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-33.5</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-40.52</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-7.02</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-1.17</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1.58</v>
-      </c>
-      <c r="E13" s="9">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>126.24</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-15.3</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-141.54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="D14" s="7">
-        <v>4.56</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-3.55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-50.44</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-51.78</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>3.95</v>
-      </c>
-      <c r="D15" s="7">
-        <v>3.07</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>173.89</v>
+      </c>
+      <c r="D59" s="6">
+        <v>49.61</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-124.28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-0.9</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-1.29</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-3.27</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-1.73</v>
-      </c>
-      <c r="E17" s="9">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-10.32</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-11.61</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1.15</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-2.24</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-3.39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>1.87</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-2.84</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-4.71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>6.97</v>
-      </c>
-      <c r="D21" s="7">
-        <v>10.84</v>
-      </c>
-      <c r="E21" s="9">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-8.69</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-8.16</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>5.06</v>
-      </c>
-      <c r="D23" s="7">
-        <v>4.03</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-3.06</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-4.01</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>46.58</v>
-      </c>
-      <c r="D25" s="7">
-        <v>47.53</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-25.47</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-24.55</v>
-      </c>
-      <c r="E26" s="9">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>19.14</v>
-      </c>
-      <c r="D27" s="7">
-        <v>21.14</v>
-      </c>
-      <c r="E27" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>53.45</v>
-      </c>
-      <c r="D28" s="7">
-        <v>53.03</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>101.04</v>
-      </c>
-      <c r="D29" s="7">
-        <v>116.74</v>
-      </c>
-      <c r="E29" s="9">
-        <v>15.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>134.58</v>
-      </c>
-      <c r="D30" s="7">
-        <v>134</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-8.66</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-4.62</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-4.43</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>14.15</v>
-      </c>
-      <c r="D33" s="7">
-        <v>14.54</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-9.460000000000001</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-9.65</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>11.02</v>
-      </c>
-      <c r="D35" s="7">
-        <v>10.36</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-1.99</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-2.24</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>4.32</v>
-      </c>
-      <c r="D37" s="7">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="E37" s="9">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-3.5</v>
-      </c>
-      <c r="D38" s="7">
-        <v>0.09</v>
-      </c>
-      <c r="E38" s="9">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>1.76</v>
-      </c>
-      <c r="D39" s="7">
-        <v>3.34</v>
-      </c>
-      <c r="E39" s="9">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>1.91</v>
-      </c>
-      <c r="D40" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-4</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-5.58</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-39.31</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-40.12</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-3.65</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-3.9</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-9</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-10.45</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-9.99</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-6</v>
-      </c>
-      <c r="E45" s="9">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-14.73</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-15.95</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-21.96</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-21.73</v>
-      </c>
-      <c r="E47" s="9">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-10.31</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-10.98</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>407.7</v>
-      </c>
-      <c r="D49" s="7">
-        <v>401</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-6.7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>56.73</v>
-      </c>
-      <c r="D50" s="7">
-        <v>55.98</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="7">
-        <v>3257</v>
-      </c>
-      <c r="D51" s="7">
-        <v>3248.7</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-8.300000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="7">
-        <v>1046.25</v>
-      </c>
-      <c r="D52" s="7">
-        <v>1029.5</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-16.75</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>13.51</v>
-      </c>
-      <c r="D53" s="7">
-        <v>14.11</v>
-      </c>
-      <c r="E53" s="9">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>11.87</v>
-      </c>
-      <c r="D54" s="7">
-        <v>11.7</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>4533.5</v>
-      </c>
-      <c r="D55" s="7">
-        <v>4547</v>
-      </c>
-      <c r="E55" s="9">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>11706</v>
-      </c>
-      <c r="D56" s="7">
-        <v>11619</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-87</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" s="7">
-        <v>26</v>
-      </c>
-      <c r="D57" s="7">
-        <v>38</v>
-      </c>
-      <c r="E57" s="9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" s="7">
-        <v>38</v>
-      </c>
-      <c r="D58" s="7">
-        <v>26</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>52.8</v>
-      </c>
-      <c r="D59" s="7">
-        <v>48.59</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-4.21</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="7">
-        <v>40.36</v>
-      </c>
-      <c r="D60" s="7">
-        <v>38.38</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="7">
-        <v>55.17</v>
-      </c>
-      <c r="D61" s="7">
-        <v>54.39</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="7">
-        <v>60.27</v>
-      </c>
-      <c r="D62" s="7">
-        <v>55.53</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-4.74</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="7">
-        <v>55.13</v>
-      </c>
-      <c r="D63" s="7">
-        <v>65.09</v>
-      </c>
-      <c r="E63" s="9">
-        <v>9.960000000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>47.82</v>
-      </c>
-      <c r="D64" s="7">
-        <v>45.74</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-2.08</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>64.22</v>
-      </c>
-      <c r="D65" s="7">
-        <v>65.04000000000001</v>
-      </c>
-      <c r="E65" s="9">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>45.43</v>
-      </c>
-      <c r="D66" s="7">
-        <v>42.95</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="6" t="s">
+      <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C67" s="7">
-        <v>-39.58</v>
-      </c>
-      <c r="D67" s="7">
-        <v>-67.86</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-28.28</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="7">
-        <v>-50.5</v>
-      </c>
-      <c r="D68" s="7">
-        <v>-25.59</v>
-      </c>
-      <c r="E68" s="9">
-        <v>24.91</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="7">
-        <v>51.29</v>
-      </c>
-      <c r="D69" s="7">
-        <v>-32.32</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-83.61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="7">
-        <v>-3.48</v>
-      </c>
-      <c r="D70" s="7">
-        <v>-33.5</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-30.02</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="7">
-        <v>64.16</v>
-      </c>
-      <c r="D71" s="7">
-        <v>126.24</v>
-      </c>
-      <c r="E71" s="9">
-        <v>62.08</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="7">
-        <v>-77.45999999999999</v>
-      </c>
-      <c r="D72" s="7">
-        <v>-50.44</v>
-      </c>
-      <c r="E72" s="9">
-        <v>27.02</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="7">
-        <v>1129.83</v>
-      </c>
-      <c r="D73" s="7">
-        <v>173.89</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-955.9400000000001</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>4</v>
-      </c>
-      <c r="D74" s="7">
+      <c r="C60" s="6">
         <v>-32.47</v>
       </c>
-      <c r="E74" s="8">
-        <v>-36.47</v>
+      <c r="D60" s="6">
+        <v>-33.39</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3239,60 +2979,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>56.44</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>8</v>
       </c>
-      <c r="D2" s="12">
-        <v>52</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>51.2</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="11">
         <v>2.1</v>
       </c>
-      <c r="G2" s="12">
-        <v>3.3</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="G2" s="11">
+        <v>2</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>50</v>
       </c>
     </row>
@@ -3394,55 +3134,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="15">
-        <v>0.2861</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.2012</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1914</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1888</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1742</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1011</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.23</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.3052</v>
+      <c r="A2" s="14">
+        <v>0.288</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2019</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1987</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1898</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1757</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.09910000000000001</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2297</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.3028</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,13 +190,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>65.0 → 49.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>65.0</t>
+  </si>
+  <si>
+    <t>49.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +288,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +328,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,8 +414,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -780,14 +786,15 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -920,58 +927,58 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>398.7</v>
+        <v>402</v>
       </c>
       <c r="D2">
-        <v>-0.57</v>
+        <v>0.83</v>
       </c>
       <c r="E2">
         <v>424.7</v>
       </c>
       <c r="F2">
-        <v>268.05</v>
+        <v>269.7</v>
       </c>
       <c r="G2">
-        <v>-6.12</v>
+        <v>-5.34</v>
       </c>
       <c r="H2">
-        <v>48.74</v>
+        <v>49.05</v>
       </c>
       <c r="I2">
-        <v>-2.22</v>
+        <v>-1.26</v>
       </c>
       <c r="J2">
-        <v>-0.71</v>
+        <v>0.21</v>
       </c>
       <c r="K2">
-        <v>13.53</v>
+        <v>13.85</v>
       </c>
       <c r="L2">
-        <v>47.01</v>
+        <v>49.97</v>
       </c>
       <c r="M2">
-        <v>28.8</v>
+        <v>28.85</v>
       </c>
       <c r="N2">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="O2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>405.1</v>
+        <v>404.07</v>
       </c>
       <c r="Q2">
-        <v>405.77</v>
+        <v>405.42</v>
       </c>
       <c r="R2">
-        <v>393.1</v>
+        <v>394.26</v>
       </c>
       <c r="S2">
-        <v>355.42</v>
+        <v>355.87</v>
       </c>
       <c r="T2">
-        <v>12.18</v>
+        <v>12.96</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -986,34 +993,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>47.2</v>
+        <v>49.44</v>
       </c>
       <c r="Z2">
-        <v>3.23</v>
+        <v>2.63</v>
       </c>
       <c r="AA2">
-        <v>5.39</v>
+        <v>4.84</v>
       </c>
       <c r="AB2">
-        <v>-2.17</v>
+        <v>-2.21</v>
       </c>
       <c r="AC2">
-        <v>7.55</v>
+        <v>4.28</v>
       </c>
       <c r="AD2">
-        <v>18.26</v>
+        <v>10.53</v>
       </c>
       <c r="AE2">
-        <v>10.38</v>
+        <v>10.28</v>
       </c>
       <c r="AF2">
-        <v>-49.52</v>
+        <v>14.49</v>
       </c>
       <c r="AG2">
-        <v>426.66</v>
+        <v>426.31</v>
       </c>
       <c r="AH2">
-        <v>384.88</v>
+        <v>384.52</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1022,7 +1029,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>21.81</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1033,10 +1040,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>55.98</v>
+        <v>54.97</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1045,25 +1052,25 @@
         <v>53.89</v>
       </c>
       <c r="G3">
-        <v>-40.12</v>
+        <v>-41.2</v>
       </c>
       <c r="H3">
-        <v>3.88</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>-8.289999999999999</v>
+        <v>-6.24</v>
       </c>
       <c r="J3">
-        <v>-3.23</v>
+        <v>-4.03</v>
       </c>
       <c r="K3">
-        <v>-10.37</v>
+        <v>-12.09</v>
       </c>
       <c r="L3">
-        <v>-25.01</v>
+        <v>-25.74</v>
       </c>
       <c r="M3">
-        <v>-22.97</v>
+        <v>-23.21</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1072,19 +1079,19 @@
         <v>17</v>
       </c>
       <c r="P3">
-        <v>56.9</v>
+        <v>56.16</v>
       </c>
       <c r="Q3">
-        <v>58.77</v>
+        <v>58.65</v>
       </c>
       <c r="R3">
-        <v>59.42</v>
+        <v>59.34</v>
       </c>
       <c r="S3">
-        <v>66.65000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="T3">
-        <v>-16.01</v>
+        <v>-17.35</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1099,43 +1106,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.38</v>
+        <v>35.65</v>
       </c>
       <c r="Z3">
-        <v>-0.57</v>
+        <v>-0.8</v>
       </c>
       <c r="AA3">
-        <v>-0.1</v>
+        <v>-0.24</v>
       </c>
       <c r="AB3">
-        <v>-0.47</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AC3">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>7.78</v>
+        <v>2</v>
       </c>
       <c r="AE3">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AF3">
-        <v>-18.86</v>
+        <v>-62.35</v>
       </c>
       <c r="AG3">
-        <v>63.93</v>
+        <v>64.05</v>
       </c>
       <c r="AH3">
-        <v>53.61</v>
+        <v>53.24</v>
       </c>
       <c r="AI3">
-        <v>62.97</v>
+        <v>61.6</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>36.07</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1146,10 +1153,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3250.5</v>
+        <v>3278.7</v>
       </c>
       <c r="D4">
-        <v>0.06</v>
+        <v>0.87</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1158,46 +1165,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-3.85</v>
+        <v>-3.01</v>
       </c>
       <c r="H4">
-        <v>28.42</v>
+        <v>29.54</v>
       </c>
       <c r="I4">
-        <v>-3.85</v>
+        <v>-1.31</v>
       </c>
       <c r="J4">
-        <v>4.53</v>
+        <v>4.29</v>
       </c>
       <c r="K4">
-        <v>10.74</v>
+        <v>10.35</v>
       </c>
       <c r="L4">
-        <v>18.25</v>
+        <v>19.64</v>
       </c>
       <c r="M4">
-        <v>17.57</v>
+        <v>17.46</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>3277.24</v>
+        <v>3268.54</v>
       </c>
       <c r="Q4">
-        <v>3201.37</v>
+        <v>3206.31</v>
       </c>
       <c r="R4">
-        <v>3160.96</v>
+        <v>3165.53</v>
       </c>
       <c r="S4">
-        <v>2903.03</v>
+        <v>2904.63</v>
       </c>
       <c r="T4">
-        <v>11.97</v>
+        <v>12.88</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1212,34 +1219,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>54.54</v>
+        <v>56.93</v>
       </c>
       <c r="Z4">
-        <v>41.01</v>
+        <v>40.46</v>
       </c>
       <c r="AA4">
-        <v>36.48</v>
+        <v>37.27</v>
       </c>
       <c r="AB4">
-        <v>4.53</v>
+        <v>3.18</v>
       </c>
       <c r="AC4">
-        <v>38.48</v>
+        <v>41.28</v>
       </c>
       <c r="AD4">
-        <v>48.81</v>
+        <v>42.59</v>
       </c>
       <c r="AE4">
-        <v>78.44</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="AF4">
-        <v>89.08</v>
+        <v>104.23</v>
       </c>
       <c r="AG4">
-        <v>3381.04</v>
+        <v>3388.9</v>
       </c>
       <c r="AH4">
-        <v>3021.7</v>
+        <v>3023.73</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1248,7 +1255,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>37.65</v>
+        <v>36.74</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1259,58 +1266,58 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1049.9</v>
+        <v>1041.6</v>
       </c>
       <c r="D5">
-        <v>1.98</v>
+        <v>-0.79</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>667.05</v>
+        <v>695.25</v>
       </c>
       <c r="G5">
-        <v>-8.68</v>
+        <v>-9.4</v>
       </c>
       <c r="H5">
-        <v>57.39</v>
+        <v>49.82</v>
       </c>
       <c r="I5">
-        <v>-0.39</v>
+        <v>-0.71</v>
       </c>
       <c r="J5">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="K5">
-        <v>0.15</v>
+        <v>-4.04</v>
       </c>
       <c r="L5">
-        <v>56.04</v>
+        <v>56.15</v>
       </c>
       <c r="M5">
-        <v>19.87</v>
+        <v>20.22</v>
       </c>
       <c r="N5">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="O5">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P5">
-        <v>1050.65</v>
+        <v>1049.15</v>
       </c>
       <c r="Q5">
-        <v>1001.88</v>
+        <v>1006.39</v>
       </c>
       <c r="R5">
-        <v>991.5700000000001</v>
+        <v>991.16</v>
       </c>
       <c r="S5">
-        <v>950.59</v>
+        <v>951.52</v>
       </c>
       <c r="T5">
-        <v>10.45</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1325,34 +1332,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>59.69</v>
+        <v>57.34</v>
       </c>
       <c r="Z5">
-        <v>20.33</v>
+        <v>19.62</v>
       </c>
       <c r="AA5">
-        <v>14.33</v>
+        <v>15.38</v>
       </c>
       <c r="AB5">
-        <v>6.01</v>
+        <v>4.24</v>
       </c>
       <c r="AC5">
-        <v>58.5</v>
+        <v>46.63</v>
       </c>
       <c r="AD5">
-        <v>72.95</v>
+        <v>59.94</v>
       </c>
       <c r="AE5">
-        <v>25.6</v>
+        <v>24.67</v>
       </c>
       <c r="AF5">
-        <v>-40.52</v>
+        <v>-50.43</v>
       </c>
       <c r="AG5">
-        <v>1097.37</v>
+        <v>1100.35</v>
       </c>
       <c r="AH5">
-        <v>906.39</v>
+        <v>912.4299999999999</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1361,7 +1368,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>49.18</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1372,10 +1379,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>13.71</v>
+        <v>14.12</v>
       </c>
       <c r="D6">
-        <v>-2.83</v>
+        <v>2.99</v>
       </c>
       <c r="E6">
         <v>15.01</v>
@@ -1384,46 +1391,46 @@
         <v>6.15</v>
       </c>
       <c r="G6">
-        <v>-8.66</v>
+        <v>-5.93</v>
       </c>
       <c r="H6">
-        <v>122.93</v>
+        <v>129.59</v>
       </c>
       <c r="I6">
-        <v>6.11</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="J6">
-        <v>-0.22</v>
+        <v>4.52</v>
       </c>
       <c r="K6">
-        <v>1.41</v>
+        <v>3.98</v>
       </c>
       <c r="L6">
-        <v>107.73</v>
+        <v>118.24</v>
       </c>
       <c r="M6">
-        <v>18.98</v>
+        <v>16.97</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P6">
-        <v>13.54</v>
+        <v>13.79</v>
       </c>
       <c r="Q6">
-        <v>13.14</v>
+        <v>13.17</v>
       </c>
       <c r="R6">
-        <v>13.83</v>
+        <v>13.82</v>
       </c>
       <c r="S6">
-        <v>11.57</v>
+        <v>11.6</v>
       </c>
       <c r="T6">
-        <v>18.46</v>
+        <v>21.75</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1438,34 +1445,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>56.14</v>
+        <v>61.92</v>
       </c>
       <c r="Z6">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="AA6">
-        <v>-0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="AB6">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="AC6">
-        <v>91.25</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="AD6">
-        <v>96.34999999999999</v>
+        <v>93.13</v>
       </c>
       <c r="AE6">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="AF6">
-        <v>-15.3</v>
+        <v>122.81</v>
       </c>
       <c r="AG6">
-        <v>13.9</v>
+        <v>14.04</v>
       </c>
       <c r="AH6">
-        <v>12.38</v>
+        <v>12.31</v>
       </c>
       <c r="AI6">
         <v>12.65</v>
@@ -1474,7 +1481,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>51.19</v>
+        <v>52.72</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1485,10 +1492,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.7</v>
+        <v>11.95</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1497,25 +1504,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-15.95</v>
+        <v>-14.15</v>
       </c>
       <c r="H7">
-        <v>149.47</v>
+        <v>154.8</v>
       </c>
       <c r="I7">
-        <v>-7.14</v>
+        <v>-3.24</v>
       </c>
       <c r="J7">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="K7">
-        <v>-4.49</v>
+        <v>0.93</v>
       </c>
       <c r="L7">
-        <v>129.41</v>
+        <v>129.81</v>
       </c>
       <c r="M7">
-        <v>-30.28</v>
+        <v>-30.16</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1524,19 +1531,19 @@
         <v>93</v>
       </c>
       <c r="P7">
-        <v>11.95</v>
+        <v>11.87</v>
       </c>
       <c r="Q7">
         <v>12.2</v>
       </c>
       <c r="R7">
-        <v>11.58</v>
+        <v>11.6</v>
       </c>
       <c r="S7">
-        <v>9.880000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="T7">
-        <v>18.38</v>
+        <v>20.5</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1551,34 +1558,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>45.74</v>
+        <v>49.49</v>
       </c>
       <c r="Z7">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="AA7">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="AB7">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AC7">
-        <v>4.42</v>
+        <v>5.74</v>
       </c>
       <c r="AD7">
-        <v>12.77</v>
+        <v>7.3</v>
       </c>
       <c r="AE7">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="AF7">
-        <v>-51.78</v>
+        <v>-67.23999999999999</v>
       </c>
       <c r="AG7">
         <v>13.55</v>
       </c>
       <c r="AH7">
-        <v>10.84</v>
+        <v>10.85</v>
       </c>
       <c r="AI7">
         <v>12.88</v>
@@ -1587,7 +1594,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>31.05</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1598,10 +1605,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4547</v>
+        <v>4385.7</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-3.55</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1610,49 +1617,49 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-21.73</v>
+        <v>-24.51</v>
       </c>
       <c r="H8">
-        <v>9.43</v>
+        <v>5.55</v>
       </c>
       <c r="I8">
-        <v>4.19</v>
+        <v>-0.1</v>
       </c>
       <c r="J8">
-        <v>3.68</v>
+        <v>0.39</v>
       </c>
       <c r="K8">
-        <v>3.14</v>
+        <v>-1.17</v>
       </c>
       <c r="L8">
-        <v>-7.01</v>
+        <v>-10.03</v>
       </c>
       <c r="M8">
-        <v>20.19</v>
+        <v>19.45</v>
       </c>
       <c r="N8">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="O8">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="P8">
-        <v>4476.56</v>
+        <v>4475.64</v>
       </c>
       <c r="Q8">
-        <v>4369.09</v>
+        <v>4366.5</v>
       </c>
       <c r="R8">
-        <v>4367.67</v>
+        <v>4371.73</v>
       </c>
       <c r="S8">
-        <v>4693.59</v>
+        <v>4687.6</v>
       </c>
       <c r="T8">
-        <v>-3.12</v>
+        <v>-6.44</v>
       </c>
       <c r="U8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V8" t="s">
         <v>47</v>
@@ -1661,37 +1668,37 @@
         <v>47</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>65.04000000000001</v>
+        <v>49.33</v>
       </c>
       <c r="Z8">
-        <v>32.11</v>
+        <v>26.41</v>
       </c>
       <c r="AA8">
-        <v>4.47</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB8">
-        <v>27.64</v>
+        <v>17.55</v>
       </c>
       <c r="AC8">
-        <v>100</v>
+        <v>73.8</v>
       </c>
       <c r="AD8">
-        <v>95.67</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AE8">
-        <v>103.21</v>
+        <v>107.77</v>
       </c>
       <c r="AF8">
-        <v>49.61</v>
+        <v>-10.19</v>
       </c>
       <c r="AG8">
-        <v>4538.44</v>
+        <v>4533.02</v>
       </c>
       <c r="AH8">
-        <v>4199.73</v>
+        <v>4199.98</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1700,7 +1707,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>35.34</v>
+        <v>32.59</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1711,10 +1718,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11619</v>
+        <v>11499</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1723,46 +1730,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-10.98</v>
+        <v>-11.9</v>
       </c>
       <c r="H9">
-        <v>12.13</v>
+        <v>10.97</v>
       </c>
       <c r="I9">
-        <v>-3.48</v>
+        <v>-2.39</v>
       </c>
       <c r="J9">
-        <v>-0.92</v>
+        <v>-3.39</v>
       </c>
       <c r="K9">
-        <v>2.21</v>
+        <v>0.79</v>
       </c>
       <c r="L9">
-        <v>-6.34</v>
+        <v>-7.63</v>
       </c>
       <c r="M9">
-        <v>9.91</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N9">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="O9">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="P9">
-        <v>11723</v>
+        <v>11666.8</v>
       </c>
       <c r="Q9">
-        <v>11922.65</v>
+        <v>11892.9</v>
       </c>
       <c r="R9">
-        <v>11622.18</v>
+        <v>11636.26</v>
       </c>
       <c r="S9">
-        <v>11792.45</v>
+        <v>11789.95</v>
       </c>
       <c r="T9">
-        <v>-1.47</v>
+        <v>-2.47</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1777,34 +1784,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>42.95</v>
+        <v>39.51</v>
       </c>
       <c r="Z9">
-        <v>15.59</v>
+        <v>-12.17</v>
       </c>
       <c r="AA9">
-        <v>80.7</v>
+        <v>62.13</v>
       </c>
       <c r="AB9">
-        <v>-65.11</v>
+        <v>-74.3</v>
       </c>
       <c r="AC9">
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>5.09</v>
+        <v>2.55</v>
       </c>
       <c r="AE9">
-        <v>212.63</v>
+        <v>209.94</v>
       </c>
       <c r="AF9">
-        <v>-33.39</v>
+        <v>-27.26</v>
       </c>
       <c r="AG9">
-        <v>12240</v>
+        <v>12251.49</v>
       </c>
       <c r="AH9">
-        <v>11605.3</v>
+        <v>11534.31</v>
       </c>
       <c r="AI9">
         <v>11461.94</v>
@@ -1813,7 +1820,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>25.27</v>
+        <v>27.93</v>
       </c>
     </row>
   </sheetData>
@@ -1954,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2006,15 +2013,15 @@
         <v>58</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2026,16 +2033,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2049,10 +2056,10 @@
         <v>0.33</v>
       </c>
       <c r="D7" s="6">
-        <v>-0.71</v>
+        <v>0.21</v>
       </c>
       <c r="E7" s="7">
-        <v>-1.04</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2066,10 +2073,10 @@
         <v>-4.6</v>
       </c>
       <c r="D8" s="6">
-        <v>-3.23</v>
+        <v>-4.03</v>
       </c>
       <c r="E8" s="8">
-        <v>1.37</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2083,10 +2090,10 @@
         <v>5.72</v>
       </c>
       <c r="D9" s="6">
-        <v>4.53</v>
+        <v>4.29</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.19</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2100,10 +2107,10 @@
         <v>7.32</v>
       </c>
       <c r="D10" s="6">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="E10" s="8">
-        <v>3.88</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2117,10 +2124,10 @@
         <v>1.58</v>
       </c>
       <c r="D11" s="6">
-        <v>-0.22</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.8</v>
+        <v>4.52</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.94</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2134,10 +2141,10 @@
         <v>4.56</v>
       </c>
       <c r="D12" s="6">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="E12" s="7">
-        <v>-2.02</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2151,10 +2158,10 @@
         <v>3.07</v>
       </c>
       <c r="D13" s="6">
-        <v>3.68</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.61</v>
+        <v>0.39</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2168,10 +2175,10 @@
         <v>-1.29</v>
       </c>
       <c r="D14" s="6">
-        <v>-0.92</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.37</v>
+        <v>-3.39</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2185,10 +2192,10 @@
         <v>-1.73</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.22</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.49</v>
+        <v>-1.26</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.47</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2202,10 +2209,10 @@
         <v>-11.61</v>
       </c>
       <c r="D16" s="6">
-        <v>-8.289999999999999</v>
+        <v>-6.24</v>
       </c>
       <c r="E16" s="8">
-        <v>3.32</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2219,10 +2226,10 @@
         <v>-2.24</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.85</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.61</v>
+        <v>-1.31</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.93</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2236,10 +2243,10 @@
         <v>-2.84</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.39</v>
+        <v>-0.71</v>
       </c>
       <c r="E18" s="8">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2253,10 +2260,10 @@
         <v>10.84</v>
       </c>
       <c r="D19" s="6">
-        <v>6.11</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="E19" s="7">
-        <v>-4.73</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2270,10 +2277,10 @@
         <v>-8.16</v>
       </c>
       <c r="D20" s="6">
-        <v>-7.14</v>
+        <v>-3.24</v>
       </c>
       <c r="E20" s="8">
-        <v>1.02</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2287,10 +2294,10 @@
         <v>4.03</v>
       </c>
       <c r="D21" s="6">
-        <v>4.19</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.16</v>
+        <v>-0.1</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-4.13</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2304,10 +2311,10 @@
         <v>-4.01</v>
       </c>
       <c r="D22" s="6">
-        <v>-3.48</v>
+        <v>-2.39</v>
       </c>
       <c r="E22" s="8">
-        <v>0.53</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2321,10 +2328,10 @@
         <v>47.53</v>
       </c>
       <c r="D23" s="6">
-        <v>47.01</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.52</v>
+        <v>49.97</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2.44</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2338,10 +2345,10 @@
         <v>-24.55</v>
       </c>
       <c r="D24" s="6">
-        <v>-25.01</v>
+        <v>-25.74</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.46</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2355,10 +2362,10 @@
         <v>21.14</v>
       </c>
       <c r="D25" s="6">
-        <v>18.25</v>
+        <v>19.64</v>
       </c>
       <c r="E25" s="7">
-        <v>-2.89</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2372,10 +2379,10 @@
         <v>53.03</v>
       </c>
       <c r="D26" s="6">
-        <v>56.04</v>
+        <v>56.15</v>
       </c>
       <c r="E26" s="8">
-        <v>3.01</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2389,10 +2396,10 @@
         <v>116.74</v>
       </c>
       <c r="D27" s="6">
-        <v>107.73</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-9.01</v>
+        <v>118.24</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.5</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2406,10 +2413,10 @@
         <v>134</v>
       </c>
       <c r="D28" s="6">
-        <v>129.41</v>
+        <v>129.81</v>
       </c>
       <c r="E28" s="7">
-        <v>-4.59</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2423,10 +2430,10 @@
         <v>-8.66</v>
       </c>
       <c r="D29" s="6">
-        <v>-7.01</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.65</v>
+        <v>-10.03</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2440,10 +2447,10 @@
         <v>-4.43</v>
       </c>
       <c r="D30" s="6">
-        <v>-6.34</v>
+        <v>-7.63</v>
       </c>
       <c r="E30" s="7">
-        <v>-1.91</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2457,10 +2464,10 @@
         <v>14.54</v>
       </c>
       <c r="D31" s="6">
-        <v>13.53</v>
+        <v>13.85</v>
       </c>
       <c r="E31" s="7">
-        <v>-1.01</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2474,10 +2481,10 @@
         <v>-9.65</v>
       </c>
       <c r="D32" s="6">
-        <v>-10.37</v>
+        <v>-12.09</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.72</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2491,10 +2498,10 @@
         <v>10.36</v>
       </c>
       <c r="D33" s="6">
-        <v>10.74</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.38</v>
+        <v>10.35</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2508,10 +2515,10 @@
         <v>-2.24</v>
       </c>
       <c r="D34" s="6">
-        <v>0.15</v>
-      </c>
-      <c r="E34" s="8">
-        <v>2.39</v>
+        <v>-4.04</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2525,10 +2532,10 @@
         <v>9.720000000000001</v>
       </c>
       <c r="D35" s="6">
-        <v>1.41</v>
+        <v>3.98</v>
       </c>
       <c r="E35" s="7">
-        <v>-8.31</v>
+        <v>-5.74</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2542,10 +2549,10 @@
         <v>0.09</v>
       </c>
       <c r="D36" s="6">
-        <v>-4.49</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-4.58</v>
+        <v>0.93</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.84</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2559,10 +2566,10 @@
         <v>3.34</v>
       </c>
       <c r="D37" s="6">
-        <v>3.14</v>
+        <v>-1.17</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.2</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2576,10 +2583,10 @@
         <v>0.5</v>
       </c>
       <c r="D38" s="6">
-        <v>2.21</v>
+        <v>0.79</v>
       </c>
       <c r="E38" s="8">
-        <v>1.71</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2593,92 +2600,92 @@
         <v>-5.58</v>
       </c>
       <c r="D39" s="6">
-        <v>-6.12</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.54</v>
+        <v>-5.34</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.24</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-3.9</v>
+        <v>-40.12</v>
       </c>
       <c r="D40" s="6">
-        <v>-3.85</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.05</v>
+        <v>-41.2</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-10.45</v>
+        <v>-3.9</v>
       </c>
       <c r="D41" s="6">
-        <v>-8.68</v>
+        <v>-3.01</v>
       </c>
       <c r="E41" s="8">
-        <v>1.77</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-6</v>
+        <v>-10.45</v>
       </c>
       <c r="D42" s="6">
-        <v>-8.66</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-2.66</v>
+        <v>-9.4</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1.05</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>401</v>
+        <v>-6</v>
       </c>
       <c r="D43" s="6">
-        <v>398.7</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-2.3</v>
+        <v>-5.93</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>3248.7</v>
+        <v>-15.95</v>
       </c>
       <c r="D44" s="6">
-        <v>3250.5</v>
+        <v>-14.15</v>
       </c>
       <c r="E44" s="8">
         <v>1.8</v>
@@ -2686,36 +2693,36 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>1029.5</v>
+        <v>-21.73</v>
       </c>
       <c r="D45" s="6">
-        <v>1049.9</v>
-      </c>
-      <c r="E45" s="8">
-        <v>20.4</v>
+        <v>-24.51</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-2.78</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>14.11</v>
+        <v>-10.98</v>
       </c>
       <c r="D46" s="6">
-        <v>13.71</v>
+        <v>-11.9</v>
       </c>
       <c r="E46" s="7">
-        <v>-0.4</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2723,237 +2730,441 @@
         <v>37</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>74</v>
+        <v>401</v>
       </c>
       <c r="D47" s="6">
-        <v>62</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-12</v>
+        <v>402</v>
+      </c>
+      <c r="E47" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>62</v>
+        <v>55.98</v>
       </c>
       <c r="D48" s="6">
-        <v>74</v>
-      </c>
-      <c r="E48" s="8">
-        <v>12</v>
+        <v>54.97</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>48.59</v>
+        <v>3248.7</v>
       </c>
       <c r="D49" s="6">
-        <v>47.2</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.39</v>
+        <v>3278.7</v>
+      </c>
+      <c r="E49" s="8">
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>54.39</v>
+        <v>1029.5</v>
       </c>
       <c r="D50" s="6">
-        <v>54.54</v>
+        <v>1041.6</v>
       </c>
       <c r="E50" s="8">
-        <v>0.15</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>55.53</v>
+        <v>14.11</v>
       </c>
       <c r="D51" s="6">
-        <v>59.69</v>
+        <v>14.12</v>
       </c>
       <c r="E51" s="8">
-        <v>4.16</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>65.09</v>
+        <v>11.7</v>
       </c>
       <c r="D52" s="6">
-        <v>56.14</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-8.949999999999999</v>
+        <v>11.95</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.25</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>-67.86</v>
+        <v>4547</v>
       </c>
       <c r="D53" s="6">
-        <v>-49.52</v>
-      </c>
-      <c r="E53" s="8">
-        <v>18.34</v>
+        <v>4385.7</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-161.3</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>-25.59</v>
+        <v>11619</v>
       </c>
       <c r="D54" s="6">
-        <v>-18.86</v>
-      </c>
-      <c r="E54" s="8">
-        <v>6.73</v>
+        <v>11499</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-120</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C55" s="6">
-        <v>-32.32</v>
+        <v>38</v>
       </c>
       <c r="D55" s="6">
-        <v>89.08</v>
-      </c>
-      <c r="E55" s="8">
-        <v>121.4</v>
+        <v>26</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-12</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C56" s="6">
-        <v>-33.5</v>
+        <v>26</v>
       </c>
       <c r="D56" s="6">
-        <v>-40.52</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-7.02</v>
+        <v>38</v>
+      </c>
+      <c r="E56" s="8">
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>126.24</v>
+        <v>48.59</v>
       </c>
       <c r="D57" s="6">
-        <v>-15.3</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-141.54</v>
+        <v>49.44</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0.85</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>-50.44</v>
+        <v>38.38</v>
       </c>
       <c r="D58" s="6">
-        <v>-51.78</v>
+        <v>35.65</v>
       </c>
       <c r="E58" s="7">
-        <v>-1.34</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>173.89</v>
+        <v>54.39</v>
       </c>
       <c r="D59" s="6">
-        <v>49.61</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-124.28</v>
+        <v>56.93</v>
+      </c>
+      <c r="E59" s="8">
+        <v>2.54</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>55.53</v>
+      </c>
+      <c r="D60" s="6">
+        <v>57.34</v>
+      </c>
+      <c r="E60" s="8">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>65.09</v>
+      </c>
+      <c r="D61" s="6">
+        <v>61.92</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-3.17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>45.74</v>
+      </c>
+      <c r="D62" s="6">
+        <v>49.49</v>
+      </c>
+      <c r="E62" s="8">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="D63" s="6">
+        <v>49.33</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-15.71</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>42.95</v>
+      </c>
+      <c r="D64" s="6">
+        <v>39.51</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-3.44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C65" s="6">
+        <v>-67.86</v>
+      </c>
+      <c r="D65" s="6">
+        <v>14.49</v>
+      </c>
+      <c r="E65" s="8">
+        <v>82.34999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>-25.59</v>
+      </c>
+      <c r="D66" s="6">
+        <v>-62.35</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-36.76</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>-32.32</v>
+      </c>
+      <c r="D67" s="6">
+        <v>104.23</v>
+      </c>
+      <c r="E67" s="8">
+        <v>136.55</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>-33.5</v>
+      </c>
+      <c r="D68" s="6">
+        <v>-50.43</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-16.93</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>126.24</v>
+      </c>
+      <c r="D69" s="6">
+        <v>122.81</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-3.43</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>-50.44</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-67.23999999999999</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-16.8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>173.89</v>
+      </c>
+      <c r="D71" s="6">
+        <v>-10.19</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-184.08</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
         <v>-32.47</v>
       </c>
-      <c r="D60" s="6">
-        <v>-33.39</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-0.92</v>
+      <c r="D72" s="6">
+        <v>-27.26</v>
+      </c>
+      <c r="E72" s="8">
+        <v>5.21</v>
       </c>
     </row>
   </sheetData>
@@ -2983,28 +3194,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3018,16 +3229,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="11">
-        <v>51.2</v>
+        <v>50</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="G2" s="11">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H2" s="11">
         <v>56.1</v>
@@ -3138,16 +3349,16 @@
         <v>37</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>40</v>
-      </c>
       <c r="D1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>39</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>44</v>
@@ -3161,28 +3372,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="14">
-        <v>0.288</v>
+        <v>0.2885</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2019</v>
+        <v>0.2022</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1987</v>
+        <v>0.1945</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1898</v>
+        <v>0.1746</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1757</v>
+        <v>0.1697</v>
       </c>
       <c r="F2" s="14">
-        <v>0.09910000000000001</v>
+        <v>0.09119999999999999</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2297</v>
+        <v>-0.2321</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.3028</v>
+        <v>-0.3016</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,34 +175,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>65.0 → 49.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>65.0</t>
-  </si>
-  <si>
-    <t>49.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -404,15 +377,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -786,8 +758,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -927,58 +899,58 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="D2">
-        <v>0.83</v>
+        <v>-1.49</v>
       </c>
       <c r="E2">
         <v>424.7</v>
       </c>
       <c r="F2">
-        <v>269.7</v>
+        <v>273</v>
       </c>
       <c r="G2">
-        <v>-5.34</v>
+        <v>-6.76</v>
       </c>
       <c r="H2">
-        <v>49.05</v>
+        <v>45.05</v>
       </c>
       <c r="I2">
-        <v>-1.26</v>
+        <v>-3.64</v>
       </c>
       <c r="J2">
-        <v>0.21</v>
+        <v>-3.19</v>
       </c>
       <c r="K2">
-        <v>13.85</v>
+        <v>13.34</v>
       </c>
       <c r="L2">
-        <v>49.97</v>
+        <v>46.83</v>
       </c>
       <c r="M2">
-        <v>28.85</v>
+        <v>29.52</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P2">
-        <v>404.07</v>
+        <v>401.08</v>
       </c>
       <c r="Q2">
-        <v>405.42</v>
+        <v>405.19</v>
       </c>
       <c r="R2">
-        <v>394.26</v>
+        <v>395.15</v>
       </c>
       <c r="S2">
-        <v>355.87</v>
+        <v>356.22</v>
       </c>
       <c r="T2">
-        <v>12.96</v>
+        <v>11.17</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -993,34 +965,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>49.44</v>
+        <v>45.65</v>
       </c>
       <c r="Z2">
-        <v>2.63</v>
+        <v>1.66</v>
       </c>
       <c r="AA2">
-        <v>4.84</v>
+        <v>4.2</v>
       </c>
       <c r="AB2">
-        <v>-2.21</v>
+        <v>-2.55</v>
       </c>
       <c r="AC2">
         <v>4.28</v>
       </c>
       <c r="AD2">
-        <v>10.53</v>
+        <v>5.37</v>
       </c>
       <c r="AE2">
-        <v>10.28</v>
+        <v>10.15</v>
       </c>
       <c r="AF2">
-        <v>14.49</v>
+        <v>7.47</v>
       </c>
       <c r="AG2">
-        <v>426.31</v>
+        <v>426.4</v>
       </c>
       <c r="AH2">
-        <v>384.52</v>
+        <v>383.97</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1029,7 +1001,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>21.74</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1040,10 +1012,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>54.97</v>
+        <v>54.47</v>
       </c>
       <c r="D3">
-        <v>-1.8</v>
+        <v>-0.91</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1052,46 +1024,46 @@
         <v>53.89</v>
       </c>
       <c r="G3">
-        <v>-41.2</v>
+        <v>-41.73</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="I3">
-        <v>-6.24</v>
+        <v>-4.71</v>
       </c>
       <c r="J3">
-        <v>-4.03</v>
+        <v>-5.12</v>
       </c>
       <c r="K3">
-        <v>-12.09</v>
+        <v>-18.41</v>
       </c>
       <c r="L3">
-        <v>-25.74</v>
+        <v>-27.06</v>
       </c>
       <c r="M3">
-        <v>-23.21</v>
+        <v>-22.92</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P3">
-        <v>56.16</v>
+        <v>55.63</v>
       </c>
       <c r="Q3">
-        <v>58.65</v>
+        <v>58.52</v>
       </c>
       <c r="R3">
-        <v>59.34</v>
+        <v>59.22</v>
       </c>
       <c r="S3">
-        <v>66.51000000000001</v>
+        <v>66.36</v>
       </c>
       <c r="T3">
-        <v>-17.35</v>
+        <v>-17.92</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1106,43 +1078,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>35.65</v>
+        <v>34.35</v>
       </c>
       <c r="Z3">
-        <v>-0.8</v>
+        <v>-1.02</v>
       </c>
       <c r="AA3">
-        <v>-0.24</v>
+        <v>-0.4</v>
       </c>
       <c r="AB3">
-        <v>-0.5600000000000001</v>
+        <v>-0.62</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>2</v>
+        <v>0.09</v>
       </c>
       <c r="AE3">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AF3">
-        <v>-62.35</v>
+        <v>-65.09</v>
       </c>
       <c r="AG3">
-        <v>64.05</v>
+        <v>64.2</v>
       </c>
       <c r="AH3">
-        <v>53.24</v>
+        <v>52.84</v>
       </c>
       <c r="AI3">
-        <v>61.6</v>
+        <v>60.68</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>37.5</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,10 +1125,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3278.7</v>
+        <v>3270</v>
       </c>
       <c r="D4">
-        <v>0.87</v>
+        <v>-0.27</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1165,25 +1137,25 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-3.01</v>
+        <v>-3.27</v>
       </c>
       <c r="H4">
-        <v>29.54</v>
+        <v>29.19</v>
       </c>
       <c r="I4">
-        <v>-1.31</v>
+        <v>-1.14</v>
       </c>
       <c r="J4">
-        <v>4.29</v>
+        <v>2.84</v>
       </c>
       <c r="K4">
-        <v>10.35</v>
+        <v>3.66</v>
       </c>
       <c r="L4">
-        <v>19.64</v>
+        <v>19.09</v>
       </c>
       <c r="M4">
-        <v>17.46</v>
+        <v>17.66</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1192,19 +1164,19 @@
         <v>68</v>
       </c>
       <c r="P4">
-        <v>3268.54</v>
+        <v>3260.98</v>
       </c>
       <c r="Q4">
-        <v>3206.31</v>
+        <v>3211.5</v>
       </c>
       <c r="R4">
-        <v>3165.53</v>
+        <v>3169.02</v>
       </c>
       <c r="S4">
-        <v>2904.63</v>
+        <v>2906.23</v>
       </c>
       <c r="T4">
-        <v>12.88</v>
+        <v>12.52</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1219,34 +1191,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>56.93</v>
+        <v>55.95</v>
       </c>
       <c r="Z4">
-        <v>40.46</v>
+        <v>38.86</v>
       </c>
       <c r="AA4">
-        <v>37.27</v>
+        <v>37.59</v>
       </c>
       <c r="AB4">
-        <v>3.18</v>
+        <v>1.27</v>
       </c>
       <c r="AC4">
-        <v>41.28</v>
+        <v>43.78</v>
       </c>
       <c r="AD4">
-        <v>42.59</v>
+        <v>41.18</v>
       </c>
       <c r="AE4">
-        <v>76.20999999999999</v>
+        <v>74.75</v>
       </c>
       <c r="AF4">
-        <v>104.23</v>
+        <v>24.04</v>
       </c>
       <c r="AG4">
-        <v>3388.9</v>
+        <v>3395.19</v>
       </c>
       <c r="AH4">
-        <v>3023.73</v>
+        <v>3027.81</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1255,7 +1227,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>36.74</v>
+        <v>33.79</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,10 +1238,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1041.6</v>
+        <v>1038.95</v>
       </c>
       <c r="D5">
-        <v>-0.79</v>
+        <v>-0.25</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1278,46 +1250,46 @@
         <v>695.25</v>
       </c>
       <c r="G5">
-        <v>-9.4</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="H5">
-        <v>49.82</v>
+        <v>49.44</v>
       </c>
       <c r="I5">
-        <v>-0.71</v>
+        <v>-3.67</v>
       </c>
       <c r="J5">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K5">
-        <v>-4.04</v>
+        <v>-5.49</v>
       </c>
       <c r="L5">
-        <v>56.15</v>
+        <v>48.32</v>
       </c>
       <c r="M5">
-        <v>20.22</v>
+        <v>21.53</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P5">
-        <v>1049.15</v>
+        <v>1041.24</v>
       </c>
       <c r="Q5">
-        <v>1006.39</v>
+        <v>1010.84</v>
       </c>
       <c r="R5">
-        <v>991.16</v>
+        <v>990.4</v>
       </c>
       <c r="S5">
-        <v>951.52</v>
+        <v>952.41</v>
       </c>
       <c r="T5">
-        <v>9.470000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1332,34 +1304,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>57.34</v>
+        <v>56.57</v>
       </c>
       <c r="Z5">
-        <v>19.62</v>
+        <v>18.63</v>
       </c>
       <c r="AA5">
-        <v>15.38</v>
+        <v>16.03</v>
       </c>
       <c r="AB5">
-        <v>4.24</v>
+        <v>2.6</v>
       </c>
       <c r="AC5">
-        <v>46.63</v>
+        <v>36.27</v>
       </c>
       <c r="AD5">
-        <v>59.94</v>
+        <v>47.14</v>
       </c>
       <c r="AE5">
-        <v>24.67</v>
+        <v>24.06</v>
       </c>
       <c r="AF5">
-        <v>-50.43</v>
+        <v>-57.71</v>
       </c>
       <c r="AG5">
-        <v>1100.35</v>
+        <v>1101.94</v>
       </c>
       <c r="AH5">
-        <v>912.4299999999999</v>
+        <v>919.74</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1368,7 +1340,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>47.58</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1379,10 +1351,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.12</v>
+        <v>14.07</v>
       </c>
       <c r="D6">
-        <v>2.99</v>
+        <v>-0.35</v>
       </c>
       <c r="E6">
         <v>15.01</v>
@@ -1391,46 +1363,46 @@
         <v>6.15</v>
       </c>
       <c r="G6">
-        <v>-5.93</v>
+        <v>-6.26</v>
       </c>
       <c r="H6">
-        <v>129.59</v>
+        <v>128.78</v>
       </c>
       <c r="I6">
-        <v>9.539999999999999</v>
+        <v>4.22</v>
       </c>
       <c r="J6">
-        <v>4.52</v>
+        <v>4.3</v>
       </c>
       <c r="K6">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="L6">
-        <v>118.24</v>
+        <v>121.23</v>
       </c>
       <c r="M6">
-        <v>16.97</v>
+        <v>18.8</v>
       </c>
       <c r="N6">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="O6">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P6">
-        <v>13.79</v>
+        <v>13.9</v>
       </c>
       <c r="Q6">
-        <v>13.17</v>
+        <v>13.2</v>
       </c>
       <c r="R6">
         <v>13.82</v>
       </c>
       <c r="S6">
-        <v>11.6</v>
+        <v>11.62</v>
       </c>
       <c r="T6">
-        <v>21.75</v>
+        <v>21.04</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1445,43 +1417,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>61.92</v>
+        <v>60.87</v>
       </c>
       <c r="Z6">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA6">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="AB6">
         <v>0.17</v>
       </c>
       <c r="AC6">
-        <v>88.15000000000001</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="AD6">
-        <v>93.13</v>
+        <v>87.8</v>
       </c>
       <c r="AE6">
         <v>0.44</v>
       </c>
       <c r="AF6">
-        <v>122.81</v>
+        <v>-18.16</v>
       </c>
       <c r="AG6">
-        <v>14.04</v>
+        <v>14.14</v>
       </c>
       <c r="AH6">
-        <v>12.31</v>
+        <v>12.26</v>
       </c>
       <c r="AI6">
-        <v>12.65</v>
+        <v>12.74</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>52.72</v>
+        <v>54.04</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1492,10 +1464,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.95</v>
+        <v>11.72</v>
       </c>
       <c r="D7">
-        <v>2.14</v>
+        <v>-1.92</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1504,46 +1476,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-14.15</v>
+        <v>-15.8</v>
       </c>
       <c r="H7">
-        <v>154.8</v>
+        <v>149.89</v>
       </c>
       <c r="I7">
-        <v>-3.24</v>
+        <v>-3.22</v>
       </c>
       <c r="J7">
-        <v>2.75</v>
+        <v>-1.18</v>
       </c>
       <c r="K7">
-        <v>0.93</v>
+        <v>-5.71</v>
       </c>
       <c r="L7">
-        <v>129.81</v>
+        <v>121.13</v>
       </c>
       <c r="M7">
-        <v>-30.16</v>
+        <v>-29.8</v>
       </c>
       <c r="N7">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="O7">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P7">
-        <v>11.87</v>
+        <v>11.79</v>
       </c>
       <c r="Q7">
-        <v>12.2</v>
+        <v>12.18</v>
       </c>
       <c r="R7">
-        <v>11.6</v>
+        <v>11.61</v>
       </c>
       <c r="S7">
-        <v>9.92</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="T7">
-        <v>20.5</v>
+        <v>17.79</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1558,34 +1530,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>49.49</v>
+        <v>46.32</v>
       </c>
       <c r="Z7">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="AA7">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="AB7">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="AC7">
-        <v>5.74</v>
+        <v>5.58</v>
       </c>
       <c r="AD7">
-        <v>7.3</v>
+        <v>5.25</v>
       </c>
       <c r="AE7">
         <v>0.37</v>
       </c>
       <c r="AF7">
-        <v>-67.23999999999999</v>
+        <v>4.79</v>
       </c>
       <c r="AG7">
         <v>13.55</v>
       </c>
       <c r="AH7">
-        <v>10.85</v>
+        <v>10.81</v>
       </c>
       <c r="AI7">
         <v>12.88</v>
@@ -1594,7 +1566,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>32.53</v>
+        <v>31.13</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1605,10 +1577,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4385.7</v>
+        <v>4291.8</v>
       </c>
       <c r="D8">
-        <v>-3.55</v>
+        <v>-2.14</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1617,46 +1589,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-24.51</v>
+        <v>-26.12</v>
       </c>
       <c r="H8">
-        <v>5.55</v>
+        <v>3.29</v>
       </c>
       <c r="I8">
-        <v>-0.1</v>
+        <v>-1.68</v>
       </c>
       <c r="J8">
-        <v>0.39</v>
+        <v>-3.28</v>
       </c>
       <c r="K8">
-        <v>-1.17</v>
+        <v>-5.24</v>
       </c>
       <c r="L8">
-        <v>-10.03</v>
+        <v>-15.14</v>
       </c>
       <c r="M8">
-        <v>19.45</v>
+        <v>19.49</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="P8">
-        <v>4475.64</v>
+        <v>4461</v>
       </c>
       <c r="Q8">
-        <v>4366.5</v>
+        <v>4363.48</v>
       </c>
       <c r="R8">
-        <v>4371.73</v>
+        <v>4373.2</v>
       </c>
       <c r="S8">
-        <v>4687.6</v>
+        <v>4682.51</v>
       </c>
       <c r="T8">
-        <v>-6.44</v>
+        <v>-8.34</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1671,34 +1643,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>49.33</v>
+        <v>42.85</v>
       </c>
       <c r="Z8">
-        <v>26.41</v>
+        <v>14.16</v>
       </c>
       <c r="AA8">
-        <v>8.859999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="AB8">
-        <v>17.55</v>
+        <v>4.24</v>
       </c>
       <c r="AC8">
-        <v>73.8</v>
+        <v>40.46</v>
       </c>
       <c r="AD8">
-        <v>89.09999999999999</v>
+        <v>71.42</v>
       </c>
       <c r="AE8">
-        <v>107.77</v>
+        <v>108.38</v>
       </c>
       <c r="AF8">
-        <v>-10.19</v>
+        <v>59.1</v>
       </c>
       <c r="AG8">
-        <v>4533.02</v>
+        <v>4533.25</v>
       </c>
       <c r="AH8">
-        <v>4199.98</v>
+        <v>4193.71</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1707,7 +1679,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>32.59</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1718,10 +1690,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11499</v>
+        <v>11450</v>
       </c>
       <c r="D9">
-        <v>-1.03</v>
+        <v>-0.43</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1730,25 +1702,25 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-11.9</v>
+        <v>-12.27</v>
       </c>
       <c r="H9">
-        <v>10.97</v>
+        <v>10.5</v>
       </c>
       <c r="I9">
-        <v>-2.39</v>
+        <v>-3.71</v>
       </c>
       <c r="J9">
-        <v>-3.39</v>
+        <v>-5.32</v>
       </c>
       <c r="K9">
-        <v>0.79</v>
+        <v>-0.21</v>
       </c>
       <c r="L9">
-        <v>-7.63</v>
+        <v>-7.67</v>
       </c>
       <c r="M9">
-        <v>9.119999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="N9">
         <v>38</v>
@@ -1757,19 +1729,19 @@
         <v>43</v>
       </c>
       <c r="P9">
-        <v>11666.8</v>
+        <v>11578.6</v>
       </c>
       <c r="Q9">
-        <v>11892.9</v>
+        <v>11870.75</v>
       </c>
       <c r="R9">
-        <v>11636.26</v>
+        <v>11647.04</v>
       </c>
       <c r="S9">
-        <v>11789.95</v>
+        <v>11786.94</v>
       </c>
       <c r="T9">
-        <v>-2.47</v>
+        <v>-2.86</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1784,43 +1756,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>39.51</v>
+        <v>38.16</v>
       </c>
       <c r="Z9">
-        <v>-12.17</v>
+        <v>-37.68</v>
       </c>
       <c r="AA9">
-        <v>62.13</v>
+        <v>42.17</v>
       </c>
       <c r="AB9">
-        <v>-74.3</v>
+        <v>-79.84999999999999</v>
       </c>
       <c r="AC9">
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>209.94</v>
+        <v>202.3</v>
       </c>
       <c r="AF9">
-        <v>-27.26</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="AG9">
-        <v>12251.49</v>
+        <v>12280.41</v>
       </c>
       <c r="AH9">
-        <v>11534.31</v>
+        <v>11461.09</v>
       </c>
       <c r="AI9">
-        <v>11461.94</v>
+        <v>12054.41</v>
       </c>
       <c r="AJ9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK9">
-        <v>27.93</v>
+        <v>31.57</v>
       </c>
     </row>
   </sheetData>
@@ -1981,47 +1953,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2029,1142 +1966,1142 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>65</v>
+      <c r="B6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>0.33</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>0.21</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.12</v>
+      <c r="D7" s="5">
+        <v>-3.19</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-4.6</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-4.03</v>
       </c>
-      <c r="E8" s="8">
-        <v>0.57</v>
+      <c r="D8" s="5">
+        <v>-5.12</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>5.72</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>4.29</v>
       </c>
-      <c r="E9" s="7">
-        <v>-1.43</v>
+      <c r="D9" s="5">
+        <v>2.84</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>7.32</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>9.9</v>
       </c>
-      <c r="E10" s="8">
-        <v>2.58</v>
+      <c r="D10" s="5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>1.58</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>4.52</v>
       </c>
-      <c r="E11" s="8">
-        <v>2.94</v>
+      <c r="D11" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>4.56</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>2.75</v>
       </c>
-      <c r="E12" s="7">
-        <v>-1.81</v>
+      <c r="D12" s="5">
+        <v>-1.18</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-3.93</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>3.07</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>0.39</v>
       </c>
-      <c r="E13" s="7">
-        <v>-2.68</v>
+      <c r="D13" s="5">
+        <v>-3.28</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-3.67</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
-        <v>-1.29</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-3.39</v>
       </c>
-      <c r="E14" s="7">
-        <v>-2.1</v>
+      <c r="D14" s="5">
+        <v>-5.32</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-1.73</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-1.26</v>
       </c>
-      <c r="E15" s="8">
-        <v>0.47</v>
+      <c r="D15" s="5">
+        <v>-3.64</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-2.38</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-11.61</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-6.24</v>
       </c>
-      <c r="E16" s="8">
-        <v>5.37</v>
+      <c r="D16" s="5">
+        <v>-4.71</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.53</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-2.24</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-1.31</v>
       </c>
-      <c r="E17" s="8">
+      <c r="D17" s="5">
+        <v>-1.14</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-0.71</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-3.67</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-2.96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="D19" s="5">
+        <v>4.22</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-5.32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-3.24</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-3.22</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-1.68</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-2.39</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-3.71</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>49.97</v>
+      </c>
+      <c r="D23" s="5">
+        <v>46.83</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-3.14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-25.74</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-27.06</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>19.64</v>
+      </c>
+      <c r="D25" s="5">
+        <v>19.09</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>56.15</v>
+      </c>
+      <c r="D26" s="5">
+        <v>48.32</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-7.83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>118.24</v>
+      </c>
+      <c r="D27" s="5">
+        <v>121.23</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>129.81</v>
+      </c>
+      <c r="D28" s="5">
+        <v>121.13</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-8.68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-10.03</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-15.14</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-5.11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-7.63</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-7.67</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>13.85</v>
+      </c>
+      <c r="D31" s="5">
+        <v>13.34</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-12.09</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-18.41</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-6.32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>10.35</v>
+      </c>
+      <c r="D33" s="5">
+        <v>3.66</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-6.69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-4.04</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-5.49</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>3.98</v>
+      </c>
+      <c r="D35" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
         <v>0.93</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="D36" s="5">
+        <v>-5.71</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-6.64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-1.17</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-5.24</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-4.07</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-0.21</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-5.34</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-6.76</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-41.2</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-41.73</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-3.01</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-3.27</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-2.84</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.71</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-9.4</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>10.84</v>
-      </c>
-      <c r="D19" s="6">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="E19" s="7">
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-5.93</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-6.26</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-14.15</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-15.8</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-24.51</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-26.12</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-11.9</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-12.27</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>402</v>
+      </c>
+      <c r="D47" s="5">
+        <v>396</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>54.97</v>
+      </c>
+      <c r="D48" s="5">
+        <v>54.47</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>3278.7</v>
+      </c>
+      <c r="D49" s="5">
+        <v>3270</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-8.699999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>1041.6</v>
+      </c>
+      <c r="D50" s="5">
+        <v>1038.95</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-2.65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>14.12</v>
+      </c>
+      <c r="D51" s="5">
+        <v>14.07</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>11.95</v>
+      </c>
+      <c r="D52" s="5">
+        <v>11.72</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>4385.7</v>
+      </c>
+      <c r="D53" s="5">
+        <v>4291.8</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-93.90000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>11499</v>
+      </c>
+      <c r="D54" s="5">
+        <v>11450</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="5">
+        <v>87</v>
+      </c>
+      <c r="D55" s="5">
+        <v>99</v>
+      </c>
+      <c r="E55" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="5">
+        <v>99</v>
+      </c>
+      <c r="D56" s="5">
+        <v>87</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>49.44</v>
+      </c>
+      <c r="D57" s="5">
+        <v>45.65</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-3.79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>35.65</v>
+      </c>
+      <c r="D58" s="5">
+        <v>34.35</v>
+      </c>
+      <c r="E58" s="6">
         <v>-1.3</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>56.93</v>
+      </c>
+      <c r="D59" s="5">
+        <v>55.95</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="5">
+        <v>57.34</v>
+      </c>
+      <c r="D60" s="5">
+        <v>56.57</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>61.92</v>
+      </c>
+      <c r="D61" s="5">
+        <v>60.87</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-8.16</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-3.24</v>
-      </c>
-      <c r="E20" s="8">
-        <v>4.92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>49.49</v>
+      </c>
+      <c r="D62" s="5">
+        <v>46.32</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-3.17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>4.03</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-4.13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>49.33</v>
+      </c>
+      <c r="D63" s="5">
+        <v>42.85</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-6.48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-4.01</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-2.39</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>39.51</v>
+      </c>
+      <c r="D64" s="5">
+        <v>38.16</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>47.53</v>
-      </c>
-      <c r="D23" s="6">
-        <v>49.97</v>
-      </c>
-      <c r="E23" s="8">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>14.49</v>
+      </c>
+      <c r="D65" s="5">
+        <v>7.47</v>
+      </c>
+      <c r="E65" s="6">
+        <v>-7.02</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-24.55</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-25.74</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5">
+        <v>-62.35</v>
+      </c>
+      <c r="D66" s="5">
+        <v>-65.09</v>
+      </c>
+      <c r="E66" s="6">
+        <v>-2.74</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>21.14</v>
-      </c>
-      <c r="D25" s="6">
-        <v>19.64</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="5">
+        <v>104.23</v>
+      </c>
+      <c r="D67" s="5">
+        <v>24.04</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-80.19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>53.03</v>
-      </c>
-      <c r="D26" s="6">
-        <v>56.15</v>
-      </c>
-      <c r="E26" s="8">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="5">
+        <v>-50.43</v>
+      </c>
+      <c r="D68" s="5">
+        <v>-57.71</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-7.28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>116.74</v>
-      </c>
-      <c r="D27" s="6">
-        <v>118.24</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="5">
+        <v>122.81</v>
+      </c>
+      <c r="D69" s="5">
+        <v>-18.16</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-140.97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>134</v>
-      </c>
-      <c r="D28" s="6">
-        <v>129.81</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-4.19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="5">
+        <v>-67.23999999999999</v>
+      </c>
+      <c r="D70" s="5">
+        <v>4.79</v>
+      </c>
+      <c r="E70" s="7">
+        <v>72.03</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-8.66</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-10.03</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>-10.19</v>
+      </c>
+      <c r="D71" s="5">
+        <v>59.1</v>
+      </c>
+      <c r="E71" s="7">
+        <v>69.29000000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-4.43</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-7.63</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>14.54</v>
-      </c>
-      <c r="D31" s="6">
-        <v>13.85</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-9.65</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-12.09</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>10.36</v>
-      </c>
-      <c r="D33" s="6">
-        <v>10.35</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-2.24</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-4.04</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="D35" s="6">
-        <v>3.98</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-5.74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>0.09</v>
-      </c>
-      <c r="D36" s="6">
-        <v>0.93</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>3.34</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-1.17</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-4.51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="D38" s="6">
-        <v>0.79</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-5.58</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-40.12</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-41.2</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-3.9</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-3.01</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-10.45</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-9.4</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-6</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-5.93</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-15.95</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-14.15</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-21.73</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-24.51</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-2.78</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-10.98</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-11.9</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>401</v>
-      </c>
-      <c r="D47" s="6">
-        <v>402</v>
-      </c>
-      <c r="E47" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>55.98</v>
-      </c>
-      <c r="D48" s="6">
-        <v>54.97</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>3248.7</v>
-      </c>
-      <c r="D49" s="6">
-        <v>3278.7</v>
-      </c>
-      <c r="E49" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>1029.5</v>
-      </c>
-      <c r="D50" s="6">
-        <v>1041.6</v>
-      </c>
-      <c r="E50" s="8">
-        <v>12.1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>14.11</v>
-      </c>
-      <c r="D51" s="6">
-        <v>14.12</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>11.7</v>
-      </c>
-      <c r="D52" s="6">
-        <v>11.95</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>4547</v>
-      </c>
-      <c r="D53" s="6">
-        <v>4385.7</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-161.3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>11619</v>
-      </c>
-      <c r="D54" s="6">
-        <v>11499</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-120</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="6">
-        <v>38</v>
-      </c>
-      <c r="D55" s="6">
-        <v>26</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="6">
-        <v>26</v>
-      </c>
-      <c r="D56" s="6">
-        <v>38</v>
-      </c>
-      <c r="E56" s="8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>48.59</v>
-      </c>
-      <c r="D57" s="6">
-        <v>49.44</v>
-      </c>
-      <c r="E57" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>38.38</v>
-      </c>
-      <c r="D58" s="6">
-        <v>35.65</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-2.73</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>54.39</v>
-      </c>
-      <c r="D59" s="6">
-        <v>56.93</v>
-      </c>
-      <c r="E59" s="8">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>55.53</v>
-      </c>
-      <c r="D60" s="6">
-        <v>57.34</v>
-      </c>
-      <c r="E60" s="8">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>65.09</v>
-      </c>
-      <c r="D61" s="6">
-        <v>61.92</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-3.17</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>45.74</v>
-      </c>
-      <c r="D62" s="6">
-        <v>49.49</v>
-      </c>
-      <c r="E62" s="8">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>65.04000000000001</v>
-      </c>
-      <c r="D63" s="6">
-        <v>49.33</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-15.71</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>42.95</v>
-      </c>
-      <c r="D64" s="6">
-        <v>39.51</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="5" t="s">
+      <c r="B72" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C65" s="6">
-        <v>-67.86</v>
-      </c>
-      <c r="D65" s="6">
-        <v>14.49</v>
-      </c>
-      <c r="E65" s="8">
-        <v>82.34999999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>-25.59</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-62.35</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-36.76</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>-32.32</v>
-      </c>
-      <c r="D67" s="6">
-        <v>104.23</v>
-      </c>
-      <c r="E67" s="8">
-        <v>136.55</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>-33.5</v>
-      </c>
-      <c r="D68" s="6">
-        <v>-50.43</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-16.93</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>126.24</v>
-      </c>
-      <c r="D69" s="6">
-        <v>122.81</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-3.43</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>-50.44</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-67.23999999999999</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-16.8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>173.89</v>
-      </c>
-      <c r="D71" s="6">
-        <v>-10.19</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-184.08</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>-32.47</v>
-      </c>
-      <c r="D72" s="6">
+      <c r="C72" s="5">
         <v>-27.26</v>
       </c>
-      <c r="E72" s="8">
-        <v>5.21</v>
+      <c r="D72" s="5">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="E72" s="7">
+        <v>18.05</v>
       </c>
     </row>
   </sheetData>
@@ -3190,60 +3127,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>73</v>
+      <c r="B1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>56.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>50</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>47.6</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>1.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>1.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-0.2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-1.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>50</v>
       </c>
     </row>
@@ -3345,55 +3282,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.2885</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2022</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1945</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1746</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1697</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.09119999999999999</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2321</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.3016</v>
+      <c r="A2" s="13">
+        <v>0.2952</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2153</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1949</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.188</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1766</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0935</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2292</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.298</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,7 +175,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>45.6 → 53.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>45.6</t>
+  </si>
+  <si>
+    <t>53.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -261,14 +288,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -301,13 +328,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,14 +404,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -758,8 +786,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -899,58 +927,58 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="D2">
-        <v>-1.49</v>
+        <v>3.28</v>
       </c>
       <c r="E2">
         <v>424.7</v>
       </c>
       <c r="F2">
-        <v>273</v>
+        <v>274.85</v>
       </c>
       <c r="G2">
-        <v>-6.76</v>
+        <v>-3.7</v>
       </c>
       <c r="H2">
-        <v>45.05</v>
+        <v>48.81</v>
       </c>
       <c r="I2">
-        <v>-3.64</v>
+        <v>0.32</v>
       </c>
       <c r="J2">
-        <v>-3.19</v>
+        <v>2.1</v>
       </c>
       <c r="K2">
-        <v>13.34</v>
+        <v>14.47</v>
       </c>
       <c r="L2">
-        <v>46.83</v>
+        <v>49.82</v>
       </c>
       <c r="M2">
-        <v>29.52</v>
+        <v>30.34</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>401.08</v>
+        <v>401.34</v>
       </c>
       <c r="Q2">
-        <v>405.19</v>
+        <v>406.02</v>
       </c>
       <c r="R2">
-        <v>395.15</v>
+        <v>396.48</v>
       </c>
       <c r="S2">
-        <v>356.22</v>
+        <v>356.64</v>
       </c>
       <c r="T2">
-        <v>11.17</v>
+        <v>14.68</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -965,34 +993,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>45.65</v>
+        <v>53.89</v>
       </c>
       <c r="Z2">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AA2">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AB2">
-        <v>-2.55</v>
+        <v>-1.84</v>
       </c>
       <c r="AC2">
-        <v>4.28</v>
+        <v>18.77</v>
       </c>
       <c r="AD2">
-        <v>5.37</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AE2">
-        <v>10.15</v>
+        <v>10.44</v>
       </c>
       <c r="AF2">
-        <v>7.47</v>
+        <v>39.71</v>
       </c>
       <c r="AG2">
-        <v>426.4</v>
+        <v>426.39</v>
       </c>
       <c r="AH2">
-        <v>383.97</v>
+        <v>385.65</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1001,7 +1029,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>21.68</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1012,10 +1040,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>54.47</v>
+        <v>54.75</v>
       </c>
       <c r="D3">
-        <v>-0.91</v>
+        <v>0.51</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1024,25 +1052,25 @@
         <v>53.89</v>
       </c>
       <c r="G3">
-        <v>-41.73</v>
+        <v>-41.43</v>
       </c>
       <c r="H3">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="I3">
-        <v>-4.71</v>
+        <v>-3.49</v>
       </c>
       <c r="J3">
-        <v>-5.12</v>
+        <v>-4.03</v>
       </c>
       <c r="K3">
-        <v>-18.41</v>
+        <v>-18.71</v>
       </c>
       <c r="L3">
-        <v>-27.06</v>
+        <v>-27</v>
       </c>
       <c r="M3">
-        <v>-22.92</v>
+        <v>-22.83</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1051,19 +1079,19 @@
         <v>12</v>
       </c>
       <c r="P3">
-        <v>55.63</v>
+        <v>55.23</v>
       </c>
       <c r="Q3">
-        <v>58.52</v>
+        <v>58.45</v>
       </c>
       <c r="R3">
-        <v>59.22</v>
+        <v>59.14</v>
       </c>
       <c r="S3">
-        <v>66.36</v>
+        <v>66.23</v>
       </c>
       <c r="T3">
-        <v>-17.92</v>
+        <v>-17.33</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1078,43 +1106,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>34.35</v>
+        <v>35.76</v>
       </c>
       <c r="Z3">
-        <v>-1.02</v>
+        <v>-1.15</v>
       </c>
       <c r="AA3">
-        <v>-0.4</v>
+        <v>-0.55</v>
       </c>
       <c r="AB3">
-        <v>-0.62</v>
+        <v>-0.61</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD3">
-        <v>0.09</v>
+        <v>0.54</v>
       </c>
       <c r="AE3">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AF3">
-        <v>-65.09</v>
+        <v>-65.25</v>
       </c>
       <c r="AG3">
-        <v>64.2</v>
+        <v>64.28</v>
       </c>
       <c r="AH3">
-        <v>52.84</v>
+        <v>52.63</v>
       </c>
       <c r="AI3">
-        <v>60.68</v>
+        <v>60.65</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>39.55</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1125,10 +1153,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3270</v>
+        <v>3300</v>
       </c>
       <c r="D4">
-        <v>-0.27</v>
+        <v>0.92</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1137,46 +1165,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-3.27</v>
+        <v>-2.38</v>
       </c>
       <c r="H4">
-        <v>29.19</v>
+        <v>30.38</v>
       </c>
       <c r="I4">
-        <v>-1.14</v>
+        <v>1.32</v>
       </c>
       <c r="J4">
-        <v>2.84</v>
+        <v>4.22</v>
       </c>
       <c r="K4">
-        <v>3.66</v>
+        <v>4.59</v>
       </c>
       <c r="L4">
-        <v>19.09</v>
+        <v>19.35</v>
       </c>
       <c r="M4">
-        <v>17.66</v>
+        <v>17.87</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>3260.98</v>
+        <v>3269.58</v>
       </c>
       <c r="Q4">
-        <v>3211.5</v>
+        <v>3220.85</v>
       </c>
       <c r="R4">
-        <v>3169.02</v>
+        <v>3173.6</v>
       </c>
       <c r="S4">
-        <v>2906.23</v>
+        <v>2908.27</v>
       </c>
       <c r="T4">
-        <v>12.52</v>
+        <v>13.47</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1191,34 +1219,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>55.95</v>
+        <v>58.59</v>
       </c>
       <c r="Z4">
-        <v>38.86</v>
+        <v>39.57</v>
       </c>
       <c r="AA4">
-        <v>37.59</v>
+        <v>37.99</v>
       </c>
       <c r="AB4">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="AC4">
-        <v>43.78</v>
+        <v>46.91</v>
       </c>
       <c r="AD4">
-        <v>41.18</v>
+        <v>43.99</v>
       </c>
       <c r="AE4">
-        <v>74.75</v>
+        <v>73.69</v>
       </c>
       <c r="AF4">
-        <v>24.04</v>
+        <v>47.08</v>
       </c>
       <c r="AG4">
-        <v>3395.19</v>
+        <v>3402.45</v>
       </c>
       <c r="AH4">
-        <v>3027.81</v>
+        <v>3039.25</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1227,7 +1255,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>33.79</v>
+        <v>32.83</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1238,58 +1266,58 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1038.95</v>
+        <v>1029.85</v>
       </c>
       <c r="D5">
-        <v>-0.25</v>
+        <v>-0.88</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>695.25</v>
+        <v>700.85</v>
       </c>
       <c r="G5">
-        <v>-9.630000000000001</v>
+        <v>-10.42</v>
       </c>
       <c r="H5">
-        <v>49.44</v>
+        <v>46.94</v>
       </c>
       <c r="I5">
-        <v>-3.67</v>
+        <v>-1.57</v>
       </c>
       <c r="J5">
-        <v>9.199999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="K5">
-        <v>-5.49</v>
+        <v>-7.15</v>
       </c>
       <c r="L5">
-        <v>48.32</v>
+        <v>48.13</v>
       </c>
       <c r="M5">
-        <v>21.53</v>
+        <v>21.3</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>1041.24</v>
+        <v>1037.96</v>
       </c>
       <c r="Q5">
-        <v>1010.84</v>
+        <v>1014.55</v>
       </c>
       <c r="R5">
-        <v>990.4</v>
+        <v>990.21</v>
       </c>
       <c r="S5">
-        <v>952.41</v>
+        <v>953.3200000000001</v>
       </c>
       <c r="T5">
-        <v>9.09</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1304,34 +1332,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>56.57</v>
+        <v>53.91</v>
       </c>
       <c r="Z5">
-        <v>18.63</v>
+        <v>16.91</v>
       </c>
       <c r="AA5">
-        <v>16.03</v>
+        <v>16.21</v>
       </c>
       <c r="AB5">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="AC5">
-        <v>36.27</v>
+        <v>19.14</v>
       </c>
       <c r="AD5">
-        <v>47.14</v>
+        <v>34.01</v>
       </c>
       <c r="AE5">
-        <v>24.06</v>
+        <v>24.84</v>
       </c>
       <c r="AF5">
-        <v>-57.71</v>
+        <v>-11.61</v>
       </c>
       <c r="AG5">
-        <v>1101.94</v>
+        <v>1102.16</v>
       </c>
       <c r="AH5">
-        <v>919.74</v>
+        <v>926.9400000000001</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1340,7 +1368,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>43.71</v>
+        <v>38.21</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1351,37 +1379,37 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.07</v>
+        <v>14.03</v>
       </c>
       <c r="D6">
-        <v>-0.35</v>
+        <v>-0.28</v>
       </c>
       <c r="E6">
         <v>15.01</v>
       </c>
       <c r="F6">
-        <v>6.15</v>
+        <v>6.46</v>
       </c>
       <c r="G6">
-        <v>-6.26</v>
+        <v>-6.53</v>
       </c>
       <c r="H6">
-        <v>128.78</v>
+        <v>117.18</v>
       </c>
       <c r="I6">
-        <v>4.22</v>
+        <v>3.85</v>
       </c>
       <c r="J6">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="K6">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="L6">
-        <v>121.23</v>
+        <v>128.13</v>
       </c>
       <c r="M6">
-        <v>18.8</v>
+        <v>18.72</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1390,19 +1418,19 @@
         <v>94</v>
       </c>
       <c r="P6">
-        <v>13.9</v>
+        <v>14.01</v>
       </c>
       <c r="Q6">
-        <v>13.2</v>
+        <v>13.24</v>
       </c>
       <c r="R6">
         <v>13.82</v>
       </c>
       <c r="S6">
-        <v>11.62</v>
+        <v>11.65</v>
       </c>
       <c r="T6">
-        <v>21.04</v>
+        <v>20.42</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1417,43 +1445,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>60.87</v>
+        <v>59.99</v>
       </c>
       <c r="Z6">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AA6">
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="AB6">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AC6">
-        <v>84.01000000000001</v>
+        <v>87.78</v>
       </c>
       <c r="AD6">
-        <v>87.8</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="AE6">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="AF6">
-        <v>-18.16</v>
+        <v>-41.48</v>
       </c>
       <c r="AG6">
-        <v>14.14</v>
+        <v>14.26</v>
       </c>
       <c r="AH6">
-        <v>12.26</v>
+        <v>12.23</v>
       </c>
       <c r="AI6">
-        <v>12.74</v>
+        <v>12.79</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>54.04</v>
+        <v>55.18</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1464,10 +1492,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.72</v>
+        <v>11.68</v>
       </c>
       <c r="D7">
-        <v>-1.92</v>
+        <v>-0.34</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1476,46 +1504,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-15.8</v>
+        <v>-16.09</v>
       </c>
       <c r="H7">
-        <v>149.89</v>
+        <v>149.04</v>
       </c>
       <c r="I7">
-        <v>-3.22</v>
+        <v>-1.6</v>
       </c>
       <c r="J7">
-        <v>-1.18</v>
+        <v>-3.39</v>
       </c>
       <c r="K7">
-        <v>-5.71</v>
+        <v>-10.36</v>
       </c>
       <c r="L7">
-        <v>121.13</v>
+        <v>116.3</v>
       </c>
       <c r="M7">
-        <v>-29.8</v>
+        <v>-29.83</v>
       </c>
       <c r="N7">
         <v>87</v>
       </c>
       <c r="O7">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P7">
-        <v>11.79</v>
+        <v>11.75</v>
       </c>
       <c r="Q7">
-        <v>12.18</v>
+        <v>12.17</v>
       </c>
       <c r="R7">
-        <v>11.61</v>
+        <v>11.63</v>
       </c>
       <c r="S7">
-        <v>9.949999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="T7">
-        <v>17.79</v>
+        <v>17.01</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1530,43 +1558,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>46.32</v>
+        <v>45.77</v>
       </c>
       <c r="Z7">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AA7">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="AB7">
         <v>-0.13</v>
       </c>
       <c r="AC7">
-        <v>5.58</v>
+        <v>5.61</v>
       </c>
       <c r="AD7">
-        <v>5.25</v>
+        <v>5.64</v>
       </c>
       <c r="AE7">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AF7">
-        <v>4.79</v>
+        <v>-62.14</v>
       </c>
       <c r="AG7">
         <v>13.55</v>
       </c>
       <c r="AH7">
-        <v>10.81</v>
+        <v>10.78</v>
       </c>
       <c r="AI7">
-        <v>12.88</v>
+        <v>12.69</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>31.13</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1577,10 +1605,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4291.8</v>
+        <v>4309.5</v>
       </c>
       <c r="D8">
-        <v>-2.14</v>
+        <v>0.41</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1589,25 +1617,25 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-26.12</v>
+        <v>-25.82</v>
       </c>
       <c r="H8">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="I8">
-        <v>-1.68</v>
+        <v>-4.94</v>
       </c>
       <c r="J8">
-        <v>-3.28</v>
+        <v>-0.98</v>
       </c>
       <c r="K8">
-        <v>-5.24</v>
+        <v>-7.02</v>
       </c>
       <c r="L8">
-        <v>-15.14</v>
+        <v>-13.08</v>
       </c>
       <c r="M8">
-        <v>19.49</v>
+        <v>19.58</v>
       </c>
       <c r="N8">
         <v>26</v>
@@ -1616,19 +1644,19 @@
         <v>32</v>
       </c>
       <c r="P8">
-        <v>4461</v>
+        <v>4416.2</v>
       </c>
       <c r="Q8">
-        <v>4363.48</v>
+        <v>4363.79</v>
       </c>
       <c r="R8">
-        <v>4373.2</v>
+        <v>4374.41</v>
       </c>
       <c r="S8">
-        <v>4682.51</v>
+        <v>4677.63</v>
       </c>
       <c r="T8">
-        <v>-8.34</v>
+        <v>-7.87</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1643,34 +1671,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>42.85</v>
+        <v>44.33</v>
       </c>
       <c r="Z8">
-        <v>14.16</v>
+        <v>5.81</v>
       </c>
       <c r="AA8">
-        <v>9.92</v>
+        <v>9.1</v>
       </c>
       <c r="AB8">
-        <v>4.24</v>
+        <v>-3.29</v>
       </c>
       <c r="AC8">
-        <v>40.46</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AD8">
-        <v>71.42</v>
+        <v>41.21</v>
       </c>
       <c r="AE8">
-        <v>108.38</v>
+        <v>104.17</v>
       </c>
       <c r="AF8">
-        <v>59.1</v>
+        <v>-63.55</v>
       </c>
       <c r="AG8">
-        <v>4533.25</v>
+        <v>4533.12</v>
       </c>
       <c r="AH8">
-        <v>4193.71</v>
+        <v>4194.47</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1679,7 +1707,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>29.37</v>
+        <v>26.57</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1690,10 +1718,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11450</v>
+        <v>11575</v>
       </c>
       <c r="D9">
-        <v>-0.43</v>
+        <v>1.09</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1702,46 +1730,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-12.27</v>
+        <v>-11.32</v>
       </c>
       <c r="H9">
-        <v>10.5</v>
+        <v>11.71</v>
       </c>
       <c r="I9">
-        <v>-3.71</v>
+        <v>-1.12</v>
       </c>
       <c r="J9">
-        <v>-5.32</v>
+        <v>-2.67</v>
       </c>
       <c r="K9">
-        <v>-0.21</v>
+        <v>0.05</v>
       </c>
       <c r="L9">
-        <v>-7.67</v>
+        <v>-6.02</v>
       </c>
       <c r="M9">
-        <v>9.35</v>
+        <v>9.58</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P9">
-        <v>11578.6</v>
+        <v>11552.4</v>
       </c>
       <c r="Q9">
-        <v>11870.75</v>
+        <v>11854.1</v>
       </c>
       <c r="R9">
-        <v>11647.04</v>
+        <v>11661.22</v>
       </c>
       <c r="S9">
-        <v>11786.94</v>
+        <v>11785.08</v>
       </c>
       <c r="T9">
-        <v>-2.86</v>
+        <v>-1.78</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1756,34 +1784,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>38.16</v>
+        <v>43.45</v>
       </c>
       <c r="Z9">
-        <v>-37.68</v>
+        <v>-47.27</v>
       </c>
       <c r="AA9">
-        <v>42.17</v>
+        <v>24.28</v>
       </c>
       <c r="AB9">
-        <v>-79.84999999999999</v>
+        <v>-71.55</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE9">
-        <v>202.3</v>
+        <v>203.64</v>
       </c>
       <c r="AF9">
-        <v>-9.210000000000001</v>
+        <v>-15.99</v>
       </c>
       <c r="AG9">
-        <v>12280.41</v>
+        <v>12283.95</v>
       </c>
       <c r="AH9">
-        <v>11461.09</v>
+        <v>11424.25</v>
       </c>
       <c r="AI9">
         <v>12054.41</v>
@@ -1792,7 +1820,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>31.57</v>
+        <v>30.02</v>
       </c>
     </row>
   </sheetData>
@@ -1933,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1953,12 +1981,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>51</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1966,1142 +2029,1108 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>56</v>
+      <c r="B6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>0.21</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-3.19</v>
       </c>
-      <c r="E7" s="6">
-        <v>-3.4</v>
+      <c r="D7" s="6">
+        <v>2.1</v>
+      </c>
+      <c r="E7" s="7">
+        <v>5.29</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
+        <v>-5.12</v>
+      </c>
+      <c r="D8" s="6">
         <v>-4.03</v>
       </c>
-      <c r="D8" s="5">
-        <v>-5.12</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-1.09</v>
+      <c r="E8" s="7">
+        <v>1.09</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>4.29</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>2.84</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.45</v>
+      <c r="D9" s="6">
+        <v>4.22</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.38</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>9.9</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>9.199999999999999</v>
       </c>
-      <c r="E10" s="6">
-        <v>-0.7</v>
+      <c r="D10" s="6">
+        <v>8.41</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>4.52</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>4.3</v>
       </c>
-      <c r="E11" s="6">
-        <v>-0.22</v>
+      <c r="D11" s="6">
+        <v>3.62</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>2.75</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-1.18</v>
       </c>
-      <c r="E12" s="6">
-        <v>-3.93</v>
+      <c r="D12" s="6">
+        <v>-3.39</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>0.39</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-3.28</v>
       </c>
-      <c r="E13" s="6">
+      <c r="D13" s="6">
+        <v>-0.98</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-5.32</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-2.67</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-3.64</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.32</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-4.71</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.49</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-1.14</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1.32</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
         <v>-3.67</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-1.57</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4.22</v>
+      </c>
+      <c r="D19" s="6">
+        <v>3.85</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-3.22</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-1.6</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-1.68</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-4.94</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-3.39</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-5.32</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-3.71</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-1.12</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-1.26</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-3.64</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>46.83</v>
+      </c>
+      <c r="D23" s="6">
+        <v>49.82</v>
+      </c>
+      <c r="E23" s="7">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-27.06</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-27</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>19.09</v>
+      </c>
+      <c r="D25" s="6">
+        <v>19.35</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>48.32</v>
+      </c>
+      <c r="D26" s="6">
+        <v>48.13</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>121.23</v>
+      </c>
+      <c r="D27" s="6">
+        <v>128.13</v>
+      </c>
+      <c r="E27" s="7">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>121.13</v>
+      </c>
+      <c r="D28" s="6">
+        <v>116.3</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-4.83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-15.14</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-13.08</v>
+      </c>
+      <c r="E29" s="7">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-7.67</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-6.02</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>13.34</v>
+      </c>
+      <c r="D31" s="6">
+        <v>14.47</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-18.41</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-18.71</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>3.66</v>
+      </c>
+      <c r="D33" s="6">
+        <v>4.59</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-5.49</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-7.15</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="D35" s="6">
+        <v>2.18</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-5.71</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-10.36</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-4.65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-5.24</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-7.02</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-0.21</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-6.76</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-3.7</v>
+      </c>
+      <c r="E39" s="7">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-41.73</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-41.43</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-3.27</v>
+      </c>
+      <c r="D41" s="6">
         <v>-2.38</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="E41" s="7">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-10.42</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-6.26</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-6.53</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-15.8</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-16.09</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-26.12</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-25.82</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-12.27</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-11.32</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>396</v>
+      </c>
+      <c r="D47" s="6">
+        <v>409</v>
+      </c>
+      <c r="E47" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-6.24</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-4.71</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>54.47</v>
+      </c>
+      <c r="D48" s="6">
+        <v>54.75</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-1.31</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-1.14</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>3270</v>
+      </c>
+      <c r="D49" s="6">
+        <v>3300</v>
+      </c>
+      <c r="E49" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-0.71</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-3.67</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-2.96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>1038.95</v>
+      </c>
+      <c r="D50" s="6">
+        <v>1029.85</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="D19" s="5">
-        <v>4.22</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-5.32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>14.07</v>
+      </c>
+      <c r="D51" s="6">
+        <v>14.03</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-3.24</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-3.22</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>11.72</v>
+      </c>
+      <c r="D52" s="6">
+        <v>11.68</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-0.1</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-1.68</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>4291.8</v>
+      </c>
+      <c r="D53" s="6">
+        <v>4309.5</v>
+      </c>
+      <c r="E53" s="7">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-2.39</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-3.71</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>11450</v>
+      </c>
+      <c r="D54" s="6">
+        <v>11575</v>
+      </c>
+      <c r="E54" s="7">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>49.97</v>
-      </c>
-      <c r="D23" s="5">
-        <v>46.83</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-3.14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>45.65</v>
+      </c>
+      <c r="D55" s="6">
+        <v>53.89</v>
+      </c>
+      <c r="E55" s="7">
+        <v>8.24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-25.74</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-27.06</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>34.35</v>
+      </c>
+      <c r="D56" s="6">
+        <v>35.76</v>
+      </c>
+      <c r="E56" s="7">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>19.64</v>
-      </c>
-      <c r="D25" s="5">
-        <v>19.09</v>
-      </c>
-      <c r="E25" s="6">
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>55.95</v>
+      </c>
+      <c r="D57" s="6">
+        <v>58.59</v>
+      </c>
+      <c r="E57" s="7">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>56.57</v>
+      </c>
+      <c r="D58" s="6">
+        <v>53.91</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>60.87</v>
+      </c>
+      <c r="D59" s="6">
+        <v>59.99</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>46.32</v>
+      </c>
+      <c r="D60" s="6">
+        <v>45.77</v>
+      </c>
+      <c r="E60" s="8">
         <v>-0.55</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>42.85</v>
+      </c>
+      <c r="D61" s="6">
+        <v>44.33</v>
+      </c>
+      <c r="E61" s="7">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>38.16</v>
+      </c>
+      <c r="D62" s="6">
+        <v>43.45</v>
+      </c>
+      <c r="E62" s="7">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>7.47</v>
+      </c>
+      <c r="D63" s="6">
+        <v>39.71</v>
+      </c>
+      <c r="E63" s="7">
+        <v>32.24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-65.09</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-65.25</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>24.04</v>
+      </c>
+      <c r="D65" s="6">
+        <v>47.08</v>
+      </c>
+      <c r="E65" s="7">
+        <v>23.04</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>56.15</v>
-      </c>
-      <c r="D26" s="5">
-        <v>48.32</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-7.83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>-57.71</v>
+      </c>
+      <c r="D66" s="6">
+        <v>-11.61</v>
+      </c>
+      <c r="E66" s="7">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>118.24</v>
-      </c>
-      <c r="D27" s="5">
-        <v>121.23</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>-18.16</v>
+      </c>
+      <c r="D67" s="6">
+        <v>-41.48</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-23.32</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>129.81</v>
-      </c>
-      <c r="D28" s="5">
-        <v>121.13</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-8.68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>4.79</v>
+      </c>
+      <c r="D68" s="6">
+        <v>-62.14</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-66.93000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-10.03</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-15.14</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-5.11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>59.1</v>
+      </c>
+      <c r="D69" s="6">
+        <v>-63.55</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-122.65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-7.63</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-7.67</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>13.85</v>
-      </c>
-      <c r="D31" s="5">
-        <v>13.34</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-12.09</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-18.41</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-6.32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>10.35</v>
-      </c>
-      <c r="D33" s="5">
-        <v>3.66</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-6.69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-4.04</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-5.49</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>3.98</v>
-      </c>
-      <c r="D35" s="5">
-        <v>3.3</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>0.93</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-5.71</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-6.64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-1.17</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-5.24</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-4.07</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>0.79</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-0.21</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-5.34</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-6.76</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-41.2</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-41.73</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-3.01</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-3.27</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-9.4</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-5.93</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-6.26</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-14.15</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-15.8</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-24.51</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-26.12</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-11.9</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-12.27</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>402</v>
-      </c>
-      <c r="D47" s="5">
-        <v>396</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>54.97</v>
-      </c>
-      <c r="D48" s="5">
-        <v>54.47</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>3278.7</v>
-      </c>
-      <c r="D49" s="5">
-        <v>3270</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-8.699999999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>1041.6</v>
-      </c>
-      <c r="D50" s="5">
-        <v>1038.95</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-2.65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>14.12</v>
-      </c>
-      <c r="D51" s="5">
-        <v>14.07</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>11.95</v>
-      </c>
-      <c r="D52" s="5">
-        <v>11.72</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>4385.7</v>
-      </c>
-      <c r="D53" s="5">
-        <v>4291.8</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-93.90000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>11499</v>
-      </c>
-      <c r="D54" s="5">
-        <v>11450</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-49</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="5">
-        <v>87</v>
-      </c>
-      <c r="D55" s="5">
-        <v>99</v>
-      </c>
-      <c r="E55" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="5">
-        <v>99</v>
-      </c>
-      <c r="D56" s="5">
-        <v>87</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>49.44</v>
-      </c>
-      <c r="D57" s="5">
-        <v>45.65</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-3.79</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>35.65</v>
-      </c>
-      <c r="D58" s="5">
-        <v>34.35</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>56.93</v>
-      </c>
-      <c r="D59" s="5">
-        <v>55.95</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>57.34</v>
-      </c>
-      <c r="D60" s="5">
-        <v>56.57</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>61.92</v>
-      </c>
-      <c r="D61" s="5">
-        <v>60.87</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>49.49</v>
-      </c>
-      <c r="D62" s="5">
-        <v>46.32</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-3.17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>49.33</v>
-      </c>
-      <c r="D63" s="5">
-        <v>42.85</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-6.48</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>39.51</v>
-      </c>
-      <c r="D64" s="5">
-        <v>38.16</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="3" t="s">
+      <c r="B70" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C65" s="5">
-        <v>14.49</v>
-      </c>
-      <c r="D65" s="5">
-        <v>7.47</v>
-      </c>
-      <c r="E65" s="6">
-        <v>-7.02</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-62.35</v>
-      </c>
-      <c r="D66" s="5">
-        <v>-65.09</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>104.23</v>
-      </c>
-      <c r="D67" s="5">
-        <v>24.04</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-80.19</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>-50.43</v>
-      </c>
-      <c r="D68" s="5">
-        <v>-57.71</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-7.28</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
-        <v>122.81</v>
-      </c>
-      <c r="D69" s="5">
-        <v>-18.16</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-140.97</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="5">
-        <v>-67.23999999999999</v>
-      </c>
-      <c r="D70" s="5">
-        <v>4.79</v>
-      </c>
-      <c r="E70" s="7">
-        <v>72.03</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="5">
-        <v>-10.19</v>
-      </c>
-      <c r="D71" s="5">
-        <v>59.1</v>
-      </c>
-      <c r="E71" s="7">
-        <v>69.29000000000001</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>-27.26</v>
-      </c>
-      <c r="D72" s="5">
+      <c r="C70" s="6">
         <v>-9.210000000000001</v>
       </c>
-      <c r="E72" s="7">
-        <v>18.05</v>
+      <c r="D70" s="6">
+        <v>-15.99</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-6.78</v>
       </c>
     </row>
   </sheetData>
@@ -3127,60 +3156,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="11">
+        <v>56.44</v>
+      </c>
+      <c r="C2" s="12">
+        <v>8</v>
+      </c>
+      <c r="D2" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.44</v>
-      </c>
-      <c r="C2" s="11">
-        <v>8</v>
-      </c>
-      <c r="D2" s="10">
-        <v>47.6</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-0.2</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-1.8</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-2.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>50</v>
       </c>
     </row>
@@ -3282,55 +3311,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.2952</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2153</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1949</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.188</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1766</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0935</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2292</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.298</v>
+      <c r="A2" s="14">
+        <v>0.3034</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.213</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1958</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1872</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1787</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0958</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2283</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.2983</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,34 +175,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>45.6 → 53.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.6</t>
-  </si>
-  <si>
-    <t>53.9</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -288,14 +261,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -328,13 +301,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,15 +377,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -786,8 +758,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -927,10 +900,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>409</v>
+        <v>412.9</v>
       </c>
       <c r="D2">
-        <v>3.28</v>
+        <v>-0.02</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -939,46 +912,46 @@
         <v>274.85</v>
       </c>
       <c r="G2">
-        <v>-3.7</v>
+        <v>-2.78</v>
       </c>
       <c r="H2">
-        <v>48.81</v>
+        <v>50.23</v>
       </c>
       <c r="I2">
-        <v>0.32</v>
+        <v>3.56</v>
       </c>
       <c r="J2">
-        <v>2.1</v>
+        <v>4.84</v>
       </c>
       <c r="K2">
-        <v>14.47</v>
+        <v>13.73</v>
       </c>
       <c r="L2">
-        <v>49.82</v>
+        <v>43.69</v>
       </c>
       <c r="M2">
-        <v>30.34</v>
+        <v>32.38</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P2">
-        <v>401.34</v>
+        <v>406.58</v>
       </c>
       <c r="Q2">
-        <v>406.02</v>
+        <v>407.6</v>
       </c>
       <c r="R2">
-        <v>396.48</v>
+        <v>399.1</v>
       </c>
       <c r="S2">
-        <v>356.64</v>
+        <v>357.45</v>
       </c>
       <c r="T2">
-        <v>14.68</v>
+        <v>15.51</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -993,34 +966,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>53.89</v>
+        <v>56.03</v>
       </c>
       <c r="Z2">
-        <v>1.91</v>
+        <v>2.76</v>
       </c>
       <c r="AA2">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="AB2">
-        <v>-1.84</v>
+        <v>-0.57</v>
       </c>
       <c r="AC2">
-        <v>18.77</v>
+        <v>53.02</v>
       </c>
       <c r="AD2">
-        <v>9.109999999999999</v>
+        <v>35.2</v>
       </c>
       <c r="AE2">
-        <v>10.44</v>
+        <v>9.9</v>
       </c>
       <c r="AF2">
-        <v>39.71</v>
+        <v>-46.05</v>
       </c>
       <c r="AG2">
-        <v>426.39</v>
+        <v>427.27</v>
       </c>
       <c r="AH2">
-        <v>385.65</v>
+        <v>387.93</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1029,7 +1002,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>20.25</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1040,10 +1013,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>54.75</v>
+        <v>53.95</v>
       </c>
       <c r="D3">
-        <v>0.51</v>
+        <v>-0.74</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1052,25 +1025,25 @@
         <v>53.89</v>
       </c>
       <c r="G3">
-        <v>-41.43</v>
+        <v>-42.29</v>
       </c>
       <c r="H3">
-        <v>1.6</v>
+        <v>0.11</v>
       </c>
       <c r="I3">
-        <v>-3.49</v>
+        <v>-3.63</v>
       </c>
       <c r="J3">
-        <v>-4.03</v>
+        <v>-4.09</v>
       </c>
       <c r="K3">
-        <v>-18.71</v>
+        <v>-16.83</v>
       </c>
       <c r="L3">
-        <v>-27</v>
+        <v>-30.1</v>
       </c>
       <c r="M3">
-        <v>-22.83</v>
+        <v>-22.91</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1079,19 +1052,19 @@
         <v>12</v>
       </c>
       <c r="P3">
-        <v>55.23</v>
+        <v>54.5</v>
       </c>
       <c r="Q3">
-        <v>58.45</v>
+        <v>58.2</v>
       </c>
       <c r="R3">
-        <v>59.14</v>
+        <v>58.94</v>
       </c>
       <c r="S3">
-        <v>66.23</v>
+        <v>65.92</v>
       </c>
       <c r="T3">
-        <v>-17.33</v>
+        <v>-18.16</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1106,43 +1079,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>35.76</v>
+        <v>33.46</v>
       </c>
       <c r="Z3">
-        <v>-1.15</v>
+        <v>-1.39</v>
       </c>
       <c r="AA3">
-        <v>-0.55</v>
+        <v>-0.83</v>
       </c>
       <c r="AB3">
-        <v>-0.61</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AC3">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AD3">
-        <v>0.54</v>
+        <v>1.82</v>
       </c>
       <c r="AE3">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AF3">
-        <v>-65.25</v>
+        <v>-61.24</v>
       </c>
       <c r="AG3">
-        <v>64.28</v>
+        <v>64.53</v>
       </c>
       <c r="AH3">
-        <v>52.63</v>
+        <v>51.88</v>
       </c>
       <c r="AI3">
-        <v>60.65</v>
+        <v>59.99</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>41.32</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,10 +1126,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3300</v>
+        <v>3288</v>
       </c>
       <c r="D4">
-        <v>0.92</v>
+        <v>-0.6</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1165,46 +1138,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.38</v>
+        <v>-2.74</v>
       </c>
       <c r="H4">
-        <v>30.38</v>
+        <v>29.9</v>
       </c>
       <c r="I4">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="J4">
-        <v>4.22</v>
+        <v>6.43</v>
       </c>
       <c r="K4">
-        <v>4.59</v>
+        <v>3.89</v>
       </c>
       <c r="L4">
-        <v>19.35</v>
+        <v>16.25</v>
       </c>
       <c r="M4">
-        <v>17.87</v>
+        <v>18.18</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P4">
-        <v>3269.58</v>
+        <v>3288.94</v>
       </c>
       <c r="Q4">
-        <v>3220.85</v>
+        <v>3240.56</v>
       </c>
       <c r="R4">
-        <v>3173.6</v>
+        <v>3181.62</v>
       </c>
       <c r="S4">
-        <v>2908.27</v>
+        <v>2912.34</v>
       </c>
       <c r="T4">
-        <v>13.47</v>
+        <v>12.9</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1219,34 +1192,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>58.59</v>
+        <v>56.71</v>
       </c>
       <c r="Z4">
-        <v>39.57</v>
+        <v>38.83</v>
       </c>
       <c r="AA4">
-        <v>37.99</v>
+        <v>38.53</v>
       </c>
       <c r="AB4">
-        <v>1.58</v>
+        <v>0.3</v>
       </c>
       <c r="AC4">
-        <v>46.91</v>
+        <v>38.65</v>
       </c>
       <c r="AD4">
-        <v>43.99</v>
+        <v>44.39</v>
       </c>
       <c r="AE4">
-        <v>73.69</v>
+        <v>72.97</v>
       </c>
       <c r="AF4">
-        <v>47.08</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="AG4">
-        <v>3402.45</v>
+        <v>3407.23</v>
       </c>
       <c r="AH4">
-        <v>3039.25</v>
+        <v>3073.89</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1255,7 +1228,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>32.83</v>
+        <v>33.94</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,10 +1239,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1029.85</v>
+        <v>1058.5</v>
       </c>
       <c r="D5">
-        <v>-0.88</v>
+        <v>2.37</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1278,46 +1251,46 @@
         <v>700.85</v>
       </c>
       <c r="G5">
-        <v>-10.42</v>
+        <v>-7.93</v>
       </c>
       <c r="H5">
-        <v>46.94</v>
+        <v>51.03</v>
       </c>
       <c r="I5">
-        <v>-1.57</v>
+        <v>0.82</v>
       </c>
       <c r="J5">
-        <v>8.41</v>
+        <v>12.27</v>
       </c>
       <c r="K5">
-        <v>-7.15</v>
+        <v>-4.1</v>
       </c>
       <c r="L5">
-        <v>48.13</v>
+        <v>49.78</v>
       </c>
       <c r="M5">
-        <v>21.3</v>
+        <v>20.95</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="P5">
-        <v>1037.96</v>
+        <v>1040.58</v>
       </c>
       <c r="Q5">
-        <v>1014.55</v>
+        <v>1024.77</v>
       </c>
       <c r="R5">
-        <v>990.21</v>
+        <v>991.14</v>
       </c>
       <c r="S5">
-        <v>953.3200000000001</v>
+        <v>955.39</v>
       </c>
       <c r="T5">
-        <v>8.029999999999999</v>
+        <v>10.79</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1332,34 +1305,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>53.91</v>
+        <v>60.61</v>
       </c>
       <c r="Z5">
-        <v>16.91</v>
+        <v>16.54</v>
       </c>
       <c r="AA5">
-        <v>16.21</v>
+        <v>16.2</v>
       </c>
       <c r="AB5">
-        <v>0.7</v>
+        <v>0.34</v>
       </c>
       <c r="AC5">
-        <v>19.14</v>
+        <v>14.99</v>
       </c>
       <c r="AD5">
-        <v>34.01</v>
+        <v>14.73</v>
       </c>
       <c r="AE5">
-        <v>24.84</v>
+        <v>24.22</v>
       </c>
       <c r="AF5">
-        <v>-11.61</v>
+        <v>-15.63</v>
       </c>
       <c r="AG5">
-        <v>1102.16</v>
+        <v>1099.79</v>
       </c>
       <c r="AH5">
-        <v>926.9400000000001</v>
+        <v>949.75</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1368,7 +1341,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>38.21</v>
+        <v>32.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1379,58 +1352,58 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.03</v>
+        <v>14.07</v>
       </c>
       <c r="D6">
-        <v>-0.28</v>
+        <v>0.93</v>
       </c>
       <c r="E6">
         <v>15.01</v>
       </c>
       <c r="F6">
-        <v>6.46</v>
+        <v>6.49</v>
       </c>
       <c r="G6">
-        <v>-6.53</v>
+        <v>-6.26</v>
       </c>
       <c r="H6">
-        <v>117.18</v>
+        <v>116.8</v>
       </c>
       <c r="I6">
-        <v>3.85</v>
+        <v>2.63</v>
       </c>
       <c r="J6">
-        <v>3.62</v>
+        <v>7.16</v>
       </c>
       <c r="K6">
-        <v>2.18</v>
+        <v>-0.5</v>
       </c>
       <c r="L6">
-        <v>128.13</v>
+        <v>113.83</v>
       </c>
       <c r="M6">
-        <v>18.72</v>
+        <v>17.62</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P6">
-        <v>14.01</v>
+        <v>14.05</v>
       </c>
       <c r="Q6">
-        <v>13.24</v>
+        <v>13.33</v>
       </c>
       <c r="R6">
-        <v>13.82</v>
+        <v>13.8</v>
       </c>
       <c r="S6">
-        <v>11.65</v>
+        <v>11.7</v>
       </c>
       <c r="T6">
-        <v>20.42</v>
+        <v>20.3</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1445,43 +1418,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>59.99</v>
+        <v>60.06</v>
       </c>
       <c r="Z6">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="AA6">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="AB6">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="AC6">
-        <v>87.78</v>
+        <v>83.11</v>
       </c>
       <c r="AD6">
-        <v>86.65000000000001</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="AE6">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="AF6">
-        <v>-41.48</v>
+        <v>-39.93</v>
       </c>
       <c r="AG6">
-        <v>14.26</v>
+        <v>14.44</v>
       </c>
       <c r="AH6">
         <v>12.23</v>
       </c>
       <c r="AI6">
-        <v>12.79</v>
+        <v>12.89</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>55.18</v>
+        <v>57.01</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1492,10 +1465,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.68</v>
+        <v>11.35</v>
       </c>
       <c r="D7">
-        <v>-0.34</v>
+        <v>-1.3</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1504,25 +1477,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-16.09</v>
+        <v>-18.46</v>
       </c>
       <c r="H7">
-        <v>149.04</v>
+        <v>142</v>
       </c>
       <c r="I7">
-        <v>-1.6</v>
+        <v>-2.99</v>
       </c>
       <c r="J7">
-        <v>-3.39</v>
+        <v>-3.16</v>
       </c>
       <c r="K7">
-        <v>-10.36</v>
+        <v>-12.29</v>
       </c>
       <c r="L7">
-        <v>116.3</v>
+        <v>114.15</v>
       </c>
       <c r="M7">
-        <v>-29.83</v>
+        <v>-29.78</v>
       </c>
       <c r="N7">
         <v>87</v>
@@ -1531,19 +1504,19 @@
         <v>91</v>
       </c>
       <c r="P7">
-        <v>11.75</v>
+        <v>11.64</v>
       </c>
       <c r="Q7">
-        <v>12.17</v>
+        <v>12.15</v>
       </c>
       <c r="R7">
-        <v>11.63</v>
+        <v>11.66</v>
       </c>
       <c r="S7">
-        <v>9.98</v>
+        <v>10.05</v>
       </c>
       <c r="T7">
-        <v>17.01</v>
+        <v>12.99</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1558,43 +1531,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>45.77</v>
+        <v>41.27</v>
       </c>
       <c r="Z7">
+        <v>-0.04</v>
+      </c>
+      <c r="AA7">
+        <v>0.11</v>
+      </c>
+      <c r="AB7">
+        <v>-0.15</v>
+      </c>
+      <c r="AC7">
         <v>0.04</v>
       </c>
-      <c r="AA7">
-        <v>0.18</v>
-      </c>
-      <c r="AB7">
-        <v>-0.13</v>
-      </c>
-      <c r="AC7">
-        <v>5.61</v>
-      </c>
       <c r="AD7">
-        <v>5.64</v>
+        <v>2.14</v>
       </c>
       <c r="AE7">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="AF7">
-        <v>-62.14</v>
+        <v>-78.87</v>
       </c>
       <c r="AG7">
-        <v>13.55</v>
+        <v>13.57</v>
       </c>
       <c r="AH7">
-        <v>10.78</v>
+        <v>10.74</v>
       </c>
       <c r="AI7">
-        <v>12.69</v>
+        <v>12.4</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>31.15</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1605,10 +1578,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4309.5</v>
+        <v>4362.1</v>
       </c>
       <c r="D8">
-        <v>0.41</v>
+        <v>0.12</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1617,46 +1590,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-25.82</v>
+        <v>-24.91</v>
       </c>
       <c r="H8">
-        <v>3.72</v>
+        <v>4.98</v>
       </c>
       <c r="I8">
-        <v>-4.94</v>
+        <v>-4.07</v>
       </c>
       <c r="J8">
-        <v>-0.98</v>
+        <v>1.18</v>
       </c>
       <c r="K8">
-        <v>-7.02</v>
+        <v>-5.88</v>
       </c>
       <c r="L8">
-        <v>-13.08</v>
+        <v>-14.69</v>
       </c>
       <c r="M8">
-        <v>19.58</v>
+        <v>20.14</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P8">
-        <v>4416.2</v>
+        <v>4341.2</v>
       </c>
       <c r="Q8">
-        <v>4363.79</v>
+        <v>4366.91</v>
       </c>
       <c r="R8">
-        <v>4374.41</v>
+        <v>4378.86</v>
       </c>
       <c r="S8">
-        <v>4677.63</v>
+        <v>4668.89</v>
       </c>
       <c r="T8">
-        <v>-7.87</v>
+        <v>-6.57</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1671,34 +1644,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>44.33</v>
+        <v>48.64</v>
       </c>
       <c r="Z8">
-        <v>5.81</v>
+        <v>1.15</v>
       </c>
       <c r="AA8">
-        <v>9.1</v>
+        <v>6.53</v>
       </c>
       <c r="AB8">
-        <v>-3.29</v>
+        <v>-5.38</v>
       </c>
       <c r="AC8">
-        <v>9.359999999999999</v>
+        <v>18.99</v>
       </c>
       <c r="AD8">
-        <v>41.21</v>
+        <v>12.88</v>
       </c>
       <c r="AE8">
-        <v>104.17</v>
+        <v>101.5</v>
       </c>
       <c r="AF8">
-        <v>-63.55</v>
+        <v>-59.94</v>
       </c>
       <c r="AG8">
-        <v>4533.12</v>
+        <v>4534.22</v>
       </c>
       <c r="AH8">
-        <v>4194.47</v>
+        <v>4199.61</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1707,7 +1680,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>26.57</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1718,10 +1691,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11575</v>
+        <v>11504</v>
       </c>
       <c r="D9">
-        <v>1.09</v>
+        <v>-0.57</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1730,46 +1703,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-11.32</v>
+        <v>-11.86</v>
       </c>
       <c r="H9">
-        <v>11.71</v>
+        <v>11.02</v>
       </c>
       <c r="I9">
-        <v>-1.12</v>
+        <v>-0.99</v>
       </c>
       <c r="J9">
-        <v>-2.67</v>
+        <v>-2.89</v>
       </c>
       <c r="K9">
-        <v>0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="L9">
-        <v>-6.02</v>
+        <v>-10.57</v>
       </c>
       <c r="M9">
-        <v>9.58</v>
+        <v>9.56</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="P9">
-        <v>11552.4</v>
+        <v>11519.6</v>
       </c>
       <c r="Q9">
-        <v>11854.1</v>
+        <v>11821.45</v>
       </c>
       <c r="R9">
-        <v>11661.22</v>
+        <v>11683.76</v>
       </c>
       <c r="S9">
-        <v>11785.08</v>
+        <v>11781.6</v>
       </c>
       <c r="T9">
-        <v>-1.78</v>
+        <v>-2.36</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1784,34 +1757,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>43.45</v>
+        <v>41.14</v>
       </c>
       <c r="Z9">
-        <v>-47.27</v>
+        <v>-65.06999999999999</v>
       </c>
       <c r="AA9">
-        <v>24.28</v>
+        <v>-6.22</v>
       </c>
       <c r="AB9">
-        <v>-71.55</v>
+        <v>-58.85</v>
       </c>
       <c r="AC9">
-        <v>6.85</v>
+        <v>17.36</v>
       </c>
       <c r="AD9">
-        <v>2.28</v>
+        <v>12.57</v>
       </c>
       <c r="AE9">
-        <v>203.64</v>
+        <v>190.53</v>
       </c>
       <c r="AF9">
-        <v>-15.99</v>
+        <v>27.82</v>
       </c>
       <c r="AG9">
-        <v>12283.95</v>
+        <v>12293.59</v>
       </c>
       <c r="AH9">
-        <v>11424.25</v>
+        <v>11349.31</v>
       </c>
       <c r="AI9">
         <v>12054.41</v>
@@ -1820,7 +1793,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>30.02</v>
+        <v>28.37</v>
       </c>
     </row>
   </sheetData>
@@ -1981,47 +1954,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2029,1108 +1967,1108 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>65</v>
+      <c r="B6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-3.19</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
+        <v>5.29</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4.84</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-4.09</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>6.26</v>
+      </c>
+      <c r="D9" s="5">
+        <v>6.43</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D10" s="5">
+        <v>12.27</v>
+      </c>
+      <c r="E10" s="7">
+        <v>4.07</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>5.61</v>
+      </c>
+      <c r="D11" s="5">
+        <v>7.16</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-3.77</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-3.16</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1.18</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-2.84</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-2.89</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2.99</v>
+      </c>
+      <c r="D15" s="5">
+        <v>3.56</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-2.91</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.63</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1.83</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1.15</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0.82</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-1.2</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2.63</v>
+      </c>
+      <c r="E19" s="7">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-1.71</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-2.99</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-4.18</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-4.07</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-0.42</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-0.99</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>45.86</v>
+      </c>
+      <c r="D23" s="5">
+        <v>43.69</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-28.92</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-30.1</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>16.24</v>
+      </c>
+      <c r="D25" s="5">
+        <v>16.25</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>44.79</v>
+      </c>
+      <c r="D26" s="5">
+        <v>49.78</v>
+      </c>
+      <c r="E26" s="7">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>115.79</v>
+      </c>
+      <c r="D27" s="5">
+        <v>113.83</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>117.39</v>
+      </c>
+      <c r="D28" s="5">
+        <v>114.15</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-3.24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-13.41</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-14.69</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-10.57</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>13.57</v>
+      </c>
+      <c r="D31" s="5">
+        <v>13.73</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-19.31</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-16.83</v>
+      </c>
+      <c r="E32" s="7">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="D33" s="5">
+        <v>3.89</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-5.97</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-4.1</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-0.71</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-13.01</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-12.29</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-5.61</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-5.88</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-1.33</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-1.02</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-2.75</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-2.78</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-41.86</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-42.29</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-2.14</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-2.74</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-10.06</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-7.93</v>
+      </c>
+      <c r="E42" s="7">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-7.13</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-6.26</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-17.39</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-18.46</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-25</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-24.91</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-11.35</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-11.86</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>413</v>
+      </c>
+      <c r="D47" s="5">
+        <v>412.9</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>54.35</v>
+      </c>
+      <c r="D48" s="5">
+        <v>53.95</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>3308</v>
+      </c>
+      <c r="D49" s="5">
+        <v>3288</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>1034</v>
+      </c>
+      <c r="D50" s="5">
+        <v>1058.5</v>
+      </c>
+      <c r="E50" s="7">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>13.94</v>
+      </c>
+      <c r="D51" s="5">
+        <v>14.07</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>11.5</v>
+      </c>
+      <c r="D52" s="5">
+        <v>11.35</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>4356.9</v>
+      </c>
+      <c r="D53" s="5">
+        <v>4362.1</v>
+      </c>
+      <c r="E53" s="7">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>11570</v>
+      </c>
+      <c r="D54" s="5">
+        <v>11504</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>56.1</v>
+      </c>
+      <c r="D55" s="5">
+        <v>56.03</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>34.61</v>
+      </c>
+      <c r="D56" s="5">
+        <v>33.46</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>59.28</v>
+      </c>
+      <c r="D57" s="5">
+        <v>56.71</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>54.95</v>
+      </c>
+      <c r="D58" s="5">
+        <v>60.61</v>
+      </c>
+      <c r="E58" s="7">
+        <v>5.66</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>57.96</v>
+      </c>
+      <c r="D59" s="5">
+        <v>60.06</v>
+      </c>
+      <c r="E59" s="7">
         <v>2.1</v>
       </c>
-      <c r="E7" s="7">
-        <v>5.29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="5">
+        <v>43.28</v>
+      </c>
+      <c r="D60" s="5">
+        <v>41.27</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>48.21</v>
+      </c>
+      <c r="D61" s="5">
+        <v>48.64</v>
+      </c>
+      <c r="E61" s="7">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>43.29</v>
+      </c>
+      <c r="D62" s="5">
+        <v>41.14</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-2.15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-7.09</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-46.05</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-38.96</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-5.12</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-4.03</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>-59.35</v>
+      </c>
+      <c r="D64" s="5">
+        <v>-61.24</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>2.84</v>
-      </c>
-      <c r="D9" s="6">
-        <v>4.22</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>74.19</v>
+      </c>
+      <c r="D65" s="5">
+        <v>80.45999999999999</v>
+      </c>
+      <c r="E65" s="7">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D10" s="6">
-        <v>8.41</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5">
+        <v>-46.06</v>
+      </c>
+      <c r="D66" s="5">
+        <v>-15.63</v>
+      </c>
+      <c r="E66" s="7">
+        <v>30.43</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>4.3</v>
-      </c>
-      <c r="D11" s="6">
-        <v>3.62</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="5">
+        <v>-51.08</v>
+      </c>
+      <c r="D67" s="5">
+        <v>-39.93</v>
+      </c>
+      <c r="E67" s="7">
+        <v>11.15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-1.18</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-3.39</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="5">
+        <v>-64.34</v>
+      </c>
+      <c r="D68" s="5">
+        <v>-78.87</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-14.53</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-3.28</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-0.98</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="5">
+        <v>-23.7</v>
+      </c>
+      <c r="D69" s="5">
+        <v>-59.94</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-36.24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-5.32</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-2.67</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-3.64</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0.32</v>
-      </c>
-      <c r="E15" s="7">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-4.71</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.49</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1.32</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-3.67</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.57</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>4.22</v>
-      </c>
-      <c r="D19" s="6">
-        <v>3.85</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-3.22</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-1.6</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-1.68</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-4.94</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-3.71</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-1.12</v>
-      </c>
-      <c r="E22" s="7">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>46.83</v>
-      </c>
-      <c r="D23" s="6">
-        <v>49.82</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-27.06</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-27</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>19.09</v>
-      </c>
-      <c r="D25" s="6">
-        <v>19.35</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>48.32</v>
-      </c>
-      <c r="D26" s="6">
-        <v>48.13</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>121.23</v>
-      </c>
-      <c r="D27" s="6">
-        <v>128.13</v>
-      </c>
-      <c r="E27" s="7">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>121.13</v>
-      </c>
-      <c r="D28" s="6">
-        <v>116.3</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-4.83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-15.14</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-13.08</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-7.67</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-6.02</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>13.34</v>
-      </c>
-      <c r="D31" s="6">
-        <v>14.47</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-18.41</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-18.71</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>3.66</v>
-      </c>
-      <c r="D33" s="6">
-        <v>4.59</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-5.49</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-7.15</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>3.3</v>
-      </c>
-      <c r="D35" s="6">
-        <v>2.18</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-5.71</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-10.36</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-4.65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-5.24</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-7.02</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-0.21</v>
-      </c>
-      <c r="D38" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-6.76</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-3.7</v>
-      </c>
-      <c r="E39" s="7">
-        <v>3.06</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-41.73</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-41.43</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-3.27</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-2.38</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-10.42</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-6.26</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-6.53</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-15.8</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-16.09</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-26.12</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-25.82</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-12.27</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-11.32</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>396</v>
-      </c>
-      <c r="D47" s="6">
-        <v>409</v>
-      </c>
-      <c r="E47" s="7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>54.47</v>
-      </c>
-      <c r="D48" s="6">
-        <v>54.75</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>3270</v>
-      </c>
-      <c r="D49" s="6">
-        <v>3300</v>
-      </c>
-      <c r="E49" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>1038.95</v>
-      </c>
-      <c r="D50" s="6">
-        <v>1029.85</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-9.1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>14.07</v>
-      </c>
-      <c r="D51" s="6">
-        <v>14.03</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>11.72</v>
-      </c>
-      <c r="D52" s="6">
-        <v>11.68</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>4291.8</v>
-      </c>
-      <c r="D53" s="6">
-        <v>4309.5</v>
-      </c>
-      <c r="E53" s="7">
-        <v>17.7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>11450</v>
-      </c>
-      <c r="D54" s="6">
-        <v>11575</v>
-      </c>
-      <c r="E54" s="7">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>45.65</v>
-      </c>
-      <c r="D55" s="6">
-        <v>53.89</v>
-      </c>
-      <c r="E55" s="7">
-        <v>8.24</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>34.35</v>
-      </c>
-      <c r="D56" s="6">
-        <v>35.76</v>
-      </c>
-      <c r="E56" s="7">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>55.95</v>
-      </c>
-      <c r="D57" s="6">
-        <v>58.59</v>
-      </c>
-      <c r="E57" s="7">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>56.57</v>
-      </c>
-      <c r="D58" s="6">
-        <v>53.91</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>60.87</v>
-      </c>
-      <c r="D59" s="6">
-        <v>59.99</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>46.32</v>
-      </c>
-      <c r="D60" s="6">
-        <v>45.77</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>42.85</v>
-      </c>
-      <c r="D61" s="6">
-        <v>44.33</v>
-      </c>
-      <c r="E61" s="7">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>38.16</v>
-      </c>
-      <c r="D62" s="6">
-        <v>43.45</v>
-      </c>
-      <c r="E62" s="7">
-        <v>5.29</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
+      <c r="B70" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="6">
-        <v>7.47</v>
-      </c>
-      <c r="D63" s="6">
-        <v>39.71</v>
-      </c>
-      <c r="E63" s="7">
-        <v>32.24</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-65.09</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-65.25</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>24.04</v>
-      </c>
-      <c r="D65" s="6">
-        <v>47.08</v>
-      </c>
-      <c r="E65" s="7">
-        <v>23.04</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>-57.71</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-11.61</v>
-      </c>
-      <c r="E66" s="7">
-        <v>46.1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>-18.16</v>
-      </c>
-      <c r="D67" s="6">
-        <v>-41.48</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-23.32</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>4.79</v>
-      </c>
-      <c r="D68" s="6">
-        <v>-62.14</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-66.93000000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>59.1</v>
-      </c>
-      <c r="D69" s="6">
-        <v>-63.55</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-122.65</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-15.99</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-6.78</v>
+      <c r="C70" s="5">
+        <v>-45.71</v>
+      </c>
+      <c r="D70" s="5">
+        <v>27.82</v>
+      </c>
+      <c r="E70" s="7">
+        <v>73.53</v>
       </c>
     </row>
   </sheetData>
@@ -3156,60 +3094,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>73</v>
+      <c r="B1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>56.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>49.5</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>49.7</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>0.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-2.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-2.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>50</v>
       </c>
     </row>
@@ -3311,55 +3249,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.3034</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.213</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1958</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1872</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1787</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0958</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2283</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.2983</v>
+      <c r="A2" s="13">
+        <v>0.3238</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2095</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.2014</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1818</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1762</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0956</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2291</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.2978</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="84">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,7 +175,64 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-6.3% → 0.0%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-6.3%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.6 → 51.4</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.6</t>
+  </si>
+  <si>
+    <t>51.4</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>60.1 → 72.7</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>60.1</t>
+  </si>
+  <si>
+    <t>72.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -227,7 +284,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,20 +318,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -301,13 +365,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,21 +447,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -400,7 +472,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -759,8 +831,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -900,10 +971,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>412.9</v>
+        <v>410.85</v>
       </c>
       <c r="D2">
-        <v>-0.02</v>
+        <v>-0.5</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -912,46 +983,46 @@
         <v>274.85</v>
       </c>
       <c r="G2">
-        <v>-2.78</v>
+        <v>-3.26</v>
       </c>
       <c r="H2">
-        <v>50.23</v>
+        <v>49.48</v>
       </c>
       <c r="I2">
-        <v>3.56</v>
+        <v>2.2</v>
       </c>
       <c r="J2">
-        <v>4.84</v>
+        <v>2.6</v>
       </c>
       <c r="K2">
-        <v>13.73</v>
+        <v>12.59</v>
       </c>
       <c r="L2">
-        <v>43.69</v>
+        <v>44.95</v>
       </c>
       <c r="M2">
-        <v>32.38</v>
+        <v>31.02</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>406.58</v>
+        <v>408.35</v>
       </c>
       <c r="Q2">
-        <v>407.6</v>
+        <v>408.58</v>
       </c>
       <c r="R2">
-        <v>399.1</v>
+        <v>399.95</v>
       </c>
       <c r="S2">
-        <v>357.45</v>
+        <v>357.86</v>
       </c>
       <c r="T2">
-        <v>15.51</v>
+        <v>14.81</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -966,34 +1037,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>56.03</v>
+        <v>54.48</v>
       </c>
       <c r="Z2">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="AA2">
-        <v>3.33</v>
+        <v>3.24</v>
       </c>
       <c r="AB2">
-        <v>-0.57</v>
+        <v>-0.39</v>
       </c>
       <c r="AC2">
-        <v>53.02</v>
+        <v>57.08</v>
       </c>
       <c r="AD2">
-        <v>35.2</v>
+        <v>47.97</v>
       </c>
       <c r="AE2">
-        <v>9.9</v>
+        <v>9.85</v>
       </c>
       <c r="AF2">
-        <v>-46.05</v>
+        <v>2.63</v>
       </c>
       <c r="AG2">
-        <v>427.27</v>
+        <v>426.73</v>
       </c>
       <c r="AH2">
-        <v>387.93</v>
+        <v>390.42</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1002,7 +1073,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>21.21</v>
+        <v>20.32</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1013,10 +1084,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>53.95</v>
+        <v>54.48</v>
       </c>
       <c r="D3">
-        <v>-0.74</v>
+        <v>0.98</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1025,46 +1096,46 @@
         <v>53.89</v>
       </c>
       <c r="G3">
-        <v>-42.29</v>
+        <v>-41.72</v>
       </c>
       <c r="H3">
-        <v>0.11</v>
+        <v>1.09</v>
       </c>
       <c r="I3">
-        <v>-3.63</v>
+        <v>-0.89</v>
       </c>
       <c r="J3">
-        <v>-4.09</v>
+        <v>-4.5</v>
       </c>
       <c r="K3">
-        <v>-16.83</v>
+        <v>-14.95</v>
       </c>
       <c r="L3">
-        <v>-30.1</v>
+        <v>-28.56</v>
       </c>
       <c r="M3">
-        <v>-22.91</v>
+        <v>-22.74</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P3">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="Q3">
-        <v>58.2</v>
+        <v>58.09</v>
       </c>
       <c r="R3">
-        <v>58.94</v>
+        <v>58.81</v>
       </c>
       <c r="S3">
-        <v>65.92</v>
+        <v>65.8</v>
       </c>
       <c r="T3">
-        <v>-18.16</v>
+        <v>-17.21</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1079,43 +1150,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>33.46</v>
+        <v>36.49</v>
       </c>
       <c r="Z3">
-        <v>-1.39</v>
+        <v>-1.42</v>
       </c>
       <c r="AA3">
-        <v>-0.83</v>
+        <v>-0.95</v>
       </c>
       <c r="AB3">
-        <v>-0.5600000000000001</v>
+        <v>-0.47</v>
       </c>
       <c r="AC3">
-        <v>1.92</v>
+        <v>3.66</v>
       </c>
       <c r="AD3">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="AE3">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AF3">
-        <v>-61.24</v>
+        <v>-60.6</v>
       </c>
       <c r="AG3">
-        <v>64.53</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AH3">
-        <v>51.88</v>
+        <v>51.58</v>
       </c>
       <c r="AI3">
-        <v>59.99</v>
+        <v>59.39</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>45.51</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1126,10 +1197,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3288</v>
+        <v>3289.6</v>
       </c>
       <c r="D4">
-        <v>-0.6</v>
+        <v>0.05</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1138,46 +1209,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.74</v>
+        <v>-2.69</v>
       </c>
       <c r="H4">
-        <v>29.9</v>
+        <v>29.97</v>
       </c>
       <c r="I4">
-        <v>1.15</v>
+        <v>0.33</v>
       </c>
       <c r="J4">
-        <v>6.43</v>
+        <v>5.69</v>
       </c>
       <c r="K4">
-        <v>3.89</v>
+        <v>3.77</v>
       </c>
       <c r="L4">
-        <v>16.25</v>
+        <v>14.82</v>
       </c>
       <c r="M4">
-        <v>18.18</v>
+        <v>18.39</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>3288.94</v>
+        <v>3291.12</v>
       </c>
       <c r="Q4">
-        <v>3240.56</v>
+        <v>3249.23</v>
       </c>
       <c r="R4">
-        <v>3181.62</v>
+        <v>3184.12</v>
       </c>
       <c r="S4">
-        <v>2912.34</v>
+        <v>2915.29</v>
       </c>
       <c r="T4">
-        <v>12.9</v>
+        <v>12.84</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1192,34 +1263,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>56.71</v>
+        <v>56.87</v>
       </c>
       <c r="Z4">
-        <v>38.83</v>
+        <v>37.36</v>
       </c>
       <c r="AA4">
-        <v>38.53</v>
+        <v>38.29</v>
       </c>
       <c r="AB4">
-        <v>0.3</v>
+        <v>-0.93</v>
       </c>
       <c r="AC4">
-        <v>38.65</v>
+        <v>29.24</v>
       </c>
       <c r="AD4">
-        <v>44.39</v>
+        <v>38.5</v>
       </c>
       <c r="AE4">
-        <v>72.97</v>
+        <v>73.34</v>
       </c>
       <c r="AF4">
-        <v>80.45999999999999</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="AG4">
-        <v>3407.23</v>
+        <v>3406.43</v>
       </c>
       <c r="AH4">
-        <v>3073.89</v>
+        <v>3092.03</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1228,7 +1299,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>33.94</v>
+        <v>30.84</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1239,58 +1310,58 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1058.5</v>
+        <v>1051.05</v>
       </c>
       <c r="D5">
-        <v>2.37</v>
+        <v>-0.7</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>700.85</v>
+        <v>701.4</v>
       </c>
       <c r="G5">
-        <v>-7.93</v>
+        <v>-8.58</v>
       </c>
       <c r="H5">
-        <v>51.03</v>
+        <v>49.85</v>
       </c>
       <c r="I5">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="J5">
-        <v>12.27</v>
+        <v>11.19</v>
       </c>
       <c r="K5">
-        <v>-4.1</v>
+        <v>-8.58</v>
       </c>
       <c r="L5">
-        <v>49.78</v>
+        <v>49.97</v>
       </c>
       <c r="M5">
-        <v>20.95</v>
+        <v>20.22</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P5">
-        <v>1040.58</v>
+        <v>1042.47</v>
       </c>
       <c r="Q5">
-        <v>1024.77</v>
+        <v>1030.5</v>
       </c>
       <c r="R5">
-        <v>991.14</v>
+        <v>991.89</v>
       </c>
       <c r="S5">
-        <v>955.39</v>
+        <v>956.7</v>
       </c>
       <c r="T5">
-        <v>10.79</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1305,34 +1376,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>60.61</v>
+        <v>58.21</v>
       </c>
       <c r="Z5">
-        <v>16.54</v>
+        <v>16.41</v>
       </c>
       <c r="AA5">
-        <v>16.2</v>
+        <v>16.24</v>
       </c>
       <c r="AB5">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="AC5">
-        <v>14.99</v>
+        <v>23.32</v>
       </c>
       <c r="AD5">
-        <v>14.73</v>
+        <v>16.13</v>
       </c>
       <c r="AE5">
-        <v>24.22</v>
+        <v>23.78</v>
       </c>
       <c r="AF5">
-        <v>-15.63</v>
+        <v>-26.96</v>
       </c>
       <c r="AG5">
-        <v>1099.79</v>
+        <v>1093.67</v>
       </c>
       <c r="AH5">
-        <v>949.75</v>
+        <v>967.33</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1341,7 +1412,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>32.01</v>
+        <v>30.16</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1352,58 +1423,58 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.07</v>
+        <v>15.19</v>
       </c>
       <c r="D6">
-        <v>0.93</v>
+        <v>7.96</v>
       </c>
       <c r="E6">
-        <v>15.01</v>
+        <v>15.19</v>
       </c>
       <c r="F6">
         <v>6.49</v>
       </c>
       <c r="G6">
-        <v>-6.26</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>116.8</v>
+        <v>134.05</v>
       </c>
       <c r="I6">
-        <v>2.63</v>
+        <v>7.58</v>
       </c>
       <c r="J6">
-        <v>7.16</v>
+        <v>16.31</v>
       </c>
       <c r="K6">
-        <v>-0.5</v>
+        <v>7.12</v>
       </c>
       <c r="L6">
-        <v>113.83</v>
+        <v>123.71</v>
       </c>
       <c r="M6">
-        <v>17.62</v>
+        <v>19.25</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P6">
-        <v>14.05</v>
+        <v>14.26</v>
       </c>
       <c r="Q6">
-        <v>13.33</v>
+        <v>13.45</v>
       </c>
       <c r="R6">
-        <v>13.8</v>
+        <v>13.81</v>
       </c>
       <c r="S6">
-        <v>11.7</v>
+        <v>11.73</v>
       </c>
       <c r="T6">
-        <v>20.3</v>
+        <v>29.55</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1418,43 +1489,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>60.06</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="Z6">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="AA6">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="AB6">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="AC6">
-        <v>83.11</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AD6">
-        <v>84.93000000000001</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="AE6">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="AF6">
-        <v>-39.93</v>
+        <v>309.54</v>
       </c>
       <c r="AG6">
-        <v>14.44</v>
+        <v>14.81</v>
       </c>
       <c r="AH6">
-        <v>12.23</v>
+        <v>12.08</v>
       </c>
       <c r="AI6">
-        <v>12.89</v>
+        <v>13.33</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>57.01</v>
+        <v>61.02</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1465,10 +1536,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.35</v>
+        <v>11.33</v>
       </c>
       <c r="D7">
-        <v>-1.3</v>
+        <v>-0.18</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1477,46 +1548,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-18.46</v>
+        <v>-18.61</v>
       </c>
       <c r="H7">
-        <v>142</v>
+        <v>141.58</v>
       </c>
       <c r="I7">
-        <v>-2.99</v>
+        <v>-5.19</v>
       </c>
       <c r="J7">
-        <v>-3.16</v>
+        <v>-1.05</v>
       </c>
       <c r="K7">
-        <v>-12.29</v>
+        <v>-13.91</v>
       </c>
       <c r="L7">
-        <v>114.15</v>
+        <v>109.81</v>
       </c>
       <c r="M7">
-        <v>-29.78</v>
+        <v>-30.06</v>
       </c>
       <c r="N7">
         <v>87</v>
       </c>
       <c r="O7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P7">
-        <v>11.64</v>
+        <v>11.52</v>
       </c>
       <c r="Q7">
-        <v>12.15</v>
+        <v>12.17</v>
       </c>
       <c r="R7">
-        <v>11.66</v>
+        <v>11.65</v>
       </c>
       <c r="S7">
-        <v>10.05</v>
+        <v>10.08</v>
       </c>
       <c r="T7">
-        <v>12.99</v>
+        <v>12.44</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1531,43 +1602,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>41.27</v>
+        <v>41</v>
       </c>
       <c r="Z7">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="AA7">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AB7">
         <v>-0.15</v>
       </c>
       <c r="AC7">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>2.14</v>
+        <v>0.27</v>
       </c>
       <c r="AE7">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="AF7">
-        <v>-78.87</v>
+        <v>-80.18000000000001</v>
       </c>
       <c r="AG7">
-        <v>13.57</v>
+        <v>13.54</v>
       </c>
       <c r="AH7">
-        <v>10.74</v>
+        <v>10.8</v>
       </c>
       <c r="AI7">
-        <v>12.4</v>
+        <v>12.28</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>32.75</v>
+        <v>33.82</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1578,10 +1649,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4362.1</v>
+        <v>4395.3</v>
       </c>
       <c r="D8">
-        <v>0.12</v>
+        <v>0.76</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1590,46 +1661,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-24.91</v>
+        <v>-24.34</v>
       </c>
       <c r="H8">
-        <v>4.98</v>
+        <v>5.78</v>
       </c>
       <c r="I8">
-        <v>-4.07</v>
+        <v>0.22</v>
       </c>
       <c r="J8">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="K8">
-        <v>-5.88</v>
+        <v>-5.11</v>
       </c>
       <c r="L8">
-        <v>-14.69</v>
+        <v>-14.3</v>
       </c>
       <c r="M8">
-        <v>20.14</v>
+        <v>20.38</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P8">
-        <v>4341.2</v>
+        <v>4343.12</v>
       </c>
       <c r="Q8">
-        <v>4366.91</v>
+        <v>4374.68</v>
       </c>
       <c r="R8">
-        <v>4378.86</v>
+        <v>4379.15</v>
       </c>
       <c r="S8">
-        <v>4668.89</v>
+        <v>4665.38</v>
       </c>
       <c r="T8">
-        <v>-6.57</v>
+        <v>-5.79</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1644,34 +1715,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>48.64</v>
+        <v>51.37</v>
       </c>
       <c r="Z8">
-        <v>1.15</v>
+        <v>2.35</v>
       </c>
       <c r="AA8">
-        <v>6.53</v>
+        <v>5.69</v>
       </c>
       <c r="AB8">
-        <v>-5.38</v>
+        <v>-3.35</v>
       </c>
       <c r="AC8">
-        <v>18.99</v>
+        <v>29.56</v>
       </c>
       <c r="AD8">
-        <v>12.88</v>
+        <v>19.62</v>
       </c>
       <c r="AE8">
-        <v>101.5</v>
+        <v>100.18</v>
       </c>
       <c r="AF8">
-        <v>-59.94</v>
+        <v>-22.05</v>
       </c>
       <c r="AG8">
-        <v>4534.22</v>
+        <v>4531.25</v>
       </c>
       <c r="AH8">
-        <v>4199.61</v>
+        <v>4218.11</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1680,7 +1751,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>22.04</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1691,10 +1762,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11504</v>
+        <v>11540</v>
       </c>
       <c r="D9">
-        <v>-0.57</v>
+        <v>0.31</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1703,46 +1774,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-11.86</v>
+        <v>-11.58</v>
       </c>
       <c r="H9">
-        <v>11.02</v>
+        <v>11.37</v>
       </c>
       <c r="I9">
-        <v>-0.99</v>
+        <v>0.36</v>
       </c>
       <c r="J9">
-        <v>-2.89</v>
+        <v>-2.87</v>
       </c>
       <c r="K9">
-        <v>-1.02</v>
+        <v>-1.27</v>
       </c>
       <c r="L9">
-        <v>-10.57</v>
+        <v>-10.36</v>
       </c>
       <c r="M9">
-        <v>9.56</v>
+        <v>9.84</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P9">
-        <v>11519.6</v>
+        <v>11527.8</v>
       </c>
       <c r="Q9">
-        <v>11821.45</v>
+        <v>11800.65</v>
       </c>
       <c r="R9">
-        <v>11683.76</v>
+        <v>11685.24</v>
       </c>
       <c r="S9">
-        <v>11781.6</v>
+        <v>11779.75</v>
       </c>
       <c r="T9">
-        <v>-2.36</v>
+        <v>-2.04</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1757,43 +1828,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>41.14</v>
+        <v>42.81</v>
       </c>
       <c r="Z9">
-        <v>-65.06999999999999</v>
+        <v>-69.62</v>
       </c>
       <c r="AA9">
-        <v>-6.22</v>
+        <v>-18.9</v>
       </c>
       <c r="AB9">
-        <v>-58.85</v>
+        <v>-50.72</v>
       </c>
       <c r="AC9">
-        <v>17.36</v>
+        <v>17.65</v>
       </c>
       <c r="AD9">
-        <v>12.57</v>
+        <v>16.17</v>
       </c>
       <c r="AE9">
-        <v>190.53</v>
+        <v>184.71</v>
       </c>
       <c r="AF9">
-        <v>27.82</v>
+        <v>-4.59</v>
       </c>
       <c r="AG9">
-        <v>12293.59</v>
+        <v>12284.34</v>
       </c>
       <c r="AH9">
-        <v>11349.31</v>
+        <v>11316.96</v>
       </c>
       <c r="AI9">
-        <v>12054.41</v>
+        <v>12053.63</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>28.37</v>
+        <v>28.9</v>
       </c>
     </row>
   </sheetData>
@@ -1934,7 +2005,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1954,1127 +2025,1202 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>56</v>
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>5.29</v>
-      </c>
-      <c r="D7" s="5">
-        <v>4.84</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-0.45</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>4.84</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-3</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="7">
         <v>-4.09</v>
       </c>
-      <c r="E8" s="6">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D10" s="7">
+        <v>-4.5</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C11" s="7">
+        <v>6.43</v>
+      </c>
+      <c r="D11" s="7">
+        <v>5.69</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>12.27</v>
+      </c>
+      <c r="D12" s="7">
+        <v>11.19</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>7.16</v>
+      </c>
+      <c r="D13" s="7">
+        <v>16.31</v>
+      </c>
+      <c r="E13" s="9">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-3.16</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-1.05</v>
+      </c>
+      <c r="E14" s="9">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1.18</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-2.89</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-2.87</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>3.56</v>
+      </c>
+      <c r="D17" s="7">
+        <v>2.2</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-3.63</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-0.89</v>
+      </c>
+      <c r="E18" s="9">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.33</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.82</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0.91</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>2.63</v>
+      </c>
+      <c r="D21" s="7">
+        <v>7.58</v>
+      </c>
+      <c r="E21" s="9">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-2.99</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-5.19</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-4.07</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="E23" s="9">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-0.99</v>
+      </c>
+      <c r="D24" s="7">
+        <v>0.36</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>43.69</v>
+      </c>
+      <c r="D25" s="7">
+        <v>44.95</v>
+      </c>
+      <c r="E25" s="9">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-30.1</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-28.56</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>16.25</v>
+      </c>
+      <c r="D27" s="7">
+        <v>14.82</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>49.78</v>
+      </c>
+      <c r="D28" s="7">
+        <v>49.97</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>113.83</v>
+      </c>
+      <c r="D29" s="7">
+        <v>123.71</v>
+      </c>
+      <c r="E29" s="9">
+        <v>9.880000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>114.15</v>
+      </c>
+      <c r="D30" s="7">
+        <v>109.81</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-4.34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-14.69</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-14.3</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-10.57</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-10.36</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>13.73</v>
+      </c>
+      <c r="D33" s="7">
+        <v>12.59</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-16.83</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-14.95</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>3.89</v>
+      </c>
+      <c r="D35" s="7">
+        <v>3.77</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-4.1</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-8.58</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-4.48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-0.5</v>
+      </c>
+      <c r="D37" s="7">
+        <v>7.12</v>
+      </c>
+      <c r="E37" s="9">
+        <v>7.62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-12.29</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-13.91</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-5.88</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-5.11</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-1.02</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-1.27</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-2.78</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-3.26</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-42.29</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-41.72</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-2.74</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-2.69</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-7.93</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-8.58</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-6.26</v>
+      </c>
+      <c r="D45" s="7">
+        <v>0</v>
+      </c>
+      <c r="E45" s="9">
         <v>6.26</v>
       </c>
-      <c r="D9" s="5">
-        <v>6.43</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-18.46</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-18.61</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-24.91</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-24.34</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-11.86</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-11.58</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>412.9</v>
+      </c>
+      <c r="D49" s="7">
+        <v>410.85</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>53.95</v>
+      </c>
+      <c r="D50" s="7">
+        <v>54.48</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7">
+        <v>3288</v>
+      </c>
+      <c r="D51" s="7">
+        <v>3289.6</v>
+      </c>
+      <c r="E51" s="9">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="D10" s="5">
-        <v>12.27</v>
-      </c>
-      <c r="E10" s="7">
-        <v>4.07</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B52" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7">
+        <v>1058.5</v>
+      </c>
+      <c r="D52" s="7">
+        <v>1051.05</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-7.45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>5.61</v>
-      </c>
-      <c r="D11" s="5">
-        <v>7.16</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>14.07</v>
+      </c>
+      <c r="D53" s="7">
+        <v>15.19</v>
+      </c>
+      <c r="E53" s="9">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-3.77</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-3.16</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>11.35</v>
+      </c>
+      <c r="D54" s="7">
+        <v>11.33</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1.25</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1.18</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>4362.1</v>
+      </c>
+      <c r="D55" s="7">
+        <v>4395.3</v>
+      </c>
+      <c r="E55" s="9">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-2.84</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-2.89</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>11504</v>
+      </c>
+      <c r="D56" s="7">
+        <v>11540</v>
+      </c>
+      <c r="E56" s="9">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>2.99</v>
-      </c>
-      <c r="D15" s="5">
-        <v>3.56</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>56.03</v>
+      </c>
+      <c r="D57" s="7">
+        <v>54.48</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-2.91</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-3.63</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>33.46</v>
+      </c>
+      <c r="D58" s="7">
+        <v>36.49</v>
+      </c>
+      <c r="E58" s="9">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>1.83</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1.15</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>56.71</v>
+      </c>
+      <c r="D59" s="7">
+        <v>56.87</v>
+      </c>
+      <c r="E59" s="9">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.44</v>
-      </c>
-      <c r="D18" s="5">
-        <v>0.82</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="7">
+        <v>60.61</v>
+      </c>
+      <c r="D60" s="7">
+        <v>58.21</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-1.2</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="B61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="7">
+        <v>60.06</v>
+      </c>
+      <c r="D61" s="7">
+        <v>72.70999999999999</v>
+      </c>
+      <c r="E61" s="9">
+        <v>12.65</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>41.27</v>
+      </c>
+      <c r="D62" s="7">
+        <v>41</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>48.64</v>
+      </c>
+      <c r="D63" s="7">
+        <v>51.37</v>
+      </c>
+      <c r="E63" s="9">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>41.14</v>
+      </c>
+      <c r="D64" s="7">
+        <v>42.81</v>
+      </c>
+      <c r="E64" s="9">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7">
+        <v>-46.05</v>
+      </c>
+      <c r="D65" s="7">
         <v>2.63</v>
       </c>
-      <c r="E19" s="7">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="E65" s="9">
+        <v>48.68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="7">
+        <v>-61.24</v>
+      </c>
+      <c r="D66" s="7">
+        <v>-60.6</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="7">
+        <v>80.45999999999999</v>
+      </c>
+      <c r="D67" s="7">
+        <v>83.26000000000001</v>
+      </c>
+      <c r="E67" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="7">
+        <v>-15.63</v>
+      </c>
+      <c r="D68" s="7">
+        <v>-26.96</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-11.33</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="7">
+        <v>-39.93</v>
+      </c>
+      <c r="D69" s="7">
+        <v>309.54</v>
+      </c>
+      <c r="E69" s="9">
+        <v>349.47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-1.71</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-2.99</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B70" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="7">
+        <v>-78.87</v>
+      </c>
+      <c r="D70" s="7">
+        <v>-80.18000000000001</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-4.18</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-4.07</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>-59.94</v>
+      </c>
+      <c r="D71" s="7">
+        <v>-22.05</v>
+      </c>
+      <c r="E71" s="9">
+        <v>37.89</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-0.42</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-0.99</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>45.86</v>
-      </c>
-      <c r="D23" s="5">
-        <v>43.69</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-28.92</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-30.1</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>16.24</v>
-      </c>
-      <c r="D25" s="5">
-        <v>16.25</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>44.79</v>
-      </c>
-      <c r="D26" s="5">
-        <v>49.78</v>
-      </c>
-      <c r="E26" s="7">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>115.79</v>
-      </c>
-      <c r="D27" s="5">
-        <v>113.83</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>117.39</v>
-      </c>
-      <c r="D28" s="5">
-        <v>114.15</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-3.24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-13.41</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-14.69</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-10.57</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>13.57</v>
-      </c>
-      <c r="D31" s="5">
-        <v>13.73</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-19.31</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-16.83</v>
-      </c>
-      <c r="E32" s="7">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>4.3</v>
-      </c>
-      <c r="D33" s="5">
-        <v>3.89</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-5.97</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-4.1</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-0.71</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-0.5</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-13.01</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-12.29</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-5.61</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-5.88</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-1.33</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-1.02</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-2.75</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-2.78</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-41.86</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-42.29</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-2.14</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-2.74</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-10.06</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-7.93</v>
-      </c>
-      <c r="E42" s="7">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-7.13</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-6.26</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-17.39</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-18.46</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-25</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-24.91</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-11.35</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-11.86</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>413</v>
-      </c>
-      <c r="D47" s="5">
-        <v>412.9</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>54.35</v>
-      </c>
-      <c r="D48" s="5">
-        <v>53.95</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>3308</v>
-      </c>
-      <c r="D49" s="5">
-        <v>3288</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>1034</v>
-      </c>
-      <c r="D50" s="5">
-        <v>1058.5</v>
-      </c>
-      <c r="E50" s="7">
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>13.94</v>
-      </c>
-      <c r="D51" s="5">
-        <v>14.07</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>11.5</v>
-      </c>
-      <c r="D52" s="5">
-        <v>11.35</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>4356.9</v>
-      </c>
-      <c r="D53" s="5">
-        <v>4362.1</v>
-      </c>
-      <c r="E53" s="7">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>11570</v>
-      </c>
-      <c r="D54" s="5">
-        <v>11504</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-66</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>56.1</v>
-      </c>
-      <c r="D55" s="5">
-        <v>56.03</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>34.61</v>
-      </c>
-      <c r="D56" s="5">
-        <v>33.46</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>59.28</v>
-      </c>
-      <c r="D57" s="5">
-        <v>56.71</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-2.57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>54.95</v>
-      </c>
-      <c r="D58" s="5">
-        <v>60.61</v>
-      </c>
-      <c r="E58" s="7">
-        <v>5.66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>57.96</v>
-      </c>
-      <c r="D59" s="5">
-        <v>60.06</v>
-      </c>
-      <c r="E59" s="7">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>43.28</v>
-      </c>
-      <c r="D60" s="5">
-        <v>41.27</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>48.21</v>
-      </c>
-      <c r="D61" s="5">
-        <v>48.64</v>
-      </c>
-      <c r="E61" s="7">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>43.29</v>
-      </c>
-      <c r="D62" s="5">
-        <v>41.14</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="3" t="s">
+      <c r="B72" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="5">
-        <v>-7.09</v>
-      </c>
-      <c r="D63" s="5">
-        <v>-46.05</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-38.96</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-59.35</v>
-      </c>
-      <c r="D64" s="5">
-        <v>-61.24</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>74.19</v>
-      </c>
-      <c r="D65" s="5">
-        <v>80.45999999999999</v>
-      </c>
-      <c r="E65" s="7">
-        <v>6.27</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-46.06</v>
-      </c>
-      <c r="D66" s="5">
-        <v>-15.63</v>
-      </c>
-      <c r="E66" s="7">
-        <v>30.43</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>-51.08</v>
-      </c>
-      <c r="D67" s="5">
-        <v>-39.93</v>
-      </c>
-      <c r="E67" s="7">
-        <v>11.15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>-64.34</v>
-      </c>
-      <c r="D68" s="5">
-        <v>-78.87</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-14.53</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
-        <v>-23.7</v>
-      </c>
-      <c r="D69" s="5">
-        <v>-59.94</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-36.24</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="5">
-        <v>-45.71</v>
-      </c>
-      <c r="D70" s="5">
+      <c r="C72" s="7">
         <v>27.82</v>
       </c>
-      <c r="E70" s="7">
-        <v>73.53</v>
+      <c r="D72" s="7">
+        <v>-4.59</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-32.41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3094,60 +3240,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="12">
+        <v>56.44</v>
+      </c>
+      <c r="C2" s="13">
+        <v>8</v>
+      </c>
+      <c r="D2" s="12">
+        <v>51.7</v>
+      </c>
+      <c r="E2" s="12">
         <v>60</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.44</v>
-      </c>
-      <c r="C2" s="11">
-        <v>8</v>
-      </c>
-      <c r="D2" s="10">
-        <v>49.7</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>2.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-2.9</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-2.5</v>
+      </c>
+      <c r="H2" s="12">
         <v>56.1</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>50</v>
       </c>
     </row>
@@ -3249,55 +3395,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.3238</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2095</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2014</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1818</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1762</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0956</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2291</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.2978</v>
+      <c r="A2" s="15">
+        <v>0.3102</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.2038</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2022</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1925</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1839</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0984</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.2274</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.3006</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,49 +190,40 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-6.3% → 0.0%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-6.3%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.6 → 51.4</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.6</t>
-  </si>
-  <si>
-    <t>51.4</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>60.1 → 72.7</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>60.1</t>
+    <t>42.8 → 50.3</t>
+  </si>
+  <si>
+    <t>42.8</t>
+  </si>
+  <si>
+    <t>50.3</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>72.7 → 69.9</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
   </si>
   <si>
     <t>72.7</t>
+  </si>
+  <si>
+    <t>69.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -325,7 +316,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -371,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,8 +449,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -830,8 +821,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -971,10 +962,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>410.85</v>
+        <v>410</v>
       </c>
       <c r="D2">
-        <v>-0.5</v>
+        <v>-0.21</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -983,46 +974,46 @@
         <v>274.85</v>
       </c>
       <c r="G2">
-        <v>-3.26</v>
+        <v>-3.46</v>
       </c>
       <c r="H2">
-        <v>49.48</v>
+        <v>49.17</v>
       </c>
       <c r="I2">
-        <v>2.2</v>
+        <v>3.54</v>
       </c>
       <c r="J2">
-        <v>2.6</v>
+        <v>4.77</v>
       </c>
       <c r="K2">
-        <v>12.59</v>
+        <v>12.36</v>
       </c>
       <c r="L2">
-        <v>44.95</v>
+        <v>40.75</v>
       </c>
       <c r="M2">
-        <v>31.02</v>
+        <v>31</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P2">
-        <v>408.35</v>
+        <v>411.15</v>
       </c>
       <c r="Q2">
-        <v>408.58</v>
+        <v>409.2</v>
       </c>
       <c r="R2">
-        <v>399.95</v>
+        <v>400.68</v>
       </c>
       <c r="S2">
-        <v>357.86</v>
+        <v>358.22</v>
       </c>
       <c r="T2">
-        <v>14.81</v>
+        <v>14.45</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1037,34 +1028,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>54.48</v>
+        <v>53.82</v>
       </c>
       <c r="Z2">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="AA2">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="AB2">
-        <v>-0.39</v>
+        <v>-0.34</v>
       </c>
       <c r="AC2">
-        <v>57.08</v>
+        <v>63.79</v>
       </c>
       <c r="AD2">
-        <v>47.97</v>
+        <v>57.97</v>
       </c>
       <c r="AE2">
-        <v>9.85</v>
+        <v>9.67</v>
       </c>
       <c r="AF2">
-        <v>2.63</v>
+        <v>-43.6</v>
       </c>
       <c r="AG2">
-        <v>426.73</v>
+        <v>426.6</v>
       </c>
       <c r="AH2">
-        <v>390.42</v>
+        <v>391.79</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1073,7 +1064,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>20.32</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1084,10 +1075,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>54.48</v>
+        <v>54.52</v>
       </c>
       <c r="D3">
-        <v>0.98</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1096,25 +1087,25 @@
         <v>53.89</v>
       </c>
       <c r="G3">
-        <v>-41.72</v>
+        <v>-41.68</v>
       </c>
       <c r="H3">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="I3">
-        <v>-0.89</v>
+        <v>0.09</v>
       </c>
       <c r="J3">
-        <v>-4.5</v>
+        <v>-3.84</v>
       </c>
       <c r="K3">
-        <v>-14.95</v>
+        <v>-14.89</v>
       </c>
       <c r="L3">
-        <v>-28.56</v>
+        <v>-27.93</v>
       </c>
       <c r="M3">
-        <v>-22.74</v>
+        <v>-22.92</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1123,19 +1114,19 @@
         <v>14</v>
       </c>
       <c r="P3">
-        <v>54.4</v>
+        <v>54.41</v>
       </c>
       <c r="Q3">
-        <v>58.09</v>
+        <v>57.91</v>
       </c>
       <c r="R3">
-        <v>58.81</v>
+        <v>58.68</v>
       </c>
       <c r="S3">
-        <v>65.8</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="T3">
-        <v>-17.21</v>
+        <v>-16.99</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1150,34 +1141,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>36.49</v>
+        <v>36.72</v>
       </c>
       <c r="Z3">
-        <v>-1.42</v>
+        <v>-1.43</v>
       </c>
       <c r="AA3">
-        <v>-0.95</v>
+        <v>-1.05</v>
       </c>
       <c r="AB3">
-        <v>-0.47</v>
+        <v>-0.38</v>
       </c>
       <c r="AC3">
-        <v>3.66</v>
+        <v>6.98</v>
       </c>
       <c r="AD3">
-        <v>2.5</v>
+        <v>4.19</v>
       </c>
       <c r="AE3">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AF3">
-        <v>-60.6</v>
+        <v>-45.77</v>
       </c>
       <c r="AG3">
-        <v>64.59999999999999</v>
+        <v>64.62</v>
       </c>
       <c r="AH3">
-        <v>51.58</v>
+        <v>51.21</v>
       </c>
       <c r="AI3">
         <v>59.39</v>
@@ -1186,7 +1177,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>47.75</v>
+        <v>47.18</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1197,10 +1188,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3289.6</v>
+        <v>3299.9</v>
       </c>
       <c r="D4">
-        <v>0.05</v>
+        <v>0.31</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1209,46 +1200,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.69</v>
+        <v>-2.38</v>
       </c>
       <c r="H4">
-        <v>29.97</v>
+        <v>30.37</v>
       </c>
       <c r="I4">
-        <v>0.33</v>
+        <v>0.91</v>
       </c>
       <c r="J4">
-        <v>5.69</v>
+        <v>5.89</v>
       </c>
       <c r="K4">
-        <v>3.77</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
-        <v>14.82</v>
+        <v>14.53</v>
       </c>
       <c r="M4">
-        <v>18.39</v>
+        <v>18.61</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>3291.12</v>
+        <v>3297.1</v>
       </c>
       <c r="Q4">
-        <v>3249.23</v>
+        <v>3258.58</v>
       </c>
       <c r="R4">
-        <v>3184.12</v>
+        <v>3187.31</v>
       </c>
       <c r="S4">
-        <v>2915.29</v>
+        <v>2918.17</v>
       </c>
       <c r="T4">
-        <v>12.84</v>
+        <v>13.08</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1263,34 +1254,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>56.87</v>
+        <v>57.96</v>
       </c>
       <c r="Z4">
-        <v>37.36</v>
+        <v>36.6</v>
       </c>
       <c r="AA4">
-        <v>38.29</v>
+        <v>37.95</v>
       </c>
       <c r="AB4">
-        <v>-0.93</v>
+        <v>-1.35</v>
       </c>
       <c r="AC4">
-        <v>29.24</v>
+        <v>21.2</v>
       </c>
       <c r="AD4">
-        <v>38.5</v>
+        <v>29.7</v>
       </c>
       <c r="AE4">
-        <v>73.34</v>
+        <v>71.5</v>
       </c>
       <c r="AF4">
-        <v>83.26000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="AG4">
-        <v>3406.43</v>
+        <v>3403.41</v>
       </c>
       <c r="AH4">
-        <v>3092.03</v>
+        <v>3113.74</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1299,7 +1290,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>30.84</v>
+        <v>28.77</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1310,10 +1301,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1051.05</v>
+        <v>1053</v>
       </c>
       <c r="D5">
-        <v>-0.7</v>
+        <v>0.19</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1322,46 +1313,46 @@
         <v>701.4</v>
       </c>
       <c r="G5">
-        <v>-8.58</v>
+        <v>-8.41</v>
       </c>
       <c r="H5">
-        <v>49.85</v>
+        <v>50.13</v>
       </c>
       <c r="I5">
-        <v>0.91</v>
+        <v>1.35</v>
       </c>
       <c r="J5">
-        <v>11.19</v>
+        <v>12.45</v>
       </c>
       <c r="K5">
-        <v>-8.58</v>
+        <v>-8.41</v>
       </c>
       <c r="L5">
-        <v>49.97</v>
+        <v>48.88</v>
       </c>
       <c r="M5">
-        <v>20.22</v>
+        <v>20.64</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P5">
-        <v>1042.47</v>
+        <v>1045.28</v>
       </c>
       <c r="Q5">
-        <v>1030.5</v>
+        <v>1035.03</v>
       </c>
       <c r="R5">
-        <v>991.89</v>
+        <v>993.3</v>
       </c>
       <c r="S5">
-        <v>956.7</v>
+        <v>958.01</v>
       </c>
       <c r="T5">
-        <v>9.859999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1376,34 +1367,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>58.21</v>
+        <v>58.67</v>
       </c>
       <c r="Z5">
-        <v>16.41</v>
+        <v>16.27</v>
       </c>
       <c r="AA5">
         <v>16.24</v>
       </c>
       <c r="AB5">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
       <c r="AC5">
-        <v>23.32</v>
+        <v>30.54</v>
       </c>
       <c r="AD5">
-        <v>16.13</v>
+        <v>22.95</v>
       </c>
       <c r="AE5">
-        <v>23.78</v>
+        <v>23.53</v>
       </c>
       <c r="AF5">
-        <v>-26.96</v>
+        <v>-52.81</v>
       </c>
       <c r="AG5">
-        <v>1093.67</v>
+        <v>1090.13</v>
       </c>
       <c r="AH5">
-        <v>967.33</v>
+        <v>979.9299999999999</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1412,7 +1403,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>30.16</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1423,10 +1414,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>15.19</v>
+        <v>15.06</v>
       </c>
       <c r="D6">
-        <v>7.96</v>
+        <v>-0.86</v>
       </c>
       <c r="E6">
         <v>15.19</v>
@@ -1435,25 +1426,25 @@
         <v>6.49</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>-0.86</v>
       </c>
       <c r="H6">
-        <v>134.05</v>
+        <v>132.05</v>
       </c>
       <c r="I6">
-        <v>7.58</v>
+        <v>7.04</v>
       </c>
       <c r="J6">
-        <v>16.31</v>
+        <v>16.29</v>
       </c>
       <c r="K6">
-        <v>7.12</v>
+        <v>6.21</v>
       </c>
       <c r="L6">
-        <v>123.71</v>
+        <v>129.92</v>
       </c>
       <c r="M6">
-        <v>19.25</v>
+        <v>20.62</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1462,19 +1453,19 @@
         <v>95</v>
       </c>
       <c r="P6">
-        <v>14.26</v>
+        <v>14.46</v>
       </c>
       <c r="Q6">
-        <v>13.45</v>
+        <v>13.55</v>
       </c>
       <c r="R6">
-        <v>13.81</v>
+        <v>13.82</v>
       </c>
       <c r="S6">
-        <v>11.73</v>
+        <v>11.75</v>
       </c>
       <c r="T6">
-        <v>29.55</v>
+        <v>28.14</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1489,43 +1480,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>72.70999999999999</v>
+        <v>69.94</v>
       </c>
       <c r="Z6">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="AA6">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AB6">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="AC6">
-        <v>88.09999999999999</v>
+        <v>92.67</v>
       </c>
       <c r="AD6">
-        <v>85.04000000000001</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="AE6">
         <v>0.45</v>
       </c>
       <c r="AF6">
-        <v>309.54</v>
+        <v>9.93</v>
       </c>
       <c r="AG6">
-        <v>14.81</v>
+        <v>15.08</v>
       </c>
       <c r="AH6">
-        <v>12.08</v>
+        <v>12.02</v>
       </c>
       <c r="AI6">
-        <v>13.33</v>
+        <v>13.86</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>61.02</v>
+        <v>64.55</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1536,10 +1527,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.33</v>
+        <v>11.11</v>
       </c>
       <c r="D7">
-        <v>-0.18</v>
+        <v>-1.94</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1548,25 +1539,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-18.61</v>
+        <v>-20.19</v>
       </c>
       <c r="H7">
-        <v>141.58</v>
+        <v>136.89</v>
       </c>
       <c r="I7">
-        <v>-5.19</v>
+        <v>-5.2</v>
       </c>
       <c r="J7">
-        <v>-1.05</v>
+        <v>0.82</v>
       </c>
       <c r="K7">
-        <v>-13.91</v>
+        <v>-15.58</v>
       </c>
       <c r="L7">
-        <v>109.81</v>
+        <v>110.02</v>
       </c>
       <c r="M7">
-        <v>-30.06</v>
+        <v>-29.95</v>
       </c>
       <c r="N7">
         <v>87</v>
@@ -1575,19 +1566,19 @@
         <v>92</v>
       </c>
       <c r="P7">
-        <v>11.52</v>
+        <v>11.39</v>
       </c>
       <c r="Q7">
-        <v>12.17</v>
+        <v>12.15</v>
       </c>
       <c r="R7">
-        <v>11.65</v>
+        <v>11.63</v>
       </c>
       <c r="S7">
-        <v>10.08</v>
+        <v>10.11</v>
       </c>
       <c r="T7">
-        <v>12.44</v>
+        <v>9.93</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1602,43 +1593,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>41</v>
+        <v>38.01</v>
       </c>
       <c r="Z7">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="AA7">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="AB7">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="AC7">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>0.27</v>
+        <v>0.01</v>
       </c>
       <c r="AE7">
         <v>0.31</v>
       </c>
       <c r="AF7">
-        <v>-80.18000000000001</v>
+        <v>-58.99</v>
       </c>
       <c r="AG7">
-        <v>13.54</v>
+        <v>13.56</v>
       </c>
       <c r="AH7">
-        <v>10.8</v>
+        <v>10.75</v>
       </c>
       <c r="AI7">
-        <v>12.28</v>
+        <v>12.05</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>33.82</v>
+        <v>36.12</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1649,10 +1640,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4395.3</v>
+        <v>4424.9</v>
       </c>
       <c r="D8">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1661,49 +1652,49 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-24.34</v>
+        <v>-23.83</v>
       </c>
       <c r="H8">
-        <v>5.78</v>
+        <v>6.49</v>
       </c>
       <c r="I8">
-        <v>0.22</v>
+        <v>3.1</v>
       </c>
       <c r="J8">
-        <v>1.15</v>
+        <v>4.36</v>
       </c>
       <c r="K8">
-        <v>-5.11</v>
+        <v>-4.47</v>
       </c>
       <c r="L8">
-        <v>-14.3</v>
+        <v>-13.08</v>
       </c>
       <c r="M8">
-        <v>20.38</v>
+        <v>20.7</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="P8">
-        <v>4343.12</v>
+        <v>4369.74</v>
       </c>
       <c r="Q8">
-        <v>4374.68</v>
+        <v>4380.45</v>
       </c>
       <c r="R8">
-        <v>4379.15</v>
+        <v>4379.36</v>
       </c>
       <c r="S8">
-        <v>4665.38</v>
+        <v>4661.1</v>
       </c>
       <c r="T8">
-        <v>-5.79</v>
+        <v>-5.07</v>
       </c>
       <c r="U8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V8" t="s">
         <v>47</v>
@@ -1712,37 +1703,37 @@
         <v>47</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>51.37</v>
+        <v>53.73</v>
       </c>
       <c r="Z8">
-        <v>2.35</v>
+        <v>5.62</v>
       </c>
       <c r="AA8">
-        <v>5.69</v>
+        <v>5.68</v>
       </c>
       <c r="AB8">
-        <v>-3.35</v>
+        <v>-0.06</v>
       </c>
       <c r="AC8">
-        <v>29.56</v>
+        <v>37.85</v>
       </c>
       <c r="AD8">
-        <v>19.62</v>
+        <v>28.8</v>
       </c>
       <c r="AE8">
-        <v>100.18</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="AF8">
-        <v>-22.05</v>
+        <v>-40.15</v>
       </c>
       <c r="AG8">
-        <v>4531.25</v>
+        <v>4535.4</v>
       </c>
       <c r="AH8">
-        <v>4218.11</v>
+        <v>4225.51</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1751,7 +1742,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>20.69</v>
+        <v>20.78</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1762,10 +1753,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11540</v>
+        <v>11717</v>
       </c>
       <c r="D9">
-        <v>0.31</v>
+        <v>1.53</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1774,46 +1765,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-11.58</v>
+        <v>-10.23</v>
       </c>
       <c r="H9">
-        <v>11.37</v>
+        <v>13.08</v>
       </c>
       <c r="I9">
-        <v>0.36</v>
+        <v>2.33</v>
       </c>
       <c r="J9">
-        <v>-2.87</v>
+        <v>-2</v>
       </c>
       <c r="K9">
-        <v>-1.27</v>
+        <v>0.24</v>
       </c>
       <c r="L9">
-        <v>-10.36</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="M9">
-        <v>9.84</v>
+        <v>10.4</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P9">
-        <v>11527.8</v>
+        <v>11581.2</v>
       </c>
       <c r="Q9">
-        <v>11800.65</v>
+        <v>11786.6</v>
       </c>
       <c r="R9">
-        <v>11685.24</v>
+        <v>11691.76</v>
       </c>
       <c r="S9">
-        <v>11779.75</v>
+        <v>11779.09</v>
       </c>
       <c r="T9">
-        <v>-2.04</v>
+        <v>-0.53</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1828,34 +1819,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>42.81</v>
+        <v>50.27</v>
       </c>
       <c r="Z9">
-        <v>-69.62</v>
+        <v>-58.27</v>
       </c>
       <c r="AA9">
-        <v>-18.9</v>
+        <v>-26.77</v>
       </c>
       <c r="AB9">
-        <v>-50.72</v>
+        <v>-31.5</v>
       </c>
       <c r="AC9">
-        <v>17.65</v>
+        <v>29.59</v>
       </c>
       <c r="AD9">
-        <v>16.17</v>
+        <v>21.53</v>
       </c>
       <c r="AE9">
-        <v>184.71</v>
+        <v>191.52</v>
       </c>
       <c r="AF9">
-        <v>-4.59</v>
+        <v>-11.54</v>
       </c>
       <c r="AG9">
-        <v>12284.34</v>
+        <v>12262.42</v>
       </c>
       <c r="AH9">
-        <v>11316.96</v>
+        <v>11310.78</v>
       </c>
       <c r="AI9">
         <v>12053.63</v>
@@ -1864,7 +1855,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>28.9</v>
+        <v>27.55</v>
       </c>
     </row>
   </sheetData>
@@ -2045,7 +2036,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2057,30 +2048,30 @@
         <v>58</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2088,24 +2079,24 @@
         <v>41</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2117,16 +2108,16 @@
         <v>0</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2137,13 +2128,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>4.84</v>
+        <v>2.6</v>
       </c>
       <c r="D9" s="7">
-        <v>2.6</v>
+        <v>4.77</v>
       </c>
       <c r="E9" s="8">
-        <v>-2.24</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2154,13 +2145,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>-4.09</v>
+        <v>-4.5</v>
       </c>
       <c r="D10" s="7">
-        <v>-4.5</v>
+        <v>-3.84</v>
       </c>
       <c r="E10" s="8">
-        <v>-0.41</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2171,13 +2162,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>6.43</v>
+        <v>5.69</v>
       </c>
       <c r="D11" s="7">
-        <v>5.69</v>
+        <v>5.89</v>
       </c>
       <c r="E11" s="8">
-        <v>-0.74</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2188,13 +2179,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>12.27</v>
+        <v>11.19</v>
       </c>
       <c r="D12" s="7">
-        <v>11.19</v>
+        <v>12.45</v>
       </c>
       <c r="E12" s="8">
-        <v>-1.08</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2205,13 +2196,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>7.16</v>
+        <v>16.31</v>
       </c>
       <c r="D13" s="7">
-        <v>16.31</v>
+        <v>16.29</v>
       </c>
       <c r="E13" s="9">
-        <v>9.15</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2222,13 +2213,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-3.16</v>
+        <v>-1.05</v>
       </c>
       <c r="D14" s="7">
-        <v>-1.05</v>
-      </c>
-      <c r="E14" s="9">
-        <v>2.11</v>
+        <v>0.82</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.87</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2239,13 +2230,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="D15" s="7">
-        <v>1.15</v>
+        <v>4.36</v>
       </c>
       <c r="E15" s="8">
-        <v>-0.03</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2256,13 +2247,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-2.89</v>
+        <v>-2.87</v>
       </c>
       <c r="D16" s="7">
-        <v>-2.87</v>
-      </c>
-      <c r="E16" s="9">
-        <v>0.02</v>
+        <v>-2</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.87</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2273,13 +2264,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>3.56</v>
+        <v>2.2</v>
       </c>
       <c r="D17" s="7">
-        <v>2.2</v>
+        <v>3.54</v>
       </c>
       <c r="E17" s="8">
-        <v>-1.36</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2290,13 +2281,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>-3.63</v>
+        <v>-0.89</v>
       </c>
       <c r="D18" s="7">
-        <v>-0.89</v>
-      </c>
-      <c r="E18" s="9">
-        <v>2.74</v>
+        <v>0.09</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.98</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2307,13 +2298,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>1.15</v>
+        <v>0.33</v>
       </c>
       <c r="D19" s="7">
-        <v>0.33</v>
+        <v>0.91</v>
       </c>
       <c r="E19" s="8">
-        <v>-0.82</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2324,13 +2315,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="D20" s="7">
-        <v>0.91</v>
-      </c>
-      <c r="E20" s="9">
-        <v>0.09</v>
+        <v>1.35</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.44</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2341,13 +2332,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>2.63</v>
+        <v>7.58</v>
       </c>
       <c r="D21" s="7">
-        <v>7.58</v>
+        <v>7.04</v>
       </c>
       <c r="E21" s="9">
-        <v>4.95</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2358,13 +2349,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>-2.99</v>
+        <v>-5.19</v>
       </c>
       <c r="D22" s="7">
-        <v>-5.19</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-2.2</v>
+        <v>-5.2</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2375,13 +2366,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>-4.07</v>
+        <v>0.22</v>
       </c>
       <c r="D23" s="7">
-        <v>0.22</v>
-      </c>
-      <c r="E23" s="9">
-        <v>4.29</v>
+        <v>3.1</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2.88</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2392,13 +2383,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>-0.99</v>
+        <v>0.36</v>
       </c>
       <c r="D24" s="7">
-        <v>0.36</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1.35</v>
+        <v>2.33</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.97</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2409,13 +2400,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="7">
-        <v>43.69</v>
+        <v>44.95</v>
       </c>
       <c r="D25" s="7">
-        <v>44.95</v>
+        <v>40.75</v>
       </c>
       <c r="E25" s="9">
-        <v>1.26</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2426,13 +2417,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="7">
-        <v>-30.1</v>
+        <v>-28.56</v>
       </c>
       <c r="D26" s="7">
-        <v>-28.56</v>
-      </c>
-      <c r="E26" s="9">
-        <v>1.54</v>
+        <v>-27.93</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.63</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2443,13 +2434,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>16.25</v>
+        <v>14.82</v>
       </c>
       <c r="D27" s="7">
-        <v>14.82</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.43</v>
+        <v>14.53</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2460,13 +2451,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>49.78</v>
+        <v>49.97</v>
       </c>
       <c r="D28" s="7">
-        <v>49.97</v>
+        <v>48.88</v>
       </c>
       <c r="E28" s="9">
-        <v>0.19</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2477,13 +2468,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>113.83</v>
+        <v>123.71</v>
       </c>
       <c r="D29" s="7">
-        <v>123.71</v>
-      </c>
-      <c r="E29" s="9">
-        <v>9.880000000000001</v>
+        <v>129.92</v>
+      </c>
+      <c r="E29" s="8">
+        <v>6.21</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2494,13 +2485,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>114.15</v>
+        <v>109.81</v>
       </c>
       <c r="D30" s="7">
-        <v>109.81</v>
+        <v>110.02</v>
       </c>
       <c r="E30" s="8">
-        <v>-4.34</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2511,13 +2502,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>-14.69</v>
+        <v>-14.3</v>
       </c>
       <c r="D31" s="7">
-        <v>-14.3</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0.39</v>
+        <v>-13.08</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.22</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2528,13 +2519,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>-10.57</v>
+        <v>-10.36</v>
       </c>
       <c r="D32" s="7">
-        <v>-10.36</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.21</v>
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.4</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2545,13 +2536,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="7">
-        <v>13.73</v>
+        <v>12.59</v>
       </c>
       <c r="D33" s="7">
-        <v>12.59</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-1.14</v>
+        <v>12.36</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2562,13 +2553,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="7">
-        <v>-16.83</v>
+        <v>-14.95</v>
       </c>
       <c r="D34" s="7">
-        <v>-14.95</v>
-      </c>
-      <c r="E34" s="9">
-        <v>1.88</v>
+        <v>-14.89</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.06</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2579,13 +2570,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="7">
-        <v>3.89</v>
+        <v>3.77</v>
       </c>
       <c r="D35" s="7">
-        <v>3.77</v>
+        <v>4.1</v>
       </c>
       <c r="E35" s="8">
-        <v>-0.12</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2596,13 +2587,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>-4.1</v>
+        <v>-8.58</v>
       </c>
       <c r="D36" s="7">
-        <v>-8.58</v>
+        <v>-8.41</v>
       </c>
       <c r="E36" s="8">
-        <v>-4.48</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2613,13 +2604,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>-0.5</v>
+        <v>7.12</v>
       </c>
       <c r="D37" s="7">
-        <v>7.12</v>
+        <v>6.21</v>
       </c>
       <c r="E37" s="9">
-        <v>7.62</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2630,13 +2621,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>-12.29</v>
+        <v>-13.91</v>
       </c>
       <c r="D38" s="7">
-        <v>-13.91</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1.62</v>
+        <v>-15.58</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2647,13 +2638,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>-5.88</v>
+        <v>-5.11</v>
       </c>
       <c r="D39" s="7">
-        <v>-5.11</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0.77</v>
+        <v>-4.47</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.64</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2664,13 +2655,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>-1.02</v>
+        <v>-1.27</v>
       </c>
       <c r="D40" s="7">
-        <v>-1.27</v>
+        <v>0.24</v>
       </c>
       <c r="E40" s="8">
-        <v>-0.25</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2681,13 +2672,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="7">
-        <v>-2.78</v>
+        <v>-3.26</v>
       </c>
       <c r="D41" s="7">
-        <v>-3.26</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.48</v>
+        <v>-3.46</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2698,13 +2689,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="7">
-        <v>-42.29</v>
+        <v>-41.72</v>
       </c>
       <c r="D42" s="7">
-        <v>-41.72</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.57</v>
+        <v>-41.68</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.04</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2715,13 +2706,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="7">
-        <v>-2.74</v>
+        <v>-2.69</v>
       </c>
       <c r="D43" s="7">
-        <v>-2.69</v>
-      </c>
-      <c r="E43" s="9">
-        <v>0.05</v>
+        <v>-2.38</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.31</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2732,13 +2723,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="7">
-        <v>-7.93</v>
+        <v>-8.58</v>
       </c>
       <c r="D44" s="7">
-        <v>-8.58</v>
+        <v>-8.41</v>
       </c>
       <c r="E44" s="8">
-        <v>-0.65</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2749,13 +2740,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>-6.26</v>
+        <v>0</v>
       </c>
       <c r="D45" s="7">
-        <v>0</v>
+        <v>-0.86</v>
       </c>
       <c r="E45" s="9">
-        <v>6.26</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2766,13 +2757,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-18.46</v>
+        <v>-18.61</v>
       </c>
       <c r="D46" s="7">
-        <v>-18.61</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.15</v>
+        <v>-20.19</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2783,13 +2774,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-24.91</v>
+        <v>-24.34</v>
       </c>
       <c r="D47" s="7">
-        <v>-24.34</v>
-      </c>
-      <c r="E47" s="9">
-        <v>0.57</v>
+        <v>-23.83</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.51</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2800,13 +2791,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-11.86</v>
+        <v>-11.58</v>
       </c>
       <c r="D48" s="7">
-        <v>-11.58</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0.28</v>
+        <v>-10.23</v>
+      </c>
+      <c r="E48" s="8">
+        <v>1.35</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2817,13 +2808,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="7">
-        <v>412.9</v>
+        <v>410.85</v>
       </c>
       <c r="D49" s="7">
-        <v>410.85</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-2.05</v>
+        <v>410</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2834,13 +2825,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="7">
-        <v>53.95</v>
+        <v>54.48</v>
       </c>
       <c r="D50" s="7">
-        <v>54.48</v>
-      </c>
-      <c r="E50" s="9">
-        <v>0.53</v>
+        <v>54.52</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.04</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2851,13 +2842,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="7">
-        <v>3288</v>
+        <v>3289.6</v>
       </c>
       <c r="D51" s="7">
-        <v>3289.6</v>
-      </c>
-      <c r="E51" s="9">
-        <v>1.6</v>
+        <v>3299.9</v>
+      </c>
+      <c r="E51" s="8">
+        <v>10.3</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2868,13 +2859,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="7">
-        <v>1058.5</v>
+        <v>1051.05</v>
       </c>
       <c r="D52" s="7">
-        <v>1051.05</v>
+        <v>1053</v>
       </c>
       <c r="E52" s="8">
-        <v>-7.45</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2885,13 +2876,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="7">
-        <v>14.07</v>
+        <v>15.19</v>
       </c>
       <c r="D53" s="7">
-        <v>15.19</v>
+        <v>15.06</v>
       </c>
       <c r="E53" s="9">
-        <v>1.12</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2902,13 +2893,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="7">
-        <v>11.35</v>
+        <v>11.33</v>
       </c>
       <c r="D54" s="7">
-        <v>11.33</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.02</v>
+        <v>11.11</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2919,13 +2910,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>4362.1</v>
+        <v>4395.3</v>
       </c>
       <c r="D55" s="7">
-        <v>4395.3</v>
-      </c>
-      <c r="E55" s="9">
-        <v>33.2</v>
+        <v>4424.9</v>
+      </c>
+      <c r="E55" s="8">
+        <v>29.6</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2936,13 +2927,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>11504</v>
+        <v>11540</v>
       </c>
       <c r="D56" s="7">
-        <v>11540</v>
-      </c>
-      <c r="E56" s="9">
-        <v>36</v>
+        <v>11717</v>
+      </c>
+      <c r="E56" s="8">
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2953,13 +2944,13 @@
         <v>24</v>
       </c>
       <c r="C57" s="7">
-        <v>56.03</v>
+        <v>54.48</v>
       </c>
       <c r="D57" s="7">
-        <v>54.48</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-1.55</v>
+        <v>53.82</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2970,13 +2961,13 @@
         <v>24</v>
       </c>
       <c r="C58" s="7">
-        <v>33.46</v>
+        <v>36.49</v>
       </c>
       <c r="D58" s="7">
-        <v>36.49</v>
-      </c>
-      <c r="E58" s="9">
-        <v>3.03</v>
+        <v>36.72</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.23</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2987,13 +2978,13 @@
         <v>24</v>
       </c>
       <c r="C59" s="7">
-        <v>56.71</v>
+        <v>56.87</v>
       </c>
       <c r="D59" s="7">
-        <v>56.87</v>
-      </c>
-      <c r="E59" s="9">
-        <v>0.16</v>
+        <v>57.96</v>
+      </c>
+      <c r="E59" s="8">
+        <v>1.09</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3004,13 +2995,13 @@
         <v>24</v>
       </c>
       <c r="C60" s="7">
-        <v>60.61</v>
+        <v>58.21</v>
       </c>
       <c r="D60" s="7">
-        <v>58.21</v>
+        <v>58.67</v>
       </c>
       <c r="E60" s="8">
-        <v>-2.4</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3021,13 +3012,13 @@
         <v>24</v>
       </c>
       <c r="C61" s="7">
-        <v>60.06</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="D61" s="7">
-        <v>72.70999999999999</v>
+        <v>69.94</v>
       </c>
       <c r="E61" s="9">
-        <v>12.65</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3038,13 +3029,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="7">
-        <v>41.27</v>
+        <v>41</v>
       </c>
       <c r="D62" s="7">
-        <v>41</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.27</v>
+        <v>38.01</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-2.99</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3055,13 +3046,13 @@
         <v>24</v>
       </c>
       <c r="C63" s="7">
-        <v>48.64</v>
+        <v>51.37</v>
       </c>
       <c r="D63" s="7">
-        <v>51.37</v>
-      </c>
-      <c r="E63" s="9">
-        <v>2.73</v>
+        <v>53.73</v>
+      </c>
+      <c r="E63" s="8">
+        <v>2.36</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3072,13 +3063,13 @@
         <v>24</v>
       </c>
       <c r="C64" s="7">
-        <v>41.14</v>
+        <v>42.81</v>
       </c>
       <c r="D64" s="7">
-        <v>42.81</v>
-      </c>
-      <c r="E64" s="9">
-        <v>1.67</v>
+        <v>50.27</v>
+      </c>
+      <c r="E64" s="8">
+        <v>7.46</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3089,13 +3080,13 @@
         <v>31</v>
       </c>
       <c r="C65" s="7">
-        <v>-46.05</v>
+        <v>2.63</v>
       </c>
       <c r="D65" s="7">
-        <v>2.63</v>
+        <v>-43.6</v>
       </c>
       <c r="E65" s="9">
-        <v>48.68</v>
+        <v>-46.23</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3106,13 +3097,13 @@
         <v>31</v>
       </c>
       <c r="C66" s="7">
-        <v>-61.24</v>
+        <v>-60.6</v>
       </c>
       <c r="D66" s="7">
-        <v>-60.6</v>
-      </c>
-      <c r="E66" s="9">
-        <v>0.64</v>
+        <v>-45.77</v>
+      </c>
+      <c r="E66" s="8">
+        <v>14.83</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3123,13 +3114,13 @@
         <v>31</v>
       </c>
       <c r="C67" s="7">
-        <v>80.45999999999999</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="D67" s="7">
-        <v>83.26000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="E67" s="9">
-        <v>2.8</v>
+        <v>-74.94</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3140,13 +3131,13 @@
         <v>31</v>
       </c>
       <c r="C68" s="7">
-        <v>-15.63</v>
+        <v>-26.96</v>
       </c>
       <c r="D68" s="7">
-        <v>-26.96</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-11.33</v>
+        <v>-52.81</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-25.85</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3157,13 +3148,13 @@
         <v>31</v>
       </c>
       <c r="C69" s="7">
-        <v>-39.93</v>
+        <v>309.54</v>
       </c>
       <c r="D69" s="7">
-        <v>309.54</v>
+        <v>9.93</v>
       </c>
       <c r="E69" s="9">
-        <v>349.47</v>
+        <v>-299.61</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3174,13 +3165,13 @@
         <v>31</v>
       </c>
       <c r="C70" s="7">
-        <v>-78.87</v>
+        <v>-80.18000000000001</v>
       </c>
       <c r="D70" s="7">
-        <v>-80.18000000000001</v>
+        <v>-58.99</v>
       </c>
       <c r="E70" s="8">
-        <v>-1.31</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3191,13 +3182,13 @@
         <v>31</v>
       </c>
       <c r="C71" s="7">
-        <v>-59.94</v>
+        <v>-22.05</v>
       </c>
       <c r="D71" s="7">
-        <v>-22.05</v>
+        <v>-40.15</v>
       </c>
       <c r="E71" s="9">
-        <v>37.89</v>
+        <v>-18.1</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3208,13 +3199,13 @@
         <v>31</v>
       </c>
       <c r="C72" s="7">
-        <v>27.82</v>
+        <v>-4.59</v>
       </c>
       <c r="D72" s="7">
-        <v>-4.59</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-32.41</v>
+        <v>-11.54</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-6.95</v>
       </c>
     </row>
   </sheetData>
@@ -3244,28 +3235,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3279,16 +3270,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="12">
-        <v>51.7</v>
+        <v>52.4</v>
       </c>
       <c r="E2" s="12">
         <v>60</v>
       </c>
       <c r="F2" s="12">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="G2" s="12">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="H2" s="12">
         <v>56.1</v>
@@ -3422,28 +3413,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="15">
-        <v>0.3102</v>
+        <v>0.31</v>
       </c>
       <c r="B2" s="15">
-        <v>0.2038</v>
+        <v>0.207</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2022</v>
+        <v>0.2064</v>
       </c>
       <c r="D2" s="15">
-        <v>0.1925</v>
+        <v>0.2062</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1839</v>
+        <v>0.1861</v>
       </c>
       <c r="F2" s="15">
-        <v>0.0984</v>
+        <v>0.104</v>
       </c>
       <c r="G2" s="15">
-        <v>-0.2274</v>
+        <v>-0.2292</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.3006</v>
+        <v>-0.2995</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,40 +190,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>42.8 → 50.3</t>
-  </si>
-  <si>
-    <t>42.8</t>
-  </si>
-  <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>72.7 → 69.9</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>72.7</t>
-  </si>
-  <si>
-    <t>69.9</t>
+    <t>58.7 → 49.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>58.7</t>
+  </si>
+  <si>
+    <t>49.9</t>
+  </si>
+  <si>
+    <t>53.7 → 48.5</t>
+  </si>
+  <si>
+    <t>53.7</t>
+  </si>
+  <si>
+    <t>48.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -275,7 +263,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,27 +297,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -356,19 +337,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -438,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -446,15 +421,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -463,7 +437,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -965,7 +939,7 @@
         <v>410</v>
       </c>
       <c r="D2">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -980,19 +954,19 @@
         <v>49.17</v>
       </c>
       <c r="I2">
-        <v>3.54</v>
+        <v>0.24</v>
       </c>
       <c r="J2">
-        <v>4.77</v>
+        <v>3.12</v>
       </c>
       <c r="K2">
-        <v>12.36</v>
+        <v>12.85</v>
       </c>
       <c r="L2">
-        <v>40.75</v>
+        <v>43.18</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>30.6</v>
       </c>
       <c r="N2">
         <v>74</v>
@@ -1001,19 +975,19 @@
         <v>82</v>
       </c>
       <c r="P2">
-        <v>411.15</v>
+        <v>411.35</v>
       </c>
       <c r="Q2">
-        <v>409.2</v>
+        <v>410</v>
       </c>
       <c r="R2">
-        <v>400.68</v>
+        <v>401.43</v>
       </c>
       <c r="S2">
-        <v>358.22</v>
+        <v>358.61</v>
       </c>
       <c r="T2">
-        <v>14.45</v>
+        <v>14.33</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1031,31 +1005,31 @@
         <v>53.82</v>
       </c>
       <c r="Z2">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AA2">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="AB2">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="AC2">
-        <v>63.79</v>
+        <v>70.64</v>
       </c>
       <c r="AD2">
-        <v>57.97</v>
+        <v>63.84</v>
       </c>
       <c r="AE2">
-        <v>9.67</v>
+        <v>9.34</v>
       </c>
       <c r="AF2">
-        <v>-43.6</v>
+        <v>-60.03</v>
       </c>
       <c r="AG2">
-        <v>426.6</v>
+        <v>425.87</v>
       </c>
       <c r="AH2">
-        <v>391.79</v>
+        <v>394.12</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1064,7 +1038,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>20.44</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1075,58 +1049,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>54.52</v>
+        <v>53.64</v>
       </c>
       <c r="D3">
-        <v>0.07000000000000001</v>
+        <v>-1.61</v>
       </c>
       <c r="E3">
         <v>93.48</v>
       </c>
       <c r="F3">
-        <v>53.89</v>
+        <v>53.64</v>
       </c>
       <c r="G3">
-        <v>-41.68</v>
+        <v>-42.62</v>
       </c>
       <c r="H3">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.09</v>
+        <v>-2.03</v>
       </c>
       <c r="J3">
-        <v>-3.84</v>
+        <v>-7.61</v>
       </c>
       <c r="K3">
-        <v>-14.89</v>
+        <v>-16.98</v>
       </c>
       <c r="L3">
-        <v>-27.93</v>
+        <v>-33.98</v>
       </c>
       <c r="M3">
-        <v>-22.92</v>
+        <v>-23.32</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="P3">
-        <v>54.41</v>
+        <v>54.19</v>
       </c>
       <c r="Q3">
-        <v>57.91</v>
+        <v>57.65</v>
       </c>
       <c r="R3">
-        <v>58.68</v>
+        <v>58.52</v>
       </c>
       <c r="S3">
-        <v>65.68000000000001</v>
+        <v>65.55</v>
       </c>
       <c r="T3">
-        <v>-16.99</v>
+        <v>-18.17</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1141,43 +1115,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>36.72</v>
+        <v>33.77</v>
       </c>
       <c r="Z3">
-        <v>-1.43</v>
+        <v>-1.49</v>
       </c>
       <c r="AA3">
-        <v>-1.05</v>
+        <v>-1.13</v>
       </c>
       <c r="AB3">
-        <v>-0.38</v>
+        <v>-0.35</v>
       </c>
       <c r="AC3">
-        <v>6.98</v>
+        <v>7.5</v>
       </c>
       <c r="AD3">
-        <v>4.19</v>
+        <v>6.05</v>
       </c>
       <c r="AE3">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AF3">
-        <v>-45.77</v>
+        <v>-56.93</v>
       </c>
       <c r="AG3">
-        <v>64.62</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AH3">
-        <v>51.21</v>
+        <v>50.7</v>
       </c>
       <c r="AI3">
-        <v>59.39</v>
+        <v>59.14</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>47.18</v>
+        <v>48.17</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1188,10 +1162,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3299.9</v>
+        <v>3258</v>
       </c>
       <c r="D4">
-        <v>0.31</v>
+        <v>-1.27</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1200,46 +1174,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.38</v>
+        <v>-3.62</v>
       </c>
       <c r="H4">
-        <v>30.37</v>
+        <v>28.72</v>
       </c>
       <c r="I4">
-        <v>0.91</v>
+        <v>-1.27</v>
       </c>
       <c r="J4">
-        <v>5.89</v>
+        <v>4.66</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>4.34</v>
       </c>
       <c r="L4">
-        <v>14.53</v>
+        <v>15.79</v>
       </c>
       <c r="M4">
-        <v>18.61</v>
+        <v>17.99</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P4">
-        <v>3297.1</v>
+        <v>3288.7</v>
       </c>
       <c r="Q4">
-        <v>3258.58</v>
+        <v>3266.23</v>
       </c>
       <c r="R4">
-        <v>3187.31</v>
+        <v>3189.46</v>
       </c>
       <c r="S4">
-        <v>2918.17</v>
+        <v>2920.64</v>
       </c>
       <c r="T4">
-        <v>13.08</v>
+        <v>11.55</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1254,34 +1228,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>57.96</v>
+        <v>52.19</v>
       </c>
       <c r="Z4">
-        <v>36.6</v>
+        <v>32.25</v>
       </c>
       <c r="AA4">
-        <v>37.95</v>
+        <v>36.81</v>
       </c>
       <c r="AB4">
-        <v>-1.35</v>
+        <v>-4.56</v>
       </c>
       <c r="AC4">
-        <v>21.2</v>
+        <v>15.33</v>
       </c>
       <c r="AD4">
-        <v>29.7</v>
+        <v>21.92</v>
       </c>
       <c r="AE4">
-        <v>71.5</v>
+        <v>69.39</v>
       </c>
       <c r="AF4">
-        <v>8.32</v>
+        <v>-30.92</v>
       </c>
       <c r="AG4">
-        <v>3403.41</v>
+        <v>3391.75</v>
       </c>
       <c r="AH4">
-        <v>3113.74</v>
+        <v>3140.72</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1290,7 +1264,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>28.77</v>
+        <v>26.57</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1301,10 +1275,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1053</v>
+        <v>1024</v>
       </c>
       <c r="D5">
-        <v>0.19</v>
+        <v>-2.75</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1313,46 +1287,46 @@
         <v>701.4</v>
       </c>
       <c r="G5">
-        <v>-8.41</v>
+        <v>-10.93</v>
       </c>
       <c r="H5">
-        <v>50.13</v>
+        <v>45.99</v>
       </c>
       <c r="I5">
-        <v>1.35</v>
+        <v>-0.57</v>
       </c>
       <c r="J5">
-        <v>12.45</v>
+        <v>6.4</v>
       </c>
       <c r="K5">
-        <v>-8.41</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L5">
-        <v>48.88</v>
+        <v>45.41</v>
       </c>
       <c r="M5">
-        <v>20.64</v>
+        <v>19.2</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>1045.28</v>
+        <v>1044.11</v>
       </c>
       <c r="Q5">
-        <v>1035.03</v>
+        <v>1037.71</v>
       </c>
       <c r="R5">
-        <v>993.3</v>
+        <v>993.62</v>
       </c>
       <c r="S5">
-        <v>958.01</v>
+        <v>959.21</v>
       </c>
       <c r="T5">
-        <v>9.91</v>
+        <v>6.75</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1367,34 +1341,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>58.67</v>
+        <v>49.88</v>
       </c>
       <c r="Z5">
-        <v>16.27</v>
+        <v>13.67</v>
       </c>
       <c r="AA5">
-        <v>16.24</v>
+        <v>15.73</v>
       </c>
       <c r="AB5">
-        <v>0.03</v>
+        <v>-2.06</v>
       </c>
       <c r="AC5">
-        <v>30.54</v>
+        <v>17.56</v>
       </c>
       <c r="AD5">
-        <v>22.95</v>
+        <v>23.81</v>
       </c>
       <c r="AE5">
-        <v>23.53</v>
+        <v>24.83</v>
       </c>
       <c r="AF5">
-        <v>-52.81</v>
+        <v>-23.94</v>
       </c>
       <c r="AG5">
-        <v>1090.13</v>
+        <v>1084.1</v>
       </c>
       <c r="AH5">
-        <v>979.9299999999999</v>
+        <v>991.3200000000001</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1403,7 +1377,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>28.95</v>
+        <v>26.12</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1414,10 +1388,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>15.06</v>
+        <v>14.97</v>
       </c>
       <c r="D6">
-        <v>-0.86</v>
+        <v>-0.6</v>
       </c>
       <c r="E6">
         <v>15.19</v>
@@ -1426,46 +1400,46 @@
         <v>6.49</v>
       </c>
       <c r="G6">
-        <v>-0.86</v>
+        <v>-1.45</v>
       </c>
       <c r="H6">
-        <v>132.05</v>
+        <v>130.66</v>
       </c>
       <c r="I6">
-        <v>7.04</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
-        <v>16.29</v>
+        <v>14.71</v>
       </c>
       <c r="K6">
-        <v>6.21</v>
+        <v>7.01</v>
       </c>
       <c r="L6">
-        <v>129.92</v>
+        <v>111.74</v>
       </c>
       <c r="M6">
-        <v>20.62</v>
+        <v>20.07</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P6">
-        <v>14.46</v>
+        <v>14.65</v>
       </c>
       <c r="Q6">
-        <v>13.55</v>
+        <v>13.65</v>
       </c>
       <c r="R6">
         <v>13.82</v>
       </c>
       <c r="S6">
-        <v>11.75</v>
+        <v>11.78</v>
       </c>
       <c r="T6">
-        <v>28.14</v>
+        <v>27.08</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1480,34 +1454,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>69.94</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="Z6">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="AA6">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="AB6">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AC6">
-        <v>92.67</v>
+        <v>92.83</v>
       </c>
       <c r="AD6">
-        <v>87.95999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="AE6">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AF6">
-        <v>9.93</v>
+        <v>-3.14</v>
       </c>
       <c r="AG6">
-        <v>15.08</v>
+        <v>15.27</v>
       </c>
       <c r="AH6">
-        <v>12.02</v>
+        <v>12.03</v>
       </c>
       <c r="AI6">
         <v>13.86</v>
@@ -1516,7 +1490,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>64.55</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1530,7 +1504,7 @@
         <v>11.11</v>
       </c>
       <c r="D7">
-        <v>-1.94</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1545,40 +1519,40 @@
         <v>136.89</v>
       </c>
       <c r="I7">
-        <v>-5.2</v>
+        <v>-4.88</v>
       </c>
       <c r="J7">
-        <v>0.82</v>
+        <v>-2.29</v>
       </c>
       <c r="K7">
-        <v>-15.58</v>
+        <v>-11.19</v>
       </c>
       <c r="L7">
-        <v>110.02</v>
+        <v>114.48</v>
       </c>
       <c r="M7">
-        <v>-29.95</v>
+        <v>-30.35</v>
       </c>
       <c r="N7">
         <v>87</v>
       </c>
       <c r="O7">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P7">
-        <v>11.39</v>
+        <v>11.28</v>
       </c>
       <c r="Q7">
-        <v>12.15</v>
+        <v>12.11</v>
       </c>
       <c r="R7">
-        <v>11.63</v>
+        <v>11.61</v>
       </c>
       <c r="S7">
-        <v>10.11</v>
+        <v>10.14</v>
       </c>
       <c r="T7">
-        <v>9.93</v>
+        <v>9.6</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1596,40 +1570,40 @@
         <v>38.01</v>
       </c>
       <c r="Z7">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="AA7">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="AB7">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="AC7">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="AF7">
-        <v>-58.99</v>
+        <v>-41.84</v>
       </c>
       <c r="AG7">
-        <v>13.56</v>
+        <v>13.59</v>
       </c>
       <c r="AH7">
-        <v>10.75</v>
+        <v>10.64</v>
       </c>
       <c r="AI7">
-        <v>12.05</v>
+        <v>11.9</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>36.12</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1640,10 +1614,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4424.9</v>
+        <v>4363.8</v>
       </c>
       <c r="D8">
-        <v>0.67</v>
+        <v>-1.38</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1652,25 +1626,25 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-23.83</v>
+        <v>-24.89</v>
       </c>
       <c r="H8">
-        <v>6.49</v>
+        <v>5.02</v>
       </c>
       <c r="I8">
-        <v>3.1</v>
+        <v>1.26</v>
       </c>
       <c r="J8">
-        <v>4.36</v>
+        <v>1.26</v>
       </c>
       <c r="K8">
-        <v>-4.47</v>
+        <v>-2.8</v>
       </c>
       <c r="L8">
-        <v>-13.08</v>
+        <v>-13.41</v>
       </c>
       <c r="M8">
-        <v>20.7</v>
+        <v>20.04</v>
       </c>
       <c r="N8">
         <v>26</v>
@@ -1679,19 +1653,19 @@
         <v>43</v>
       </c>
       <c r="P8">
-        <v>4369.74</v>
+        <v>4380.6</v>
       </c>
       <c r="Q8">
-        <v>4380.45</v>
+        <v>4382.76</v>
       </c>
       <c r="R8">
-        <v>4379.36</v>
+        <v>4378.02</v>
       </c>
       <c r="S8">
-        <v>4661.1</v>
+        <v>4656.62</v>
       </c>
       <c r="T8">
-        <v>-5.07</v>
+        <v>-6.29</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1706,34 +1680,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>53.73</v>
+        <v>48.49</v>
       </c>
       <c r="Z8">
-        <v>5.62</v>
+        <v>3.25</v>
       </c>
       <c r="AA8">
-        <v>5.68</v>
+        <v>5.19</v>
       </c>
       <c r="AB8">
-        <v>-0.06</v>
+        <v>-1.95</v>
       </c>
       <c r="AC8">
-        <v>37.85</v>
+        <v>37.64</v>
       </c>
       <c r="AD8">
-        <v>28.8</v>
+        <v>35.02</v>
       </c>
       <c r="AE8">
-        <v>97.06999999999999</v>
+        <v>97.28</v>
       </c>
       <c r="AF8">
-        <v>-40.15</v>
+        <v>-26.58</v>
       </c>
       <c r="AG8">
-        <v>4535.4</v>
+        <v>4535.13</v>
       </c>
       <c r="AH8">
-        <v>4225.51</v>
+        <v>4230.39</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1742,7 +1716,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>20.78</v>
+        <v>18.59</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1756,7 +1730,7 @@
         <v>11717</v>
       </c>
       <c r="D9">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1771,37 +1745,37 @@
         <v>13.08</v>
       </c>
       <c r="I9">
-        <v>2.33</v>
+        <v>1.23</v>
       </c>
       <c r="J9">
-        <v>-2</v>
+        <v>-2.34</v>
       </c>
       <c r="K9">
-        <v>0.24</v>
+        <v>2.05</v>
       </c>
       <c r="L9">
-        <v>-8.960000000000001</v>
+        <v>-6.93</v>
       </c>
       <c r="M9">
-        <v>10.4</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="P9">
-        <v>11581.2</v>
+        <v>11609.6</v>
       </c>
       <c r="Q9">
-        <v>11786.6</v>
+        <v>11780.1</v>
       </c>
       <c r="R9">
-        <v>11691.76</v>
+        <v>11698.64</v>
       </c>
       <c r="S9">
-        <v>11779.09</v>
+        <v>11779.04</v>
       </c>
       <c r="T9">
         <v>-0.53</v>
@@ -1822,31 +1796,31 @@
         <v>50.27</v>
       </c>
       <c r="Z9">
-        <v>-58.27</v>
+        <v>-48.71</v>
       </c>
       <c r="AA9">
-        <v>-26.77</v>
+        <v>-31.16</v>
       </c>
       <c r="AB9">
-        <v>-31.5</v>
+        <v>-17.55</v>
       </c>
       <c r="AC9">
-        <v>29.59</v>
+        <v>47.15</v>
       </c>
       <c r="AD9">
-        <v>21.53</v>
+        <v>31.46</v>
       </c>
       <c r="AE9">
-        <v>191.52</v>
+        <v>187.91</v>
       </c>
       <c r="AF9">
-        <v>-11.54</v>
+        <v>41.88</v>
       </c>
       <c r="AG9">
-        <v>12262.42</v>
+        <v>12255.99</v>
       </c>
       <c r="AH9">
-        <v>11310.78</v>
+        <v>11304.21</v>
       </c>
       <c r="AI9">
         <v>12053.63</v>
@@ -1855,7 +1829,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>27.55</v>
+        <v>26.38</v>
       </c>
     </row>
   </sheetData>
@@ -1996,7 +1970,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2036,7 +2010,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2048,1170 +2022,997 @@
         <v>58</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>58</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>4.77</v>
+      </c>
+      <c r="D8" s="6">
+        <v>3.12</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-3.84</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-7.61</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-3.77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>5.89</v>
+      </c>
+      <c r="D10" s="6">
+        <v>4.66</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>12.45</v>
+      </c>
+      <c r="D11" s="6">
+        <v>6.4</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-6.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>16.29</v>
+      </c>
+      <c r="D12" s="6">
+        <v>14.71</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.82</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-2.29</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-3.11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>4.36</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1.26</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-2</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-2.34</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2.6</v>
-      </c>
-      <c r="D9" s="7">
-        <v>4.77</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>3.54</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-4.5</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-3.84</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.03</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>5.69</v>
-      </c>
-      <c r="D11" s="7">
-        <v>5.89</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.27</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>11.19</v>
-      </c>
-      <c r="D12" s="7">
-        <v>12.45</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1.35</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-0.57</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>7.04</v>
+      </c>
+      <c r="D20" s="6">
+        <v>6.7</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-5.2</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-4.88</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="D22" s="6">
         <v>1.26</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="E22" s="7">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1.23</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>40.75</v>
+      </c>
+      <c r="D24" s="6">
+        <v>43.18</v>
+      </c>
+      <c r="E24" s="8">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-27.93</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-33.98</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-6.05</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>14.53</v>
+      </c>
+      <c r="D26" s="6">
+        <v>15.79</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>48.88</v>
+      </c>
+      <c r="D27" s="6">
+        <v>45.41</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3.47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>16.31</v>
-      </c>
-      <c r="D13" s="7">
-        <v>16.29</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>129.92</v>
+      </c>
+      <c r="D28" s="6">
+        <v>111.74</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-18.18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-1.05</v>
-      </c>
-      <c r="D14" s="7">
-        <v>0.82</v>
-      </c>
-      <c r="E14" s="8">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>110.02</v>
+      </c>
+      <c r="D29" s="6">
+        <v>114.48</v>
+      </c>
+      <c r="E29" s="8">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1.15</v>
-      </c>
-      <c r="D15" s="7">
-        <v>4.36</v>
-      </c>
-      <c r="E15" s="8">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-13.08</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-13.41</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-2.87</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-2</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-6.93</v>
+      </c>
+      <c r="E31" s="8">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>2.2</v>
-      </c>
-      <c r="D17" s="7">
-        <v>3.54</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>12.36</v>
+      </c>
+      <c r="D32" s="6">
+        <v>12.85</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-0.89</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0.09</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-14.89</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-16.98</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>0.33</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0.91</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>4.1</v>
+      </c>
+      <c r="D34" s="6">
+        <v>4.34</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0.91</v>
-      </c>
-      <c r="D20" s="7">
-        <v>1.35</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-8.41</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>7.58</v>
-      </c>
-      <c r="D21" s="7">
-        <v>7.04</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>6.21</v>
+      </c>
+      <c r="D36" s="6">
+        <v>7.01</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-5.19</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-5.2</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-15.58</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-11.19</v>
+      </c>
+      <c r="E37" s="8">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>0.22</v>
-      </c>
-      <c r="D23" s="7">
-        <v>3.1</v>
-      </c>
-      <c r="E23" s="8">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-4.47</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-2.8</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>0.36</v>
-      </c>
-      <c r="D24" s="7">
-        <v>2.33</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="D39" s="6">
+        <v>2.05</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-41.68</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-42.62</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-2.38</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-3.62</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-8.41</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-10.93</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-0.86</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-1.45</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-23.83</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-24.89</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>54.52</v>
+      </c>
+      <c r="D45" s="6">
+        <v>53.64</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>3299.9</v>
+      </c>
+      <c r="D46" s="6">
+        <v>3258</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-41.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1053</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1024</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>15.06</v>
+      </c>
+      <c r="D48" s="6">
+        <v>14.97</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>4424.9</v>
+      </c>
+      <c r="D49" s="6">
+        <v>4363.8</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-61.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>36.72</v>
+      </c>
+      <c r="D50" s="6">
+        <v>33.77</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-2.95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>57.96</v>
+      </c>
+      <c r="D51" s="6">
+        <v>52.19</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-5.77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>58.67</v>
+      </c>
+      <c r="D52" s="6">
+        <v>49.88</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-8.789999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>69.94</v>
+      </c>
+      <c r="D53" s="6">
+        <v>68.01000000000001</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>53.73</v>
+      </c>
+      <c r="D54" s="6">
+        <v>48.49</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-5.24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>44.95</v>
-      </c>
-      <c r="D25" s="7">
-        <v>40.75</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-4.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B55" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="6">
+        <v>-43.6</v>
+      </c>
+      <c r="D55" s="6">
+        <v>-60.03</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-16.43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-28.56</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-27.93</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-45.77</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-56.93</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-11.16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>14.82</v>
-      </c>
-      <c r="D27" s="7">
-        <v>14.53</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>8.32</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-30.92</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-39.24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>49.97</v>
-      </c>
-      <c r="D28" s="7">
-        <v>48.88</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-52.81</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-23.94</v>
+      </c>
+      <c r="E58" s="8">
+        <v>28.87</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>123.71</v>
-      </c>
-      <c r="D29" s="7">
-        <v>129.92</v>
-      </c>
-      <c r="E29" s="8">
-        <v>6.21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>9.93</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-3.14</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-13.07</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>109.81</v>
-      </c>
-      <c r="D30" s="7">
-        <v>110.02</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-58.99</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-41.84</v>
+      </c>
+      <c r="E60" s="8">
+        <v>17.15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-14.3</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-13.08</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-40.15</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-26.58</v>
+      </c>
+      <c r="E61" s="8">
+        <v>13.57</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-10.36</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="E32" s="8">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>12.59</v>
-      </c>
-      <c r="D33" s="7">
-        <v>12.36</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-14.95</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-14.89</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>3.77</v>
-      </c>
-      <c r="D35" s="7">
-        <v>4.1</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-8.58</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-8.41</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>7.12</v>
-      </c>
-      <c r="D37" s="7">
-        <v>6.21</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-13.91</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-15.58</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-5.11</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-4.47</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-1.27</v>
-      </c>
-      <c r="D40" s="7">
-        <v>0.24</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-3.26</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-3.46</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-41.72</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-41.68</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-2.69</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-2.38</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-8.58</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-8.41</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>0</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-0.86</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-18.61</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-20.19</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-24.34</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-23.83</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-11.58</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-10.23</v>
-      </c>
-      <c r="E48" s="8">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>410.85</v>
-      </c>
-      <c r="D49" s="7">
-        <v>410</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>54.48</v>
-      </c>
-      <c r="D50" s="7">
-        <v>54.52</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="7">
-        <v>3289.6</v>
-      </c>
-      <c r="D51" s="7">
-        <v>3299.9</v>
-      </c>
-      <c r="E51" s="8">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="7">
-        <v>1051.05</v>
-      </c>
-      <c r="D52" s="7">
-        <v>1053</v>
-      </c>
-      <c r="E52" s="8">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>15.19</v>
-      </c>
-      <c r="D53" s="7">
-        <v>15.06</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>11.33</v>
-      </c>
-      <c r="D54" s="7">
-        <v>11.11</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>4395.3</v>
-      </c>
-      <c r="D55" s="7">
-        <v>4424.9</v>
-      </c>
-      <c r="E55" s="8">
-        <v>29.6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>11540</v>
-      </c>
-      <c r="D56" s="7">
-        <v>11717</v>
-      </c>
-      <c r="E56" s="8">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>54.48</v>
-      </c>
-      <c r="D57" s="7">
-        <v>53.82</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>36.49</v>
-      </c>
-      <c r="D58" s="7">
-        <v>36.72</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>56.87</v>
-      </c>
-      <c r="D59" s="7">
-        <v>57.96</v>
-      </c>
-      <c r="E59" s="8">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="7">
-        <v>58.21</v>
-      </c>
-      <c r="D60" s="7">
-        <v>58.67</v>
-      </c>
-      <c r="E60" s="8">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="7">
-        <v>72.70999999999999</v>
-      </c>
-      <c r="D61" s="7">
-        <v>69.94</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-2.77</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="7">
-        <v>41</v>
-      </c>
-      <c r="D62" s="7">
-        <v>38.01</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-2.99</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="7">
-        <v>51.37</v>
-      </c>
-      <c r="D63" s="7">
-        <v>53.73</v>
-      </c>
-      <c r="E63" s="8">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>42.81</v>
-      </c>
-      <c r="D64" s="7">
-        <v>50.27</v>
-      </c>
-      <c r="E64" s="8">
-        <v>7.46</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C65" s="7">
-        <v>2.63</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-43.6</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-46.23</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>-60.6</v>
-      </c>
-      <c r="D66" s="7">
-        <v>-45.77</v>
-      </c>
-      <c r="E66" s="8">
-        <v>14.83</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="7">
-        <v>83.26000000000001</v>
-      </c>
-      <c r="D67" s="7">
-        <v>8.32</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-74.94</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="7">
-        <v>-26.96</v>
-      </c>
-      <c r="D68" s="7">
-        <v>-52.81</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-25.85</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="7">
-        <v>309.54</v>
-      </c>
-      <c r="D69" s="7">
-        <v>9.93</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-299.61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="7">
-        <v>-80.18000000000001</v>
-      </c>
-      <c r="D70" s="7">
-        <v>-58.99</v>
-      </c>
-      <c r="E70" s="8">
-        <v>21.19</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="7">
-        <v>-22.05</v>
-      </c>
-      <c r="D71" s="7">
-        <v>-40.15</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-18.1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="7">
-        <v>-4.59</v>
-      </c>
-      <c r="D72" s="7">
+      <c r="C62" s="6">
         <v>-11.54</v>
       </c>
-      <c r="E72" s="9">
-        <v>-6.95</v>
+      <c r="D62" s="6">
+        <v>41.88</v>
+      </c>
+      <c r="E62" s="8">
+        <v>53.42</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3231,60 +3032,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>56.44</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>8</v>
       </c>
-      <c r="D2" s="12">
-        <v>52.4</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
-        <v>4.8</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-2.6</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>2.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-1.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>50</v>
       </c>
     </row>
@@ -3386,55 +3187,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="15">
-        <v>0.31</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.207</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2064</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2062</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1861</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.104</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.2292</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.2995</v>
+      <c r="A2" s="14">
+        <v>0.306</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2007</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2004</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.192</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1799</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0964</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2332</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.3035</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="86">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,25 +193,52 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>58.7 → 49.9</t>
+    <t>49.9 → 53.4</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>49.9</t>
+  </si>
+  <si>
+    <t>53.4</t>
+  </si>
+  <si>
+    <t>48.5 → 50.5</t>
+  </si>
+  <si>
+    <t>48.5</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.4% → -3.4%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.4%</t>
+  </si>
+  <si>
+    <t>-3.4%</t>
+  </si>
+  <si>
+    <t>50.3 → 45.3</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>58.7</t>
-  </si>
-  <si>
-    <t>49.9</t>
-  </si>
-  <si>
-    <t>53.7 → 48.5</t>
-  </si>
-  <si>
-    <t>53.7</t>
-  </si>
-  <si>
-    <t>48.5</t>
+    <t>50.3</t>
+  </si>
+  <si>
+    <t>45.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -263,7 +290,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,20 +324,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,13 +371,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -421,14 +461,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -437,7 +479,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -936,10 +978,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>410</v>
+        <v>405.55</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -948,25 +990,25 @@
         <v>274.85</v>
       </c>
       <c r="G2">
-        <v>-3.46</v>
+        <v>-4.51</v>
       </c>
       <c r="H2">
-        <v>49.17</v>
+        <v>47.55</v>
       </c>
       <c r="I2">
-        <v>0.24</v>
+        <v>-1.8</v>
       </c>
       <c r="J2">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="K2">
-        <v>12.85</v>
+        <v>15.69</v>
       </c>
       <c r="L2">
-        <v>43.18</v>
+        <v>42.2</v>
       </c>
       <c r="M2">
-        <v>30.6</v>
+        <v>29.92</v>
       </c>
       <c r="N2">
         <v>74</v>
@@ -975,19 +1017,19 @@
         <v>82</v>
       </c>
       <c r="P2">
-        <v>411.35</v>
+        <v>409.86</v>
       </c>
       <c r="Q2">
-        <v>410</v>
+        <v>410.06</v>
       </c>
       <c r="R2">
-        <v>401.43</v>
+        <v>402.13</v>
       </c>
       <c r="S2">
-        <v>358.61</v>
+        <v>358.99</v>
       </c>
       <c r="T2">
-        <v>14.33</v>
+        <v>12.97</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1002,34 +1044,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>53.82</v>
+        <v>50.11</v>
       </c>
       <c r="Z2">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="AA2">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="AB2">
-        <v>-0.32</v>
+        <v>-0.61</v>
       </c>
       <c r="AC2">
-        <v>70.64</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="AD2">
-        <v>63.84</v>
+        <v>66.92</v>
       </c>
       <c r="AE2">
-        <v>9.34</v>
+        <v>9.07</v>
       </c>
       <c r="AF2">
-        <v>-60.03</v>
+        <v>-68.65000000000001</v>
       </c>
       <c r="AG2">
-        <v>425.87</v>
+        <v>425.85</v>
       </c>
       <c r="AH2">
-        <v>394.12</v>
+        <v>394.26</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1038,7 +1080,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>19.79</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1049,58 +1091,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>53.64</v>
+        <v>52.49</v>
       </c>
       <c r="D3">
-        <v>-1.61</v>
+        <v>-2.14</v>
       </c>
       <c r="E3">
         <v>93.48</v>
       </c>
       <c r="F3">
-        <v>53.64</v>
+        <v>52.49</v>
       </c>
       <c r="G3">
-        <v>-42.62</v>
+        <v>-43.85</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-2.03</v>
+        <v>-3.42</v>
       </c>
       <c r="J3">
-        <v>-7.61</v>
+        <v>-10.94</v>
       </c>
       <c r="K3">
-        <v>-16.98</v>
+        <v>-16.36</v>
       </c>
       <c r="L3">
-        <v>-33.98</v>
+        <v>-35.97</v>
       </c>
       <c r="M3">
-        <v>-23.32</v>
+        <v>-24.11</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P3">
-        <v>54.19</v>
+        <v>53.82</v>
       </c>
       <c r="Q3">
-        <v>57.65</v>
+        <v>57.26</v>
       </c>
       <c r="R3">
-        <v>58.52</v>
+        <v>58.34</v>
       </c>
       <c r="S3">
-        <v>65.55</v>
+        <v>65.42</v>
       </c>
       <c r="T3">
-        <v>-18.17</v>
+        <v>-19.76</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1115,43 +1157,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>33.77</v>
+        <v>30.34</v>
       </c>
       <c r="Z3">
-        <v>-1.49</v>
+        <v>-1.61</v>
       </c>
       <c r="AA3">
-        <v>-1.13</v>
+        <v>-1.23</v>
       </c>
       <c r="AB3">
-        <v>-0.35</v>
+        <v>-0.38</v>
       </c>
       <c r="AC3">
-        <v>7.5</v>
+        <v>4.14</v>
       </c>
       <c r="AD3">
-        <v>6.05</v>
+        <v>6.2</v>
       </c>
       <c r="AE3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF3">
-        <v>-56.93</v>
+        <v>-40.21</v>
       </c>
       <c r="AG3">
-        <v>64.59999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="AH3">
-        <v>50.7</v>
+        <v>50.06</v>
       </c>
       <c r="AI3">
-        <v>59.14</v>
+        <v>58.13</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>48.17</v>
+        <v>50.44</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1162,10 +1204,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3258</v>
+        <v>3290</v>
       </c>
       <c r="D4">
-        <v>-1.27</v>
+        <v>0.98</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1174,46 +1216,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-3.62</v>
+        <v>-2.68</v>
       </c>
       <c r="H4">
-        <v>28.72</v>
+        <v>29.98</v>
       </c>
       <c r="I4">
-        <v>-1.27</v>
+        <v>-0.54</v>
       </c>
       <c r="J4">
-        <v>4.66</v>
+        <v>5.96</v>
       </c>
       <c r="K4">
-        <v>4.34</v>
+        <v>6.04</v>
       </c>
       <c r="L4">
-        <v>15.79</v>
+        <v>17.02</v>
       </c>
       <c r="M4">
-        <v>17.99</v>
+        <v>18.03</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>3288.7</v>
+        <v>3285.1</v>
       </c>
       <c r="Q4">
-        <v>3266.23</v>
+        <v>3275.69</v>
       </c>
       <c r="R4">
-        <v>3189.46</v>
+        <v>3192.36</v>
       </c>
       <c r="S4">
-        <v>2920.64</v>
+        <v>2923.22</v>
       </c>
       <c r="T4">
-        <v>11.55</v>
+        <v>12.55</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1228,34 +1270,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>52.19</v>
+        <v>55.81</v>
       </c>
       <c r="Z4">
-        <v>32.25</v>
+        <v>31.02</v>
       </c>
       <c r="AA4">
-        <v>36.81</v>
+        <v>35.66</v>
       </c>
       <c r="AB4">
-        <v>-4.56</v>
+        <v>-4.63</v>
       </c>
       <c r="AC4">
-        <v>15.33</v>
+        <v>22.02</v>
       </c>
       <c r="AD4">
-        <v>21.92</v>
+        <v>19.51</v>
       </c>
       <c r="AE4">
-        <v>69.39</v>
+        <v>68.97</v>
       </c>
       <c r="AF4">
-        <v>-30.92</v>
+        <v>-37.49</v>
       </c>
       <c r="AG4">
-        <v>3391.75</v>
+        <v>3374.35</v>
       </c>
       <c r="AH4">
-        <v>3140.72</v>
+        <v>3177.04</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1264,7 +1306,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>26.57</v>
+        <v>23.83</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1275,10 +1317,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1024</v>
+        <v>1037.4</v>
       </c>
       <c r="D5">
-        <v>-2.75</v>
+        <v>1.31</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1287,46 +1329,46 @@
         <v>701.4</v>
       </c>
       <c r="G5">
-        <v>-10.93</v>
+        <v>-9.77</v>
       </c>
       <c r="H5">
-        <v>45.99</v>
+        <v>47.9</v>
       </c>
       <c r="I5">
-        <v>-0.57</v>
+        <v>0.33</v>
       </c>
       <c r="J5">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="K5">
-        <v>-9.119999999999999</v>
+        <v>-9.1</v>
       </c>
       <c r="L5">
-        <v>45.41</v>
+        <v>44.92</v>
       </c>
       <c r="M5">
-        <v>19.2</v>
+        <v>18.99</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>1044.11</v>
+        <v>1044.79</v>
       </c>
       <c r="Q5">
-        <v>1037.71</v>
+        <v>1040.86</v>
       </c>
       <c r="R5">
-        <v>993.62</v>
+        <v>994.2</v>
       </c>
       <c r="S5">
-        <v>959.21</v>
+        <v>960.4299999999999</v>
       </c>
       <c r="T5">
-        <v>6.75</v>
+        <v>8.01</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1341,34 +1383,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.88</v>
+        <v>53.36</v>
       </c>
       <c r="Z5">
-        <v>13.67</v>
+        <v>12.54</v>
       </c>
       <c r="AA5">
-        <v>15.73</v>
+        <v>15.09</v>
       </c>
       <c r="AB5">
-        <v>-2.06</v>
+        <v>-2.55</v>
       </c>
       <c r="AC5">
-        <v>17.56</v>
+        <v>14.69</v>
       </c>
       <c r="AD5">
-        <v>23.81</v>
+        <v>20.93</v>
       </c>
       <c r="AE5">
-        <v>24.83</v>
+        <v>24.02</v>
       </c>
       <c r="AF5">
-        <v>-23.94</v>
+        <v>-64.91</v>
       </c>
       <c r="AG5">
-        <v>1084.1</v>
+        <v>1076.46</v>
       </c>
       <c r="AH5">
-        <v>991.3200000000001</v>
+        <v>1005.25</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1377,7 +1419,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>26.12</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1388,10 +1430,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.97</v>
+        <v>14.68</v>
       </c>
       <c r="D6">
-        <v>-0.6</v>
+        <v>-1.94</v>
       </c>
       <c r="E6">
         <v>15.19</v>
@@ -1400,46 +1442,46 @@
         <v>6.49</v>
       </c>
       <c r="G6">
-        <v>-1.45</v>
+        <v>-3.36</v>
       </c>
       <c r="H6">
-        <v>130.66</v>
+        <v>126.19</v>
       </c>
       <c r="I6">
-        <v>6.7</v>
+        <v>5.31</v>
       </c>
       <c r="J6">
-        <v>14.71</v>
+        <v>14.06</v>
       </c>
       <c r="K6">
-        <v>7.01</v>
+        <v>5.23</v>
       </c>
       <c r="L6">
-        <v>111.74</v>
+        <v>98.38</v>
       </c>
       <c r="M6">
-        <v>20.07</v>
+        <v>19.82</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P6">
-        <v>14.65</v>
+        <v>14.79</v>
       </c>
       <c r="Q6">
-        <v>13.65</v>
+        <v>13.73</v>
       </c>
       <c r="R6">
-        <v>13.82</v>
+        <v>13.81</v>
       </c>
       <c r="S6">
-        <v>11.78</v>
+        <v>11.8</v>
       </c>
       <c r="T6">
-        <v>27.08</v>
+        <v>24.38</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1454,34 +1496,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>68.01000000000001</v>
+        <v>62.06</v>
       </c>
       <c r="Z6">
         <v>0.37</v>
       </c>
       <c r="AA6">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="AB6">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AC6">
-        <v>92.83</v>
+        <v>82.05</v>
       </c>
       <c r="AD6">
-        <v>91.2</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="AE6">
         <v>0.44</v>
       </c>
       <c r="AF6">
-        <v>-3.14</v>
+        <v>-16.99</v>
       </c>
       <c r="AG6">
-        <v>15.27</v>
+        <v>15.39</v>
       </c>
       <c r="AH6">
-        <v>12.03</v>
+        <v>12.08</v>
       </c>
       <c r="AI6">
         <v>13.86</v>
@@ -1490,7 +1532,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>65.8</v>
+        <v>62.46</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1501,10 +1543,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.11</v>
+        <v>11.3</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1513,46 +1555,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-20.19</v>
+        <v>-18.82</v>
       </c>
       <c r="H7">
-        <v>136.89</v>
+        <v>140.94</v>
       </c>
       <c r="I7">
-        <v>-4.88</v>
+        <v>-1.74</v>
       </c>
       <c r="J7">
-        <v>-2.29</v>
+        <v>-5.28</v>
       </c>
       <c r="K7">
-        <v>-11.19</v>
+        <v>-9.02</v>
       </c>
       <c r="L7">
-        <v>114.48</v>
+        <v>108.1</v>
       </c>
       <c r="M7">
-        <v>-30.35</v>
+        <v>-30.63</v>
       </c>
       <c r="N7">
         <v>87</v>
       </c>
       <c r="O7">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P7">
-        <v>11.28</v>
+        <v>11.24</v>
       </c>
       <c r="Q7">
-        <v>12.11</v>
+        <v>12.05</v>
       </c>
       <c r="R7">
-        <v>11.61</v>
+        <v>11.59</v>
       </c>
       <c r="S7">
-        <v>10.14</v>
+        <v>10.17</v>
       </c>
       <c r="T7">
-        <v>9.6</v>
+        <v>11.13</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1567,34 +1609,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>38.01</v>
+        <v>42.23</v>
       </c>
       <c r="Z7">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="AA7">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="AB7">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>8.77</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE7">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="AF7">
-        <v>-41.84</v>
+        <v>-53.06</v>
       </c>
       <c r="AG7">
-        <v>13.59</v>
+        <v>13.56</v>
       </c>
       <c r="AH7">
-        <v>10.64</v>
+        <v>10.55</v>
       </c>
       <c r="AI7">
         <v>11.9</v>
@@ -1603,7 +1645,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>39.2</v>
+        <v>38.85</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1614,10 +1656,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4363.8</v>
+        <v>4387.9</v>
       </c>
       <c r="D8">
-        <v>-1.38</v>
+        <v>0.55</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1626,46 +1668,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-24.89</v>
+        <v>-24.47</v>
       </c>
       <c r="H8">
-        <v>5.02</v>
+        <v>5.6</v>
       </c>
       <c r="I8">
-        <v>1.26</v>
+        <v>0.71</v>
       </c>
       <c r="J8">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="K8">
-        <v>-2.8</v>
+        <v>0.68</v>
       </c>
       <c r="L8">
-        <v>-13.41</v>
+        <v>-11.81</v>
       </c>
       <c r="M8">
-        <v>20.04</v>
+        <v>19.75</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P8">
-        <v>4380.6</v>
+        <v>4386.8</v>
       </c>
       <c r="Q8">
-        <v>4382.76</v>
+        <v>4387.01</v>
       </c>
       <c r="R8">
-        <v>4378.02</v>
+        <v>4376.96</v>
       </c>
       <c r="S8">
-        <v>4656.62</v>
+        <v>4652.63</v>
       </c>
       <c r="T8">
-        <v>-6.29</v>
+        <v>-5.69</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1680,34 +1722,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>48.49</v>
+        <v>50.54</v>
       </c>
       <c r="Z8">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="AA8">
-        <v>5.19</v>
+        <v>4.81</v>
       </c>
       <c r="AB8">
-        <v>-1.95</v>
+        <v>-1.54</v>
       </c>
       <c r="AC8">
-        <v>37.64</v>
+        <v>36.4</v>
       </c>
       <c r="AD8">
-        <v>35.02</v>
+        <v>37.3</v>
       </c>
       <c r="AE8">
-        <v>97.28</v>
+        <v>94.31</v>
       </c>
       <c r="AF8">
-        <v>-26.58</v>
+        <v>-77.69</v>
       </c>
       <c r="AG8">
-        <v>4535.13</v>
+        <v>4534.67</v>
       </c>
       <c r="AH8">
-        <v>4230.39</v>
+        <v>4239.35</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1716,7 +1758,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>18.59</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1727,10 +1769,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11717</v>
+        <v>11589</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1739,46 +1781,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-10.23</v>
+        <v>-11.21</v>
       </c>
       <c r="H9">
-        <v>13.08</v>
+        <v>11.84</v>
       </c>
       <c r="I9">
-        <v>1.23</v>
+        <v>0.16</v>
       </c>
       <c r="J9">
-        <v>-2.34</v>
+        <v>-2.18</v>
       </c>
       <c r="K9">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="L9">
-        <v>-6.93</v>
+        <v>-8.07</v>
       </c>
       <c r="M9">
-        <v>9.640000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P9">
-        <v>11609.6</v>
+        <v>11613.4</v>
       </c>
       <c r="Q9">
-        <v>11780.1</v>
+        <v>11764.4</v>
       </c>
       <c r="R9">
-        <v>11698.64</v>
+        <v>11701.82</v>
       </c>
       <c r="S9">
-        <v>11779.04</v>
+        <v>11777.86</v>
       </c>
       <c r="T9">
-        <v>-0.53</v>
+        <v>-1.6</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1793,34 +1835,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>50.27</v>
+        <v>45.32</v>
       </c>
       <c r="Z9">
-        <v>-48.71</v>
+        <v>-50.88</v>
       </c>
       <c r="AA9">
-        <v>-31.16</v>
+        <v>-35.11</v>
       </c>
       <c r="AB9">
-        <v>-17.55</v>
+        <v>-15.78</v>
       </c>
       <c r="AC9">
-        <v>47.15</v>
+        <v>58.21</v>
       </c>
       <c r="AD9">
-        <v>31.46</v>
+        <v>44.98</v>
       </c>
       <c r="AE9">
-        <v>187.91</v>
+        <v>190.42</v>
       </c>
       <c r="AF9">
-        <v>41.88</v>
+        <v>3.68</v>
       </c>
       <c r="AG9">
-        <v>12255.99</v>
+        <v>12243.93</v>
       </c>
       <c r="AH9">
-        <v>11304.21</v>
+        <v>11284.87</v>
       </c>
       <c r="AI9">
         <v>12053.63</v>
@@ -1829,7 +1871,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>26.38</v>
+        <v>23.94</v>
       </c>
     </row>
   </sheetData>
@@ -1970,7 +2012,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2048,971 +2090,1164 @@
         <v>63</v>
       </c>
     </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>4.77</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C10" s="8">
         <v>3.12</v>
       </c>
-      <c r="E8" s="7">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D10" s="8">
+        <v>2.92</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-3.84</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C11" s="8">
         <v>-7.61</v>
       </c>
-      <c r="E9" s="7">
-        <v>-3.77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D11" s="8">
+        <v>-10.94</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-3.33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>5.89</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C12" s="8">
         <v>4.66</v>
       </c>
-      <c r="E10" s="7">
+      <c r="D12" s="8">
+        <v>5.96</v>
+      </c>
+      <c r="E12" s="10">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="8">
+        <v>6.4</v>
+      </c>
+      <c r="D13" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="E13" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="8">
+        <v>14.71</v>
+      </c>
+      <c r="D14" s="8">
+        <v>14.06</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="8">
+        <v>-2.29</v>
+      </c>
+      <c r="D15" s="8">
+        <v>-5.28</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-2.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="8">
+        <v>1.26</v>
+      </c>
+      <c r="D16" s="8">
+        <v>1.63</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="8">
+        <v>-2.34</v>
+      </c>
+      <c r="D17" s="8">
+        <v>-2.18</v>
+      </c>
+      <c r="E17" s="10">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="8">
+        <v>0.24</v>
+      </c>
+      <c r="D18" s="8">
+        <v>-1.8</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-2.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="8">
+        <v>-2.03</v>
+      </c>
+      <c r="D19" s="8">
+        <v>-3.42</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="8">
+        <v>-1.27</v>
+      </c>
+      <c r="D20" s="8">
+        <v>-0.54</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="8">
+        <v>-0.57</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="8">
+        <v>6.7</v>
+      </c>
+      <c r="D22" s="8">
+        <v>5.31</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="8">
+        <v>-4.88</v>
+      </c>
+      <c r="D23" s="8">
+        <v>-1.74</v>
+      </c>
+      <c r="E23" s="10">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="8">
+        <v>1.26</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0.71</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="8">
+        <v>1.23</v>
+      </c>
+      <c r="D25" s="8">
+        <v>0.16</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="8">
+        <v>43.18</v>
+      </c>
+      <c r="D26" s="8">
+        <v>42.2</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="8">
+        <v>-33.98</v>
+      </c>
+      <c r="D27" s="8">
+        <v>-35.97</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="8">
+        <v>15.79</v>
+      </c>
+      <c r="D28" s="8">
+        <v>17.02</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="8">
+        <v>45.41</v>
+      </c>
+      <c r="D29" s="8">
+        <v>44.92</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="8">
+        <v>111.74</v>
+      </c>
+      <c r="D30" s="8">
+        <v>98.38</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-13.36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="8">
+        <v>114.48</v>
+      </c>
+      <c r="D31" s="8">
+        <v>108.1</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-6.38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="8">
+        <v>-13.41</v>
+      </c>
+      <c r="D32" s="8">
+        <v>-11.81</v>
+      </c>
+      <c r="E32" s="10">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="8">
+        <v>-6.93</v>
+      </c>
+      <c r="D33" s="8">
+        <v>-8.07</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="8">
+        <v>12.85</v>
+      </c>
+      <c r="D34" s="8">
+        <v>15.69</v>
+      </c>
+      <c r="E34" s="10">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="8">
+        <v>-16.98</v>
+      </c>
+      <c r="D35" s="8">
+        <v>-16.36</v>
+      </c>
+      <c r="E35" s="10">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="8">
+        <v>4.34</v>
+      </c>
+      <c r="D36" s="8">
+        <v>6.04</v>
+      </c>
+      <c r="E36" s="10">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="8">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="D37" s="8">
+        <v>-9.1</v>
+      </c>
+      <c r="E37" s="10">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="8">
+        <v>7.01</v>
+      </c>
+      <c r="D38" s="8">
+        <v>5.23</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="8">
+        <v>-11.19</v>
+      </c>
+      <c r="D39" s="8">
+        <v>-9.02</v>
+      </c>
+      <c r="E39" s="10">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="8">
+        <v>-2.8</v>
+      </c>
+      <c r="D40" s="8">
+        <v>0.68</v>
+      </c>
+      <c r="E40" s="10">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="8">
+        <v>2.05</v>
+      </c>
+      <c r="D41" s="8">
+        <v>3.18</v>
+      </c>
+      <c r="E41" s="10">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="8">
+        <v>-3.46</v>
+      </c>
+      <c r="D42" s="8">
+        <v>-4.51</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="8">
+        <v>-42.62</v>
+      </c>
+      <c r="D43" s="8">
+        <v>-43.85</v>
+      </c>
+      <c r="E43" s="9">
         <v>-1.23</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="8">
+        <v>-3.62</v>
+      </c>
+      <c r="D44" s="8">
+        <v>-2.68</v>
+      </c>
+      <c r="E44" s="10">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>12.45</v>
-      </c>
-      <c r="D11" s="6">
-        <v>6.4</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-6.05</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B45" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="8">
+        <v>-10.93</v>
+      </c>
+      <c r="D45" s="8">
+        <v>-9.77</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>16.29</v>
-      </c>
-      <c r="D12" s="6">
-        <v>14.71</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B46" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="8">
+        <v>-1.45</v>
+      </c>
+      <c r="D46" s="8">
+        <v>-3.36</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.82</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.29</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-3.11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="8">
+        <v>-20.19</v>
+      </c>
+      <c r="D47" s="8">
+        <v>-18.82</v>
+      </c>
+      <c r="E47" s="10">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>4.36</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1.26</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B48" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="8">
+        <v>-24.89</v>
+      </c>
+      <c r="D48" s="8">
+        <v>-24.47</v>
+      </c>
+      <c r="E48" s="10">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.34</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B49" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="8">
+        <v>-10.23</v>
+      </c>
+      <c r="D49" s="8">
+        <v>-11.21</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>3.54</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.24</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-3.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B50" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="8">
+        <v>410</v>
+      </c>
+      <c r="D50" s="8">
+        <v>405.55</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-4.45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.09</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-2.03</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B51" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="8">
+        <v>53.64</v>
+      </c>
+      <c r="D51" s="8">
+        <v>52.49</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.27</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B52" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="8">
+        <v>3258</v>
+      </c>
+      <c r="D52" s="8">
+        <v>3290</v>
+      </c>
+      <c r="E52" s="10">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1.35</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-0.57</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B53" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="8">
+        <v>1024</v>
+      </c>
+      <c r="D53" s="8">
+        <v>1037.4</v>
+      </c>
+      <c r="E53" s="10">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>7.04</v>
-      </c>
-      <c r="D20" s="6">
-        <v>6.7</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B54" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="8">
+        <v>14.97</v>
+      </c>
+      <c r="D54" s="8">
+        <v>14.68</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-5.2</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-4.88</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B55" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="8">
+        <v>11.11</v>
+      </c>
+      <c r="D55" s="8">
+        <v>11.3</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>3.1</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1.26</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B56" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="8">
+        <v>4363.8</v>
+      </c>
+      <c r="D56" s="8">
+        <v>4387.9</v>
+      </c>
+      <c r="E56" s="10">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>2.33</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1.23</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B57" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="8">
+        <v>11717</v>
+      </c>
+      <c r="D57" s="8">
+        <v>11589</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>40.75</v>
-      </c>
-      <c r="D24" s="6">
-        <v>43.18</v>
-      </c>
-      <c r="E24" s="8">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B58" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="8">
+        <v>53.82</v>
+      </c>
+      <c r="D58" s="8">
+        <v>50.11</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-3.71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-27.93</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-33.98</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-6.05</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B59" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="8">
+        <v>33.77</v>
+      </c>
+      <c r="D59" s="8">
+        <v>30.34</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-3.43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>14.53</v>
-      </c>
-      <c r="D26" s="6">
-        <v>15.79</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B60" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="8">
+        <v>52.19</v>
+      </c>
+      <c r="D60" s="8">
+        <v>55.81</v>
+      </c>
+      <c r="E60" s="10">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>48.88</v>
-      </c>
-      <c r="D27" s="6">
-        <v>45.41</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-3.47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B61" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="8">
+        <v>49.88</v>
+      </c>
+      <c r="D61" s="8">
+        <v>53.36</v>
+      </c>
+      <c r="E61" s="10">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>129.92</v>
-      </c>
-      <c r="D28" s="6">
-        <v>111.74</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-18.18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B62" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="8">
+        <v>68.01000000000001</v>
+      </c>
+      <c r="D62" s="8">
+        <v>62.06</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-5.95</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>110.02</v>
-      </c>
-      <c r="D29" s="6">
-        <v>114.48</v>
-      </c>
-      <c r="E29" s="8">
-        <v>4.46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B63" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="8">
+        <v>38.01</v>
+      </c>
+      <c r="D63" s="8">
+        <v>42.23</v>
+      </c>
+      <c r="E63" s="10">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-13.08</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-13.41</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B64" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="8">
+        <v>48.49</v>
+      </c>
+      <c r="D64" s="8">
+        <v>50.54</v>
+      </c>
+      <c r="E64" s="10">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-6.93</v>
-      </c>
-      <c r="E31" s="8">
-        <v>2.03</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B65" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="8">
+        <v>50.27</v>
+      </c>
+      <c r="D65" s="8">
+        <v>45.32</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-4.95</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>12.36</v>
-      </c>
-      <c r="D32" s="6">
-        <v>12.85</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B66" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="8">
+        <v>-60.03</v>
+      </c>
+      <c r="D66" s="8">
+        <v>-68.65000000000001</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-8.619999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-14.89</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-16.98</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.09</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B67" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="8">
+        <v>-56.93</v>
+      </c>
+      <c r="D67" s="8">
+        <v>-40.21</v>
+      </c>
+      <c r="E67" s="10">
+        <v>16.72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>4.1</v>
-      </c>
-      <c r="D34" s="6">
-        <v>4.34</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B68" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="8">
+        <v>-30.92</v>
+      </c>
+      <c r="D68" s="8">
+        <v>-37.49</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-6.57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-8.41</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-9.119999999999999</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B69" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="8">
+        <v>-23.94</v>
+      </c>
+      <c r="D69" s="8">
+        <v>-64.91</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-40.97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>6.21</v>
-      </c>
-      <c r="D36" s="6">
-        <v>7.01</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B70" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="8">
+        <v>-3.14</v>
+      </c>
+      <c r="D70" s="8">
+        <v>-16.99</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-13.85</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-15.58</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-11.19</v>
-      </c>
-      <c r="E37" s="8">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B71" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="8">
+        <v>-41.84</v>
+      </c>
+      <c r="D71" s="8">
+        <v>-53.06</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-11.22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-4.47</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-2.8</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B72" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="8">
+        <v>-26.58</v>
+      </c>
+      <c r="D72" s="8">
+        <v>-77.69</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-51.11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>0.24</v>
-      </c>
-      <c r="D39" s="6">
-        <v>2.05</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-41.68</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-42.62</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-2.38</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-3.62</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-8.41</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-10.93</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-2.52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-0.86</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-1.45</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-23.83</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-24.89</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>54.52</v>
-      </c>
-      <c r="D45" s="6">
-        <v>53.64</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>3299.9</v>
-      </c>
-      <c r="D46" s="6">
-        <v>3258</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-41.9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1053</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1024</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-29</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>15.06</v>
-      </c>
-      <c r="D48" s="6">
-        <v>14.97</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>4424.9</v>
-      </c>
-      <c r="D49" s="6">
-        <v>4363.8</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-61.1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>36.72</v>
-      </c>
-      <c r="D50" s="6">
-        <v>33.77</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-2.95</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>57.96</v>
-      </c>
-      <c r="D51" s="6">
-        <v>52.19</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-5.77</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>58.67</v>
-      </c>
-      <c r="D52" s="6">
-        <v>49.88</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-8.789999999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>69.94</v>
-      </c>
-      <c r="D53" s="6">
-        <v>68.01000000000001</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>53.73</v>
-      </c>
-      <c r="D54" s="6">
-        <v>48.49</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-5.24</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="5" t="s">
+      <c r="B73" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C55" s="6">
-        <v>-43.6</v>
-      </c>
-      <c r="D55" s="6">
-        <v>-60.03</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-16.43</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="6">
-        <v>-45.77</v>
-      </c>
-      <c r="D56" s="6">
-        <v>-56.93</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-11.16</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="6">
-        <v>8.32</v>
-      </c>
-      <c r="D57" s="6">
-        <v>-30.92</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-39.24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>-52.81</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-23.94</v>
-      </c>
-      <c r="E58" s="8">
-        <v>28.87</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>9.93</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-3.14</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-13.07</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-58.99</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-41.84</v>
-      </c>
-      <c r="E60" s="8">
-        <v>17.15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-40.15</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-26.58</v>
-      </c>
-      <c r="E61" s="8">
-        <v>13.57</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-11.54</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C73" s="8">
         <v>41.88</v>
       </c>
-      <c r="E62" s="8">
-        <v>53.42</v>
+      <c r="D73" s="8">
+        <v>3.68</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-38.2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3032,60 +3267,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>76</v>
+      <c r="B1" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="13">
         <v>56.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="14">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>49.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="13">
+        <v>48.7</v>
+      </c>
+      <c r="E2" s="13">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>2.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-1.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="13">
+        <v>1.6</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.5</v>
+      </c>
+      <c r="H2" s="13">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="13">
         <v>50</v>
       </c>
     </row>
@@ -3187,55 +3422,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="15" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.306</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2007</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2004</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.192</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1799</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0964</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2332</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.3035</v>
+      <c r="A2" s="16">
+        <v>0.2992</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.1982</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.1975</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.1899</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.1803</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.0901</v>
+      </c>
+      <c r="G2" s="16">
+        <v>-0.2411</v>
+      </c>
+      <c r="H2" s="16">
+        <v>-0.3063</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="85">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,55 +190,52 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.7% → -0.3%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.7%</t>
+  </si>
+  <si>
+    <t>-0.3%</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.9 → 53.4</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.9</t>
+    <t>53.4 → 47.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>53.4</t>
   </si>
   <si>
-    <t>48.5 → 50.5</t>
-  </si>
-  <si>
-    <t>48.5</t>
+    <t>47.5</t>
+  </si>
+  <si>
+    <t>50.5 → 47.6</t>
   </si>
   <si>
     <t>50.5</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.4% → -3.4%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.4%</t>
-  </si>
-  <si>
-    <t>-3.4%</t>
-  </si>
-  <si>
-    <t>50.3 → 45.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>45.3</t>
+    <t>47.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -290,7 +287,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,20 +328,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -372,12 +362,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -462,15 +446,14 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -479,7 +462,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -838,7 +821,8 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -978,10 +962,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>405.55</v>
+        <v>409.4</v>
       </c>
       <c r="D2">
-        <v>-1.09</v>
+        <v>0.95</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -990,46 +974,46 @@
         <v>274.85</v>
       </c>
       <c r="G2">
-        <v>-4.51</v>
+        <v>-3.6</v>
       </c>
       <c r="H2">
-        <v>47.55</v>
+        <v>48.95</v>
       </c>
       <c r="I2">
-        <v>-1.8</v>
+        <v>-0.85</v>
       </c>
       <c r="J2">
-        <v>2.92</v>
+        <v>1.26</v>
       </c>
       <c r="K2">
-        <v>15.69</v>
+        <v>16.54</v>
       </c>
       <c r="L2">
-        <v>42.2</v>
+        <v>45.69</v>
       </c>
       <c r="M2">
-        <v>29.92</v>
+        <v>30.58</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P2">
-        <v>409.86</v>
+        <v>409.16</v>
       </c>
       <c r="Q2">
-        <v>410.06</v>
+        <v>409.31</v>
       </c>
       <c r="R2">
-        <v>402.13</v>
+        <v>402.8</v>
       </c>
       <c r="S2">
-        <v>358.99</v>
+        <v>359.39</v>
       </c>
       <c r="T2">
-        <v>12.97</v>
+        <v>13.92</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1044,34 +1028,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>50.11</v>
+        <v>53.12</v>
       </c>
       <c r="Z2">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AA2">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AB2">
-        <v>-0.61</v>
+        <v>-0.53</v>
       </c>
       <c r="AC2">
-        <v>66.31999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AD2">
-        <v>66.92</v>
+        <v>67.02</v>
       </c>
       <c r="AE2">
-        <v>9.07</v>
+        <v>9.24</v>
       </c>
       <c r="AF2">
-        <v>-68.65000000000001</v>
+        <v>49.97</v>
       </c>
       <c r="AG2">
-        <v>425.85</v>
+        <v>423.6</v>
       </c>
       <c r="AH2">
-        <v>394.26</v>
+        <v>395.02</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1080,7 +1064,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>17.3</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1091,58 +1075,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>52.49</v>
+        <v>52.1</v>
       </c>
       <c r="D3">
-        <v>-2.14</v>
+        <v>-0.74</v>
       </c>
       <c r="E3">
         <v>93.48</v>
       </c>
       <c r="F3">
-        <v>52.49</v>
+        <v>52.1</v>
       </c>
       <c r="G3">
-        <v>-43.85</v>
+        <v>-44.27</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-3.42</v>
+        <v>-3.43</v>
       </c>
       <c r="J3">
-        <v>-10.94</v>
+        <v>-13.51</v>
       </c>
       <c r="K3">
-        <v>-16.36</v>
+        <v>-15.83</v>
       </c>
       <c r="L3">
-        <v>-35.97</v>
+        <v>-36.89</v>
       </c>
       <c r="M3">
-        <v>-24.11</v>
+        <v>-24.2</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P3">
-        <v>53.82</v>
+        <v>53.45</v>
       </c>
       <c r="Q3">
-        <v>57.26</v>
+        <v>56.75</v>
       </c>
       <c r="R3">
-        <v>58.34</v>
+        <v>58.17</v>
       </c>
       <c r="S3">
-        <v>65.42</v>
+        <v>65.27</v>
       </c>
       <c r="T3">
-        <v>-19.76</v>
+        <v>-20.18</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1157,43 +1141,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>30.34</v>
+        <v>29.25</v>
       </c>
       <c r="Z3">
-        <v>-1.61</v>
+        <v>-1.71</v>
       </c>
       <c r="AA3">
-        <v>-1.23</v>
+        <v>-1.33</v>
       </c>
       <c r="AB3">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="AC3">
-        <v>4.14</v>
+        <v>0.52</v>
       </c>
       <c r="AD3">
-        <v>6.2</v>
+        <v>4.05</v>
       </c>
       <c r="AE3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AF3">
-        <v>-40.21</v>
+        <v>-24.38</v>
       </c>
       <c r="AG3">
-        <v>64.45999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="AH3">
-        <v>50.06</v>
+        <v>49.62</v>
       </c>
       <c r="AI3">
-        <v>58.13</v>
+        <v>57.42</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>50.44</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1204,10 +1188,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3290</v>
+        <v>3371</v>
       </c>
       <c r="D4">
-        <v>0.98</v>
+        <v>2.46</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1216,46 +1200,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.68</v>
+        <v>-0.28</v>
       </c>
       <c r="H4">
-        <v>29.98</v>
+        <v>33.18</v>
       </c>
       <c r="I4">
-        <v>-0.54</v>
+        <v>2.52</v>
       </c>
       <c r="J4">
-        <v>5.96</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="K4">
-        <v>6.04</v>
+        <v>8.83</v>
       </c>
       <c r="L4">
-        <v>17.02</v>
+        <v>20.56</v>
       </c>
       <c r="M4">
-        <v>18.03</v>
+        <v>18.12</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="P4">
-        <v>3285.1</v>
+        <v>3301.7</v>
       </c>
       <c r="Q4">
-        <v>3275.69</v>
+        <v>3281.24</v>
       </c>
       <c r="R4">
-        <v>3192.36</v>
+        <v>3196.79</v>
       </c>
       <c r="S4">
-        <v>2923.22</v>
+        <v>2926.23</v>
       </c>
       <c r="T4">
-        <v>12.55</v>
+        <v>15.2</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1270,34 +1254,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>55.81</v>
+        <v>63.36</v>
       </c>
       <c r="Z4">
-        <v>31.02</v>
+        <v>36.17</v>
       </c>
       <c r="AA4">
-        <v>35.66</v>
+        <v>35.76</v>
       </c>
       <c r="AB4">
-        <v>-4.63</v>
+        <v>0.41</v>
       </c>
       <c r="AC4">
-        <v>22.02</v>
+        <v>46.31</v>
       </c>
       <c r="AD4">
-        <v>19.51</v>
+        <v>27.89</v>
       </c>
       <c r="AE4">
-        <v>68.97</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="AF4">
-        <v>-37.49</v>
+        <v>-7.32</v>
       </c>
       <c r="AG4">
-        <v>3374.35</v>
+        <v>3388.31</v>
       </c>
       <c r="AH4">
-        <v>3177.04</v>
+        <v>3174.18</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1306,7 +1290,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>23.83</v>
+        <v>24.62</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1317,10 +1301,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1037.4</v>
+        <v>1015.45</v>
       </c>
       <c r="D5">
-        <v>1.31</v>
+        <v>-2.12</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1329,46 +1313,46 @@
         <v>701.4</v>
       </c>
       <c r="G5">
-        <v>-9.77</v>
+        <v>-11.68</v>
       </c>
       <c r="H5">
-        <v>47.9</v>
+        <v>44.77</v>
       </c>
       <c r="I5">
-        <v>0.33</v>
+        <v>-4.07</v>
       </c>
       <c r="J5">
-        <v>6.9</v>
+        <v>4.21</v>
       </c>
       <c r="K5">
-        <v>-9.1</v>
+        <v>-11.41</v>
       </c>
       <c r="L5">
-        <v>44.92</v>
+        <v>43.89</v>
       </c>
       <c r="M5">
-        <v>18.99</v>
+        <v>17.42</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P5">
-        <v>1044.79</v>
+        <v>1036.18</v>
       </c>
       <c r="Q5">
-        <v>1040.86</v>
+        <v>1041.89</v>
       </c>
       <c r="R5">
-        <v>994.2</v>
+        <v>994.3099999999999</v>
       </c>
       <c r="S5">
-        <v>960.4299999999999</v>
+        <v>961.53</v>
       </c>
       <c r="T5">
-        <v>8.01</v>
+        <v>5.61</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1383,34 +1367,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>53.36</v>
+        <v>47.54</v>
       </c>
       <c r="Z5">
-        <v>12.54</v>
+        <v>9.76</v>
       </c>
       <c r="AA5">
-        <v>15.09</v>
+        <v>14.03</v>
       </c>
       <c r="AB5">
-        <v>-2.55</v>
+        <v>-4.26</v>
       </c>
       <c r="AC5">
-        <v>14.69</v>
+        <v>5.46</v>
       </c>
       <c r="AD5">
-        <v>20.93</v>
+        <v>12.57</v>
       </c>
       <c r="AE5">
-        <v>24.02</v>
+        <v>24.59</v>
       </c>
       <c r="AF5">
-        <v>-64.91</v>
+        <v>22.84</v>
       </c>
       <c r="AG5">
-        <v>1076.46</v>
+        <v>1072.78</v>
       </c>
       <c r="AH5">
-        <v>1005.25</v>
+        <v>1010.99</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1419,7 +1403,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>23.67</v>
+        <v>24.67</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1430,10 +1414,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.68</v>
+        <v>14.33</v>
       </c>
       <c r="D6">
-        <v>-1.94</v>
+        <v>-2.38</v>
       </c>
       <c r="E6">
         <v>15.19</v>
@@ -1442,88 +1426,88 @@
         <v>6.49</v>
       </c>
       <c r="G6">
-        <v>-3.36</v>
+        <v>-5.66</v>
       </c>
       <c r="H6">
-        <v>126.19</v>
+        <v>120.8</v>
       </c>
       <c r="I6">
-        <v>5.31</v>
+        <v>1.85</v>
       </c>
       <c r="J6">
-        <v>14.06</v>
+        <v>10.15</v>
       </c>
       <c r="K6">
-        <v>5.23</v>
+        <v>1.2</v>
       </c>
       <c r="L6">
-        <v>98.38</v>
+        <v>113.56</v>
       </c>
       <c r="M6">
-        <v>19.82</v>
+        <v>18.63</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P6">
-        <v>14.79</v>
+        <v>14.85</v>
       </c>
       <c r="Q6">
-        <v>13.73</v>
+        <v>13.81</v>
       </c>
       <c r="R6">
-        <v>13.81</v>
+        <v>13.8</v>
       </c>
       <c r="S6">
-        <v>11.8</v>
+        <v>11.82</v>
       </c>
       <c r="T6">
-        <v>24.38</v>
+        <v>21.21</v>
       </c>
       <c r="U6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V6" t="s">
         <v>46</v>
       </c>
       <c r="W6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6">
-        <v>62.06</v>
+        <v>55.73</v>
       </c>
       <c r="Z6">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="AA6">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="AB6">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="AC6">
-        <v>82.05</v>
+        <v>52.63</v>
       </c>
       <c r="AD6">
-        <v>89.18000000000001</v>
+        <v>75.83</v>
       </c>
       <c r="AE6">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="AF6">
-        <v>-16.99</v>
+        <v>-8.75</v>
       </c>
       <c r="AG6">
-        <v>15.39</v>
+        <v>15.43</v>
       </c>
       <c r="AH6">
-        <v>12.08</v>
+        <v>12.19</v>
       </c>
       <c r="AI6">
         <v>13.86</v>
@@ -1532,7 +1516,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>62.46</v>
+        <v>56.54</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1543,10 +1527,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="D7">
-        <v>1.71</v>
+        <v>-1.77</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1555,46 +1539,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-18.82</v>
+        <v>-20.26</v>
       </c>
       <c r="H7">
-        <v>140.94</v>
+        <v>136.67</v>
       </c>
       <c r="I7">
-        <v>-1.74</v>
+        <v>-2.2</v>
       </c>
       <c r="J7">
-        <v>-5.28</v>
+        <v>-11.34</v>
       </c>
       <c r="K7">
-        <v>-9.02</v>
+        <v>-7.35</v>
       </c>
       <c r="L7">
-        <v>108.1</v>
+        <v>97.16</v>
       </c>
       <c r="M7">
-        <v>-30.63</v>
+        <v>-30.32</v>
       </c>
       <c r="N7">
         <v>87</v>
       </c>
       <c r="O7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P7">
-        <v>11.24</v>
+        <v>11.19</v>
       </c>
       <c r="Q7">
-        <v>12.05</v>
+        <v>11.95</v>
       </c>
       <c r="R7">
-        <v>11.59</v>
+        <v>11.57</v>
       </c>
       <c r="S7">
-        <v>10.17</v>
+        <v>10.2</v>
       </c>
       <c r="T7">
-        <v>11.13</v>
+        <v>8.84</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1609,34 +1593,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>42.23</v>
+        <v>39.2</v>
       </c>
       <c r="Z7">
-        <v>-0.17</v>
+        <v>-0.19</v>
       </c>
       <c r="AA7">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AB7">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AC7">
-        <v>8.77</v>
+        <v>11.86</v>
       </c>
       <c r="AD7">
-        <v>2.92</v>
+        <v>6.88</v>
       </c>
       <c r="AE7">
         <v>0.29</v>
       </c>
       <c r="AF7">
-        <v>-53.06</v>
+        <v>-66.23999999999999</v>
       </c>
       <c r="AG7">
-        <v>13.56</v>
+        <v>13.42</v>
       </c>
       <c r="AH7">
-        <v>10.55</v>
+        <v>10.48</v>
       </c>
       <c r="AI7">
         <v>11.9</v>
@@ -1645,7 +1629,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>38.85</v>
+        <v>38.75</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1656,10 +1640,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4387.9</v>
+        <v>4353.4</v>
       </c>
       <c r="D8">
-        <v>0.55</v>
+        <v>-0.79</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1668,46 +1652,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-24.47</v>
+        <v>-25.06</v>
       </c>
       <c r="H8">
-        <v>5.6</v>
+        <v>4.77</v>
       </c>
       <c r="I8">
-        <v>0.71</v>
+        <v>-0.2</v>
       </c>
       <c r="J8">
-        <v>1.63</v>
+        <v>1.17</v>
       </c>
       <c r="K8">
-        <v>0.68</v>
+        <v>-0.19</v>
       </c>
       <c r="L8">
-        <v>-11.81</v>
+        <v>-11.67</v>
       </c>
       <c r="M8">
-        <v>19.75</v>
+        <v>19.61</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P8">
-        <v>4386.8</v>
+        <v>4385.06</v>
       </c>
       <c r="Q8">
-        <v>4387.01</v>
+        <v>4387.34</v>
       </c>
       <c r="R8">
-        <v>4376.96</v>
+        <v>4375.54</v>
       </c>
       <c r="S8">
-        <v>4652.63</v>
+        <v>4648.12</v>
       </c>
       <c r="T8">
-        <v>-5.69</v>
+        <v>-6.34</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1722,34 +1706,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>50.54</v>
+        <v>47.62</v>
       </c>
       <c r="Z8">
-        <v>3.27</v>
+        <v>0.5</v>
       </c>
       <c r="AA8">
-        <v>4.81</v>
+        <v>3.95</v>
       </c>
       <c r="AB8">
-        <v>-1.54</v>
+        <v>-3.44</v>
       </c>
       <c r="AC8">
-        <v>36.4</v>
+        <v>27.22</v>
       </c>
       <c r="AD8">
-        <v>37.3</v>
+        <v>33.75</v>
       </c>
       <c r="AE8">
-        <v>94.31</v>
+        <v>94.13</v>
       </c>
       <c r="AF8">
-        <v>-77.69</v>
+        <v>-77.93000000000001</v>
       </c>
       <c r="AG8">
-        <v>4534.67</v>
+        <v>4534.65</v>
       </c>
       <c r="AH8">
-        <v>4239.35</v>
+        <v>4240.03</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1758,7 +1742,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>16.68</v>
+        <v>16.06</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1769,10 +1753,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11589</v>
+        <v>11450</v>
       </c>
       <c r="D9">
-        <v>-1.09</v>
+        <v>-1.2</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1781,46 +1765,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-11.21</v>
+        <v>-12.27</v>
       </c>
       <c r="H9">
-        <v>11.84</v>
+        <v>10.5</v>
       </c>
       <c r="I9">
-        <v>0.16</v>
+        <v>-0.47</v>
       </c>
       <c r="J9">
-        <v>-2.18</v>
+        <v>-3.81</v>
       </c>
       <c r="K9">
-        <v>3.18</v>
+        <v>2.55</v>
       </c>
       <c r="L9">
-        <v>-8.07</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="M9">
-        <v>9.01</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P9">
-        <v>11613.4</v>
+        <v>11602.6</v>
       </c>
       <c r="Q9">
-        <v>11764.4</v>
+        <v>11734.2</v>
       </c>
       <c r="R9">
-        <v>11701.82</v>
+        <v>11703.48</v>
       </c>
       <c r="S9">
-        <v>11777.86</v>
+        <v>11775.5</v>
       </c>
       <c r="T9">
-        <v>-1.6</v>
+        <v>-2.76</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1835,34 +1819,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>45.32</v>
+        <v>40.63</v>
       </c>
       <c r="Z9">
-        <v>-50.88</v>
+        <v>-63.09</v>
       </c>
       <c r="AA9">
-        <v>-35.11</v>
+        <v>-40.7</v>
       </c>
       <c r="AB9">
-        <v>-15.78</v>
+        <v>-22.39</v>
       </c>
       <c r="AC9">
-        <v>58.21</v>
+        <v>45.9</v>
       </c>
       <c r="AD9">
-        <v>44.98</v>
+        <v>50.42</v>
       </c>
       <c r="AE9">
-        <v>190.42</v>
+        <v>189.24</v>
       </c>
       <c r="AF9">
-        <v>3.68</v>
+        <v>69.55</v>
       </c>
       <c r="AG9">
-        <v>12243.93</v>
+        <v>12213.01</v>
       </c>
       <c r="AH9">
-        <v>11284.87</v>
+        <v>11255.39</v>
       </c>
       <c r="AI9">
         <v>12053.63</v>
@@ -1871,7 +1855,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>23.94</v>
+        <v>23.75</v>
       </c>
     </row>
   </sheetData>
@@ -2012,7 +1996,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2052,7 +2036,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2072,1182 +2056,1202 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="E5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>2.92</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.26</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-10.94</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-13.51</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>5.96</v>
+      </c>
+      <c r="D13" s="7">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>6.9</v>
+      </c>
+      <c r="D14" s="7">
+        <v>4.21</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-2.69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="6" t="s">
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>14.06</v>
+      </c>
+      <c r="D15" s="7">
+        <v>10.15</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-3.91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-5.28</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-11.34</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-6.06</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1.63</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1.17</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
+      <c r="B18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-2.18</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-3.81</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8">
-        <v>3.12</v>
-      </c>
-      <c r="D10" s="8">
-        <v>2.92</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-1.8</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-0.85</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-3.42</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-3.43</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-0.54</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2.52</v>
+      </c>
+      <c r="E21" s="9">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>0.33</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-4.07</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-4.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>5.31</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1.85</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-3.46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-1.74</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-2.2</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="D25" s="7">
         <v>-0.2</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
+      <c r="E25" s="8">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0.16</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-0.47</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>42.2</v>
+      </c>
+      <c r="D27" s="7">
+        <v>45.69</v>
+      </c>
+      <c r="E27" s="9">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="8">
-        <v>-7.61</v>
-      </c>
-      <c r="D11" s="8">
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-35.97</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-36.89</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>17.02</v>
+      </c>
+      <c r="D29" s="7">
+        <v>20.56</v>
+      </c>
+      <c r="E29" s="9">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>44.92</v>
+      </c>
+      <c r="D30" s="7">
+        <v>43.89</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>98.38</v>
+      </c>
+      <c r="D31" s="7">
+        <v>113.56</v>
+      </c>
+      <c r="E31" s="9">
+        <v>15.18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>108.1</v>
+      </c>
+      <c r="D32" s="7">
+        <v>97.16</v>
+      </c>
+      <c r="E32" s="8">
         <v>-10.94</v>
       </c>
-      <c r="E11" s="9">
-        <v>-3.33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-11.81</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-11.67</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-8.07</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>15.69</v>
+      </c>
+      <c r="D35" s="7">
+        <v>16.54</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-16.36</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-15.83</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8">
-        <v>4.66</v>
-      </c>
-      <c r="D12" s="8">
-        <v>5.96</v>
-      </c>
-      <c r="E12" s="10">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>6.04</v>
+      </c>
+      <c r="D37" s="7">
+        <v>8.83</v>
+      </c>
+      <c r="E37" s="9">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>6.4</v>
-      </c>
-      <c r="D13" s="8">
-        <v>6.9</v>
-      </c>
-      <c r="E13" s="10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-9.1</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-11.41</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>14.71</v>
-      </c>
-      <c r="D14" s="8">
-        <v>14.06</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>5.23</v>
+      </c>
+      <c r="D39" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-4.03</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>-2.29</v>
-      </c>
-      <c r="D15" s="8">
-        <v>-5.28</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-2.99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-9.02</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-7.35</v>
+      </c>
+      <c r="E40" s="9">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8">
-        <v>1.26</v>
-      </c>
-      <c r="D16" s="8">
-        <v>1.63</v>
-      </c>
-      <c r="E16" s="10">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.68</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-0.19</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="8">
-        <v>-2.34</v>
-      </c>
-      <c r="D17" s="8">
-        <v>-2.18</v>
-      </c>
-      <c r="E17" s="10">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>3.18</v>
+      </c>
+      <c r="D42" s="7">
+        <v>2.55</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="8">
-        <v>0.24</v>
-      </c>
-      <c r="D18" s="8">
-        <v>-1.8</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-2.04</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-4.51</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-3.6</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-2.03</v>
-      </c>
-      <c r="D19" s="8">
-        <v>-3.42</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-43.85</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-44.27</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="8">
-        <v>-1.27</v>
-      </c>
-      <c r="D20" s="8">
-        <v>-0.54</v>
-      </c>
-      <c r="E20" s="10">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-2.68</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-0.28</v>
+      </c>
+      <c r="E45" s="9">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="8">
-        <v>-0.57</v>
-      </c>
-      <c r="D21" s="8">
-        <v>0.33</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-9.77</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-11.68</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>6.7</v>
-      </c>
-      <c r="D22" s="8">
-        <v>5.31</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-3.36</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-5.66</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8">
-        <v>-4.88</v>
-      </c>
-      <c r="D23" s="8">
-        <v>-1.74</v>
-      </c>
-      <c r="E23" s="10">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-18.82</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-20.26</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="8">
-        <v>1.26</v>
-      </c>
-      <c r="D24" s="8">
-        <v>0.71</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-24.47</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-25.06</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="8">
-        <v>1.23</v>
-      </c>
-      <c r="D25" s="8">
-        <v>0.16</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-11.21</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-12.27</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="8">
-        <v>43.18</v>
-      </c>
-      <c r="D26" s="8">
-        <v>42.2</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
+      <c r="B51" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7">
+        <v>405.55</v>
+      </c>
+      <c r="D51" s="7">
+        <v>409.4</v>
+      </c>
+      <c r="E51" s="9">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="8">
-        <v>-33.98</v>
-      </c>
-      <c r="D27" s="8">
-        <v>-35.97</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-1.99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
+      <c r="B52" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7">
+        <v>52.49</v>
+      </c>
+      <c r="D52" s="7">
+        <v>52.1</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="8">
-        <v>15.79</v>
-      </c>
-      <c r="D28" s="8">
-        <v>17.02</v>
-      </c>
-      <c r="E28" s="10">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>3290</v>
+      </c>
+      <c r="D53" s="7">
+        <v>3371</v>
+      </c>
+      <c r="E53" s="9">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="8">
-        <v>45.41</v>
-      </c>
-      <c r="D29" s="8">
-        <v>44.92</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>1037.4</v>
+      </c>
+      <c r="D54" s="7">
+        <v>1015.45</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-21.95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="8">
-        <v>111.74</v>
-      </c>
-      <c r="D30" s="8">
-        <v>98.38</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-13.36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>14.68</v>
+      </c>
+      <c r="D55" s="7">
+        <v>14.33</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="8">
-        <v>114.48</v>
-      </c>
-      <c r="D31" s="8">
-        <v>108.1</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-6.38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>11.3</v>
+      </c>
+      <c r="D56" s="7">
+        <v>11.1</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="8">
-        <v>-13.41</v>
-      </c>
-      <c r="D32" s="8">
-        <v>-11.81</v>
-      </c>
-      <c r="E32" s="10">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>4387.9</v>
+      </c>
+      <c r="D57" s="7">
+        <v>4353.4</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-34.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="8">
-        <v>-6.93</v>
-      </c>
-      <c r="D33" s="8">
-        <v>-8.07</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>11589</v>
+      </c>
+      <c r="D58" s="7">
+        <v>11450</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-139</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="8">
-        <v>12.85</v>
-      </c>
-      <c r="D34" s="8">
-        <v>15.69</v>
-      </c>
-      <c r="E34" s="10">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>50.11</v>
+      </c>
+      <c r="D59" s="7">
+        <v>53.12</v>
+      </c>
+      <c r="E59" s="9">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="8">
-        <v>-16.98</v>
-      </c>
-      <c r="D35" s="8">
-        <v>-16.36</v>
-      </c>
-      <c r="E35" s="10">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
+      <c r="B60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="7">
+        <v>30.34</v>
+      </c>
+      <c r="D60" s="7">
+        <v>29.25</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="8">
-        <v>4.34</v>
-      </c>
-      <c r="D36" s="8">
-        <v>6.04</v>
-      </c>
-      <c r="E36" s="10">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
+      <c r="B61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="7">
+        <v>55.81</v>
+      </c>
+      <c r="D61" s="7">
+        <v>63.36</v>
+      </c>
+      <c r="E61" s="9">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="8">
-        <v>-9.119999999999999</v>
-      </c>
-      <c r="D37" s="8">
-        <v>-9.1</v>
-      </c>
-      <c r="E37" s="10">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>53.36</v>
+      </c>
+      <c r="D62" s="7">
+        <v>47.54</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-5.82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="8">
-        <v>7.01</v>
-      </c>
-      <c r="D38" s="8">
-        <v>5.23</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>62.06</v>
+      </c>
+      <c r="D63" s="7">
+        <v>55.73</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-6.33</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="8">
-        <v>-11.19</v>
-      </c>
-      <c r="D39" s="8">
-        <v>-9.02</v>
-      </c>
-      <c r="E39" s="10">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>42.23</v>
+      </c>
+      <c r="D64" s="7">
+        <v>39.2</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-3.03</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="8">
-        <v>-2.8</v>
-      </c>
-      <c r="D40" s="8">
-        <v>0.68</v>
-      </c>
-      <c r="E40" s="10">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>50.54</v>
+      </c>
+      <c r="D65" s="7">
+        <v>47.62</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-2.92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="8">
-        <v>2.05</v>
-      </c>
-      <c r="D41" s="8">
-        <v>3.18</v>
-      </c>
-      <c r="E41" s="10">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>45.32</v>
+      </c>
+      <c r="D66" s="7">
+        <v>40.63</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-4.69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="8">
-        <v>-3.46</v>
-      </c>
-      <c r="D42" s="8">
-        <v>-4.51</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
+      <c r="B67" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="7">
+        <v>-68.65000000000001</v>
+      </c>
+      <c r="D67" s="7">
+        <v>49.97</v>
+      </c>
+      <c r="E67" s="9">
+        <v>118.62</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="8">
-        <v>-42.62</v>
-      </c>
-      <c r="D43" s="8">
-        <v>-43.85</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
+      <c r="B68" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="7">
+        <v>-40.21</v>
+      </c>
+      <c r="D68" s="7">
+        <v>-24.38</v>
+      </c>
+      <c r="E68" s="9">
+        <v>15.83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="8">
-        <v>-3.62</v>
-      </c>
-      <c r="D44" s="8">
-        <v>-2.68</v>
-      </c>
-      <c r="E44" s="10">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
+      <c r="B69" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="7">
+        <v>-37.49</v>
+      </c>
+      <c r="D69" s="7">
+        <v>-7.32</v>
+      </c>
+      <c r="E69" s="9">
+        <v>30.17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="8">
-        <v>-10.93</v>
-      </c>
-      <c r="D45" s="8">
-        <v>-9.77</v>
-      </c>
-      <c r="E45" s="10">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
+      <c r="B70" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="7">
+        <v>-64.91</v>
+      </c>
+      <c r="D70" s="7">
+        <v>22.84</v>
+      </c>
+      <c r="E70" s="9">
+        <v>87.75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="8">
-        <v>-1.45</v>
-      </c>
-      <c r="D46" s="8">
-        <v>-3.36</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>-16.99</v>
+      </c>
+      <c r="D71" s="7">
+        <v>-8.75</v>
+      </c>
+      <c r="E71" s="9">
+        <v>8.24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="8">
-        <v>-20.19</v>
-      </c>
-      <c r="D47" s="8">
-        <v>-18.82</v>
-      </c>
-      <c r="E47" s="10">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>-53.06</v>
+      </c>
+      <c r="D72" s="7">
+        <v>-66.23999999999999</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-13.18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="8">
-        <v>-24.89</v>
-      </c>
-      <c r="D48" s="8">
-        <v>-24.47</v>
-      </c>
-      <c r="E48" s="10">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>-77.69</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-77.93000000000001</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="8">
-        <v>-10.23</v>
-      </c>
-      <c r="D49" s="8">
-        <v>-11.21</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="8">
-        <v>410</v>
-      </c>
-      <c r="D50" s="8">
-        <v>405.55</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-4.45</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="8">
-        <v>53.64</v>
-      </c>
-      <c r="D51" s="8">
-        <v>52.49</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="8">
-        <v>3258</v>
-      </c>
-      <c r="D52" s="8">
-        <v>3290</v>
-      </c>
-      <c r="E52" s="10">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="8">
-        <v>1024</v>
-      </c>
-      <c r="D53" s="8">
-        <v>1037.4</v>
-      </c>
-      <c r="E53" s="10">
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="8">
-        <v>14.97</v>
-      </c>
-      <c r="D54" s="8">
-        <v>14.68</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="8">
-        <v>11.11</v>
-      </c>
-      <c r="D55" s="8">
-        <v>11.3</v>
-      </c>
-      <c r="E55" s="10">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="8">
-        <v>4363.8</v>
-      </c>
-      <c r="D56" s="8">
-        <v>4387.9</v>
-      </c>
-      <c r="E56" s="10">
-        <v>24.1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="8">
-        <v>11717</v>
-      </c>
-      <c r="D57" s="8">
-        <v>11589</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-128</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="8">
-        <v>53.82</v>
-      </c>
-      <c r="D58" s="8">
-        <v>50.11</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-3.71</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="8">
-        <v>33.77</v>
-      </c>
-      <c r="D59" s="8">
-        <v>30.34</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-3.43</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="8">
-        <v>52.19</v>
-      </c>
-      <c r="D60" s="8">
-        <v>55.81</v>
-      </c>
-      <c r="E60" s="10">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="8">
-        <v>49.88</v>
-      </c>
-      <c r="D61" s="8">
-        <v>53.36</v>
-      </c>
-      <c r="E61" s="10">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="8">
-        <v>68.01000000000001</v>
-      </c>
-      <c r="D62" s="8">
-        <v>62.06</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-5.95</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="8">
-        <v>38.01</v>
-      </c>
-      <c r="D63" s="8">
-        <v>42.23</v>
-      </c>
-      <c r="E63" s="10">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="8">
-        <v>48.49</v>
-      </c>
-      <c r="D64" s="8">
-        <v>50.54</v>
-      </c>
-      <c r="E64" s="10">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="8">
-        <v>50.27</v>
-      </c>
-      <c r="D65" s="8">
-        <v>45.32</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-4.95</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="7" t="s">
+      <c r="B74" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C66" s="8">
-        <v>-60.03</v>
-      </c>
-      <c r="D66" s="8">
-        <v>-68.65000000000001</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-8.619999999999999</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="8">
-        <v>-56.93</v>
-      </c>
-      <c r="D67" s="8">
-        <v>-40.21</v>
-      </c>
-      <c r="E67" s="10">
-        <v>16.72</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="8">
-        <v>-30.92</v>
-      </c>
-      <c r="D68" s="8">
-        <v>-37.49</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-6.57</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="8">
-        <v>-23.94</v>
-      </c>
-      <c r="D69" s="8">
-        <v>-64.91</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-40.97</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="8">
-        <v>-3.14</v>
-      </c>
-      <c r="D70" s="8">
-        <v>-16.99</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-13.85</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="8">
-        <v>-41.84</v>
-      </c>
-      <c r="D71" s="8">
-        <v>-53.06</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-11.22</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="8">
-        <v>-26.58</v>
-      </c>
-      <c r="D72" s="8">
-        <v>-77.69</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-51.11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="8">
-        <v>41.88</v>
-      </c>
-      <c r="D73" s="8">
+      <c r="C74" s="7">
         <v>3.68</v>
       </c>
-      <c r="E73" s="9">
-        <v>-38.2</v>
+      <c r="D74" s="7">
+        <v>69.55</v>
+      </c>
+      <c r="E74" s="9">
+        <v>65.87</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3267,61 +3271,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I1" s="11" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="12">
         <v>56.44</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="13">
         <v>8</v>
       </c>
-      <c r="D2" s="13">
-        <v>48.7</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="D2" s="12">
+        <v>47.1</v>
+      </c>
+      <c r="E2" s="12">
         <v>60</v>
       </c>
-      <c r="F2" s="13">
-        <v>1.6</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.5</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="F2" s="12">
+        <v>-0.4</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-0.7</v>
+      </c>
+      <c r="H2" s="12">
         <v>56.1</v>
       </c>
-      <c r="I2" s="13">
-        <v>50</v>
+      <c r="I2" s="12">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3422,55 +3426,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="16">
-        <v>0.2992</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.1982</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.1975</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.1899</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.1803</v>
-      </c>
-      <c r="F2" s="16">
-        <v>0.0901</v>
-      </c>
-      <c r="G2" s="16">
-        <v>-0.2411</v>
-      </c>
-      <c r="H2" s="16">
-        <v>-0.3063</v>
+      <c r="A2" s="15">
+        <v>0.3058</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1961</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1863</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1812</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1742</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.08380000000000001</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.242</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.3032</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,52 +190,40 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.7% → -0.3%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.7%</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-0.3% → -2.2%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>-0.3%</t>
   </si>
   <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
+    <t>-2.2%</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>53.1 → 42.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>53.1</t>
+  </si>
+  <si>
+    <t>42.4</t>
   </si>
   <si>
     <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>53.4 → 47.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.4</t>
-  </si>
-  <si>
-    <t>47.5</t>
-  </si>
-  <si>
-    <t>50.5 → 47.6</t>
-  </si>
-  <si>
-    <t>50.5</t>
-  </si>
-  <si>
-    <t>47.6</t>
+    <t>Yes → No</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -287,7 +275,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,7 +309,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -333,8 +321,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,13 +356,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -449,11 +450,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -462,7 +463,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -821,8 +822,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -962,10 +962,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>409.4</v>
+        <v>394.45</v>
       </c>
       <c r="D2">
-        <v>0.95</v>
+        <v>-3.65</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -974,46 +974,46 @@
         <v>274.85</v>
       </c>
       <c r="G2">
-        <v>-3.6</v>
+        <v>-7.12</v>
       </c>
       <c r="H2">
-        <v>48.95</v>
+        <v>43.51</v>
       </c>
       <c r="I2">
-        <v>-0.85</v>
+        <v>-3.99</v>
       </c>
       <c r="J2">
-        <v>1.26</v>
+        <v>-7.05</v>
       </c>
       <c r="K2">
-        <v>16.54</v>
+        <v>13.1</v>
       </c>
       <c r="L2">
-        <v>45.69</v>
+        <v>42.17</v>
       </c>
       <c r="M2">
-        <v>30.58</v>
+        <v>29.66</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>409.16</v>
+        <v>405.88</v>
       </c>
       <c r="Q2">
-        <v>409.31</v>
+        <v>408.03</v>
       </c>
       <c r="R2">
-        <v>402.8</v>
+        <v>402.85</v>
       </c>
       <c r="S2">
-        <v>359.39</v>
+        <v>359.7</v>
       </c>
       <c r="T2">
-        <v>13.92</v>
+        <v>9.66</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1028,34 +1028,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>53.12</v>
+        <v>42.42</v>
       </c>
       <c r="Z2">
-        <v>2.25</v>
+        <v>0.99</v>
       </c>
       <c r="AA2">
-        <v>2.78</v>
+        <v>2.43</v>
       </c>
       <c r="AB2">
-        <v>-0.53</v>
+        <v>-1.44</v>
       </c>
       <c r="AC2">
-        <v>64.09999999999999</v>
+        <v>38.05</v>
       </c>
       <c r="AD2">
-        <v>67.02</v>
+        <v>56.16</v>
       </c>
       <c r="AE2">
-        <v>9.24</v>
+        <v>9.94</v>
       </c>
       <c r="AF2">
-        <v>49.97</v>
+        <v>-29.17</v>
       </c>
       <c r="AG2">
-        <v>423.6</v>
+        <v>422.86</v>
       </c>
       <c r="AH2">
-        <v>395.02</v>
+        <v>393.21</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1064,7 +1064,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>18.54</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1075,37 +1075,37 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>52.1</v>
+        <v>51.1</v>
       </c>
       <c r="D3">
-        <v>-0.74</v>
+        <v>-1.92</v>
       </c>
       <c r="E3">
         <v>93.48</v>
       </c>
       <c r="F3">
-        <v>52.1</v>
+        <v>51.1</v>
       </c>
       <c r="G3">
-        <v>-44.27</v>
+        <v>-45.34</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-3.43</v>
+        <v>-6.2</v>
       </c>
       <c r="J3">
-        <v>-13.51</v>
+        <v>-18.12</v>
       </c>
       <c r="K3">
-        <v>-15.83</v>
+        <v>-15.59</v>
       </c>
       <c r="L3">
-        <v>-36.89</v>
+        <v>-34.55</v>
       </c>
       <c r="M3">
-        <v>-24.2</v>
+        <v>-24.48</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1114,19 +1114,19 @@
         <v>8</v>
       </c>
       <c r="P3">
-        <v>53.45</v>
+        <v>52.77</v>
       </c>
       <c r="Q3">
-        <v>56.75</v>
+        <v>56.25</v>
       </c>
       <c r="R3">
-        <v>58.17</v>
+        <v>57.97</v>
       </c>
       <c r="S3">
-        <v>65.27</v>
+        <v>65.13</v>
       </c>
       <c r="T3">
-        <v>-20.18</v>
+        <v>-21.54</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1141,43 +1141,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>29.25</v>
+        <v>26.62</v>
       </c>
       <c r="Z3">
-        <v>-1.71</v>
+        <v>-1.86</v>
       </c>
       <c r="AA3">
-        <v>-1.33</v>
+        <v>-1.43</v>
       </c>
       <c r="AB3">
-        <v>-0.39</v>
+        <v>-0.43</v>
       </c>
       <c r="AC3">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>4.05</v>
+        <v>1.55</v>
       </c>
       <c r="AE3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF3">
-        <v>-24.38</v>
+        <v>-49.81</v>
       </c>
       <c r="AG3">
-        <v>63.87</v>
+        <v>63.51</v>
       </c>
       <c r="AH3">
-        <v>49.62</v>
+        <v>49</v>
       </c>
       <c r="AI3">
-        <v>57.42</v>
+        <v>56.58</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>52.9</v>
+        <v>55.82</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1188,10 +1188,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3371</v>
+        <v>3305</v>
       </c>
       <c r="D4">
-        <v>2.46</v>
+        <v>-1.96</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1200,46 +1200,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-0.28</v>
+        <v>-2.23</v>
       </c>
       <c r="H4">
-        <v>33.18</v>
+        <v>30.58</v>
       </c>
       <c r="I4">
-        <v>2.52</v>
+        <v>0.47</v>
       </c>
       <c r="J4">
-        <v>8.710000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="K4">
-        <v>8.83</v>
+        <v>6.56</v>
       </c>
       <c r="L4">
-        <v>20.56</v>
+        <v>18.7</v>
       </c>
       <c r="M4">
-        <v>18.12</v>
+        <v>17.88</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>3301.7</v>
+        <v>3304.78</v>
       </c>
       <c r="Q4">
-        <v>3281.24</v>
+        <v>3289.59</v>
       </c>
       <c r="R4">
-        <v>3196.79</v>
+        <v>3199.39</v>
       </c>
       <c r="S4">
-        <v>2926.23</v>
+        <v>2928.87</v>
       </c>
       <c r="T4">
-        <v>15.2</v>
+        <v>12.84</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1254,34 +1254,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>63.36</v>
+        <v>55.1</v>
       </c>
       <c r="Z4">
-        <v>36.17</v>
+        <v>34.53</v>
       </c>
       <c r="AA4">
-        <v>35.76</v>
+        <v>35.51</v>
       </c>
       <c r="AB4">
-        <v>0.41</v>
+        <v>-0.98</v>
       </c>
       <c r="AC4">
-        <v>46.31</v>
+        <v>54.98</v>
       </c>
       <c r="AD4">
-        <v>27.89</v>
+        <v>41.1</v>
       </c>
       <c r="AE4">
-        <v>72.68000000000001</v>
+        <v>73.48</v>
       </c>
       <c r="AF4">
-        <v>-7.32</v>
+        <v>-27.78</v>
       </c>
       <c r="AG4">
-        <v>3388.31</v>
+        <v>3373.08</v>
       </c>
       <c r="AH4">
-        <v>3174.18</v>
+        <v>3206.11</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1290,7 +1290,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>24.62</v>
+        <v>25.31</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1301,37 +1301,37 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1015.45</v>
+        <v>1014.4</v>
       </c>
       <c r="D5">
-        <v>-2.12</v>
+        <v>-0.1</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>701.4</v>
+        <v>703.95</v>
       </c>
       <c r="G5">
-        <v>-11.68</v>
+        <v>-11.77</v>
       </c>
       <c r="H5">
-        <v>44.77</v>
+        <v>44.1</v>
       </c>
       <c r="I5">
-        <v>-4.07</v>
+        <v>-3.49</v>
       </c>
       <c r="J5">
-        <v>4.21</v>
+        <v>1.96</v>
       </c>
       <c r="K5">
-        <v>-11.41</v>
+        <v>-10.93</v>
       </c>
       <c r="L5">
-        <v>43.89</v>
+        <v>44.63</v>
       </c>
       <c r="M5">
-        <v>17.42</v>
+        <v>17.91</v>
       </c>
       <c r="N5">
         <v>62</v>
@@ -1340,19 +1340,19 @@
         <v>73</v>
       </c>
       <c r="P5">
-        <v>1036.18</v>
+        <v>1028.85</v>
       </c>
       <c r="Q5">
-        <v>1041.89</v>
+        <v>1041.61</v>
       </c>
       <c r="R5">
         <v>994.3099999999999</v>
       </c>
       <c r="S5">
-        <v>961.53</v>
+        <v>962.54</v>
       </c>
       <c r="T5">
-        <v>5.61</v>
+        <v>5.39</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1367,34 +1367,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>47.54</v>
+        <v>47.27</v>
       </c>
       <c r="Z5">
-        <v>9.76</v>
+        <v>7.39</v>
       </c>
       <c r="AA5">
-        <v>14.03</v>
+        <v>12.7</v>
       </c>
       <c r="AB5">
-        <v>-4.26</v>
+        <v>-5.31</v>
       </c>
       <c r="AC5">
         <v>5.46</v>
       </c>
       <c r="AD5">
-        <v>12.57</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AE5">
-        <v>24.59</v>
+        <v>24.54</v>
       </c>
       <c r="AF5">
-        <v>22.84</v>
+        <v>-41.13</v>
       </c>
       <c r="AG5">
-        <v>1072.78</v>
+        <v>1073.42</v>
       </c>
       <c r="AH5">
-        <v>1010.99</v>
+        <v>1009.79</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1403,7 +1403,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>24.67</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1414,10 +1414,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.33</v>
+        <v>14.06</v>
       </c>
       <c r="D6">
-        <v>-2.38</v>
+        <v>-1.88</v>
       </c>
       <c r="E6">
         <v>15.19</v>
@@ -1426,46 +1426,46 @@
         <v>6.49</v>
       </c>
       <c r="G6">
-        <v>-5.66</v>
+        <v>-7.44</v>
       </c>
       <c r="H6">
-        <v>120.8</v>
+        <v>116.64</v>
       </c>
       <c r="I6">
-        <v>1.85</v>
+        <v>-7.44</v>
       </c>
       <c r="J6">
-        <v>10.15</v>
+        <v>9.33</v>
       </c>
       <c r="K6">
-        <v>1.2</v>
+        <v>-5.32</v>
       </c>
       <c r="L6">
-        <v>113.56</v>
+        <v>114</v>
       </c>
       <c r="M6">
-        <v>18.63</v>
+        <v>18.18</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P6">
-        <v>14.85</v>
+        <v>14.62</v>
       </c>
       <c r="Q6">
-        <v>13.81</v>
+        <v>13.87</v>
       </c>
       <c r="R6">
-        <v>13.8</v>
+        <v>13.78</v>
       </c>
       <c r="S6">
-        <v>11.82</v>
+        <v>11.84</v>
       </c>
       <c r="T6">
-        <v>21.21</v>
+        <v>18.75</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1480,34 +1480,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>55.73</v>
+        <v>51.37</v>
       </c>
       <c r="Z6">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="AA6">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="AB6">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="AC6">
-        <v>52.63</v>
+        <v>24.06</v>
       </c>
       <c r="AD6">
-        <v>75.83</v>
+        <v>52.91</v>
       </c>
       <c r="AE6">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="AF6">
-        <v>-8.75</v>
+        <v>-31.25</v>
       </c>
       <c r="AG6">
         <v>15.43</v>
       </c>
       <c r="AH6">
-        <v>12.19</v>
+        <v>12.3</v>
       </c>
       <c r="AI6">
         <v>13.86</v>
@@ -1516,7 +1516,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>56.54</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1530,7 +1530,7 @@
         <v>11.1</v>
       </c>
       <c r="D7">
-        <v>-1.77</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1545,40 +1545,40 @@
         <v>136.67</v>
       </c>
       <c r="I7">
-        <v>-2.2</v>
+        <v>-2.03</v>
       </c>
       <c r="J7">
-        <v>-11.34</v>
+        <v>-15.53</v>
       </c>
       <c r="K7">
-        <v>-7.35</v>
+        <v>-6.49</v>
       </c>
       <c r="L7">
-        <v>97.16</v>
+        <v>104.42</v>
       </c>
       <c r="M7">
-        <v>-30.32</v>
+        <v>-30.7</v>
       </c>
       <c r="N7">
         <v>87</v>
       </c>
       <c r="O7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P7">
-        <v>11.19</v>
+        <v>11.14</v>
       </c>
       <c r="Q7">
-        <v>11.95</v>
+        <v>11.83</v>
       </c>
       <c r="R7">
-        <v>11.57</v>
+        <v>11.56</v>
       </c>
       <c r="S7">
-        <v>10.2</v>
+        <v>10.23</v>
       </c>
       <c r="T7">
-        <v>8.84</v>
+        <v>8.51</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1596,40 +1596,40 @@
         <v>39.2</v>
       </c>
       <c r="Z7">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="AA7">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="AB7">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AC7">
-        <v>11.86</v>
+        <v>15.33</v>
       </c>
       <c r="AD7">
-        <v>6.88</v>
+        <v>11.99</v>
       </c>
       <c r="AE7">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AF7">
-        <v>-66.23999999999999</v>
+        <v>-79.87</v>
       </c>
       <c r="AG7">
-        <v>13.42</v>
+        <v>13.15</v>
       </c>
       <c r="AH7">
-        <v>10.48</v>
+        <v>10.51</v>
       </c>
       <c r="AI7">
-        <v>11.9</v>
+        <v>11.87</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>38.75</v>
+        <v>39.27</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1640,10 +1640,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4353.4</v>
+        <v>4353.2</v>
       </c>
       <c r="D8">
-        <v>-0.79</v>
+        <v>-0</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1652,46 +1652,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-25.06</v>
+        <v>-25.07</v>
       </c>
       <c r="H8">
         <v>4.77</v>
       </c>
       <c r="I8">
-        <v>-0.2</v>
+        <v>-0.96</v>
       </c>
       <c r="J8">
-        <v>1.17</v>
+        <v>0.15</v>
       </c>
       <c r="K8">
-        <v>-0.19</v>
+        <v>0.71</v>
       </c>
       <c r="L8">
-        <v>-11.67</v>
+        <v>-10.74</v>
       </c>
       <c r="M8">
-        <v>19.61</v>
+        <v>19.7</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P8">
-        <v>4385.06</v>
+        <v>4376.64</v>
       </c>
       <c r="Q8">
-        <v>4387.34</v>
+        <v>4387.78</v>
       </c>
       <c r="R8">
-        <v>4375.54</v>
+        <v>4373.94</v>
       </c>
       <c r="S8">
-        <v>4648.12</v>
+        <v>4643.51</v>
       </c>
       <c r="T8">
-        <v>-6.34</v>
+        <v>-6.25</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1706,34 +1706,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>47.62</v>
+        <v>47.61</v>
       </c>
       <c r="Z8">
-        <v>0.5</v>
+        <v>-1.69</v>
       </c>
       <c r="AA8">
-        <v>3.95</v>
+        <v>2.82</v>
       </c>
       <c r="AB8">
-        <v>-3.44</v>
+        <v>-4.51</v>
       </c>
       <c r="AC8">
-        <v>27.22</v>
+        <v>25.88</v>
       </c>
       <c r="AD8">
-        <v>33.75</v>
+        <v>29.83</v>
       </c>
       <c r="AE8">
-        <v>94.13</v>
+        <v>92.84</v>
       </c>
       <c r="AF8">
-        <v>-77.93000000000001</v>
+        <v>-68.8</v>
       </c>
       <c r="AG8">
-        <v>4534.65</v>
+        <v>4534.6</v>
       </c>
       <c r="AH8">
-        <v>4240.03</v>
+        <v>4240.97</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1742,7 +1742,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>16.06</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1753,10 +1753,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11450</v>
+        <v>11400</v>
       </c>
       <c r="D9">
-        <v>-1.2</v>
+        <v>-0.44</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1765,25 +1765,25 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-12.27</v>
+        <v>-12.66</v>
       </c>
       <c r="H9">
-        <v>10.5</v>
+        <v>10.02</v>
       </c>
       <c r="I9">
-        <v>-0.47</v>
+        <v>-1.21</v>
       </c>
       <c r="J9">
-        <v>-3.81</v>
+        <v>-5.43</v>
       </c>
       <c r="K9">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="L9">
-        <v>-9.199999999999999</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="M9">
-        <v>8.380000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="N9">
         <v>38</v>
@@ -1792,22 +1792,22 @@
         <v>44</v>
       </c>
       <c r="P9">
-        <v>11602.6</v>
+        <v>11574.6</v>
       </c>
       <c r="Q9">
-        <v>11734.2</v>
+        <v>11701.7</v>
       </c>
       <c r="R9">
-        <v>11703.48</v>
+        <v>11703.44</v>
       </c>
       <c r="S9">
-        <v>11775.5</v>
+        <v>11772.83</v>
       </c>
       <c r="T9">
-        <v>-2.76</v>
+        <v>-3.17</v>
       </c>
       <c r="U9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V9" t="s">
         <v>47</v>
@@ -1816,46 +1816,46 @@
         <v>47</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>40.63</v>
+        <v>39.06</v>
       </c>
       <c r="Z9">
-        <v>-63.09</v>
+        <v>-75.93000000000001</v>
       </c>
       <c r="AA9">
-        <v>-40.7</v>
+        <v>-47.75</v>
       </c>
       <c r="AB9">
-        <v>-22.39</v>
+        <v>-28.18</v>
       </c>
       <c r="AC9">
-        <v>45.9</v>
+        <v>26.96</v>
       </c>
       <c r="AD9">
-        <v>50.42</v>
+        <v>43.69</v>
       </c>
       <c r="AE9">
-        <v>189.24</v>
+        <v>187.15</v>
       </c>
       <c r="AF9">
-        <v>69.55</v>
+        <v>-25.02</v>
       </c>
       <c r="AG9">
-        <v>12213.01</v>
+        <v>12178.49</v>
       </c>
       <c r="AH9">
-        <v>11255.39</v>
+        <v>11224.91</v>
       </c>
       <c r="AI9">
-        <v>12053.63</v>
+        <v>12031.46</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>23.75</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1996,7 +1996,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2055,1203 +2055,1112 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="5" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="E8" s="3" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1.26</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-7.05</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-8.31</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>76</v>
+      <c r="A10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-13.51</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-18.12</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-4.61</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>2.92</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="D11" s="7">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="E11" s="8">
-        <v>-1.66</v>
+        <v>-7.33</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-10.94</v>
+        <v>4.21</v>
       </c>
       <c r="D12" s="7">
-        <v>-13.51</v>
+        <v>1.96</v>
       </c>
       <c r="E12" s="8">
-        <v>-2.57</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>5.96</v>
+        <v>10.15</v>
       </c>
       <c r="D13" s="7">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="E13" s="9">
-        <v>2.75</v>
+        <v>9.33</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>6.9</v>
+        <v>-11.34</v>
       </c>
       <c r="D14" s="7">
-        <v>4.21</v>
+        <v>-15.53</v>
       </c>
       <c r="E14" s="8">
-        <v>-2.69</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>14.06</v>
+        <v>1.17</v>
       </c>
       <c r="D15" s="7">
-        <v>10.15</v>
+        <v>0.15</v>
       </c>
       <c r="E15" s="8">
-        <v>-3.91</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-5.28</v>
+        <v>-3.81</v>
       </c>
       <c r="D16" s="7">
-        <v>-11.34</v>
+        <v>-5.43</v>
       </c>
       <c r="E16" s="8">
-        <v>-6.06</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>1.63</v>
+        <v>-0.85</v>
       </c>
       <c r="D17" s="7">
-        <v>1.17</v>
+        <v>-3.99</v>
       </c>
       <c r="E17" s="8">
-        <v>-0.46</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>-2.18</v>
+        <v>-3.43</v>
       </c>
       <c r="D18" s="7">
-        <v>-3.81</v>
+        <v>-6.2</v>
       </c>
       <c r="E18" s="8">
-        <v>-1.63</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>-1.8</v>
+        <v>2.52</v>
       </c>
       <c r="D19" s="7">
-        <v>-0.85</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0.95</v>
+        <v>0.47</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-3.42</v>
+        <v>-4.07</v>
       </c>
       <c r="D20" s="7">
-        <v>-3.43</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.01</v>
+        <v>-3.49</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0.58</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-0.54</v>
+        <v>1.85</v>
       </c>
       <c r="D21" s="7">
-        <v>2.52</v>
-      </c>
-      <c r="E21" s="9">
-        <v>3.06</v>
+        <v>-7.44</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-9.289999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>0.33</v>
+        <v>-2.2</v>
       </c>
       <c r="D22" s="7">
-        <v>-4.07</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-4.4</v>
+        <v>-2.03</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.17</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>5.31</v>
+        <v>-0.2</v>
       </c>
       <c r="D23" s="7">
-        <v>1.85</v>
+        <v>-0.96</v>
       </c>
       <c r="E23" s="8">
-        <v>-3.46</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>-1.74</v>
+        <v>-0.47</v>
       </c>
       <c r="D24" s="7">
-        <v>-2.2</v>
+        <v>-1.21</v>
       </c>
       <c r="E24" s="8">
-        <v>-0.46</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" s="7">
-        <v>0.71</v>
+        <v>45.69</v>
       </c>
       <c r="D25" s="7">
-        <v>-0.2</v>
+        <v>42.17</v>
       </c>
       <c r="E25" s="8">
-        <v>-0.91</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="7">
-        <v>0.16</v>
+        <v>-36.89</v>
       </c>
       <c r="D26" s="7">
-        <v>-0.47</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.63</v>
+        <v>-34.55</v>
+      </c>
+      <c r="E26" s="9">
+        <v>2.34</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>42.2</v>
+        <v>20.56</v>
       </c>
       <c r="D27" s="7">
-        <v>45.69</v>
-      </c>
-      <c r="E27" s="9">
-        <v>3.49</v>
+        <v>18.7</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>-35.97</v>
+        <v>43.89</v>
       </c>
       <c r="D28" s="7">
-        <v>-36.89</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.92</v>
+        <v>44.63</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.74</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>17.02</v>
+        <v>113.56</v>
       </c>
       <c r="D29" s="7">
-        <v>20.56</v>
+        <v>114</v>
       </c>
       <c r="E29" s="9">
-        <v>3.54</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>44.92</v>
+        <v>97.16</v>
       </c>
       <c r="D30" s="7">
-        <v>43.89</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.03</v>
+        <v>104.42</v>
+      </c>
+      <c r="E30" s="9">
+        <v>7.26</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>98.38</v>
+        <v>-11.67</v>
       </c>
       <c r="D31" s="7">
-        <v>113.56</v>
+        <v>-10.74</v>
       </c>
       <c r="E31" s="9">
-        <v>15.18</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>108.1</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D32" s="7">
-        <v>97.16</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-10.94</v>
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="7">
-        <v>-11.81</v>
+        <v>16.54</v>
       </c>
       <c r="D33" s="7">
-        <v>-11.67</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.14</v>
+        <v>13.1</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-3.44</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="7">
-        <v>-8.07</v>
+        <v>-15.83</v>
       </c>
       <c r="D34" s="7">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.13</v>
+        <v>-15.59</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.24</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="7">
-        <v>15.69</v>
+        <v>8.83</v>
       </c>
       <c r="D35" s="7">
-        <v>16.54</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.85</v>
+        <v>6.56</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>-16.36</v>
+        <v>-11.41</v>
       </c>
       <c r="D36" s="7">
-        <v>-15.83</v>
+        <v>-10.93</v>
       </c>
       <c r="E36" s="9">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>6.04</v>
+        <v>1.2</v>
       </c>
       <c r="D37" s="7">
-        <v>8.83</v>
-      </c>
-      <c r="E37" s="9">
-        <v>2.79</v>
+        <v>-5.32</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-6.52</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>-9.1</v>
+        <v>-7.35</v>
       </c>
       <c r="D38" s="7">
-        <v>-11.41</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-2.31</v>
+        <v>-6.49</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0.86</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>5.23</v>
+        <v>-0.19</v>
       </c>
       <c r="D39" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-4.03</v>
+        <v>0.71</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.9</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>-9.02</v>
+        <v>2.55</v>
       </c>
       <c r="D40" s="7">
-        <v>-7.35</v>
+        <v>2.69</v>
       </c>
       <c r="E40" s="9">
-        <v>1.67</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C41" s="7">
-        <v>0.68</v>
+        <v>-3.6</v>
       </c>
       <c r="D41" s="7">
-        <v>-0.19</v>
+        <v>-7.12</v>
       </c>
       <c r="E41" s="8">
-        <v>-0.87</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C42" s="7">
-        <v>3.18</v>
+        <v>-44.27</v>
       </c>
       <c r="D42" s="7">
-        <v>2.55</v>
+        <v>-45.34</v>
       </c>
       <c r="E42" s="8">
-        <v>-0.63</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="7">
-        <v>-4.51</v>
+        <v>-0.28</v>
       </c>
       <c r="D43" s="7">
-        <v>-3.6</v>
-      </c>
-      <c r="E43" s="9">
-        <v>0.91</v>
+        <v>-2.23</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="7">
-        <v>-43.85</v>
+        <v>-11.68</v>
       </c>
       <c r="D44" s="7">
-        <v>-44.27</v>
+        <v>-11.77</v>
       </c>
       <c r="E44" s="8">
-        <v>-0.42</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>-2.68</v>
+        <v>-5.66</v>
       </c>
       <c r="D45" s="7">
-        <v>-0.28</v>
-      </c>
-      <c r="E45" s="9">
-        <v>2.4</v>
+        <v>-7.44</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-9.77</v>
+        <v>-25.06</v>
       </c>
       <c r="D46" s="7">
-        <v>-11.68</v>
+        <v>-25.07</v>
       </c>
       <c r="E46" s="8">
-        <v>-1.91</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-3.36</v>
+        <v>-12.27</v>
       </c>
       <c r="D47" s="7">
-        <v>-5.66</v>
+        <v>-12.66</v>
       </c>
       <c r="E47" s="8">
-        <v>-2.3</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C48" s="7">
-        <v>-18.82</v>
+        <v>409.4</v>
       </c>
       <c r="D48" s="7">
-        <v>-20.26</v>
+        <v>394.45</v>
       </c>
       <c r="E48" s="8">
-        <v>-1.44</v>
+        <v>-14.95</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C49" s="7">
-        <v>-24.47</v>
+        <v>52.1</v>
       </c>
       <c r="D49" s="7">
-        <v>-25.06</v>
+        <v>51.1</v>
       </c>
       <c r="E49" s="8">
-        <v>-0.59</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C50" s="7">
-        <v>-11.21</v>
+        <v>3371</v>
       </c>
       <c r="D50" s="7">
-        <v>-12.27</v>
+        <v>3305</v>
       </c>
       <c r="E50" s="8">
-        <v>-1.06</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C51" s="7">
-        <v>405.55</v>
+        <v>1015.45</v>
       </c>
       <c r="D51" s="7">
-        <v>409.4</v>
-      </c>
-      <c r="E51" s="9">
-        <v>3.85</v>
+        <v>1014.4</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="7">
-        <v>52.49</v>
+        <v>14.33</v>
       </c>
       <c r="D52" s="7">
-        <v>52.1</v>
+        <v>14.06</v>
       </c>
       <c r="E52" s="8">
-        <v>-0.39</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="7">
-        <v>3290</v>
+        <v>4353.4</v>
       </c>
       <c r="D53" s="7">
-        <v>3371</v>
-      </c>
-      <c r="E53" s="9">
-        <v>81</v>
+        <v>4353.2</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="7">
-        <v>1037.4</v>
+        <v>11450</v>
       </c>
       <c r="D54" s="7">
-        <v>1015.45</v>
+        <v>11400</v>
       </c>
       <c r="E54" s="8">
-        <v>-21.95</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C55" s="7">
-        <v>14.68</v>
+        <v>53.12</v>
       </c>
       <c r="D55" s="7">
-        <v>14.33</v>
+        <v>42.42</v>
       </c>
       <c r="E55" s="8">
-        <v>-0.35</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C56" s="7">
-        <v>11.3</v>
+        <v>29.25</v>
       </c>
       <c r="D56" s="7">
-        <v>11.1</v>
+        <v>26.62</v>
       </c>
       <c r="E56" s="8">
-        <v>-0.2</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C57" s="7">
-        <v>4387.9</v>
+        <v>63.36</v>
       </c>
       <c r="D57" s="7">
-        <v>4353.4</v>
+        <v>55.1</v>
       </c>
       <c r="E57" s="8">
-        <v>-34.5</v>
+        <v>-8.26</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C58" s="7">
-        <v>11589</v>
+        <v>47.54</v>
       </c>
       <c r="D58" s="7">
-        <v>11450</v>
+        <v>47.27</v>
       </c>
       <c r="E58" s="8">
-        <v>-139</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="7">
-        <v>50.11</v>
+        <v>55.73</v>
       </c>
       <c r="D59" s="7">
-        <v>53.12</v>
-      </c>
-      <c r="E59" s="9">
-        <v>3.01</v>
+        <v>51.37</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-4.36</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="7">
-        <v>30.34</v>
+        <v>47.62</v>
       </c>
       <c r="D60" s="7">
-        <v>29.25</v>
+        <v>47.61</v>
       </c>
       <c r="E60" s="8">
-        <v>-1.09</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="7">
-        <v>55.81</v>
+        <v>40.63</v>
       </c>
       <c r="D61" s="7">
-        <v>63.36</v>
-      </c>
-      <c r="E61" s="9">
-        <v>7.55</v>
+        <v>39.06</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C62" s="7">
-        <v>53.36</v>
+        <v>49.97</v>
       </c>
       <c r="D62" s="7">
-        <v>47.54</v>
+        <v>-29.17</v>
       </c>
       <c r="E62" s="8">
-        <v>-5.82</v>
+        <v>-79.14</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C63" s="7">
-        <v>62.06</v>
+        <v>-24.38</v>
       </c>
       <c r="D63" s="7">
-        <v>55.73</v>
+        <v>-49.81</v>
       </c>
       <c r="E63" s="8">
-        <v>-6.33</v>
+        <v>-25.43</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C64" s="7">
-        <v>42.23</v>
+        <v>-7.32</v>
       </c>
       <c r="D64" s="7">
-        <v>39.2</v>
+        <v>-27.78</v>
       </c>
       <c r="E64" s="8">
-        <v>-3.03</v>
+        <v>-20.46</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C65" s="7">
-        <v>50.54</v>
+        <v>22.84</v>
       </c>
       <c r="D65" s="7">
-        <v>47.62</v>
+        <v>-41.13</v>
       </c>
       <c r="E65" s="8">
-        <v>-2.92</v>
+        <v>-63.97</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C66" s="7">
-        <v>45.32</v>
+        <v>-8.75</v>
       </c>
       <c r="D66" s="7">
-        <v>40.63</v>
+        <v>-31.25</v>
       </c>
       <c r="E66" s="8">
-        <v>-4.69</v>
+        <v>-22.5</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C67" s="7">
-        <v>-68.65000000000001</v>
+        <v>-66.23999999999999</v>
       </c>
       <c r="D67" s="7">
-        <v>49.97</v>
-      </c>
-      <c r="E67" s="9">
-        <v>118.62</v>
+        <v>-79.87</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-13.63</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="7">
-        <v>-40.21</v>
+        <v>-77.93000000000001</v>
       </c>
       <c r="D68" s="7">
-        <v>-24.38</v>
+        <v>-68.8</v>
       </c>
       <c r="E68" s="9">
-        <v>15.83</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="7">
-        <v>-37.49</v>
+        <v>69.55</v>
       </c>
       <c r="D69" s="7">
-        <v>-7.32</v>
-      </c>
-      <c r="E69" s="9">
-        <v>30.17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="7">
-        <v>-64.91</v>
-      </c>
-      <c r="D70" s="7">
-        <v>22.84</v>
-      </c>
-      <c r="E70" s="9">
-        <v>87.75</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="7">
-        <v>-16.99</v>
-      </c>
-      <c r="D71" s="7">
-        <v>-8.75</v>
-      </c>
-      <c r="E71" s="9">
-        <v>8.24</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="7">
-        <v>-53.06</v>
-      </c>
-      <c r="D72" s="7">
-        <v>-66.23999999999999</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-13.18</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="7">
-        <v>-77.69</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-77.93000000000001</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>3.68</v>
-      </c>
-      <c r="D74" s="7">
-        <v>69.55</v>
-      </c>
-      <c r="E74" s="9">
-        <v>65.87</v>
+        <v>-25.02</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-94.56999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3275,28 +3184,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3310,16 +3219,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="12">
-        <v>47.1</v>
+        <v>43.6</v>
       </c>
       <c r="E2" s="12">
         <v>60</v>
       </c>
       <c r="F2" s="12">
-        <v>-0.4</v>
+        <v>-4.2</v>
       </c>
       <c r="G2" s="12">
-        <v>-0.7</v>
+        <v>-1.9</v>
       </c>
       <c r="H2" s="12">
         <v>56.1</v>
@@ -3436,10 +3345,10 @@
         <v>41</v>
       </c>
       <c r="D1" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>40</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>44</v>
@@ -3453,28 +3362,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="15">
-        <v>0.3058</v>
+        <v>0.2966</v>
       </c>
       <c r="B2" s="15">
-        <v>0.1961</v>
+        <v>0.197</v>
       </c>
       <c r="C2" s="15">
-        <v>0.1863</v>
+        <v>0.1818</v>
       </c>
       <c r="D2" s="15">
-        <v>0.1812</v>
+        <v>0.1791</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1742</v>
+        <v>0.1788</v>
       </c>
       <c r="F2" s="15">
-        <v>0.08380000000000001</v>
+        <v>0.08470000000000001</v>
       </c>
       <c r="G2" s="15">
-        <v>-0.242</v>
+        <v>-0.2448</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.3032</v>
+        <v>-0.307</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,55 +175,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-0.3% → -2.2%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-0.3%</t>
-  </si>
-  <si>
-    <t>-2.2%</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>53.1 → 42.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.1</t>
-  </si>
-  <si>
-    <t>42.4</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -275,7 +227,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,7 +261,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -321,15 +273,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -356,19 +301,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -438,23 +377,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -463,7 +400,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -821,8 +758,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -962,10 +899,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>394.45</v>
+        <v>397.05</v>
       </c>
       <c r="D2">
-        <v>-3.65</v>
+        <v>0.66</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -974,46 +911,46 @@
         <v>274.85</v>
       </c>
       <c r="G2">
-        <v>-7.12</v>
+        <v>-6.51</v>
       </c>
       <c r="H2">
-        <v>43.51</v>
+        <v>44.46</v>
       </c>
       <c r="I2">
-        <v>-3.99</v>
+        <v>-3.16</v>
       </c>
       <c r="J2">
-        <v>-7.05</v>
+        <v>-5.46</v>
       </c>
       <c r="K2">
-        <v>13.1</v>
+        <v>12.27</v>
       </c>
       <c r="L2">
-        <v>42.17</v>
+        <v>42.9</v>
       </c>
       <c r="M2">
-        <v>29.66</v>
+        <v>29.8</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P2">
-        <v>405.88</v>
+        <v>403.29</v>
       </c>
       <c r="Q2">
-        <v>408.03</v>
+        <v>406.65</v>
       </c>
       <c r="R2">
-        <v>402.85</v>
+        <v>403.11</v>
       </c>
       <c r="S2">
-        <v>359.7</v>
+        <v>360.03</v>
       </c>
       <c r="T2">
-        <v>9.66</v>
+        <v>10.28</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1028,34 +965,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>42.42</v>
+        <v>44.51</v>
       </c>
       <c r="Z2">
-        <v>0.99</v>
+        <v>0.19</v>
       </c>
       <c r="AA2">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="AB2">
-        <v>-1.44</v>
+        <v>-1.78</v>
       </c>
       <c r="AC2">
-        <v>38.05</v>
+        <v>28.92</v>
       </c>
       <c r="AD2">
-        <v>56.16</v>
+        <v>43.69</v>
       </c>
       <c r="AE2">
-        <v>9.94</v>
+        <v>10.09</v>
       </c>
       <c r="AF2">
-        <v>-29.17</v>
+        <v>58.03</v>
       </c>
       <c r="AG2">
-        <v>422.86</v>
+        <v>420.02</v>
       </c>
       <c r="AH2">
-        <v>393.21</v>
+        <v>393.28</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1064,7 +1001,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>22.04</v>
+        <v>26.28</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1075,58 +1012,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>51.1</v>
+        <v>50.47</v>
       </c>
       <c r="D3">
-        <v>-1.92</v>
+        <v>-1.23</v>
       </c>
       <c r="E3">
         <v>93.48</v>
       </c>
       <c r="F3">
-        <v>51.1</v>
+        <v>50.47</v>
       </c>
       <c r="G3">
-        <v>-45.34</v>
+        <v>-46.01</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-6.2</v>
+        <v>-7.43</v>
       </c>
       <c r="J3">
-        <v>-18.12</v>
+        <v>-17.26</v>
       </c>
       <c r="K3">
-        <v>-15.59</v>
+        <v>-17.3</v>
       </c>
       <c r="L3">
-        <v>-34.55</v>
+        <v>-34.75</v>
       </c>
       <c r="M3">
-        <v>-24.48</v>
+        <v>-25.42</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P3">
-        <v>52.77</v>
+        <v>51.96</v>
       </c>
       <c r="Q3">
-        <v>56.25</v>
+        <v>55.67</v>
       </c>
       <c r="R3">
-        <v>57.97</v>
+        <v>57.79</v>
       </c>
       <c r="S3">
-        <v>65.13</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="T3">
-        <v>-21.54</v>
+        <v>-22.34</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1141,43 +1078,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>26.62</v>
+        <v>25.09</v>
       </c>
       <c r="Z3">
-        <v>-1.86</v>
+        <v>-2</v>
       </c>
       <c r="AA3">
-        <v>-1.43</v>
+        <v>-1.55</v>
       </c>
       <c r="AB3">
-        <v>-0.43</v>
+        <v>-0.45</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.55</v>
+        <v>0.17</v>
       </c>
       <c r="AE3">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AF3">
-        <v>-49.81</v>
+        <v>-30.45</v>
       </c>
       <c r="AG3">
-        <v>63.51</v>
+        <v>62.82</v>
       </c>
       <c r="AH3">
-        <v>49</v>
+        <v>48.52</v>
       </c>
       <c r="AI3">
-        <v>56.58</v>
+        <v>55.66</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>55.82</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1188,10 +1125,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3305</v>
+        <v>3294.9</v>
       </c>
       <c r="D4">
-        <v>-1.96</v>
+        <v>-0.31</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1200,46 +1137,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.23</v>
+        <v>-2.53</v>
       </c>
       <c r="H4">
-        <v>30.58</v>
+        <v>30.18</v>
       </c>
       <c r="I4">
-        <v>0.47</v>
+        <v>-0.15</v>
       </c>
       <c r="J4">
-        <v>1.38</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>6.56</v>
+        <v>6.17</v>
       </c>
       <c r="L4">
-        <v>18.7</v>
+        <v>18.71</v>
       </c>
       <c r="M4">
-        <v>17.88</v>
+        <v>17.6</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>3304.78</v>
+        <v>3303.78</v>
       </c>
       <c r="Q4">
-        <v>3289.59</v>
+        <v>3293.14</v>
       </c>
       <c r="R4">
-        <v>3199.39</v>
+        <v>3202.4</v>
       </c>
       <c r="S4">
-        <v>2928.87</v>
+        <v>2931.43</v>
       </c>
       <c r="T4">
-        <v>12.84</v>
+        <v>12.4</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1254,34 +1191,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>55.1</v>
+        <v>53.94</v>
       </c>
       <c r="Z4">
-        <v>34.53</v>
+        <v>32.04</v>
       </c>
       <c r="AA4">
-        <v>35.51</v>
+        <v>34.82</v>
       </c>
       <c r="AB4">
-        <v>-0.98</v>
+        <v>-2.78</v>
       </c>
       <c r="AC4">
-        <v>54.98</v>
+        <v>47.22</v>
       </c>
       <c r="AD4">
-        <v>41.1</v>
+        <v>49.5</v>
       </c>
       <c r="AE4">
-        <v>73.48</v>
+        <v>73.2</v>
       </c>
       <c r="AF4">
-        <v>-27.78</v>
+        <v>-5.86</v>
       </c>
       <c r="AG4">
-        <v>3373.08</v>
+        <v>3370.71</v>
       </c>
       <c r="AH4">
-        <v>3206.11</v>
+        <v>3215.57</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1290,7 +1227,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>25.31</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1301,37 +1238,37 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1014.4</v>
+        <v>1009.7</v>
       </c>
       <c r="D5">
-        <v>-0.1</v>
+        <v>-0.46</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>703.95</v>
+        <v>719.6</v>
       </c>
       <c r="G5">
-        <v>-11.77</v>
+        <v>-12.18</v>
       </c>
       <c r="H5">
-        <v>44.1</v>
+        <v>40.31</v>
       </c>
       <c r="I5">
-        <v>-3.49</v>
+        <v>-4.11</v>
       </c>
       <c r="J5">
-        <v>1.96</v>
+        <v>-1.01</v>
       </c>
       <c r="K5">
-        <v>-10.93</v>
+        <v>-10.3</v>
       </c>
       <c r="L5">
-        <v>44.63</v>
+        <v>43.43</v>
       </c>
       <c r="M5">
-        <v>17.91</v>
+        <v>17.86</v>
       </c>
       <c r="N5">
         <v>62</v>
@@ -1340,19 +1277,19 @@
         <v>73</v>
       </c>
       <c r="P5">
-        <v>1028.85</v>
+        <v>1020.19</v>
       </c>
       <c r="Q5">
-        <v>1041.61</v>
+        <v>1040.09</v>
       </c>
       <c r="R5">
-        <v>994.3099999999999</v>
+        <v>994.77</v>
       </c>
       <c r="S5">
-        <v>962.54</v>
+        <v>963.5700000000001</v>
       </c>
       <c r="T5">
-        <v>5.39</v>
+        <v>4.79</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1367,34 +1304,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>47.27</v>
+        <v>46.03</v>
       </c>
       <c r="Z5">
-        <v>7.39</v>
+        <v>5.08</v>
       </c>
       <c r="AA5">
-        <v>12.7</v>
+        <v>11.17</v>
       </c>
       <c r="AB5">
-        <v>-5.31</v>
+        <v>-6.1</v>
       </c>
       <c r="AC5">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>8.539999999999999</v>
+        <v>3.64</v>
       </c>
       <c r="AE5">
-        <v>24.54</v>
+        <v>23.94</v>
       </c>
       <c r="AF5">
-        <v>-41.13</v>
+        <v>-58.29</v>
       </c>
       <c r="AG5">
-        <v>1073.42</v>
+        <v>1074.97</v>
       </c>
       <c r="AH5">
-        <v>1009.79</v>
+        <v>1005.21</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1403,7 +1340,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>24.6</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1414,58 +1351,58 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.06</v>
+        <v>14.53</v>
       </c>
       <c r="D6">
-        <v>-1.88</v>
+        <v>3.34</v>
       </c>
       <c r="E6">
         <v>15.19</v>
       </c>
       <c r="F6">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
       <c r="G6">
-        <v>-7.44</v>
+        <v>-4.34</v>
       </c>
       <c r="H6">
-        <v>116.64</v>
+        <v>123.2</v>
       </c>
       <c r="I6">
-        <v>-7.44</v>
+        <v>-3.52</v>
       </c>
       <c r="J6">
-        <v>9.33</v>
+        <v>12.64</v>
       </c>
       <c r="K6">
-        <v>-5.32</v>
+        <v>-2.68</v>
       </c>
       <c r="L6">
-        <v>114</v>
+        <v>123.88</v>
       </c>
       <c r="M6">
-        <v>18.18</v>
+        <v>15.24</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P6">
-        <v>14.62</v>
+        <v>14.51</v>
       </c>
       <c r="Q6">
-        <v>13.87</v>
+        <v>13.95</v>
       </c>
       <c r="R6">
         <v>13.78</v>
       </c>
       <c r="S6">
-        <v>11.84</v>
+        <v>11.86</v>
       </c>
       <c r="T6">
-        <v>18.75</v>
+        <v>22.53</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1480,34 +1417,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>51.37</v>
+        <v>57.59</v>
       </c>
       <c r="Z6">
         <v>0.3</v>
       </c>
       <c r="AA6">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AB6">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AC6">
-        <v>24.06</v>
+        <v>11.21</v>
       </c>
       <c r="AD6">
-        <v>52.91</v>
+        <v>29.3</v>
       </c>
       <c r="AE6">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="AF6">
-        <v>-31.25</v>
+        <v>13.48</v>
       </c>
       <c r="AG6">
-        <v>15.43</v>
+        <v>15.46</v>
       </c>
       <c r="AH6">
-        <v>12.3</v>
+        <v>12.45</v>
       </c>
       <c r="AI6">
         <v>13.86</v>
@@ -1516,7 +1453,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>49.78</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1527,10 +1464,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.1</v>
+        <v>11.27</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1539,46 +1476,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-20.26</v>
+        <v>-19.04</v>
       </c>
       <c r="H7">
-        <v>136.67</v>
+        <v>140.3</v>
       </c>
       <c r="I7">
-        <v>-2.03</v>
+        <v>1.44</v>
       </c>
       <c r="J7">
-        <v>-15.53</v>
+        <v>-16.7</v>
       </c>
       <c r="K7">
-        <v>-6.49</v>
+        <v>-5.93</v>
       </c>
       <c r="L7">
-        <v>104.42</v>
+        <v>117.99</v>
       </c>
       <c r="M7">
-        <v>-30.7</v>
+        <v>-30.82</v>
       </c>
       <c r="N7">
         <v>87</v>
       </c>
       <c r="O7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P7">
-        <v>11.14</v>
+        <v>11.18</v>
       </c>
       <c r="Q7">
-        <v>11.83</v>
+        <v>11.73</v>
       </c>
       <c r="R7">
-        <v>11.56</v>
+        <v>11.55</v>
       </c>
       <c r="S7">
-        <v>10.23</v>
+        <v>10.26</v>
       </c>
       <c r="T7">
-        <v>8.51</v>
+        <v>9.84</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1593,34 +1530,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>39.2</v>
+        <v>43.21</v>
       </c>
       <c r="Z7">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="AA7">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="AB7">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="AC7">
-        <v>15.33</v>
+        <v>21.66</v>
       </c>
       <c r="AD7">
-        <v>11.99</v>
+        <v>16.28</v>
       </c>
       <c r="AE7">
         <v>0.27</v>
       </c>
       <c r="AF7">
-        <v>-79.87</v>
+        <v>-37.76</v>
       </c>
       <c r="AG7">
-        <v>13.15</v>
+        <v>12.88</v>
       </c>
       <c r="AH7">
-        <v>10.51</v>
+        <v>10.58</v>
       </c>
       <c r="AI7">
         <v>11.87</v>
@@ -1629,7 +1566,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>39.27</v>
+        <v>36.16</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1640,10 +1577,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4353.2</v>
+        <v>4325</v>
       </c>
       <c r="D8">
-        <v>-0</v>
+        <v>-0.65</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1652,46 +1589,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-25.07</v>
+        <v>-25.55</v>
       </c>
       <c r="H8">
-        <v>4.77</v>
+        <v>4.09</v>
       </c>
       <c r="I8">
-        <v>-0.96</v>
+        <v>-2.26</v>
       </c>
       <c r="J8">
-        <v>0.15</v>
+        <v>-0.44</v>
       </c>
       <c r="K8">
-        <v>0.71</v>
+        <v>1.15</v>
       </c>
       <c r="L8">
-        <v>-10.74</v>
+        <v>-11.12</v>
       </c>
       <c r="M8">
-        <v>19.7</v>
+        <v>19.07</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P8">
-        <v>4376.64</v>
+        <v>4356.66</v>
       </c>
       <c r="Q8">
-        <v>4387.78</v>
+        <v>4387.11</v>
       </c>
       <c r="R8">
-        <v>4373.94</v>
+        <v>4373.71</v>
       </c>
       <c r="S8">
-        <v>4643.51</v>
+        <v>4638.47</v>
       </c>
       <c r="T8">
-        <v>-6.25</v>
+        <v>-6.76</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1706,34 +1643,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>47.61</v>
+        <v>45.13</v>
       </c>
       <c r="Z8">
-        <v>-1.69</v>
+        <v>-5.63</v>
       </c>
       <c r="AA8">
-        <v>2.82</v>
+        <v>1.13</v>
       </c>
       <c r="AB8">
-        <v>-4.51</v>
+        <v>-6.76</v>
       </c>
       <c r="AC8">
-        <v>25.88</v>
+        <v>17.76</v>
       </c>
       <c r="AD8">
-        <v>29.83</v>
+        <v>23.62</v>
       </c>
       <c r="AE8">
-        <v>92.84</v>
+        <v>92.33</v>
       </c>
       <c r="AF8">
-        <v>-68.8</v>
+        <v>-57.05</v>
       </c>
       <c r="AG8">
-        <v>4534.6</v>
+        <v>4535</v>
       </c>
       <c r="AH8">
-        <v>4240.97</v>
+        <v>4239.22</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1742,7 +1679,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>16.04</v>
+        <v>17.64</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1753,10 +1690,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11400</v>
+        <v>11393</v>
       </c>
       <c r="D9">
-        <v>-0.44</v>
+        <v>-0.06</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1765,46 +1702,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-12.66</v>
+        <v>-12.71</v>
       </c>
       <c r="H9">
-        <v>10.02</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I9">
-        <v>-1.21</v>
+        <v>-2.77</v>
       </c>
       <c r="J9">
-        <v>-5.43</v>
+        <v>-5.45</v>
       </c>
       <c r="K9">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="L9">
-        <v>-8.949999999999999</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="M9">
-        <v>8.470000000000001</v>
+        <v>7.94</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P9">
-        <v>11574.6</v>
+        <v>11509.8</v>
       </c>
       <c r="Q9">
-        <v>11701.7</v>
+        <v>11661.85</v>
       </c>
       <c r="R9">
-        <v>11703.44</v>
+        <v>11705.16</v>
       </c>
       <c r="S9">
-        <v>11772.83</v>
+        <v>11770.42</v>
       </c>
       <c r="T9">
-        <v>-3.17</v>
+        <v>-3.21</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1819,43 +1756,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>39.06</v>
+        <v>38.84</v>
       </c>
       <c r="Z9">
-        <v>-75.93000000000001</v>
+        <v>-85.68000000000001</v>
       </c>
       <c r="AA9">
-        <v>-47.75</v>
+        <v>-55.33</v>
       </c>
       <c r="AB9">
-        <v>-28.18</v>
+        <v>-30.34</v>
       </c>
       <c r="AC9">
-        <v>26.96</v>
+        <v>10.64</v>
       </c>
       <c r="AD9">
-        <v>43.69</v>
+        <v>27.84</v>
       </c>
       <c r="AE9">
-        <v>187.15</v>
+        <v>189.5</v>
       </c>
       <c r="AF9">
-        <v>-25.02</v>
+        <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>12178.49</v>
+        <v>12098.32</v>
       </c>
       <c r="AH9">
-        <v>11224.91</v>
+        <v>11225.38</v>
       </c>
       <c r="AI9">
-        <v>12031.46</v>
+        <v>11857.5</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1996,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2016,1151 +1953,1127 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-7.05</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-5.46</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.59</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-18.12</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-17.26</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.86</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1.38</v>
+      </c>
+      <c r="D9" s="5">
+        <v>5</v>
+      </c>
+      <c r="E9" s="6">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-1.01</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>9.33</v>
+      </c>
+      <c r="D11" s="5">
+        <v>12.64</v>
+      </c>
+      <c r="E11" s="6">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-15.53</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-16.7</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.44</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-5.43</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-5.45</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1.26</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-7.05</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-8.31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-3.99</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-3.16</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-13.51</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-18.12</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-4.61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-6.2</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-7.43</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.38</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-7.33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.15</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>4.21</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.96</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-3.49</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-4.11</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>10.15</v>
-      </c>
-      <c r="D13" s="7">
-        <v>9.33</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-7.44</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-3.52</v>
+      </c>
+      <c r="E19" s="6">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-11.34</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-15.53</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-4.19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-2.03</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1.44</v>
+      </c>
+      <c r="E20" s="6">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1.17</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0.15</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-0.96</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-2.26</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-3.81</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-5.43</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-1.21</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-2.77</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-0.85</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-3.99</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-3.14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>42.17</v>
+      </c>
+      <c r="D23" s="5">
+        <v>42.9</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-3.43</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-6.2</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-2.77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-34.55</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-34.75</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>2.52</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>18.7</v>
+      </c>
+      <c r="D25" s="5">
+        <v>18.71</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>44.63</v>
+      </c>
+      <c r="D26" s="5">
+        <v>43.43</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>114</v>
+      </c>
+      <c r="D27" s="5">
+        <v>123.88</v>
+      </c>
+      <c r="E27" s="6">
+        <v>9.880000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>104.42</v>
+      </c>
+      <c r="D28" s="5">
+        <v>117.99</v>
+      </c>
+      <c r="E28" s="6">
+        <v>13.57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-10.74</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-11.12</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>13.1</v>
+      </c>
+      <c r="D31" s="5">
+        <v>12.27</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-15.59</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-17.3</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>6.56</v>
+      </c>
+      <c r="D33" s="5">
+        <v>6.17</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-10.93</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-10.3</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-5.32</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-2.68</v>
+      </c>
+      <c r="E35" s="6">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-6.49</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-5.93</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>0.71</v>
+      </c>
+      <c r="D37" s="5">
+        <v>1.15</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>2.69</v>
+      </c>
+      <c r="D38" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-7.12</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-6.51</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-45.34</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-46.01</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-2.23</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-2.53</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-11.77</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-12.18</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-7.44</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-4.34</v>
+      </c>
+      <c r="E43" s="6">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-20.26</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-19.04</v>
+      </c>
+      <c r="E44" s="6">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-25.07</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-25.55</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-12.66</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-12.71</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>394.45</v>
+      </c>
+      <c r="D47" s="5">
+        <v>397.05</v>
+      </c>
+      <c r="E47" s="6">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>51.1</v>
+      </c>
+      <c r="D48" s="5">
+        <v>50.47</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>3305</v>
+      </c>
+      <c r="D49" s="5">
+        <v>3294.9</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-10.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>1014.4</v>
+      </c>
+      <c r="D50" s="5">
+        <v>1009.7</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-4.7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>14.06</v>
+      </c>
+      <c r="D51" s="5">
+        <v>14.53</v>
+      </c>
+      <c r="E51" s="6">
         <v>0.47</v>
       </c>
-      <c r="E19" s="8">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>11.1</v>
+      </c>
+      <c r="D52" s="5">
+        <v>11.27</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>4353.2</v>
+      </c>
+      <c r="D53" s="5">
+        <v>4325</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-28.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>11400</v>
+      </c>
+      <c r="D54" s="5">
+        <v>11393</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>42.42</v>
+      </c>
+      <c r="D55" s="5">
+        <v>44.51</v>
+      </c>
+      <c r="E55" s="6">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>26.62</v>
+      </c>
+      <c r="D56" s="5">
+        <v>25.09</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>55.1</v>
+      </c>
+      <c r="D57" s="5">
+        <v>53.94</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-4.07</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-3.49</v>
-      </c>
-      <c r="E20" s="9">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>47.27</v>
+      </c>
+      <c r="D58" s="5">
+        <v>46.03</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>1.85</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-7.44</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-9.289999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>51.37</v>
+      </c>
+      <c r="D59" s="5">
+        <v>57.59</v>
+      </c>
+      <c r="E59" s="6">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-2.2</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-2.03</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="5">
+        <v>39.2</v>
+      </c>
+      <c r="D60" s="5">
+        <v>43.21</v>
+      </c>
+      <c r="E60" s="6">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-0.2</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-0.96</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>47.61</v>
+      </c>
+      <c r="D61" s="5">
+        <v>45.13</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-0.47</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-1.21</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>39.06</v>
+      </c>
+      <c r="D62" s="5">
+        <v>38.84</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>45.69</v>
-      </c>
-      <c r="D25" s="7">
-        <v>42.17</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-3.52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-29.17</v>
+      </c>
+      <c r="D63" s="5">
+        <v>58.03</v>
+      </c>
+      <c r="E63" s="6">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-36.89</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-34.55</v>
-      </c>
-      <c r="E26" s="9">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>-49.81</v>
+      </c>
+      <c r="D64" s="5">
+        <v>-30.45</v>
+      </c>
+      <c r="E64" s="6">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>20.56</v>
-      </c>
-      <c r="D27" s="7">
-        <v>18.7</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>-27.78</v>
+      </c>
+      <c r="D65" s="5">
+        <v>-5.86</v>
+      </c>
+      <c r="E65" s="6">
+        <v>21.92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>43.89</v>
-      </c>
-      <c r="D28" s="7">
-        <v>44.63</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5">
+        <v>-41.13</v>
+      </c>
+      <c r="D66" s="5">
+        <v>-58.29</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-17.16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>113.56</v>
-      </c>
-      <c r="D29" s="7">
-        <v>114</v>
-      </c>
-      <c r="E29" s="9">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="5">
+        <v>-31.25</v>
+      </c>
+      <c r="D67" s="5">
+        <v>13.48</v>
+      </c>
+      <c r="E67" s="6">
+        <v>44.73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>97.16</v>
-      </c>
-      <c r="D30" s="7">
-        <v>104.42</v>
-      </c>
-      <c r="E30" s="9">
-        <v>7.26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="5">
+        <v>-79.87</v>
+      </c>
+      <c r="D68" s="5">
+        <v>-37.76</v>
+      </c>
+      <c r="E68" s="6">
+        <v>42.11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-11.67</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-10.74</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="5">
+        <v>-68.8</v>
+      </c>
+      <c r="D69" s="5">
+        <v>-57.05</v>
+      </c>
+      <c r="E69" s="6">
+        <v>11.75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>16.54</v>
-      </c>
-      <c r="D33" s="7">
-        <v>13.1</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-15.83</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-15.59</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>8.83</v>
-      </c>
-      <c r="D35" s="7">
-        <v>6.56</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-11.41</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-10.93</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-5.32</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-6.52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-7.35</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-6.49</v>
-      </c>
-      <c r="E38" s="9">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-0.19</v>
-      </c>
-      <c r="D39" s="7">
-        <v>0.71</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>2.55</v>
-      </c>
-      <c r="D40" s="7">
-        <v>2.69</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-3.6</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-7.12</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-3.52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-44.27</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-45.34</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-0.28</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-2.23</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-11.68</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-11.77</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-5.66</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-7.44</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-25.06</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-25.07</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-12.27</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-12.66</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>409.4</v>
-      </c>
-      <c r="D48" s="7">
-        <v>394.45</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-14.95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>52.1</v>
-      </c>
-      <c r="D49" s="7">
-        <v>51.1</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>3371</v>
-      </c>
-      <c r="D50" s="7">
-        <v>3305</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-66</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="7">
-        <v>1015.45</v>
-      </c>
-      <c r="D51" s="7">
-        <v>1014.4</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="7">
-        <v>14.33</v>
-      </c>
-      <c r="D52" s="7">
-        <v>14.06</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>4353.4</v>
-      </c>
-      <c r="D53" s="7">
-        <v>4353.2</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>11450</v>
-      </c>
-      <c r="D54" s="7">
-        <v>11400</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>53.12</v>
-      </c>
-      <c r="D55" s="7">
-        <v>42.42</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-10.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>29.25</v>
-      </c>
-      <c r="D56" s="7">
-        <v>26.62</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>63.36</v>
-      </c>
-      <c r="D57" s="7">
-        <v>55.1</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-8.26</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>47.54</v>
-      </c>
-      <c r="D58" s="7">
-        <v>47.27</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>55.73</v>
-      </c>
-      <c r="D59" s="7">
-        <v>51.37</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-4.36</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="7">
-        <v>47.62</v>
-      </c>
-      <c r="D60" s="7">
-        <v>47.61</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="7">
-        <v>40.63</v>
-      </c>
-      <c r="D61" s="7">
-        <v>39.06</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="6" t="s">
+      <c r="B70" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="7">
-        <v>49.97</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-29.17</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-79.14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-24.38</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-49.81</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-25.43</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-7.32</v>
-      </c>
-      <c r="D64" s="7">
-        <v>-27.78</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-20.46</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>22.84</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-41.13</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-63.97</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>-8.75</v>
-      </c>
-      <c r="D66" s="7">
-        <v>-31.25</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-22.5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="7">
-        <v>-66.23999999999999</v>
-      </c>
-      <c r="D67" s="7">
-        <v>-79.87</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-13.63</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="7">
-        <v>-77.93000000000001</v>
-      </c>
-      <c r="D68" s="7">
-        <v>-68.8</v>
-      </c>
-      <c r="E68" s="9">
-        <v>9.130000000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="7">
-        <v>69.55</v>
-      </c>
-      <c r="D69" s="7">
+      <c r="C70" s="5">
         <v>-25.02</v>
       </c>
-      <c r="E69" s="8">
-        <v>-94.56999999999999</v>
+      <c r="D70" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="E70" s="6">
+        <v>26.86</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3180,60 +3093,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>80</v>
+      <c r="B1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>56.44</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="12">
-        <v>43.6</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>44.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
-        <v>-4.2</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-1.9</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>-3.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-1.6</v>
+      </c>
+      <c r="H2" s="10">
         <v>56.1</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>60</v>
       </c>
     </row>
@@ -3335,55 +3248,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="15">
-        <v>0.2966</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.197</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1818</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1791</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1788</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.08470000000000001</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.2448</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.307</v>
+      <c r="A2" s="13">
+        <v>0.298</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1907</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1786</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.176</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1524</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0794</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2542</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.3082</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -766,7 +766,7 @@
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -899,10 +899,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>397.05</v>
+        <v>402</v>
       </c>
       <c r="D2">
-        <v>0.66</v>
+        <v>1.25</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -911,46 +911,46 @@
         <v>274.85</v>
       </c>
       <c r="G2">
-        <v>-6.51</v>
+        <v>-5.34</v>
       </c>
       <c r="H2">
-        <v>44.46</v>
+        <v>46.26</v>
       </c>
       <c r="I2">
-        <v>-3.16</v>
+        <v>-1.95</v>
       </c>
       <c r="J2">
-        <v>-5.46</v>
+        <v>-5.34</v>
       </c>
       <c r="K2">
-        <v>12.27</v>
+        <v>12.45</v>
       </c>
       <c r="L2">
-        <v>42.9</v>
+        <v>43.55</v>
       </c>
       <c r="M2">
-        <v>29.8</v>
+        <v>30.54</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>403.29</v>
+        <v>401.69</v>
       </c>
       <c r="Q2">
-        <v>406.65</v>
+        <v>405.68</v>
       </c>
       <c r="R2">
-        <v>403.11</v>
+        <v>403.26</v>
       </c>
       <c r="S2">
-        <v>360.03</v>
+        <v>360.36</v>
       </c>
       <c r="T2">
-        <v>10.28</v>
+        <v>11.55</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -965,34 +965,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>44.51</v>
+        <v>48.36</v>
       </c>
       <c r="Z2">
-        <v>0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="AA2">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="AB2">
-        <v>-1.78</v>
+        <v>-1.61</v>
       </c>
       <c r="AC2">
-        <v>28.92</v>
+        <v>19.58</v>
       </c>
       <c r="AD2">
-        <v>43.69</v>
+        <v>28.85</v>
       </c>
       <c r="AE2">
-        <v>10.09</v>
+        <v>9.73</v>
       </c>
       <c r="AF2">
-        <v>58.03</v>
+        <v>-39.29</v>
       </c>
       <c r="AG2">
-        <v>420.02</v>
+        <v>417.2</v>
       </c>
       <c r="AH2">
-        <v>393.28</v>
+        <v>394.15</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1001,7 +1001,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>26.28</v>
+        <v>26.84</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1012,58 +1012,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>50.47</v>
+        <v>50.41</v>
       </c>
       <c r="D3">
-        <v>-1.23</v>
+        <v>-0.12</v>
       </c>
       <c r="E3">
         <v>93.48</v>
       </c>
       <c r="F3">
-        <v>50.47</v>
+        <v>50.41</v>
       </c>
       <c r="G3">
-        <v>-46.01</v>
+        <v>-46.07</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-7.43</v>
+        <v>-6.02</v>
       </c>
       <c r="J3">
-        <v>-17.26</v>
+        <v>-18.82</v>
       </c>
       <c r="K3">
-        <v>-17.3</v>
+        <v>-16.11</v>
       </c>
       <c r="L3">
-        <v>-34.75</v>
+        <v>-39.52</v>
       </c>
       <c r="M3">
-        <v>-25.42</v>
+        <v>-25.49</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P3">
-        <v>51.96</v>
+        <v>51.31</v>
       </c>
       <c r="Q3">
-        <v>55.67</v>
+        <v>55.03</v>
       </c>
       <c r="R3">
-        <v>57.79</v>
+        <v>57.57</v>
       </c>
       <c r="S3">
-        <v>64.98999999999999</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="T3">
-        <v>-22.34</v>
+        <v>-22.27</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1078,34 +1078,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>25.09</v>
+        <v>24.95</v>
       </c>
       <c r="Z3">
-        <v>-2</v>
+        <v>-2.09</v>
       </c>
       <c r="AA3">
-        <v>-1.55</v>
+        <v>-1.66</v>
       </c>
       <c r="AB3">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AF3">
-        <v>-30.45</v>
+        <v>-48.92</v>
       </c>
       <c r="AG3">
-        <v>62.82</v>
+        <v>61.59</v>
       </c>
       <c r="AH3">
-        <v>48.52</v>
+        <v>48.47</v>
       </c>
       <c r="AI3">
         <v>55.66</v>
@@ -1114,7 +1114,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>58.6</v>
+        <v>59.06</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1125,10 +1125,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3294.9</v>
+        <v>3310</v>
       </c>
       <c r="D4">
-        <v>-0.31</v>
+        <v>0.46</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1137,25 +1137,25 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.53</v>
+        <v>-2.09</v>
       </c>
       <c r="H4">
-        <v>30.18</v>
+        <v>30.77</v>
       </c>
       <c r="I4">
-        <v>-0.15</v>
+        <v>1.6</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>2.67</v>
       </c>
       <c r="K4">
-        <v>6.17</v>
+        <v>7.2</v>
       </c>
       <c r="L4">
-        <v>18.71</v>
+        <v>18.05</v>
       </c>
       <c r="M4">
-        <v>17.6</v>
+        <v>17.53</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1164,19 +1164,19 @@
         <v>70</v>
       </c>
       <c r="P4">
-        <v>3303.78</v>
+        <v>3314.18</v>
       </c>
       <c r="Q4">
-        <v>3293.14</v>
+        <v>3297.64</v>
       </c>
       <c r="R4">
-        <v>3202.4</v>
+        <v>3206.04</v>
       </c>
       <c r="S4">
-        <v>2931.43</v>
+        <v>2934.03</v>
       </c>
       <c r="T4">
-        <v>12.4</v>
+        <v>12.81</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1191,34 +1191,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>53.94</v>
+        <v>55.45</v>
       </c>
       <c r="Z4">
-        <v>32.04</v>
+        <v>30.93</v>
       </c>
       <c r="AA4">
-        <v>34.82</v>
+        <v>34.04</v>
       </c>
       <c r="AB4">
-        <v>-2.78</v>
+        <v>-3.11</v>
       </c>
       <c r="AC4">
-        <v>47.22</v>
+        <v>23.6</v>
       </c>
       <c r="AD4">
-        <v>49.5</v>
+        <v>41.93</v>
       </c>
       <c r="AE4">
-        <v>73.2</v>
+        <v>71.55</v>
       </c>
       <c r="AF4">
-        <v>-5.86</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="AG4">
-        <v>3370.71</v>
+        <v>3367.39</v>
       </c>
       <c r="AH4">
-        <v>3215.57</v>
+        <v>3227.89</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1227,7 +1227,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>21.96</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1238,58 +1238,58 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1009.7</v>
+        <v>1010</v>
       </c>
       <c r="D5">
-        <v>-0.46</v>
+        <v>0.03</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>719.6</v>
+        <v>720.95</v>
       </c>
       <c r="G5">
-        <v>-12.18</v>
+        <v>-12.15</v>
       </c>
       <c r="H5">
-        <v>40.31</v>
+        <v>40.09</v>
       </c>
       <c r="I5">
-        <v>-4.11</v>
+        <v>-1.37</v>
       </c>
       <c r="J5">
-        <v>-1.01</v>
+        <v>-2.88</v>
       </c>
       <c r="K5">
-        <v>-10.3</v>
+        <v>-7.56</v>
       </c>
       <c r="L5">
-        <v>43.43</v>
+        <v>40.36</v>
       </c>
       <c r="M5">
-        <v>17.86</v>
+        <v>17.64</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P5">
-        <v>1020.19</v>
+        <v>1017.39</v>
       </c>
       <c r="Q5">
-        <v>1040.09</v>
+        <v>1039.24</v>
       </c>
       <c r="R5">
-        <v>994.77</v>
+        <v>995.4400000000001</v>
       </c>
       <c r="S5">
-        <v>963.5700000000001</v>
+        <v>964.59</v>
       </c>
       <c r="T5">
-        <v>4.79</v>
+        <v>4.71</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1304,34 +1304,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>46.03</v>
+        <v>46.13</v>
       </c>
       <c r="Z5">
-        <v>5.08</v>
+        <v>3.23</v>
       </c>
       <c r="AA5">
-        <v>11.17</v>
+        <v>9.59</v>
       </c>
       <c r="AB5">
-        <v>-6.1</v>
+        <v>-6.36</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AD5">
-        <v>3.64</v>
+        <v>1.89</v>
       </c>
       <c r="AE5">
-        <v>23.94</v>
+        <v>23.69</v>
       </c>
       <c r="AF5">
-        <v>-58.29</v>
+        <v>-65.95999999999999</v>
       </c>
       <c r="AG5">
-        <v>1074.97</v>
+        <v>1076.22</v>
       </c>
       <c r="AH5">
-        <v>1005.21</v>
+        <v>1002.26</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1340,7 +1340,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>26.1</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1351,10 +1351,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.53</v>
+        <v>14.48</v>
       </c>
       <c r="D6">
-        <v>3.34</v>
+        <v>-0.34</v>
       </c>
       <c r="E6">
         <v>15.19</v>
@@ -1363,25 +1363,25 @@
         <v>6.51</v>
       </c>
       <c r="G6">
-        <v>-4.34</v>
+        <v>-4.67</v>
       </c>
       <c r="H6">
-        <v>123.2</v>
+        <v>122.43</v>
       </c>
       <c r="I6">
-        <v>-3.52</v>
+        <v>-3.27</v>
       </c>
       <c r="J6">
-        <v>12.64</v>
+        <v>13.12</v>
       </c>
       <c r="K6">
-        <v>-2.68</v>
+        <v>-3.14</v>
       </c>
       <c r="L6">
-        <v>123.88</v>
+        <v>121.41</v>
       </c>
       <c r="M6">
-        <v>15.24</v>
+        <v>14.84</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1390,19 +1390,19 @@
         <v>93</v>
       </c>
       <c r="P6">
-        <v>14.51</v>
+        <v>14.42</v>
       </c>
       <c r="Q6">
-        <v>13.95</v>
+        <v>14.04</v>
       </c>
       <c r="R6">
-        <v>13.78</v>
+        <v>13.79</v>
       </c>
       <c r="S6">
-        <v>11.86</v>
+        <v>11.88</v>
       </c>
       <c r="T6">
-        <v>22.53</v>
+        <v>21.93</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1417,34 +1417,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>57.59</v>
+        <v>56.76</v>
       </c>
       <c r="Z6">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="AA6">
         <v>0.26</v>
       </c>
       <c r="AB6">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="AC6">
-        <v>11.21</v>
+        <v>18.12</v>
       </c>
       <c r="AD6">
-        <v>29.3</v>
+        <v>17.79</v>
       </c>
       <c r="AE6">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="AF6">
-        <v>13.48</v>
+        <v>-44.96</v>
       </c>
       <c r="AG6">
-        <v>15.46</v>
+        <v>15.43</v>
       </c>
       <c r="AH6">
-        <v>12.45</v>
+        <v>12.66</v>
       </c>
       <c r="AI6">
         <v>13.86</v>
@@ -1453,7 +1453,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>43.17</v>
+        <v>37.44</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1464,10 +1464,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.27</v>
+        <v>11.05</v>
       </c>
       <c r="D7">
-        <v>1.53</v>
+        <v>-1.95</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1476,46 +1476,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-19.04</v>
+        <v>-20.62</v>
       </c>
       <c r="H7">
-        <v>140.3</v>
+        <v>135.61</v>
       </c>
       <c r="I7">
-        <v>1.44</v>
+        <v>-0.54</v>
       </c>
       <c r="J7">
-        <v>-16.7</v>
+        <v>-16.67</v>
       </c>
       <c r="K7">
-        <v>-5.93</v>
+        <v>-4.49</v>
       </c>
       <c r="L7">
-        <v>117.99</v>
+        <v>115.82</v>
       </c>
       <c r="M7">
-        <v>-30.82</v>
+        <v>-30.9</v>
       </c>
       <c r="N7">
         <v>87</v>
       </c>
       <c r="O7">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P7">
-        <v>11.18</v>
+        <v>11.16</v>
       </c>
       <c r="Q7">
-        <v>11.73</v>
+        <v>11.63</v>
       </c>
       <c r="R7">
-        <v>11.55</v>
+        <v>11.54</v>
       </c>
       <c r="S7">
-        <v>10.26</v>
+        <v>10.29</v>
       </c>
       <c r="T7">
-        <v>9.84</v>
+        <v>7.37</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1530,34 +1530,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>43.21</v>
+        <v>39.58</v>
       </c>
       <c r="Z7">
-        <v>-0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="AA7">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="AB7">
         <v>-0.08</v>
       </c>
       <c r="AC7">
-        <v>21.66</v>
+        <v>23.11</v>
       </c>
       <c r="AD7">
-        <v>16.28</v>
+        <v>20.03</v>
       </c>
       <c r="AE7">
         <v>0.27</v>
       </c>
       <c r="AF7">
-        <v>-37.76</v>
+        <v>-41.22</v>
       </c>
       <c r="AG7">
-        <v>12.88</v>
+        <v>12.65</v>
       </c>
       <c r="AH7">
-        <v>10.58</v>
+        <v>10.61</v>
       </c>
       <c r="AI7">
         <v>11.87</v>
@@ -1566,7 +1566,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>36.16</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1577,10 +1577,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4325</v>
+        <v>4354.5</v>
       </c>
       <c r="D8">
-        <v>-0.65</v>
+        <v>0.68</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1589,46 +1589,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-25.55</v>
+        <v>-25.05</v>
       </c>
       <c r="H8">
-        <v>4.09</v>
+        <v>4.8</v>
       </c>
       <c r="I8">
-        <v>-2.26</v>
+        <v>-0.21</v>
       </c>
       <c r="J8">
-        <v>-0.44</v>
+        <v>0.37</v>
       </c>
       <c r="K8">
-        <v>1.15</v>
+        <v>3.07</v>
       </c>
       <c r="L8">
-        <v>-11.12</v>
+        <v>-13.75</v>
       </c>
       <c r="M8">
-        <v>19.07</v>
+        <v>19.6</v>
       </c>
       <c r="N8">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="O8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P8">
-        <v>4356.66</v>
+        <v>4354.8</v>
       </c>
       <c r="Q8">
-        <v>4387.11</v>
+        <v>4389.08</v>
       </c>
       <c r="R8">
-        <v>4373.71</v>
+        <v>4373.1</v>
       </c>
       <c r="S8">
-        <v>4638.47</v>
+        <v>4633.45</v>
       </c>
       <c r="T8">
-        <v>-6.76</v>
+        <v>-6.02</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1643,34 +1643,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>45.13</v>
+        <v>48.17</v>
       </c>
       <c r="Z8">
-        <v>-5.63</v>
+        <v>-6.31</v>
       </c>
       <c r="AA8">
-        <v>1.13</v>
+        <v>-0.36</v>
       </c>
       <c r="AB8">
-        <v>-6.76</v>
+        <v>-5.95</v>
       </c>
       <c r="AC8">
-        <v>17.76</v>
+        <v>18.58</v>
       </c>
       <c r="AD8">
-        <v>23.62</v>
+        <v>20.74</v>
       </c>
       <c r="AE8">
-        <v>92.33</v>
+        <v>91.89</v>
       </c>
       <c r="AF8">
-        <v>-57.05</v>
+        <v>-68.08</v>
       </c>
       <c r="AG8">
-        <v>4535</v>
+        <v>4533.94</v>
       </c>
       <c r="AH8">
-        <v>4239.22</v>
+        <v>4244.23</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1679,7 +1679,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>17.64</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1690,10 +1690,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11393</v>
+        <v>11275</v>
       </c>
       <c r="D9">
-        <v>-0.06</v>
+        <v>-1.04</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1702,46 +1702,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-12.71</v>
+        <v>-13.61</v>
       </c>
       <c r="H9">
-        <v>9.949999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="I9">
-        <v>-2.77</v>
+        <v>-3.77</v>
       </c>
       <c r="J9">
-        <v>-5.45</v>
+        <v>-7.51</v>
       </c>
       <c r="K9">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="L9">
-        <v>-9.869999999999999</v>
+        <v>-12.09</v>
       </c>
       <c r="M9">
-        <v>7.94</v>
+        <v>7.78</v>
       </c>
       <c r="N9">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="O9">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P9">
-        <v>11509.8</v>
+        <v>11421.4</v>
       </c>
       <c r="Q9">
-        <v>11661.85</v>
+        <v>11621.85</v>
       </c>
       <c r="R9">
-        <v>11705.16</v>
+        <v>11702.06</v>
       </c>
       <c r="S9">
-        <v>11770.42</v>
+        <v>11767.91</v>
       </c>
       <c r="T9">
-        <v>-3.21</v>
+        <v>-4.19</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1756,34 +1756,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>38.84</v>
+        <v>35.15</v>
       </c>
       <c r="Z9">
-        <v>-85.68000000000001</v>
+        <v>-101.75</v>
       </c>
       <c r="AA9">
-        <v>-55.33</v>
+        <v>-64.62</v>
       </c>
       <c r="AB9">
-        <v>-30.34</v>
+        <v>-37.13</v>
       </c>
       <c r="AC9">
-        <v>10.64</v>
+        <v>4.36</v>
       </c>
       <c r="AD9">
-        <v>27.84</v>
+        <v>13.99</v>
       </c>
       <c r="AE9">
-        <v>189.5</v>
+        <v>188.46</v>
       </c>
       <c r="AF9">
-        <v>1.84</v>
+        <v>7.88</v>
       </c>
       <c r="AG9">
-        <v>12098.32</v>
+        <v>12045.34</v>
       </c>
       <c r="AH9">
-        <v>11225.38</v>
+        <v>11198.36</v>
       </c>
       <c r="AI9">
         <v>11857.5</v>
@@ -1792,7 +1792,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>27</v>
+        <v>28.15</v>
       </c>
     </row>
   </sheetData>
@@ -1933,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1990,13 +1990,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.05</v>
+        <v>-5.46</v>
       </c>
       <c r="D7" s="5">
-        <v>-5.46</v>
+        <v>-5.34</v>
       </c>
       <c r="E7" s="6">
-        <v>1.59</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2007,13 +2007,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-18.12</v>
+        <v>-17.26</v>
       </c>
       <c r="D8" s="5">
-        <v>-17.26</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0.86</v>
+        <v>-18.82</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2024,13 +2024,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>1.38</v>
+        <v>5</v>
       </c>
       <c r="D9" s="5">
-        <v>5</v>
-      </c>
-      <c r="E9" s="6">
-        <v>3.62</v>
+        <v>2.67</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.33</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2041,13 +2041,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>1.96</v>
+        <v>-1.01</v>
       </c>
       <c r="D10" s="5">
-        <v>-1.01</v>
+        <v>-2.88</v>
       </c>
       <c r="E10" s="7">
-        <v>-2.97</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2058,13 +2058,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>9.33</v>
+        <v>12.64</v>
       </c>
       <c r="D11" s="5">
-        <v>12.64</v>
+        <v>13.12</v>
       </c>
       <c r="E11" s="6">
-        <v>3.31</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2075,13 +2075,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-15.53</v>
+        <v>-16.7</v>
       </c>
       <c r="D12" s="5">
-        <v>-16.7</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.17</v>
+        <v>-16.67</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.03</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2092,13 +2092,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>0.15</v>
+        <v>-0.44</v>
       </c>
       <c r="D13" s="5">
-        <v>-0.44</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.59</v>
+        <v>0.37</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2109,13 +2109,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>-5.43</v>
+        <v>-5.45</v>
       </c>
       <c r="D14" s="5">
-        <v>-5.45</v>
+        <v>-7.51</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.02</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2126,13 +2126,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-3.99</v>
+        <v>-3.16</v>
       </c>
       <c r="D15" s="5">
-        <v>-3.16</v>
+        <v>-1.95</v>
       </c>
       <c r="E15" s="6">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2143,13 +2143,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-6.2</v>
+        <v>-7.43</v>
       </c>
       <c r="D16" s="5">
-        <v>-7.43</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.23</v>
+        <v>-6.02</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1.41</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2160,13 +2160,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>0.47</v>
+        <v>-0.15</v>
       </c>
       <c r="D17" s="5">
-        <v>-0.15</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.62</v>
+        <v>1.6</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.75</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2177,13 +2177,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-3.49</v>
+        <v>-4.11</v>
       </c>
       <c r="D18" s="5">
-        <v>-4.11</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.62</v>
+        <v>-1.37</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2.74</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2194,13 +2194,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-7.44</v>
+        <v>-3.52</v>
       </c>
       <c r="D19" s="5">
-        <v>-3.52</v>
+        <v>-3.27</v>
       </c>
       <c r="E19" s="6">
-        <v>3.92</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2211,13 +2211,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>-2.03</v>
+        <v>1.44</v>
       </c>
       <c r="D20" s="5">
-        <v>1.44</v>
-      </c>
-      <c r="E20" s="6">
-        <v>3.47</v>
+        <v>-0.54</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2228,13 +2228,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>-0.96</v>
+        <v>-2.26</v>
       </c>
       <c r="D21" s="5">
-        <v>-2.26</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.3</v>
+        <v>-0.21</v>
+      </c>
+      <c r="E21" s="6">
+        <v>2.05</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2245,13 +2245,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>-1.21</v>
+        <v>-2.77</v>
       </c>
       <c r="D22" s="5">
-        <v>-2.77</v>
+        <v>-3.77</v>
       </c>
       <c r="E22" s="7">
-        <v>-1.56</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2262,13 +2262,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>42.17</v>
+        <v>42.9</v>
       </c>
       <c r="D23" s="5">
-        <v>42.9</v>
+        <v>43.55</v>
       </c>
       <c r="E23" s="6">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2279,13 +2279,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-34.55</v>
+        <v>-34.75</v>
       </c>
       <c r="D24" s="5">
-        <v>-34.75</v>
+        <v>-39.52</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.2</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2296,13 +2296,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>18.7</v>
+        <v>18.71</v>
       </c>
       <c r="D25" s="5">
-        <v>18.71</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.01</v>
+        <v>18.05</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2313,13 +2313,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>44.63</v>
+        <v>43.43</v>
       </c>
       <c r="D26" s="5">
-        <v>43.43</v>
+        <v>40.36</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.2</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2330,13 +2330,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>114</v>
+        <v>123.88</v>
       </c>
       <c r="D27" s="5">
-        <v>123.88</v>
-      </c>
-      <c r="E27" s="6">
-        <v>9.880000000000001</v>
+        <v>121.41</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.47</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2347,13 +2347,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="5">
-        <v>104.42</v>
+        <v>117.99</v>
       </c>
       <c r="D28" s="5">
-        <v>117.99</v>
-      </c>
-      <c r="E28" s="6">
-        <v>13.57</v>
+        <v>115.82</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2364,13 +2364,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>-10.74</v>
+        <v>-11.12</v>
       </c>
       <c r="D29" s="5">
-        <v>-11.12</v>
+        <v>-13.75</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.38</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2381,13 +2381,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="5">
-        <v>-8.949999999999999</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="D30" s="5">
-        <v>-9.869999999999999</v>
+        <v>-12.09</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.92</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2398,13 +2398,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>13.1</v>
+        <v>12.27</v>
       </c>
       <c r="D31" s="5">
-        <v>12.27</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.83</v>
+        <v>12.45</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.18</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2415,13 +2415,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>-15.59</v>
+        <v>-17.3</v>
       </c>
       <c r="D32" s="5">
-        <v>-17.3</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.71</v>
+        <v>-16.11</v>
+      </c>
+      <c r="E32" s="6">
+        <v>1.19</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2432,13 +2432,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>6.56</v>
+        <v>6.17</v>
       </c>
       <c r="D33" s="5">
-        <v>6.17</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.39</v>
+        <v>7.2</v>
+      </c>
+      <c r="E33" s="6">
+        <v>1.03</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2449,13 +2449,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>-10.93</v>
+        <v>-10.3</v>
       </c>
       <c r="D34" s="5">
-        <v>-10.3</v>
+        <v>-7.56</v>
       </c>
       <c r="E34" s="6">
-        <v>0.63</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2466,13 +2466,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>-5.32</v>
+        <v>-2.68</v>
       </c>
       <c r="D35" s="5">
-        <v>-2.68</v>
-      </c>
-      <c r="E35" s="6">
-        <v>2.64</v>
+        <v>-3.14</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2483,13 +2483,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>-6.49</v>
+        <v>-5.93</v>
       </c>
       <c r="D36" s="5">
-        <v>-5.93</v>
+        <v>-4.49</v>
       </c>
       <c r="E36" s="6">
-        <v>0.5600000000000001</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2500,13 +2500,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>0.71</v>
+        <v>1.15</v>
       </c>
       <c r="D37" s="5">
-        <v>1.15</v>
+        <v>3.07</v>
       </c>
       <c r="E37" s="6">
-        <v>0.44</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2517,13 +2517,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="D38" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.91</v>
+        <v>3.33</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2534,13 +2534,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-7.12</v>
+        <v>-6.51</v>
       </c>
       <c r="D39" s="5">
-        <v>-6.51</v>
+        <v>-5.34</v>
       </c>
       <c r="E39" s="6">
-        <v>0.61</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2551,13 +2551,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-45.34</v>
+        <v>-46.01</v>
       </c>
       <c r="D40" s="5">
-        <v>-46.01</v>
+        <v>-46.07</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.67</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2568,13 +2568,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-2.23</v>
+        <v>-2.53</v>
       </c>
       <c r="D41" s="5">
-        <v>-2.53</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.3</v>
+        <v>-2.09</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.44</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2585,13 +2585,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="5">
-        <v>-11.77</v>
+        <v>-12.18</v>
       </c>
       <c r="D42" s="5">
-        <v>-12.18</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.41</v>
+        <v>-12.15</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0.03</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2602,13 +2602,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="5">
-        <v>-7.44</v>
+        <v>-4.34</v>
       </c>
       <c r="D43" s="5">
-        <v>-4.34</v>
-      </c>
-      <c r="E43" s="6">
-        <v>3.1</v>
+        <v>-4.67</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2619,13 +2619,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="5">
-        <v>-20.26</v>
+        <v>-19.04</v>
       </c>
       <c r="D44" s="5">
-        <v>-19.04</v>
-      </c>
-      <c r="E44" s="6">
-        <v>1.22</v>
+        <v>-20.62</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2636,13 +2636,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="5">
-        <v>-25.07</v>
+        <v>-25.55</v>
       </c>
       <c r="D45" s="5">
-        <v>-25.55</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.48</v>
+        <v>-25.05</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.5</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2653,13 +2653,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="5">
-        <v>-12.66</v>
+        <v>-12.71</v>
       </c>
       <c r="D46" s="5">
-        <v>-12.71</v>
+        <v>-13.61</v>
       </c>
       <c r="E46" s="7">
-        <v>-0.05</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2670,13 +2670,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>394.45</v>
+        <v>397.05</v>
       </c>
       <c r="D47" s="5">
-        <v>397.05</v>
+        <v>402</v>
       </c>
       <c r="E47" s="6">
-        <v>2.6</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2687,13 +2687,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>51.1</v>
+        <v>50.47</v>
       </c>
       <c r="D48" s="5">
-        <v>50.47</v>
+        <v>50.41</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.63</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2704,13 +2704,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="5">
-        <v>3305</v>
+        <v>3294.9</v>
       </c>
       <c r="D49" s="5">
-        <v>3294.9</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-10.1</v>
+        <v>3310</v>
+      </c>
+      <c r="E49" s="6">
+        <v>15.1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2721,13 +2721,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="5">
-        <v>1014.4</v>
+        <v>1009.7</v>
       </c>
       <c r="D50" s="5">
-        <v>1009.7</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-4.7</v>
+        <v>1010</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.3</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2738,13 +2738,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="5">
-        <v>14.06</v>
+        <v>14.53</v>
       </c>
       <c r="D51" s="5">
-        <v>14.53</v>
-      </c>
-      <c r="E51" s="6">
-        <v>0.47</v>
+        <v>14.48</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2755,13 +2755,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="5">
-        <v>11.1</v>
+        <v>11.27</v>
       </c>
       <c r="D52" s="5">
-        <v>11.27</v>
-      </c>
-      <c r="E52" s="6">
-        <v>0.17</v>
+        <v>11.05</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2772,13 +2772,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="5">
-        <v>4353.2</v>
+        <v>4325</v>
       </c>
       <c r="D53" s="5">
-        <v>4325</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-28.2</v>
+        <v>4354.5</v>
+      </c>
+      <c r="E53" s="6">
+        <v>29.5</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2789,285 +2789,319 @@
         <v>2</v>
       </c>
       <c r="C54" s="5">
-        <v>11400</v>
+        <v>11393</v>
       </c>
       <c r="D54" s="5">
-        <v>11393</v>
+        <v>11275</v>
       </c>
       <c r="E54" s="7">
-        <v>-7</v>
+        <v>-118</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C55" s="5">
-        <v>42.42</v>
+        <v>26</v>
       </c>
       <c r="D55" s="5">
-        <v>44.51</v>
+        <v>38</v>
       </c>
       <c r="E55" s="6">
-        <v>2.09</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="5">
         <v>38</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>26.62</v>
-      </c>
       <c r="D56" s="5">
-        <v>25.09</v>
+        <v>26</v>
       </c>
       <c r="E56" s="7">
-        <v>-1.53</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C57" s="5">
-        <v>55.1</v>
+        <v>44.51</v>
       </c>
       <c r="D57" s="5">
-        <v>53.94</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-1.16</v>
+        <v>48.36</v>
+      </c>
+      <c r="E57" s="6">
+        <v>3.85</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C58" s="5">
-        <v>47.27</v>
+        <v>25.09</v>
       </c>
       <c r="D58" s="5">
-        <v>46.03</v>
+        <v>24.95</v>
       </c>
       <c r="E58" s="7">
-        <v>-1.24</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="5">
-        <v>51.37</v>
+        <v>53.94</v>
       </c>
       <c r="D59" s="5">
-        <v>57.59</v>
+        <v>55.45</v>
       </c>
       <c r="E59" s="6">
-        <v>6.22</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="5">
-        <v>39.2</v>
+        <v>46.03</v>
       </c>
       <c r="D60" s="5">
-        <v>43.21</v>
+        <v>46.13</v>
       </c>
       <c r="E60" s="6">
-        <v>4.01</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="5">
-        <v>47.61</v>
+        <v>57.59</v>
       </c>
       <c r="D61" s="5">
-        <v>45.13</v>
+        <v>56.76</v>
       </c>
       <c r="E61" s="7">
-        <v>-2.48</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="5">
-        <v>39.06</v>
+        <v>43.21</v>
       </c>
       <c r="D62" s="5">
-        <v>38.84</v>
+        <v>39.58</v>
       </c>
       <c r="E62" s="7">
-        <v>-0.22</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C63" s="5">
-        <v>-29.17</v>
+        <v>45.13</v>
       </c>
       <c r="D63" s="5">
-        <v>58.03</v>
+        <v>48.17</v>
       </c>
       <c r="E63" s="6">
-        <v>87.2</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C64" s="5">
-        <v>-49.81</v>
+        <v>38.84</v>
       </c>
       <c r="D64" s="5">
-        <v>-30.45</v>
-      </c>
-      <c r="E64" s="6">
-        <v>19.36</v>
+        <v>35.15</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-3.69</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C65" s="5">
-        <v>-27.78</v>
+        <v>58.03</v>
       </c>
       <c r="D65" s="5">
-        <v>-5.86</v>
-      </c>
-      <c r="E65" s="6">
-        <v>21.92</v>
+        <v>-39.29</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-97.31999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C66" s="5">
-        <v>-41.13</v>
+        <v>-30.45</v>
       </c>
       <c r="D66" s="5">
-        <v>-58.29</v>
+        <v>-48.92</v>
       </c>
       <c r="E66" s="7">
-        <v>-17.16</v>
+        <v>-18.47</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C67" s="5">
-        <v>-31.25</v>
+        <v>-5.86</v>
       </c>
       <c r="D67" s="5">
-        <v>13.48</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="E67" s="6">
-        <v>44.73</v>
+        <v>103.62</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="5">
-        <v>-79.87</v>
+        <v>-58.29</v>
       </c>
       <c r="D68" s="5">
-        <v>-37.76</v>
-      </c>
-      <c r="E68" s="6">
-        <v>42.11</v>
+        <v>-65.95999999999999</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-7.67</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="5">
-        <v>-68.8</v>
+        <v>13.48</v>
       </c>
       <c r="D69" s="5">
-        <v>-57.05</v>
-      </c>
-      <c r="E69" s="6">
-        <v>11.75</v>
+        <v>-44.96</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-58.44</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C70" s="5">
-        <v>-25.02</v>
+        <v>-37.76</v>
       </c>
       <c r="D70" s="5">
+        <v>-41.22</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-3.46</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>-57.05</v>
+      </c>
+      <c r="D71" s="5">
+        <v>-68.08</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-11.03</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
         <v>1.84</v>
       </c>
-      <c r="E70" s="6">
-        <v>26.86</v>
+      <c r="D72" s="5">
+        <v>7.88</v>
+      </c>
+      <c r="E72" s="6">
+        <v>6.04</v>
       </c>
     </row>
   </sheetData>
@@ -3138,10 +3172,10 @@
         <v>60</v>
       </c>
       <c r="F2" s="10">
-        <v>-3.6</v>
+        <v>-4.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-1.6</v>
+        <v>-0.7</v>
       </c>
       <c r="H2" s="10">
         <v>56.1</v>
@@ -3275,28 +3309,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="13">
-        <v>0.298</v>
+        <v>0.3054</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1907</v>
+        <v>0.196</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1786</v>
+        <v>0.1764</v>
       </c>
       <c r="D2" s="13">
-        <v>0.176</v>
+        <v>0.1753</v>
       </c>
       <c r="E2" s="13">
-        <v>0.1524</v>
+        <v>0.1484</v>
       </c>
       <c r="F2" s="13">
-        <v>0.0794</v>
+        <v>0.07780000000000001</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.2542</v>
+        <v>-0.2549</v>
       </c>
       <c r="H2" s="13">
-        <v>-0.3082</v>
+        <v>-0.309</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="86">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,7 +175,70 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.1% → -1.7%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.1%</t>
+  </si>
+  <si>
+    <t>-1.7%</t>
+  </si>
+  <si>
+    <t>-4.7% → -1.1%</t>
+  </si>
+  <si>
+    <t>-4.7%</t>
+  </si>
+  <si>
+    <t>-1.1%</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.4 → 50.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.4</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>24.9 → 40.9</t>
+  </si>
+  <si>
+    <t>24.9</t>
+  </si>
+  <si>
+    <t>40.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -377,14 +440,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -758,8 +822,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -899,58 +963,58 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>402</v>
+        <v>404.9</v>
       </c>
       <c r="D2">
-        <v>1.25</v>
+        <v>0.72</v>
       </c>
       <c r="E2">
         <v>424.7</v>
       </c>
       <c r="F2">
-        <v>274.85</v>
+        <v>277.55</v>
       </c>
       <c r="G2">
-        <v>-5.34</v>
+        <v>-4.66</v>
       </c>
       <c r="H2">
-        <v>46.26</v>
+        <v>45.88</v>
       </c>
       <c r="I2">
-        <v>-1.95</v>
+        <v>-0.16</v>
       </c>
       <c r="J2">
-        <v>-5.34</v>
+        <v>-3.94</v>
       </c>
       <c r="K2">
-        <v>12.45</v>
+        <v>17.7</v>
       </c>
       <c r="L2">
-        <v>43.55</v>
+        <v>47.32</v>
       </c>
       <c r="M2">
-        <v>30.54</v>
+        <v>30.39</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P2">
-        <v>401.69</v>
+        <v>401.56</v>
       </c>
       <c r="Q2">
-        <v>405.68</v>
+        <v>405.52</v>
       </c>
       <c r="R2">
-        <v>403.26</v>
+        <v>403.54</v>
       </c>
       <c r="S2">
-        <v>360.36</v>
+        <v>360.72</v>
       </c>
       <c r="T2">
-        <v>11.55</v>
+        <v>12.25</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -965,34 +1029,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>48.36</v>
+        <v>50.53</v>
       </c>
       <c r="Z2">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AA2">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="AB2">
-        <v>-1.61</v>
+        <v>-1.25</v>
       </c>
       <c r="AC2">
-        <v>19.58</v>
+        <v>39.33</v>
       </c>
       <c r="AD2">
-        <v>28.85</v>
+        <v>29.28</v>
       </c>
       <c r="AE2">
-        <v>9.73</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AF2">
-        <v>-39.29</v>
+        <v>-29.99</v>
       </c>
       <c r="AG2">
-        <v>417.2</v>
+        <v>416.99</v>
       </c>
       <c r="AH2">
-        <v>394.15</v>
+        <v>394.05</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1001,7 +1065,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>26.84</v>
+        <v>24.52</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1012,10 +1076,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>50.41</v>
+        <v>52.97</v>
       </c>
       <c r="D3">
-        <v>-0.12</v>
+        <v>5.08</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1024,46 +1088,46 @@
         <v>50.41</v>
       </c>
       <c r="G3">
-        <v>-46.07</v>
+        <v>-43.34</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="I3">
-        <v>-6.02</v>
+        <v>0.91</v>
       </c>
       <c r="J3">
-        <v>-18.82</v>
+        <v>-16.27</v>
       </c>
       <c r="K3">
-        <v>-16.11</v>
+        <v>-10.66</v>
       </c>
       <c r="L3">
-        <v>-39.52</v>
+        <v>-36.43</v>
       </c>
       <c r="M3">
-        <v>-25.49</v>
+        <v>-24.59</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P3">
-        <v>51.31</v>
+        <v>51.41</v>
       </c>
       <c r="Q3">
-        <v>55.03</v>
+        <v>54.51</v>
       </c>
       <c r="R3">
-        <v>57.57</v>
+        <v>57.43</v>
       </c>
       <c r="S3">
-        <v>64.84999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="T3">
-        <v>-22.27</v>
+        <v>-18.16</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1078,34 +1142,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>24.95</v>
+        <v>40.87</v>
       </c>
       <c r="Z3">
-        <v>-2.09</v>
+        <v>-1.94</v>
       </c>
       <c r="AA3">
-        <v>-1.66</v>
+        <v>-1.71</v>
       </c>
       <c r="AB3">
-        <v>-0.44</v>
+        <v>-0.23</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="AE3">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AF3">
-        <v>-48.92</v>
+        <v>29.41</v>
       </c>
       <c r="AG3">
-        <v>61.59</v>
+        <v>59.83</v>
       </c>
       <c r="AH3">
-        <v>48.47</v>
+        <v>49.19</v>
       </c>
       <c r="AI3">
         <v>55.66</v>
@@ -1114,7 +1178,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>59.06</v>
+        <v>53.08</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1125,10 +1189,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3310</v>
+        <v>3322</v>
       </c>
       <c r="D4">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1137,25 +1201,25 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.09</v>
+        <v>-1.73</v>
       </c>
       <c r="H4">
-        <v>30.77</v>
+        <v>31.25</v>
       </c>
       <c r="I4">
-        <v>1.6</v>
+        <v>0.97</v>
       </c>
       <c r="J4">
-        <v>2.67</v>
+        <v>3.17</v>
       </c>
       <c r="K4">
-        <v>7.2</v>
+        <v>8.91</v>
       </c>
       <c r="L4">
-        <v>18.05</v>
+        <v>19.51</v>
       </c>
       <c r="M4">
-        <v>17.53</v>
+        <v>17.32</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1164,19 +1228,19 @@
         <v>70</v>
       </c>
       <c r="P4">
-        <v>3314.18</v>
+        <v>3320.58</v>
       </c>
       <c r="Q4">
-        <v>3297.64</v>
+        <v>3297.59</v>
       </c>
       <c r="R4">
-        <v>3206.04</v>
+        <v>3209.95</v>
       </c>
       <c r="S4">
-        <v>2934.03</v>
+        <v>2936.83</v>
       </c>
       <c r="T4">
-        <v>12.81</v>
+        <v>13.12</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1191,34 +1255,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>55.45</v>
+        <v>56.66</v>
       </c>
       <c r="Z4">
-        <v>30.93</v>
+        <v>30.67</v>
       </c>
       <c r="AA4">
-        <v>34.04</v>
+        <v>33.37</v>
       </c>
       <c r="AB4">
-        <v>-3.11</v>
+        <v>-2.7</v>
       </c>
       <c r="AC4">
-        <v>23.6</v>
+        <v>28.27</v>
       </c>
       <c r="AD4">
-        <v>41.93</v>
+        <v>33.03</v>
       </c>
       <c r="AE4">
-        <v>71.55</v>
+        <v>71.05</v>
       </c>
       <c r="AF4">
-        <v>97.76000000000001</v>
+        <v>-28.34</v>
       </c>
       <c r="AG4">
-        <v>3367.39</v>
+        <v>3367.26</v>
       </c>
       <c r="AH4">
-        <v>3227.89</v>
+        <v>3227.92</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1227,7 +1291,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>20.66</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1238,58 +1302,58 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D5">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>720.95</v>
+        <v>738.75</v>
       </c>
       <c r="G5">
-        <v>-12.15</v>
+        <v>-12.06</v>
       </c>
       <c r="H5">
-        <v>40.09</v>
+        <v>36.85</v>
       </c>
       <c r="I5">
-        <v>-1.37</v>
+        <v>-2.54</v>
       </c>
       <c r="J5">
-        <v>-2.88</v>
+        <v>-1.56</v>
       </c>
       <c r="K5">
-        <v>-7.56</v>
+        <v>-4.84</v>
       </c>
       <c r="L5">
-        <v>40.36</v>
+        <v>40.23</v>
       </c>
       <c r="M5">
-        <v>17.64</v>
+        <v>17.29</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P5">
-        <v>1017.39</v>
+        <v>1012.11</v>
       </c>
       <c r="Q5">
-        <v>1039.24</v>
+        <v>1036.81</v>
       </c>
       <c r="R5">
-        <v>995.4400000000001</v>
+        <v>996.59</v>
       </c>
       <c r="S5">
-        <v>964.59</v>
+        <v>965.66</v>
       </c>
       <c r="T5">
-        <v>4.71</v>
+        <v>4.7</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1304,34 +1368,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>46.13</v>
+        <v>46.47</v>
       </c>
       <c r="Z5">
-        <v>3.23</v>
+        <v>1.82</v>
       </c>
       <c r="AA5">
-        <v>9.59</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AB5">
-        <v>-6.36</v>
+        <v>-6.21</v>
       </c>
       <c r="AC5">
-        <v>0.22</v>
+        <v>1.24</v>
       </c>
       <c r="AD5">
-        <v>1.89</v>
+        <v>0.49</v>
       </c>
       <c r="AE5">
-        <v>23.69</v>
+        <v>23.13</v>
       </c>
       <c r="AF5">
-        <v>-65.95999999999999</v>
+        <v>-10.51</v>
       </c>
       <c r="AG5">
-        <v>1076.22</v>
+        <v>1074.54</v>
       </c>
       <c r="AH5">
-        <v>1002.26</v>
+        <v>999.08</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1340,7 +1404,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>24.75</v>
+        <v>23.58</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1351,58 +1415,58 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.48</v>
+        <v>15.02</v>
       </c>
       <c r="D6">
-        <v>-0.34</v>
+        <v>3.73</v>
       </c>
       <c r="E6">
         <v>15.19</v>
       </c>
       <c r="F6">
-        <v>6.51</v>
+        <v>6.57</v>
       </c>
       <c r="G6">
-        <v>-4.67</v>
+        <v>-1.12</v>
       </c>
       <c r="H6">
-        <v>122.43</v>
+        <v>128.61</v>
       </c>
       <c r="I6">
-        <v>-3.27</v>
+        <v>2.32</v>
       </c>
       <c r="J6">
-        <v>13.12</v>
+        <v>18.92</v>
       </c>
       <c r="K6">
-        <v>-3.14</v>
+        <v>4.31</v>
       </c>
       <c r="L6">
-        <v>121.41</v>
+        <v>130.72</v>
       </c>
       <c r="M6">
-        <v>14.84</v>
+        <v>15.7</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P6">
-        <v>14.42</v>
+        <v>14.48</v>
       </c>
       <c r="Q6">
-        <v>14.04</v>
+        <v>14.16</v>
       </c>
       <c r="R6">
-        <v>13.79</v>
+        <v>13.81</v>
       </c>
       <c r="S6">
-        <v>11.88</v>
+        <v>11.9</v>
       </c>
       <c r="T6">
-        <v>21.93</v>
+        <v>26.25</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1417,34 +1481,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>56.76</v>
+        <v>62.97</v>
       </c>
       <c r="Z6">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="AA6">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="AB6">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="AC6">
-        <v>18.12</v>
+        <v>36.23</v>
       </c>
       <c r="AD6">
-        <v>17.79</v>
+        <v>21.85</v>
       </c>
       <c r="AE6">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="AF6">
-        <v>-44.96</v>
+        <v>10.11</v>
       </c>
       <c r="AG6">
-        <v>15.43</v>
+        <v>15.47</v>
       </c>
       <c r="AH6">
-        <v>12.66</v>
+        <v>12.85</v>
       </c>
       <c r="AI6">
         <v>13.86</v>
@@ -1453,7 +1517,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>37.44</v>
+        <v>35.89</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1464,10 +1528,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.05</v>
+        <v>10.9</v>
       </c>
       <c r="D7">
-        <v>-1.95</v>
+        <v>-1.36</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1476,46 +1540,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-20.62</v>
+        <v>-21.7</v>
       </c>
       <c r="H7">
-        <v>135.61</v>
+        <v>132.41</v>
       </c>
       <c r="I7">
-        <v>-0.54</v>
+        <v>-3.54</v>
       </c>
       <c r="J7">
-        <v>-16.67</v>
+        <v>-16.15</v>
       </c>
       <c r="K7">
-        <v>-4.49</v>
+        <v>-1.98</v>
       </c>
       <c r="L7">
-        <v>115.82</v>
+        <v>108.41</v>
       </c>
       <c r="M7">
-        <v>-30.9</v>
+        <v>-31.31</v>
       </c>
       <c r="N7">
         <v>87</v>
       </c>
       <c r="O7">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P7">
-        <v>11.16</v>
+        <v>11.08</v>
       </c>
       <c r="Q7">
-        <v>11.63</v>
+        <v>11.54</v>
       </c>
       <c r="R7">
         <v>11.54</v>
       </c>
       <c r="S7">
-        <v>10.29</v>
+        <v>10.32</v>
       </c>
       <c r="T7">
-        <v>7.37</v>
+        <v>5.61</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1530,43 +1594,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>39.58</v>
+        <v>37.27</v>
       </c>
       <c r="Z7">
-        <v>-0.21</v>
+        <v>-0.23</v>
       </c>
       <c r="AA7">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="AB7">
         <v>-0.08</v>
       </c>
       <c r="AC7">
-        <v>23.11</v>
+        <v>19.64</v>
       </c>
       <c r="AD7">
-        <v>20.03</v>
+        <v>21.47</v>
       </c>
       <c r="AE7">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="AF7">
-        <v>-41.22</v>
+        <v>-54.35</v>
       </c>
       <c r="AG7">
-        <v>12.65</v>
+        <v>12.47</v>
       </c>
       <c r="AH7">
         <v>10.61</v>
       </c>
       <c r="AI7">
-        <v>11.87</v>
+        <v>11.75</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>33.99</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1577,10 +1641,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4354.5</v>
+        <v>4323.8</v>
       </c>
       <c r="D8">
-        <v>0.68</v>
+        <v>-0.71</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1589,46 +1653,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-25.05</v>
+        <v>-25.57</v>
       </c>
       <c r="H8">
-        <v>4.8</v>
+        <v>4.06</v>
       </c>
       <c r="I8">
-        <v>-0.21</v>
+        <v>-1.46</v>
       </c>
       <c r="J8">
-        <v>0.37</v>
+        <v>0.2</v>
       </c>
       <c r="K8">
-        <v>3.07</v>
+        <v>3.37</v>
       </c>
       <c r="L8">
-        <v>-13.75</v>
+        <v>-15.06</v>
       </c>
       <c r="M8">
-        <v>19.6</v>
+        <v>19.43</v>
       </c>
       <c r="N8">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="O8">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P8">
-        <v>4354.8</v>
+        <v>4341.98</v>
       </c>
       <c r="Q8">
-        <v>4389.08</v>
+        <v>4386.74</v>
       </c>
       <c r="R8">
-        <v>4373.1</v>
+        <v>4371.63</v>
       </c>
       <c r="S8">
-        <v>4633.45</v>
+        <v>4628.96</v>
       </c>
       <c r="T8">
-        <v>-6.02</v>
+        <v>-6.59</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1643,34 +1707,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>48.17</v>
+        <v>45.36</v>
       </c>
       <c r="Z8">
-        <v>-6.31</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="AA8">
-        <v>-0.36</v>
+        <v>-2.13</v>
       </c>
       <c r="AB8">
-        <v>-5.95</v>
+        <v>-7.09</v>
       </c>
       <c r="AC8">
-        <v>18.58</v>
+        <v>19.12</v>
       </c>
       <c r="AD8">
-        <v>20.74</v>
+        <v>18.49</v>
       </c>
       <c r="AE8">
-        <v>91.89</v>
+        <v>89.14</v>
       </c>
       <c r="AF8">
-        <v>-68.08</v>
+        <v>-69.75</v>
       </c>
       <c r="AG8">
-        <v>4533.94</v>
+        <v>4534.34</v>
       </c>
       <c r="AH8">
-        <v>4244.23</v>
+        <v>4239.14</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1679,7 +1743,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>17.05</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1690,10 +1754,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11275</v>
+        <v>11408</v>
       </c>
       <c r="D9">
-        <v>-1.04</v>
+        <v>1.18</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1702,46 +1766,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-13.61</v>
+        <v>-12.6</v>
       </c>
       <c r="H9">
-        <v>8.81</v>
+        <v>10.09</v>
       </c>
       <c r="I9">
-        <v>-3.77</v>
+        <v>-1.56</v>
       </c>
       <c r="J9">
-        <v>-7.51</v>
+        <v>-5.52</v>
       </c>
       <c r="K9">
-        <v>3.33</v>
+        <v>5.68</v>
       </c>
       <c r="L9">
-        <v>-12.09</v>
+        <v>-10.38</v>
       </c>
       <c r="M9">
-        <v>7.78</v>
+        <v>7.98</v>
       </c>
       <c r="N9">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="O9">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P9">
-        <v>11421.4</v>
+        <v>11385.2</v>
       </c>
       <c r="Q9">
-        <v>11621.85</v>
+        <v>11587</v>
       </c>
       <c r="R9">
-        <v>11702.06</v>
+        <v>11700.44</v>
       </c>
       <c r="S9">
-        <v>11767.91</v>
+        <v>11766.42</v>
       </c>
       <c r="T9">
-        <v>-4.19</v>
+        <v>-3.05</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1756,34 +1820,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>35.15</v>
+        <v>41.85</v>
       </c>
       <c r="Z9">
-        <v>-101.75</v>
+        <v>-102.58</v>
       </c>
       <c r="AA9">
-        <v>-64.62</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="AB9">
-        <v>-37.13</v>
+        <v>-30.37</v>
       </c>
       <c r="AC9">
-        <v>4.36</v>
+        <v>16.63</v>
       </c>
       <c r="AD9">
-        <v>13.99</v>
+        <v>10.54</v>
       </c>
       <c r="AE9">
-        <v>188.46</v>
+        <v>186.36</v>
       </c>
       <c r="AF9">
-        <v>7.88</v>
+        <v>21.55</v>
       </c>
       <c r="AG9">
-        <v>12045.34</v>
+        <v>11954.03</v>
       </c>
       <c r="AH9">
-        <v>11198.36</v>
+        <v>11219.97</v>
       </c>
       <c r="AI9">
         <v>11857.5</v>
@@ -1792,7 +1856,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>28.15</v>
+        <v>29.14</v>
       </c>
     </row>
   </sheetData>
@@ -1933,7 +1997,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1953,1161 +2017,1256 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-5.46</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-5.34</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.12</v>
+        <v>71</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-17.26</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-18.82</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.56</v>
-      </c>
+      <c r="A8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-5.34</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-3.94</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-18.82</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-16.27</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>5</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C12" s="6">
         <v>2.67</v>
       </c>
-      <c r="E9" s="7">
-        <v>-2.33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D12" s="6">
+        <v>3.17</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-1.01</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C13" s="6">
         <v>-2.88</v>
       </c>
-      <c r="E10" s="7">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-1.56</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>12.64</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C14" s="6">
         <v>13.12</v>
       </c>
-      <c r="E11" s="6">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D14" s="6">
+        <v>18.92</v>
+      </c>
+      <c r="E14" s="7">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-16.7</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C15" s="6">
         <v>-16.67</v>
       </c>
-      <c r="E12" s="6">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-16.15</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-0.44</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C16" s="6">
         <v>0.37</v>
       </c>
-      <c r="E13" s="6">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D16" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5">
-        <v>-5.45</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C17" s="6">
         <v>-7.51</v>
       </c>
-      <c r="E14" s="7">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-5.52</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-3.16</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C18" s="6">
         <v>-1.95</v>
       </c>
-      <c r="E15" s="6">
+      <c r="D18" s="6">
+        <v>-0.16</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-6.02</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="E19" s="7">
+        <v>6.93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1.6</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-1.37</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-2.54</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-3.27</v>
+      </c>
+      <c r="D22" s="6">
+        <v>2.32</v>
+      </c>
+      <c r="E22" s="7">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.54</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-3.54</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-0.21</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-1.46</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-3.77</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-1.56</v>
+      </c>
+      <c r="E25" s="7">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>43.55</v>
+      </c>
+      <c r="D26" s="6">
+        <v>47.32</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-39.52</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-36.43</v>
+      </c>
+      <c r="E27" s="7">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>18.05</v>
+      </c>
+      <c r="D28" s="6">
+        <v>19.51</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>40.36</v>
+      </c>
+      <c r="D29" s="6">
+        <v>40.23</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>121.41</v>
+      </c>
+      <c r="D30" s="6">
+        <v>130.72</v>
+      </c>
+      <c r="E30" s="7">
+        <v>9.31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>115.82</v>
+      </c>
+      <c r="D31" s="6">
+        <v>108.41</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-7.41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-13.75</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-15.06</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-12.09</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-10.38</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>12.45</v>
+      </c>
+      <c r="D34" s="6">
+        <v>17.7</v>
+      </c>
+      <c r="E34" s="7">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-16.11</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-10.66</v>
+      </c>
+      <c r="E35" s="7">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>7.2</v>
+      </c>
+      <c r="D36" s="6">
+        <v>8.91</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-7.56</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-4.84</v>
+      </c>
+      <c r="E37" s="7">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-3.14</v>
+      </c>
+      <c r="D38" s="6">
+        <v>4.31</v>
+      </c>
+      <c r="E38" s="7">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-4.49</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-1.98</v>
+      </c>
+      <c r="E39" s="7">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>3.07</v>
+      </c>
+      <c r="D40" s="6">
+        <v>3.37</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="D41" s="6">
+        <v>5.68</v>
+      </c>
+      <c r="E41" s="7">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-5.34</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-4.66</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-46.07</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-43.34</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-2.09</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-1.73</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-12.15</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-12.06</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-4.67</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-1.12</v>
+      </c>
+      <c r="E46" s="7">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-20.62</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-21.7</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-25.05</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-25.57</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-13.61</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-12.6</v>
+      </c>
+      <c r="E49" s="7">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>402</v>
+      </c>
+      <c r="D50" s="6">
+        <v>404.9</v>
+      </c>
+      <c r="E50" s="7">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>50.41</v>
+      </c>
+      <c r="D51" s="6">
+        <v>52.97</v>
+      </c>
+      <c r="E51" s="7">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>3310</v>
+      </c>
+      <c r="D52" s="6">
+        <v>3322</v>
+      </c>
+      <c r="E52" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>1010</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1011</v>
+      </c>
+      <c r="E53" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>14.48</v>
+      </c>
+      <c r="D54" s="6">
+        <v>15.02</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>11.05</v>
+      </c>
+      <c r="D55" s="6">
+        <v>10.9</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>4354.5</v>
+      </c>
+      <c r="D56" s="6">
+        <v>4323.8</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-30.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>11275</v>
+      </c>
+      <c r="D57" s="6">
+        <v>11408</v>
+      </c>
+      <c r="E57" s="7">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="6">
+        <v>38</v>
+      </c>
+      <c r="D58" s="6">
+        <v>26</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="6">
+        <v>26</v>
+      </c>
+      <c r="D59" s="6">
+        <v>38</v>
+      </c>
+      <c r="E59" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>48.36</v>
+      </c>
+      <c r="D60" s="6">
+        <v>50.53</v>
+      </c>
+      <c r="E60" s="7">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>24.95</v>
+      </c>
+      <c r="D61" s="6">
+        <v>40.87</v>
+      </c>
+      <c r="E61" s="7">
+        <v>15.92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>55.45</v>
+      </c>
+      <c r="D62" s="6">
+        <v>56.66</v>
+      </c>
+      <c r="E62" s="7">
         <v>1.21</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>46.13</v>
+      </c>
+      <c r="D63" s="6">
+        <v>46.47</v>
+      </c>
+      <c r="E63" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>56.76</v>
+      </c>
+      <c r="D64" s="6">
+        <v>62.97</v>
+      </c>
+      <c r="E64" s="7">
+        <v>6.21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>39.58</v>
+      </c>
+      <c r="D65" s="6">
+        <v>37.27</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>48.17</v>
+      </c>
+      <c r="D66" s="6">
+        <v>45.36</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>35.15</v>
+      </c>
+      <c r="D67" s="6">
+        <v>41.85</v>
+      </c>
+      <c r="E67" s="7">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>-39.29</v>
+      </c>
+      <c r="D68" s="6">
+        <v>-29.99</v>
+      </c>
+      <c r="E68" s="7">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-7.43</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-6.02</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>-48.92</v>
+      </c>
+      <c r="D69" s="6">
+        <v>29.41</v>
+      </c>
+      <c r="E69" s="7">
+        <v>78.33</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-0.15</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>97.76000000000001</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-28.34</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-126.1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-4.11</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.37</v>
-      </c>
-      <c r="E18" s="6">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>-65.95999999999999</v>
+      </c>
+      <c r="D71" s="6">
+        <v>-10.51</v>
+      </c>
+      <c r="E71" s="7">
+        <v>55.45</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-3.52</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-3.27</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-44.96</v>
+      </c>
+      <c r="D72" s="6">
+        <v>10.11</v>
+      </c>
+      <c r="E72" s="7">
+        <v>55.07</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1.44</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-0.54</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-41.22</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-54.35</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-13.13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-2.26</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.21</v>
-      </c>
-      <c r="E21" s="6">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-68.08</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-69.75</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-2.77</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-3.77</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>42.9</v>
-      </c>
-      <c r="D23" s="5">
-        <v>43.55</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-34.75</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-39.52</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-4.77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>18.71</v>
-      </c>
-      <c r="D25" s="5">
-        <v>18.05</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>43.43</v>
-      </c>
-      <c r="D26" s="5">
-        <v>40.36</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>123.88</v>
-      </c>
-      <c r="D27" s="5">
-        <v>121.41</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>117.99</v>
-      </c>
-      <c r="D28" s="5">
-        <v>115.82</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-11.12</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-13.75</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-9.869999999999999</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-12.09</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>12.27</v>
-      </c>
-      <c r="D31" s="5">
-        <v>12.45</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-17.3</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-16.11</v>
-      </c>
-      <c r="E32" s="6">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>6.17</v>
-      </c>
-      <c r="D33" s="5">
-        <v>7.2</v>
-      </c>
-      <c r="E33" s="6">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-10.3</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-7.56</v>
-      </c>
-      <c r="E34" s="6">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-2.68</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-3.14</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-5.93</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-4.49</v>
-      </c>
-      <c r="E36" s="6">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>1.15</v>
-      </c>
-      <c r="D37" s="5">
-        <v>3.07</v>
-      </c>
-      <c r="E37" s="6">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="D38" s="5">
-        <v>3.33</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-6.51</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-5.34</v>
-      </c>
-      <c r="E39" s="6">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-46.01</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-46.07</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-2.53</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-2.09</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-12.18</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-12.15</v>
-      </c>
-      <c r="E42" s="6">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-4.34</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-4.67</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-19.04</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-20.62</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-25.55</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-25.05</v>
-      </c>
-      <c r="E45" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-12.71</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-13.61</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>397.05</v>
-      </c>
-      <c r="D47" s="5">
-        <v>402</v>
-      </c>
-      <c r="E47" s="6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>50.47</v>
-      </c>
-      <c r="D48" s="5">
-        <v>50.41</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>3294.9</v>
-      </c>
-      <c r="D49" s="5">
-        <v>3310</v>
-      </c>
-      <c r="E49" s="6">
-        <v>15.1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>1009.7</v>
-      </c>
-      <c r="D50" s="5">
-        <v>1010</v>
-      </c>
-      <c r="E50" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>14.53</v>
-      </c>
-      <c r="D51" s="5">
-        <v>14.48</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>11.27</v>
-      </c>
-      <c r="D52" s="5">
-        <v>11.05</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>4325</v>
-      </c>
-      <c r="D53" s="5">
-        <v>4354.5</v>
-      </c>
-      <c r="E53" s="6">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>11393</v>
-      </c>
-      <c r="D54" s="5">
-        <v>11275</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-118</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="5">
-        <v>26</v>
-      </c>
-      <c r="D55" s="5">
-        <v>38</v>
-      </c>
-      <c r="E55" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="5">
-        <v>38</v>
-      </c>
-      <c r="D56" s="5">
-        <v>26</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>44.51</v>
-      </c>
-      <c r="D57" s="5">
-        <v>48.36</v>
-      </c>
-      <c r="E57" s="6">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>25.09</v>
-      </c>
-      <c r="D58" s="5">
-        <v>24.95</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>53.94</v>
-      </c>
-      <c r="D59" s="5">
-        <v>55.45</v>
-      </c>
-      <c r="E59" s="6">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>46.03</v>
-      </c>
-      <c r="D60" s="5">
-        <v>46.13</v>
-      </c>
-      <c r="E60" s="6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>57.59</v>
-      </c>
-      <c r="D61" s="5">
-        <v>56.76</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>43.21</v>
-      </c>
-      <c r="D62" s="5">
-        <v>39.58</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-3.63</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>45.13</v>
-      </c>
-      <c r="D63" s="5">
-        <v>48.17</v>
-      </c>
-      <c r="E63" s="6">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>38.84</v>
-      </c>
-      <c r="D64" s="5">
-        <v>35.15</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-3.69</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="3" t="s">
+      <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C65" s="5">
-        <v>58.03</v>
-      </c>
-      <c r="D65" s="5">
-        <v>-39.29</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-97.31999999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-30.45</v>
-      </c>
-      <c r="D66" s="5">
-        <v>-48.92</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-18.47</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>-5.86</v>
-      </c>
-      <c r="D67" s="5">
-        <v>97.76000000000001</v>
-      </c>
-      <c r="E67" s="6">
-        <v>103.62</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>-58.29</v>
-      </c>
-      <c r="D68" s="5">
-        <v>-65.95999999999999</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-7.67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
-        <v>13.48</v>
-      </c>
-      <c r="D69" s="5">
-        <v>-44.96</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-58.44</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="5">
-        <v>-37.76</v>
-      </c>
-      <c r="D70" s="5">
-        <v>-41.22</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="5">
-        <v>-57.05</v>
-      </c>
-      <c r="D71" s="5">
-        <v>-68.08</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-11.03</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>1.84</v>
-      </c>
-      <c r="D72" s="5">
+      <c r="C75" s="6">
         <v>7.88</v>
       </c>
-      <c r="E72" s="6">
-        <v>6.04</v>
+      <c r="D75" s="6">
+        <v>21.55</v>
+      </c>
+      <c r="E75" s="7">
+        <v>13.67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3127,60 +3286,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="11">
+        <v>56.44</v>
+      </c>
+      <c r="C2" s="12">
+        <v>8</v>
+      </c>
+      <c r="D2" s="11">
+        <v>47.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.44</v>
-      </c>
-      <c r="C2" s="11">
-        <v>8</v>
-      </c>
-      <c r="D2" s="10">
-        <v>44.3</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-4.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-0.7</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-2.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>2.8</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -3282,55 +3441,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.3054</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.196</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1764</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1753</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1484</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.07780000000000001</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2549</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.309</v>
+      <c r="A2" s="14">
+        <v>0.3039</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1943</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1732</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1729</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.157</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.07980000000000001</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2459</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.3131</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,55 +190,40 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.1% → -1.7%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.1%</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.7% → -2.3%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>-1.7%</t>
   </si>
   <si>
-    <t>-4.7% → -1.1%</t>
-  </si>
-  <si>
-    <t>-4.7%</t>
-  </si>
-  <si>
-    <t>-1.1%</t>
+    <t>-2.3%</t>
   </si>
   <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.4 → 50.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.4</t>
+    <t>50.5 → 49.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.5</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>24.9 → 40.9</t>
-  </si>
-  <si>
-    <t>24.9</t>
-  </si>
-  <si>
-    <t>40.9</t>
+    <t>49.3</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -290,7 +275,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,7 +309,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -336,8 +321,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,13 +356,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -448,14 +446,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -464,7 +463,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -822,8 +821,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -963,10 +962,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>404.9</v>
+        <v>403.25</v>
       </c>
       <c r="D2">
-        <v>0.72</v>
+        <v>-0.41</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -975,46 +974,46 @@
         <v>277.55</v>
       </c>
       <c r="G2">
-        <v>-4.66</v>
+        <v>-5.05</v>
       </c>
       <c r="H2">
-        <v>45.88</v>
+        <v>45.29</v>
       </c>
       <c r="I2">
-        <v>-0.16</v>
+        <v>-1.5</v>
       </c>
       <c r="J2">
-        <v>-3.94</v>
+        <v>-1.18</v>
       </c>
       <c r="K2">
-        <v>17.7</v>
+        <v>14.77</v>
       </c>
       <c r="L2">
-        <v>47.32</v>
+        <v>44.4</v>
       </c>
       <c r="M2">
-        <v>30.39</v>
+        <v>29.07</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P2">
-        <v>401.56</v>
+        <v>400.33</v>
       </c>
       <c r="Q2">
-        <v>405.52</v>
+        <v>405.29</v>
       </c>
       <c r="R2">
-        <v>403.54</v>
+        <v>403.9</v>
       </c>
       <c r="S2">
-        <v>360.72</v>
+        <v>361.09</v>
       </c>
       <c r="T2">
-        <v>12.25</v>
+        <v>11.68</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1029,34 +1028,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>50.53</v>
+        <v>49.26</v>
       </c>
       <c r="Z2">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AA2">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="AB2">
-        <v>-1.25</v>
+        <v>-1.07</v>
       </c>
       <c r="AC2">
-        <v>39.33</v>
+        <v>50.9</v>
       </c>
       <c r="AD2">
-        <v>29.28</v>
+        <v>36.6</v>
       </c>
       <c r="AE2">
-        <v>9.550000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AF2">
-        <v>-29.99</v>
+        <v>-20.84</v>
       </c>
       <c r="AG2">
-        <v>416.99</v>
+        <v>416.76</v>
       </c>
       <c r="AH2">
-        <v>394.05</v>
+        <v>393.83</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1065,7 +1064,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>24.52</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1076,10 +1075,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>52.97</v>
+        <v>53.21</v>
       </c>
       <c r="D3">
-        <v>5.08</v>
+        <v>0.45</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1088,46 +1087,46 @@
         <v>50.41</v>
       </c>
       <c r="G3">
-        <v>-43.34</v>
+        <v>-43.08</v>
       </c>
       <c r="H3">
-        <v>5.08</v>
+        <v>5.55</v>
       </c>
       <c r="I3">
-        <v>0.91</v>
+        <v>2.13</v>
       </c>
       <c r="J3">
-        <v>-16.27</v>
+        <v>-15.98</v>
       </c>
       <c r="K3">
-        <v>-10.66</v>
+        <v>-11.98</v>
       </c>
       <c r="L3">
-        <v>-36.43</v>
+        <v>-34.64</v>
       </c>
       <c r="M3">
-        <v>-24.59</v>
+        <v>-24.43</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P3">
-        <v>51.41</v>
+        <v>51.63</v>
       </c>
       <c r="Q3">
-        <v>54.51</v>
+        <v>54.12</v>
       </c>
       <c r="R3">
-        <v>57.43</v>
+        <v>57.32</v>
       </c>
       <c r="S3">
-        <v>64.73</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="T3">
-        <v>-18.16</v>
+        <v>-17.63</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1142,34 +1141,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>40.87</v>
+        <v>42.11</v>
       </c>
       <c r="Z3">
-        <v>-1.94</v>
+        <v>-1.78</v>
       </c>
       <c r="AA3">
-        <v>-1.71</v>
+        <v>-1.72</v>
       </c>
       <c r="AB3">
-        <v>-0.23</v>
+        <v>-0.05</v>
       </c>
       <c r="AC3">
+        <v>66.67</v>
+      </c>
+      <c r="AD3">
         <v>33.33</v>
       </c>
-      <c r="AD3">
-        <v>11.11</v>
-      </c>
       <c r="AE3">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AF3">
-        <v>29.41</v>
+        <v>71.02</v>
       </c>
       <c r="AG3">
-        <v>59.83</v>
+        <v>58.48</v>
       </c>
       <c r="AH3">
-        <v>49.19</v>
+        <v>49.76</v>
       </c>
       <c r="AI3">
         <v>55.66</v>
@@ -1178,7 +1177,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>53.08</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1189,10 +1188,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3322</v>
+        <v>3302.4</v>
       </c>
       <c r="D4">
-        <v>0.36</v>
+        <v>-0.59</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1201,46 +1200,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-1.73</v>
+        <v>-2.31</v>
       </c>
       <c r="H4">
-        <v>31.25</v>
+        <v>30.47</v>
       </c>
       <c r="I4">
-        <v>0.97</v>
+        <v>-2.04</v>
       </c>
       <c r="J4">
-        <v>3.17</v>
+        <v>-0.62</v>
       </c>
       <c r="K4">
-        <v>8.91</v>
+        <v>6.68</v>
       </c>
       <c r="L4">
-        <v>19.51</v>
+        <v>18.73</v>
       </c>
       <c r="M4">
-        <v>17.32</v>
+        <v>16.81</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>3320.58</v>
+        <v>3306.86</v>
       </c>
       <c r="Q4">
-        <v>3297.59</v>
+        <v>3293.68</v>
       </c>
       <c r="R4">
-        <v>3209.95</v>
+        <v>3214.39</v>
       </c>
       <c r="S4">
-        <v>2936.83</v>
+        <v>2939.61</v>
       </c>
       <c r="T4">
-        <v>13.12</v>
+        <v>12.34</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1255,34 +1254,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>56.66</v>
+        <v>54.07</v>
       </c>
       <c r="Z4">
-        <v>30.67</v>
+        <v>28.55</v>
       </c>
       <c r="AA4">
-        <v>33.37</v>
+        <v>32.4</v>
       </c>
       <c r="AB4">
-        <v>-2.7</v>
+        <v>-3.85</v>
       </c>
       <c r="AC4">
-        <v>28.27</v>
+        <v>28.66</v>
       </c>
       <c r="AD4">
-        <v>33.03</v>
+        <v>26.85</v>
       </c>
       <c r="AE4">
-        <v>71.05</v>
+        <v>68.45</v>
       </c>
       <c r="AF4">
-        <v>-28.34</v>
+        <v>-7.19</v>
       </c>
       <c r="AG4">
-        <v>3367.26</v>
+        <v>3351.55</v>
       </c>
       <c r="AH4">
-        <v>3227.92</v>
+        <v>3235.82</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1291,7 +1290,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>19.96</v>
+        <v>19.36</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1302,10 +1301,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="D5">
-        <v>0.1</v>
+        <v>-0.49</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1314,46 +1313,46 @@
         <v>738.75</v>
       </c>
       <c r="G5">
-        <v>-12.06</v>
+        <v>-12.5</v>
       </c>
       <c r="H5">
-        <v>36.85</v>
+        <v>36.18</v>
       </c>
       <c r="I5">
-        <v>-2.54</v>
+        <v>-0.93</v>
       </c>
       <c r="J5">
-        <v>-1.56</v>
+        <v>-5.06</v>
       </c>
       <c r="K5">
-        <v>-4.84</v>
+        <v>-6.57</v>
       </c>
       <c r="L5">
-        <v>40.23</v>
+        <v>35.41</v>
       </c>
       <c r="M5">
-        <v>17.29</v>
+        <v>17.5</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="P5">
-        <v>1012.11</v>
+        <v>1010.22</v>
       </c>
       <c r="Q5">
-        <v>1036.81</v>
+        <v>1034.41</v>
       </c>
       <c r="R5">
-        <v>996.59</v>
+        <v>997.4400000000001</v>
       </c>
       <c r="S5">
-        <v>965.66</v>
+        <v>966.73</v>
       </c>
       <c r="T5">
-        <v>4.7</v>
+        <v>4.06</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1368,34 +1367,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>46.47</v>
+        <v>44.92</v>
       </c>
       <c r="Z5">
-        <v>1.82</v>
+        <v>0.3</v>
       </c>
       <c r="AA5">
-        <v>8.029999999999999</v>
+        <v>6.49</v>
       </c>
       <c r="AB5">
-        <v>-6.21</v>
+        <v>-6.19</v>
       </c>
       <c r="AC5">
         <v>1.24</v>
       </c>
       <c r="AD5">
-        <v>0.49</v>
+        <v>0.9</v>
       </c>
       <c r="AE5">
-        <v>23.13</v>
+        <v>22.55</v>
       </c>
       <c r="AF5">
-        <v>-10.51</v>
+        <v>-53.66</v>
       </c>
       <c r="AG5">
-        <v>1074.54</v>
+        <v>1073.61</v>
       </c>
       <c r="AH5">
-        <v>999.08</v>
+        <v>995.21</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1404,7 +1403,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>23.58</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1415,58 +1414,58 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>15.02</v>
+        <v>15.6</v>
       </c>
       <c r="D6">
-        <v>3.73</v>
+        <v>3.86</v>
       </c>
       <c r="E6">
-        <v>15.19</v>
+        <v>15.6</v>
       </c>
       <c r="F6">
-        <v>6.57</v>
+        <v>6.61</v>
       </c>
       <c r="G6">
-        <v>-1.12</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>128.61</v>
+        <v>136.01</v>
       </c>
       <c r="I6">
-        <v>2.32</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="J6">
-        <v>18.92</v>
+        <v>22.55</v>
       </c>
       <c r="K6">
-        <v>4.31</v>
+        <v>10.33</v>
       </c>
       <c r="L6">
-        <v>130.72</v>
+        <v>137.44</v>
       </c>
       <c r="M6">
-        <v>15.7</v>
+        <v>13.59</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P6">
-        <v>14.48</v>
+        <v>14.74</v>
       </c>
       <c r="Q6">
-        <v>14.16</v>
+        <v>14.29</v>
       </c>
       <c r="R6">
-        <v>13.81</v>
+        <v>13.83</v>
       </c>
       <c r="S6">
-        <v>11.9</v>
+        <v>11.92</v>
       </c>
       <c r="T6">
-        <v>26.25</v>
+        <v>30.85</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1481,34 +1480,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>62.97</v>
+        <v>68.25</v>
       </c>
       <c r="Z6">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="AA6">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="AB6">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="AC6">
-        <v>36.23</v>
+        <v>52.89</v>
       </c>
       <c r="AD6">
-        <v>21.85</v>
+        <v>35.75</v>
       </c>
       <c r="AE6">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="AF6">
-        <v>10.11</v>
+        <v>41.04</v>
       </c>
       <c r="AG6">
-        <v>15.47</v>
+        <v>15.61</v>
       </c>
       <c r="AH6">
-        <v>12.85</v>
+        <v>12.97</v>
       </c>
       <c r="AI6">
         <v>13.86</v>
@@ -1517,7 +1516,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>35.89</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1528,10 +1527,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>10.9</v>
+        <v>11.11</v>
       </c>
       <c r="D7">
-        <v>-1.36</v>
+        <v>1.93</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1540,88 +1539,88 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-21.7</v>
+        <v>-20.19</v>
       </c>
       <c r="H7">
-        <v>132.41</v>
+        <v>136.89</v>
       </c>
       <c r="I7">
-        <v>-3.54</v>
+        <v>0.09</v>
       </c>
       <c r="J7">
-        <v>-16.15</v>
+        <v>-12.79</v>
       </c>
       <c r="K7">
-        <v>-1.98</v>
+        <v>2.4</v>
       </c>
       <c r="L7">
-        <v>108.41</v>
+        <v>109.62</v>
       </c>
       <c r="M7">
-        <v>-31.31</v>
+        <v>-30.78</v>
       </c>
       <c r="N7">
         <v>87</v>
       </c>
       <c r="O7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P7">
-        <v>11.08</v>
+        <v>11.09</v>
       </c>
       <c r="Q7">
-        <v>11.54</v>
+        <v>11.47</v>
       </c>
       <c r="R7">
         <v>11.54</v>
       </c>
       <c r="S7">
-        <v>10.32</v>
+        <v>10.35</v>
       </c>
       <c r="T7">
-        <v>5.61</v>
+        <v>7.31</v>
       </c>
       <c r="U7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V7" t="s">
         <v>46</v>
       </c>
       <c r="W7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>37.27</v>
+        <v>42.33</v>
       </c>
       <c r="Z7">
         <v>-0.23</v>
       </c>
       <c r="AA7">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="AB7">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AC7">
-        <v>19.64</v>
+        <v>23.18</v>
       </c>
       <c r="AD7">
-        <v>21.47</v>
+        <v>21.98</v>
       </c>
       <c r="AE7">
         <v>0.26</v>
       </c>
       <c r="AF7">
-        <v>-54.35</v>
+        <v>13.96</v>
       </c>
       <c r="AG7">
-        <v>12.47</v>
+        <v>12.27</v>
       </c>
       <c r="AH7">
-        <v>10.61</v>
+        <v>10.66</v>
       </c>
       <c r="AI7">
         <v>11.75</v>
@@ -1630,7 +1629,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>33.6</v>
+        <v>32.21</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1641,10 +1640,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4323.8</v>
+        <v>4298.7</v>
       </c>
       <c r="D8">
-        <v>-0.71</v>
+        <v>-0.58</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1653,25 +1652,25 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-25.57</v>
+        <v>-26.01</v>
       </c>
       <c r="H8">
-        <v>4.06</v>
+        <v>3.46</v>
       </c>
       <c r="I8">
-        <v>-1.46</v>
+        <v>-1.26</v>
       </c>
       <c r="J8">
-        <v>0.2</v>
+        <v>-1.65</v>
       </c>
       <c r="K8">
-        <v>3.37</v>
+        <v>1.9</v>
       </c>
       <c r="L8">
-        <v>-15.06</v>
+        <v>-16.86</v>
       </c>
       <c r="M8">
-        <v>19.43</v>
+        <v>19.54</v>
       </c>
       <c r="N8">
         <v>26</v>
@@ -1680,19 +1679,19 @@
         <v>40</v>
       </c>
       <c r="P8">
-        <v>4341.98</v>
+        <v>4331.04</v>
       </c>
       <c r="Q8">
-        <v>4386.74</v>
+        <v>4383.46</v>
       </c>
       <c r="R8">
-        <v>4371.63</v>
+        <v>4370.64</v>
       </c>
       <c r="S8">
-        <v>4628.96</v>
+        <v>4624.24</v>
       </c>
       <c r="T8">
-        <v>-6.59</v>
+        <v>-7.04</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1707,34 +1706,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>45.36</v>
+        <v>43.14</v>
       </c>
       <c r="Z8">
-        <v>-9.210000000000001</v>
+        <v>-13.39</v>
       </c>
       <c r="AA8">
-        <v>-2.13</v>
+        <v>-4.38</v>
       </c>
       <c r="AB8">
-        <v>-7.09</v>
+        <v>-9.01</v>
       </c>
       <c r="AC8">
-        <v>19.12</v>
+        <v>16.59</v>
       </c>
       <c r="AD8">
-        <v>18.49</v>
+        <v>18.1</v>
       </c>
       <c r="AE8">
-        <v>89.14</v>
+        <v>87.61</v>
       </c>
       <c r="AF8">
-        <v>-69.75</v>
+        <v>-61.96</v>
       </c>
       <c r="AG8">
-        <v>4534.34</v>
+        <v>4536</v>
       </c>
       <c r="AH8">
-        <v>4239.14</v>
+        <v>4230.93</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1743,7 +1742,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>16.54</v>
+        <v>17.92</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1754,10 +1753,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11408</v>
+        <v>11175</v>
       </c>
       <c r="D9">
-        <v>1.18</v>
+        <v>-2.04</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1766,46 +1765,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-12.6</v>
+        <v>-14.38</v>
       </c>
       <c r="H9">
-        <v>10.09</v>
+        <v>7.85</v>
       </c>
       <c r="I9">
-        <v>-1.56</v>
+        <v>-2.4</v>
       </c>
       <c r="J9">
-        <v>-5.52</v>
+        <v>-7.68</v>
       </c>
       <c r="K9">
-        <v>5.68</v>
+        <v>2.42</v>
       </c>
       <c r="L9">
-        <v>-10.38</v>
+        <v>-12.24</v>
       </c>
       <c r="M9">
-        <v>7.98</v>
+        <v>7.33</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="P9">
-        <v>11385.2</v>
+        <v>11330.2</v>
       </c>
       <c r="Q9">
-        <v>11587</v>
+        <v>11543.85</v>
       </c>
       <c r="R9">
-        <v>11700.44</v>
+        <v>11697.22</v>
       </c>
       <c r="S9">
-        <v>11766.42</v>
+        <v>11763.96</v>
       </c>
       <c r="T9">
-        <v>-3.05</v>
+        <v>-5.01</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1820,43 +1819,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>41.85</v>
+        <v>35.03</v>
       </c>
       <c r="Z9">
-        <v>-102.58</v>
+        <v>-120.64</v>
       </c>
       <c r="AA9">
-        <v>-72.20999999999999</v>
+        <v>-81.89</v>
       </c>
       <c r="AB9">
-        <v>-30.37</v>
+        <v>-38.74</v>
       </c>
       <c r="AC9">
-        <v>16.63</v>
+        <v>14.76</v>
       </c>
       <c r="AD9">
-        <v>10.54</v>
+        <v>11.92</v>
       </c>
       <c r="AE9">
-        <v>186.36</v>
+        <v>189.69</v>
       </c>
       <c r="AF9">
-        <v>21.55</v>
+        <v>-8.44</v>
       </c>
       <c r="AG9">
-        <v>11954.03</v>
+        <v>11889.95</v>
       </c>
       <c r="AH9">
-        <v>11219.97</v>
+        <v>11197.75</v>
       </c>
       <c r="AI9">
-        <v>11857.5</v>
+        <v>11841.57</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>29.14</v>
+        <v>31.57</v>
       </c>
     </row>
   </sheetData>
@@ -1997,7 +1996,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2056,68 +2055,68 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>63</v>
       </c>
+      <c r="E4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="A5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>72</v>
+      <c r="D6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2129,1138 +2128,1104 @@
         <v>0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="7">
         <v>-3.94</v>
       </c>
-      <c r="E10" s="7">
-        <v>1.4</v>
+      <c r="D10" s="7">
+        <v>-1.18</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.76</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-18.82</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="7">
         <v>-16.27</v>
       </c>
-      <c r="E11" s="7">
-        <v>2.55</v>
+      <c r="D11" s="7">
+        <v>-15.98</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>2.67</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="7">
         <v>3.17</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.5</v>
+      <c r="D12" s="7">
+        <v>-0.62</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-3.79</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-2.88</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="7">
         <v>-1.56</v>
       </c>
-      <c r="E13" s="7">
-        <v>1.32</v>
+      <c r="D13" s="7">
+        <v>-5.06</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
-        <v>13.12</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="7">
         <v>18.92</v>
       </c>
-      <c r="E14" s="7">
-        <v>5.8</v>
+      <c r="D14" s="7">
+        <v>22.55</v>
+      </c>
+      <c r="E14" s="8">
+        <v>3.63</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="6">
-        <v>-16.67</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="7">
         <v>-16.15</v>
       </c>
-      <c r="E15" s="7">
-        <v>0.52</v>
+      <c r="D15" s="7">
+        <v>-12.79</v>
+      </c>
+      <c r="E15" s="8">
+        <v>3.36</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="6">
-        <v>0.37</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="7">
         <v>0.2</v>
       </c>
-      <c r="E16" s="8">
-        <v>-0.17</v>
+      <c r="D16" s="7">
+        <v>-1.65</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="6">
-        <v>-7.51</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="7">
         <v>-5.52</v>
       </c>
-      <c r="E17" s="7">
-        <v>1.99</v>
+      <c r="D17" s="7">
+        <v>-7.68</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>-1.95</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="7">
         <v>-0.16</v>
       </c>
-      <c r="E18" s="7">
+      <c r="D18" s="7">
+        <v>-1.5</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.91</v>
+      </c>
+      <c r="D19" s="7">
+        <v>2.13</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.97</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-2.04</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-3.01</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-2.54</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-0.93</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>2.32</v>
+      </c>
+      <c r="D22" s="7">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="E22" s="8">
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-3.54</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0.09</v>
+      </c>
+      <c r="E23" s="8">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-1.46</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-1.26</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-1.56</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-2.4</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>47.32</v>
+      </c>
+      <c r="D26" s="7">
+        <v>44.4</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-2.92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-36.43</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-34.64</v>
+      </c>
+      <c r="E27" s="8">
         <v>1.79</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>19.51</v>
+      </c>
+      <c r="D28" s="7">
+        <v>18.73</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>40.23</v>
+      </c>
+      <c r="D29" s="7">
+        <v>35.41</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-4.82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>130.72</v>
+      </c>
+      <c r="D30" s="7">
+        <v>137.44</v>
+      </c>
+      <c r="E30" s="8">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>108.41</v>
+      </c>
+      <c r="D31" s="7">
+        <v>109.62</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-15.06</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-16.86</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-10.38</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-12.24</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>17.7</v>
+      </c>
+      <c r="D34" s="7">
+        <v>14.77</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-2.93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-6.02</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="E19" s="7">
-        <v>6.93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-10.66</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-11.98</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>1.6</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0.97</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>8.91</v>
+      </c>
+      <c r="D36" s="7">
+        <v>6.68</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-1.37</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-2.54</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-4.84</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-6.57</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-3.27</v>
-      </c>
-      <c r="D22" s="6">
-        <v>2.32</v>
-      </c>
-      <c r="E22" s="7">
-        <v>5.59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>4.31</v>
+      </c>
+      <c r="D38" s="7">
+        <v>10.33</v>
+      </c>
+      <c r="E38" s="8">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-0.54</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-3.54</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-1.98</v>
+      </c>
+      <c r="D39" s="7">
+        <v>2.4</v>
+      </c>
+      <c r="E39" s="8">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-0.21</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-1.46</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>3.37</v>
+      </c>
+      <c r="D40" s="7">
+        <v>1.9</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-3.77</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-1.56</v>
-      </c>
-      <c r="E25" s="7">
-        <v>2.21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>5.68</v>
+      </c>
+      <c r="D41" s="7">
+        <v>2.42</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>43.55</v>
-      </c>
-      <c r="D26" s="6">
-        <v>47.32</v>
-      </c>
-      <c r="E26" s="7">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-4.66</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-5.05</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-39.52</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-36.43</v>
-      </c>
-      <c r="E27" s="7">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-43.34</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-43.08</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>18.05</v>
-      </c>
-      <c r="D28" s="6">
-        <v>19.51</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-1.73</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-2.31</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>40.36</v>
-      </c>
-      <c r="D29" s="6">
-        <v>40.23</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-12.06</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-12.5</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>121.41</v>
-      </c>
-      <c r="D30" s="6">
-        <v>130.72</v>
-      </c>
-      <c r="E30" s="7">
-        <v>9.31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-1.12</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>115.82</v>
-      </c>
-      <c r="D31" s="6">
-        <v>108.41</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-7.41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-21.7</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-20.19</v>
+      </c>
+      <c r="E47" s="8">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-13.75</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-15.06</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-25.57</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-26.01</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-12.09</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-10.38</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-12.6</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-14.38</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>12.45</v>
-      </c>
-      <c r="D34" s="6">
-        <v>17.7</v>
-      </c>
-      <c r="E34" s="7">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>404.9</v>
+      </c>
+      <c r="D50" s="7">
+        <v>403.25</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-16.11</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-10.66</v>
-      </c>
-      <c r="E35" s="7">
-        <v>5.45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B51" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7">
+        <v>52.97</v>
+      </c>
+      <c r="D51" s="7">
+        <v>53.21</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>7.2</v>
-      </c>
-      <c r="D36" s="6">
-        <v>8.91</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B52" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7">
+        <v>3322</v>
+      </c>
+      <c r="D52" s="7">
+        <v>3302.4</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-19.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-7.56</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-4.84</v>
-      </c>
-      <c r="E37" s="7">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>1011</v>
+      </c>
+      <c r="D53" s="7">
+        <v>1006</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-3.14</v>
-      </c>
-      <c r="D38" s="6">
-        <v>4.31</v>
-      </c>
-      <c r="E38" s="7">
-        <v>7.45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>15.02</v>
+      </c>
+      <c r="D54" s="7">
+        <v>15.6</v>
+      </c>
+      <c r="E54" s="8">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-4.49</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-1.98</v>
-      </c>
-      <c r="E39" s="7">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>10.9</v>
+      </c>
+      <c r="D55" s="7">
+        <v>11.11</v>
+      </c>
+      <c r="E55" s="8">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>3.07</v>
-      </c>
-      <c r="D40" s="6">
-        <v>3.37</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>4323.8</v>
+      </c>
+      <c r="D56" s="7">
+        <v>4298.7</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-25.1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>3.33</v>
-      </c>
-      <c r="D41" s="6">
-        <v>5.68</v>
-      </c>
-      <c r="E41" s="7">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>11408</v>
+      </c>
+      <c r="D57" s="7">
+        <v>11175</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-233</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-4.66</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>50.53</v>
+      </c>
+      <c r="D58" s="7">
+        <v>49.26</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-46.07</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-43.34</v>
-      </c>
-      <c r="E43" s="7">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>40.87</v>
+      </c>
+      <c r="D59" s="7">
+        <v>42.11</v>
+      </c>
+      <c r="E59" s="8">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-2.09</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-1.73</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="B60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="7">
+        <v>56.66</v>
+      </c>
+      <c r="D60" s="7">
+        <v>54.07</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-2.59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-12.15</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-12.06</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="B61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="7">
+        <v>46.47</v>
+      </c>
+      <c r="D61" s="7">
+        <v>44.92</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-4.67</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-1.12</v>
-      </c>
-      <c r="E46" s="7">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>62.97</v>
+      </c>
+      <c r="D62" s="7">
+        <v>68.25</v>
+      </c>
+      <c r="E62" s="8">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-20.62</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-21.7</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>37.27</v>
+      </c>
+      <c r="D63" s="7">
+        <v>42.33</v>
+      </c>
+      <c r="E63" s="8">
+        <v>5.06</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-25.05</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-25.57</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>45.36</v>
+      </c>
+      <c r="D64" s="7">
+        <v>43.14</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-2.22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-13.61</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-12.6</v>
-      </c>
-      <c r="E49" s="7">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>41.85</v>
+      </c>
+      <c r="D65" s="7">
+        <v>35.03</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-6.82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>402</v>
-      </c>
-      <c r="D50" s="6">
-        <v>404.9</v>
-      </c>
-      <c r="E50" s="7">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="7">
+        <v>-29.99</v>
+      </c>
+      <c r="D66" s="7">
+        <v>-20.84</v>
+      </c>
+      <c r="E66" s="8">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>50.41</v>
-      </c>
-      <c r="D51" s="6">
-        <v>52.97</v>
-      </c>
-      <c r="E51" s="7">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
+      <c r="B67" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="7">
+        <v>29.41</v>
+      </c>
+      <c r="D67" s="7">
+        <v>71.02</v>
+      </c>
+      <c r="E67" s="8">
+        <v>41.61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>3310</v>
-      </c>
-      <c r="D52" s="6">
-        <v>3322</v>
-      </c>
-      <c r="E52" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="7">
+        <v>-28.34</v>
+      </c>
+      <c r="D68" s="7">
+        <v>-7.19</v>
+      </c>
+      <c r="E68" s="8">
+        <v>21.15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>1010</v>
-      </c>
-      <c r="D53" s="6">
-        <v>1011</v>
-      </c>
-      <c r="E53" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="7">
+        <v>-10.51</v>
+      </c>
+      <c r="D69" s="7">
+        <v>-53.66</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-43.15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>14.48</v>
-      </c>
-      <c r="D54" s="6">
-        <v>15.02</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="7">
+        <v>10.11</v>
+      </c>
+      <c r="D70" s="7">
+        <v>41.04</v>
+      </c>
+      <c r="E70" s="8">
+        <v>30.93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>11.05</v>
-      </c>
-      <c r="D55" s="6">
-        <v>10.9</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>-54.35</v>
+      </c>
+      <c r="D71" s="7">
+        <v>13.96</v>
+      </c>
+      <c r="E71" s="8">
+        <v>68.31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>4354.5</v>
-      </c>
-      <c r="D56" s="6">
-        <v>4323.8</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-30.7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>-69.75</v>
+      </c>
+      <c r="D72" s="7">
+        <v>-61.96</v>
+      </c>
+      <c r="E72" s="8">
+        <v>7.79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>11275</v>
-      </c>
-      <c r="D57" s="6">
-        <v>11408</v>
-      </c>
-      <c r="E57" s="7">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" s="6">
-        <v>38</v>
-      </c>
-      <c r="D58" s="6">
-        <v>26</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="6">
-        <v>26</v>
-      </c>
-      <c r="D59" s="6">
-        <v>38</v>
-      </c>
-      <c r="E59" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>48.36</v>
-      </c>
-      <c r="D60" s="6">
-        <v>50.53</v>
-      </c>
-      <c r="E60" s="7">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>24.95</v>
-      </c>
-      <c r="D61" s="6">
-        <v>40.87</v>
-      </c>
-      <c r="E61" s="7">
-        <v>15.92</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>55.45</v>
-      </c>
-      <c r="D62" s="6">
-        <v>56.66</v>
-      </c>
-      <c r="E62" s="7">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>46.13</v>
-      </c>
-      <c r="D63" s="6">
-        <v>46.47</v>
-      </c>
-      <c r="E63" s="7">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>56.76</v>
-      </c>
-      <c r="D64" s="6">
-        <v>62.97</v>
-      </c>
-      <c r="E64" s="7">
-        <v>6.21</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>39.58</v>
-      </c>
-      <c r="D65" s="6">
-        <v>37.27</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-2.31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>48.17</v>
-      </c>
-      <c r="D66" s="6">
-        <v>45.36</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-2.81</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>35.15</v>
-      </c>
-      <c r="D67" s="6">
-        <v>41.85</v>
-      </c>
-      <c r="E67" s="7">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B68" s="5" t="s">
+      <c r="B73" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C68" s="6">
-        <v>-39.29</v>
-      </c>
-      <c r="D68" s="6">
+      <c r="C73" s="7">
+        <v>21.55</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-8.44</v>
+      </c>
+      <c r="E73" s="9">
         <v>-29.99</v>
-      </c>
-      <c r="E68" s="7">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>-48.92</v>
-      </c>
-      <c r="D69" s="6">
-        <v>29.41</v>
-      </c>
-      <c r="E69" s="7">
-        <v>78.33</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>97.76000000000001</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-28.34</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-126.1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>-65.95999999999999</v>
-      </c>
-      <c r="D71" s="6">
-        <v>-10.51</v>
-      </c>
-      <c r="E71" s="7">
-        <v>55.45</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>-44.96</v>
-      </c>
-      <c r="D72" s="6">
-        <v>10.11</v>
-      </c>
-      <c r="E72" s="7">
-        <v>55.07</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-41.22</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-54.35</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-13.13</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-68.08</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-69.75</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>7.88</v>
-      </c>
-      <c r="D75" s="6">
-        <v>21.55</v>
-      </c>
-      <c r="E75" s="7">
-        <v>13.67</v>
       </c>
     </row>
   </sheetData>
@@ -3286,61 +3251,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>56.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>47.7</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>47.4</v>
+      </c>
+      <c r="E2" s="12">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-2.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>2.8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-2.8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="H2" s="12">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
-        <v>60</v>
+      <c r="I2" s="12">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3441,55 +3406,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.3039</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1943</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1732</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1729</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.157</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.07980000000000001</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2459</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.3131</v>
+      <c r="A2" s="15">
+        <v>0.2907</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1954</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.175</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1681</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1359</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0733</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.2443</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.3078</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,55 +175,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.7% → -2.3%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.7%</t>
-  </si>
-  <si>
-    <t>-2.3%</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.5 → 49.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.5</t>
-  </si>
-  <si>
-    <t>49.3</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -275,7 +227,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,13 +261,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -329,7 +274,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,12 +296,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -438,23 +377,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -463,7 +400,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -821,8 +758,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -962,58 +899,58 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>403.25</v>
+        <v>396.95</v>
       </c>
       <c r="D2">
-        <v>-0.41</v>
+        <v>-1.56</v>
       </c>
       <c r="E2">
         <v>424.7</v>
       </c>
       <c r="F2">
-        <v>277.55</v>
+        <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-5.05</v>
+        <v>-6.53</v>
       </c>
       <c r="H2">
-        <v>45.29</v>
+        <v>42.33</v>
       </c>
       <c r="I2">
-        <v>-1.5</v>
+        <v>0.63</v>
       </c>
       <c r="J2">
-        <v>-1.18</v>
+        <v>-2.65</v>
       </c>
       <c r="K2">
-        <v>14.77</v>
+        <v>15.83</v>
       </c>
       <c r="L2">
-        <v>44.4</v>
+        <v>43.02</v>
       </c>
       <c r="M2">
-        <v>29.07</v>
+        <v>28.19</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P2">
-        <v>400.33</v>
+        <v>400.83</v>
       </c>
       <c r="Q2">
-        <v>405.29</v>
+        <v>404.78</v>
       </c>
       <c r="R2">
-        <v>403.9</v>
+        <v>404</v>
       </c>
       <c r="S2">
-        <v>361.09</v>
+        <v>361.43</v>
       </c>
       <c r="T2">
-        <v>11.68</v>
+        <v>9.83</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1028,34 +965,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>49.26</v>
+        <v>44.66</v>
       </c>
       <c r="Z2">
-        <v>-0.07000000000000001</v>
+        <v>-0.65</v>
       </c>
       <c r="AA2">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AB2">
-        <v>-1.07</v>
+        <v>-1.32</v>
       </c>
       <c r="AC2">
-        <v>50.9</v>
+        <v>41.89</v>
       </c>
       <c r="AD2">
-        <v>36.6</v>
+        <v>44.04</v>
       </c>
       <c r="AE2">
-        <v>9.25</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AF2">
-        <v>-20.84</v>
+        <v>16.7</v>
       </c>
       <c r="AG2">
-        <v>416.76</v>
+        <v>416.79</v>
       </c>
       <c r="AH2">
-        <v>393.83</v>
+        <v>392.77</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1064,7 +1001,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>22.8</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1075,10 +1012,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>53.21</v>
+        <v>52.24</v>
       </c>
       <c r="D3">
-        <v>0.45</v>
+        <v>-1.82</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1087,46 +1024,46 @@
         <v>50.41</v>
       </c>
       <c r="G3">
-        <v>-43.08</v>
+        <v>-44.12</v>
       </c>
       <c r="H3">
-        <v>5.55</v>
+        <v>3.63</v>
       </c>
       <c r="I3">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="J3">
-        <v>-15.98</v>
+        <v>-14.42</v>
       </c>
       <c r="K3">
-        <v>-11.98</v>
+        <v>-11.1</v>
       </c>
       <c r="L3">
-        <v>-34.64</v>
+        <v>-36.97</v>
       </c>
       <c r="M3">
-        <v>-24.43</v>
+        <v>-24.61</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P3">
-        <v>51.63</v>
+        <v>51.86</v>
       </c>
       <c r="Q3">
-        <v>54.12</v>
+        <v>53.8</v>
       </c>
       <c r="R3">
-        <v>57.32</v>
+        <v>57.2</v>
       </c>
       <c r="S3">
-        <v>64.59999999999999</v>
+        <v>64.47</v>
       </c>
       <c r="T3">
-        <v>-17.63</v>
+        <v>-18.97</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1141,34 +1078,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>42.11</v>
+        <v>38.59</v>
       </c>
       <c r="Z3">
-        <v>-1.78</v>
+        <v>-1.71</v>
       </c>
       <c r="AA3">
         <v>-1.72</v>
       </c>
       <c r="AB3">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="AC3">
-        <v>66.67</v>
+        <v>93.16</v>
       </c>
       <c r="AD3">
-        <v>33.33</v>
+        <v>64.39</v>
       </c>
       <c r="AE3">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF3">
-        <v>71.02</v>
+        <v>-57.92</v>
       </c>
       <c r="AG3">
-        <v>58.48</v>
+        <v>57.67</v>
       </c>
       <c r="AH3">
-        <v>49.76</v>
+        <v>49.92</v>
       </c>
       <c r="AI3">
         <v>55.66</v>
@@ -1177,7 +1114,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>47.67</v>
+        <v>42.13</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1188,10 +1125,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3302.4</v>
+        <v>3306.8</v>
       </c>
       <c r="D4">
-        <v>-0.59</v>
+        <v>0.13</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1200,46 +1137,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.31</v>
+        <v>-2.18</v>
       </c>
       <c r="H4">
-        <v>30.47</v>
+        <v>30.65</v>
       </c>
       <c r="I4">
-        <v>-2.04</v>
+        <v>0.05</v>
       </c>
       <c r="J4">
-        <v>-0.62</v>
+        <v>-2.18</v>
       </c>
       <c r="K4">
-        <v>6.68</v>
+        <v>7.67</v>
       </c>
       <c r="L4">
-        <v>18.73</v>
+        <v>17.69</v>
       </c>
       <c r="M4">
-        <v>16.81</v>
+        <v>16.51</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P4">
-        <v>3306.86</v>
+        <v>3307.22</v>
       </c>
       <c r="Q4">
-        <v>3293.68</v>
+        <v>3292.91</v>
       </c>
       <c r="R4">
-        <v>3214.39</v>
+        <v>3218.53</v>
       </c>
       <c r="S4">
-        <v>2939.61</v>
+        <v>2942.4</v>
       </c>
       <c r="T4">
-        <v>12.34</v>
+        <v>12.38</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1254,34 +1191,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>54.07</v>
+        <v>54.57</v>
       </c>
       <c r="Z4">
-        <v>28.55</v>
+        <v>26.91</v>
       </c>
       <c r="AA4">
-        <v>32.4</v>
+        <v>31.31</v>
       </c>
       <c r="AB4">
-        <v>-3.85</v>
+        <v>-4.39</v>
       </c>
       <c r="AC4">
-        <v>28.66</v>
+        <v>26.05</v>
       </c>
       <c r="AD4">
-        <v>26.85</v>
+        <v>27.66</v>
       </c>
       <c r="AE4">
-        <v>68.45</v>
+        <v>66.5</v>
       </c>
       <c r="AF4">
-        <v>-7.19</v>
+        <v>-31.38</v>
       </c>
       <c r="AG4">
-        <v>3351.55</v>
+        <v>3349.58</v>
       </c>
       <c r="AH4">
-        <v>3235.82</v>
+        <v>3236.25</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1290,7 +1227,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>19.36</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1301,10 +1238,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D5">
-        <v>-0.49</v>
+        <v>0.3</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1313,46 +1250,46 @@
         <v>738.75</v>
       </c>
       <c r="G5">
-        <v>-12.5</v>
+        <v>-12.24</v>
       </c>
       <c r="H5">
-        <v>36.18</v>
+        <v>36.58</v>
       </c>
       <c r="I5">
-        <v>-0.93</v>
+        <v>-0.53</v>
       </c>
       <c r="J5">
-        <v>-5.06</v>
+        <v>-4.27</v>
       </c>
       <c r="K5">
-        <v>-6.57</v>
+        <v>-2.92</v>
       </c>
       <c r="L5">
-        <v>35.41</v>
+        <v>36.53</v>
       </c>
       <c r="M5">
-        <v>17.5</v>
+        <v>17.88</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P5">
-        <v>1010.22</v>
+        <v>1009.14</v>
       </c>
       <c r="Q5">
-        <v>1034.41</v>
+        <v>1032.4</v>
       </c>
       <c r="R5">
-        <v>997.4400000000001</v>
+        <v>998.49</v>
       </c>
       <c r="S5">
-        <v>966.73</v>
+        <v>967.78</v>
       </c>
       <c r="T5">
-        <v>4.06</v>
+        <v>4.26</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1367,34 +1304,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>44.92</v>
+        <v>46.09</v>
       </c>
       <c r="Z5">
-        <v>0.3</v>
+        <v>-0.65</v>
       </c>
       <c r="AA5">
-        <v>6.49</v>
+        <v>5.06</v>
       </c>
       <c r="AB5">
-        <v>-6.19</v>
+        <v>-5.71</v>
       </c>
       <c r="AC5">
-        <v>1.24</v>
+        <v>3.49</v>
       </c>
       <c r="AD5">
-        <v>0.9</v>
+        <v>1.99</v>
       </c>
       <c r="AE5">
-        <v>22.55</v>
+        <v>22.27</v>
       </c>
       <c r="AF5">
-        <v>-53.66</v>
+        <v>-14.86</v>
       </c>
       <c r="AG5">
-        <v>1073.61</v>
+        <v>1072.53</v>
       </c>
       <c r="AH5">
-        <v>995.21</v>
+        <v>992.28</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1403,7 +1340,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>23.49</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1414,58 +1351,58 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>15.6</v>
+        <v>15.42</v>
       </c>
       <c r="D6">
-        <v>3.86</v>
+        <v>-1.15</v>
       </c>
       <c r="E6">
         <v>15.6</v>
       </c>
       <c r="F6">
-        <v>6.61</v>
+        <v>7.23</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>-1.15</v>
       </c>
       <c r="H6">
-        <v>136.01</v>
+        <v>113.28</v>
       </c>
       <c r="I6">
-        <v>8.859999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="J6">
-        <v>22.55</v>
+        <v>19.35</v>
       </c>
       <c r="K6">
-        <v>10.33</v>
+        <v>11.1</v>
       </c>
       <c r="L6">
-        <v>137.44</v>
+        <v>133.28</v>
       </c>
       <c r="M6">
-        <v>13.59</v>
+        <v>13.88</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P6">
-        <v>14.74</v>
+        <v>15.01</v>
       </c>
       <c r="Q6">
-        <v>14.29</v>
+        <v>14.42</v>
       </c>
       <c r="R6">
-        <v>13.83</v>
+        <v>13.85</v>
       </c>
       <c r="S6">
-        <v>11.92</v>
+        <v>11.95</v>
       </c>
       <c r="T6">
-        <v>30.85</v>
+        <v>29.06</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1480,43 +1417,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>68.25</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="Z6">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="AA6">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="AB6">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AC6">
-        <v>52.89</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="AD6">
-        <v>35.75</v>
+        <v>51.7</v>
       </c>
       <c r="AE6">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="AF6">
-        <v>41.04</v>
+        <v>-31.02</v>
       </c>
       <c r="AG6">
-        <v>15.61</v>
+        <v>15.66</v>
       </c>
       <c r="AH6">
-        <v>12.97</v>
+        <v>13.18</v>
       </c>
       <c r="AI6">
-        <v>13.86</v>
+        <v>13.98</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>37.14</v>
+        <v>38.21</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1527,10 +1464,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.11</v>
+        <v>11.33</v>
       </c>
       <c r="D7">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1539,46 +1476,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-20.19</v>
+        <v>-18.61</v>
       </c>
       <c r="H7">
-        <v>136.89</v>
+        <v>141.58</v>
       </c>
       <c r="I7">
-        <v>0.09</v>
+        <v>2.07</v>
       </c>
       <c r="J7">
-        <v>-12.79</v>
+        <v>-10.08</v>
       </c>
       <c r="K7">
-        <v>2.4</v>
+        <v>4.23</v>
       </c>
       <c r="L7">
-        <v>109.62</v>
+        <v>113.37</v>
       </c>
       <c r="M7">
-        <v>-30.78</v>
+        <v>-30.55</v>
       </c>
       <c r="N7">
         <v>87</v>
       </c>
       <c r="O7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P7">
-        <v>11.09</v>
+        <v>11.13</v>
       </c>
       <c r="Q7">
-        <v>11.47</v>
+        <v>11.41</v>
       </c>
       <c r="R7">
-        <v>11.54</v>
+        <v>11.53</v>
       </c>
       <c r="S7">
-        <v>10.35</v>
+        <v>10.38</v>
       </c>
       <c r="T7">
-        <v>7.31</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1593,34 +1530,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>42.33</v>
+        <v>47.14</v>
       </c>
       <c r="Z7">
-        <v>-0.23</v>
+        <v>-0.2</v>
       </c>
       <c r="AA7">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="AB7">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="AC7">
-        <v>23.18</v>
+        <v>51.97</v>
       </c>
       <c r="AD7">
-        <v>21.98</v>
+        <v>31.6</v>
       </c>
       <c r="AE7">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AF7">
-        <v>13.96</v>
+        <v>-40.3</v>
       </c>
       <c r="AG7">
-        <v>12.27</v>
+        <v>12.1</v>
       </c>
       <c r="AH7">
-        <v>10.66</v>
+        <v>10.73</v>
       </c>
       <c r="AI7">
         <v>11.75</v>
@@ -1629,7 +1566,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>32.21</v>
+        <v>28.17</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1640,10 +1577,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4298.7</v>
+        <v>4261.7</v>
       </c>
       <c r="D8">
-        <v>-0.58</v>
+        <v>-0.86</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1652,46 +1589,46 @@
         <v>4155.1</v>
       </c>
       <c r="G8">
-        <v>-26.01</v>
+        <v>-26.64</v>
       </c>
       <c r="H8">
-        <v>3.46</v>
+        <v>2.57</v>
       </c>
       <c r="I8">
-        <v>-1.26</v>
+        <v>-2.1</v>
       </c>
       <c r="J8">
-        <v>-1.65</v>
+        <v>-2.35</v>
       </c>
       <c r="K8">
-        <v>1.9</v>
+        <v>0.31</v>
       </c>
       <c r="L8">
-        <v>-16.86</v>
+        <v>-16.56</v>
       </c>
       <c r="M8">
-        <v>19.54</v>
+        <v>18.92</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="P8">
-        <v>4331.04</v>
+        <v>4312.74</v>
       </c>
       <c r="Q8">
-        <v>4383.46</v>
+        <v>4377.03</v>
       </c>
       <c r="R8">
-        <v>4370.64</v>
+        <v>4368.89</v>
       </c>
       <c r="S8">
-        <v>4624.24</v>
+        <v>4619.02</v>
       </c>
       <c r="T8">
-        <v>-7.04</v>
+        <v>-7.74</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1706,34 +1643,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>43.14</v>
+        <v>40.04</v>
       </c>
       <c r="Z8">
-        <v>-13.39</v>
+        <v>-19.46</v>
       </c>
       <c r="AA8">
-        <v>-4.38</v>
+        <v>-7.4</v>
       </c>
       <c r="AB8">
-        <v>-9.01</v>
+        <v>-12.06</v>
       </c>
       <c r="AC8">
-        <v>16.59</v>
+        <v>8.6</v>
       </c>
       <c r="AD8">
-        <v>18.1</v>
+        <v>14.77</v>
       </c>
       <c r="AE8">
-        <v>87.61</v>
+        <v>89.84</v>
       </c>
       <c r="AF8">
-        <v>-61.96</v>
+        <v>-53.26</v>
       </c>
       <c r="AG8">
-        <v>4536</v>
+        <v>4538.91</v>
       </c>
       <c r="AH8">
-        <v>4230.93</v>
+        <v>4215.16</v>
       </c>
       <c r="AI8">
         <v>4558.89</v>
@@ -1742,7 +1679,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>17.92</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1753,10 +1690,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11175</v>
+        <v>11009</v>
       </c>
       <c r="D9">
-        <v>-2.04</v>
+        <v>-1.49</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1765,46 +1702,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-14.38</v>
+        <v>-15.65</v>
       </c>
       <c r="H9">
-        <v>7.85</v>
+        <v>6.24</v>
       </c>
       <c r="I9">
-        <v>-2.4</v>
+        <v>-3.43</v>
       </c>
       <c r="J9">
-        <v>-7.68</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="K9">
-        <v>2.42</v>
+        <v>1.32</v>
       </c>
       <c r="L9">
-        <v>-12.24</v>
+        <v>-12.98</v>
       </c>
       <c r="M9">
-        <v>7.33</v>
+        <v>7.09</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P9">
-        <v>11330.2</v>
+        <v>11252</v>
       </c>
       <c r="Q9">
-        <v>11543.85</v>
+        <v>11505.3</v>
       </c>
       <c r="R9">
-        <v>11697.22</v>
+        <v>11692.34</v>
       </c>
       <c r="S9">
-        <v>11763.96</v>
+        <v>11760.24</v>
       </c>
       <c r="T9">
-        <v>-5.01</v>
+        <v>-6.39</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1819,43 +1756,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>35.03</v>
+        <v>31.13</v>
       </c>
       <c r="Z9">
-        <v>-120.64</v>
+        <v>-146.66</v>
       </c>
       <c r="AA9">
-        <v>-81.89</v>
+        <v>-94.84999999999999</v>
       </c>
       <c r="AB9">
-        <v>-38.74</v>
+        <v>-51.81</v>
       </c>
       <c r="AC9">
         <v>14.76</v>
       </c>
       <c r="AD9">
-        <v>11.92</v>
+        <v>15.39</v>
       </c>
       <c r="AE9">
-        <v>189.69</v>
+        <v>191.86</v>
       </c>
       <c r="AF9">
-        <v>-8.44</v>
+        <v>42.97</v>
       </c>
       <c r="AG9">
-        <v>11889.95</v>
+        <v>11907.81</v>
       </c>
       <c r="AH9">
-        <v>11197.75</v>
+        <v>11102.79</v>
       </c>
       <c r="AI9">
-        <v>11841.57</v>
+        <v>11680.57</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>31.57</v>
+        <v>35.39</v>
       </c>
     </row>
   </sheetData>
@@ -1996,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2016,1222 +1953,1127 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>47</v>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-1.18</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-2.65</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-15.98</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-14.42</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.56</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-0.62</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-2.18</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-5.06</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-4.27</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>22.55</v>
+      </c>
+      <c r="D11" s="5">
+        <v>19.35</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-12.79</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-10.08</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-1.65</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-2.35</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-7.68</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-1.5</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0.63</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2.13</v>
+      </c>
+      <c r="D16" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-2.04</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-0.93</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.53</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="D19" s="5">
+        <v>9.67</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="D20" s="5">
+        <v>2.07</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-1.26</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-2.1</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-2.4</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-3.43</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>44.4</v>
+      </c>
+      <c r="D23" s="5">
+        <v>43.02</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-34.64</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-36.97</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>18.73</v>
+      </c>
+      <c r="D25" s="5">
+        <v>17.69</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>35.41</v>
+      </c>
+      <c r="D26" s="5">
+        <v>36.53</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>137.44</v>
+      </c>
+      <c r="D27" s="5">
+        <v>133.28</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-4.16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>109.62</v>
+      </c>
+      <c r="D28" s="5">
+        <v>113.37</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-16.86</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-16.56</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-12.24</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-12.98</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>14.77</v>
+      </c>
+      <c r="D31" s="5">
+        <v>15.83</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-11.98</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-11.1</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>6.68</v>
+      </c>
+      <c r="D33" s="5">
+        <v>7.67</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-6.57</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-2.92</v>
+      </c>
+      <c r="E34" s="7">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>10.33</v>
+      </c>
+      <c r="D35" s="5">
+        <v>11.1</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2.4</v>
+      </c>
+      <c r="D36" s="5">
+        <v>4.23</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>1.9</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0.31</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>2.42</v>
+      </c>
+      <c r="D38" s="5">
+        <v>1.32</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-5.05</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-6.53</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-43.08</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-44.12</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-2.31</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-2.18</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-12.5</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-12.24</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="D43" s="5">
+        <v>-1.15</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-20.19</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-18.61</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-26.01</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-26.64</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-14.38</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-15.65</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-3.94</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-1.18</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>403.25</v>
+      </c>
+      <c r="D47" s="5">
+        <v>396.95</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-6.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-16.27</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-15.98</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>53.21</v>
+      </c>
+      <c r="D48" s="5">
+        <v>52.24</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>3.17</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-0.62</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-3.79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>3302.4</v>
+      </c>
+      <c r="D49" s="5">
+        <v>3306.8</v>
+      </c>
+      <c r="E49" s="7">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-1.56</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-5.06</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-3.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>1006</v>
+      </c>
+      <c r="D50" s="5">
+        <v>1009</v>
+      </c>
+      <c r="E50" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>18.92</v>
-      </c>
-      <c r="D14" s="7">
-        <v>22.55</v>
-      </c>
-      <c r="E14" s="8">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>15.6</v>
+      </c>
+      <c r="D51" s="5">
+        <v>15.42</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-16.15</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-12.79</v>
-      </c>
-      <c r="E15" s="8">
-        <v>3.36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>11.11</v>
+      </c>
+      <c r="D52" s="5">
+        <v>11.33</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-1.65</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>4298.7</v>
+      </c>
+      <c r="D53" s="5">
+        <v>4261.7</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-5.52</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-7.68</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>11175</v>
+      </c>
+      <c r="D54" s="5">
+        <v>11009</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-166</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-0.16</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-1.5</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>49.26</v>
+      </c>
+      <c r="D55" s="5">
+        <v>44.66</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-4.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>0.91</v>
-      </c>
-      <c r="D19" s="7">
-        <v>2.13</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>42.11</v>
+      </c>
+      <c r="D56" s="5">
+        <v>38.59</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-3.52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-2.04</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-3.01</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>54.07</v>
+      </c>
+      <c r="D57" s="5">
+        <v>54.57</v>
+      </c>
+      <c r="E57" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-2.54</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-0.93</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>44.92</v>
+      </c>
+      <c r="D58" s="5">
+        <v>46.09</v>
+      </c>
+      <c r="E58" s="7">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>2.32</v>
-      </c>
-      <c r="D22" s="7">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="E22" s="8">
-        <v>6.54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>68.25</v>
+      </c>
+      <c r="D59" s="5">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-3.54</v>
-      </c>
-      <c r="D23" s="7">
-        <v>0.09</v>
-      </c>
-      <c r="E23" s="8">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="5">
+        <v>42.33</v>
+      </c>
+      <c r="D60" s="5">
+        <v>47.14</v>
+      </c>
+      <c r="E60" s="7">
+        <v>4.81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-1.46</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-1.26</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>43.14</v>
+      </c>
+      <c r="D61" s="5">
+        <v>40.04</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-1.56</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-2.4</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>35.03</v>
+      </c>
+      <c r="D62" s="5">
+        <v>31.13</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>47.32</v>
-      </c>
-      <c r="D26" s="7">
-        <v>44.4</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-2.92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-20.84</v>
+      </c>
+      <c r="D63" s="5">
+        <v>16.7</v>
+      </c>
+      <c r="E63" s="7">
+        <v>37.54</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-36.43</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-34.64</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>71.02</v>
+      </c>
+      <c r="D64" s="5">
+        <v>-57.92</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-128.94</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>19.51</v>
-      </c>
-      <c r="D28" s="7">
-        <v>18.73</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>-7.19</v>
+      </c>
+      <c r="D65" s="5">
+        <v>-31.38</v>
+      </c>
+      <c r="E65" s="6">
+        <v>-24.19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>40.23</v>
-      </c>
-      <c r="D29" s="7">
-        <v>35.41</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-4.82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5">
+        <v>-53.66</v>
+      </c>
+      <c r="D66" s="5">
+        <v>-14.86</v>
+      </c>
+      <c r="E66" s="7">
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>130.72</v>
-      </c>
-      <c r="D30" s="7">
-        <v>137.44</v>
-      </c>
-      <c r="E30" s="8">
-        <v>6.72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="5">
+        <v>41.04</v>
+      </c>
+      <c r="D67" s="5">
+        <v>-31.02</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-72.06</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>108.41</v>
-      </c>
-      <c r="D31" s="7">
-        <v>109.62</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="5">
+        <v>13.96</v>
+      </c>
+      <c r="D68" s="5">
+        <v>-40.3</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-54.26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-15.06</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-16.86</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="5">
+        <v>-61.96</v>
+      </c>
+      <c r="D69" s="5">
+        <v>-53.26</v>
+      </c>
+      <c r="E69" s="7">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-10.38</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-12.24</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>17.7</v>
-      </c>
-      <c r="D34" s="7">
-        <v>14.77</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-2.93</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-10.66</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-11.98</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>8.91</v>
-      </c>
-      <c r="D36" s="7">
-        <v>6.68</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-4.84</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-6.57</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>4.31</v>
-      </c>
-      <c r="D38" s="7">
-        <v>10.33</v>
-      </c>
-      <c r="E38" s="8">
-        <v>6.02</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-1.98</v>
-      </c>
-      <c r="D39" s="7">
-        <v>2.4</v>
-      </c>
-      <c r="E39" s="8">
-        <v>4.38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>3.37</v>
-      </c>
-      <c r="D40" s="7">
-        <v>1.9</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>5.68</v>
-      </c>
-      <c r="D41" s="7">
-        <v>2.42</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-4.66</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-5.05</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-43.34</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-43.08</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-1.73</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-2.31</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-12.06</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-12.5</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-1.12</v>
-      </c>
-      <c r="D46" s="7">
-        <v>0</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-21.7</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-20.19</v>
-      </c>
-      <c r="E47" s="8">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-25.57</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-26.01</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-12.6</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-14.38</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>404.9</v>
-      </c>
-      <c r="D50" s="7">
-        <v>403.25</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="7">
-        <v>52.97</v>
-      </c>
-      <c r="D51" s="7">
-        <v>53.21</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="7">
-        <v>3322</v>
-      </c>
-      <c r="D52" s="7">
-        <v>3302.4</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-19.6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>1011</v>
-      </c>
-      <c r="D53" s="7">
-        <v>1006</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>15.02</v>
-      </c>
-      <c r="D54" s="7">
-        <v>15.6</v>
-      </c>
-      <c r="E54" s="8">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>10.9</v>
-      </c>
-      <c r="D55" s="7">
-        <v>11.11</v>
-      </c>
-      <c r="E55" s="8">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>4323.8</v>
-      </c>
-      <c r="D56" s="7">
-        <v>4298.7</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-25.1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>11408</v>
-      </c>
-      <c r="D57" s="7">
-        <v>11175</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-233</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>50.53</v>
-      </c>
-      <c r="D58" s="7">
-        <v>49.26</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>40.87</v>
-      </c>
-      <c r="D59" s="7">
-        <v>42.11</v>
-      </c>
-      <c r="E59" s="8">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="7">
-        <v>56.66</v>
-      </c>
-      <c r="D60" s="7">
-        <v>54.07</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-2.59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="7">
-        <v>46.47</v>
-      </c>
-      <c r="D61" s="7">
-        <v>44.92</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="7">
-        <v>62.97</v>
-      </c>
-      <c r="D62" s="7">
-        <v>68.25</v>
-      </c>
-      <c r="E62" s="8">
-        <v>5.28</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="7">
-        <v>37.27</v>
-      </c>
-      <c r="D63" s="7">
-        <v>42.33</v>
-      </c>
-      <c r="E63" s="8">
-        <v>5.06</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>45.36</v>
-      </c>
-      <c r="D64" s="7">
-        <v>43.14</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>41.85</v>
-      </c>
-      <c r="D65" s="7">
-        <v>35.03</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-6.82</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="6" t="s">
+      <c r="B70" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C66" s="7">
-        <v>-29.99</v>
-      </c>
-      <c r="D66" s="7">
-        <v>-20.84</v>
-      </c>
-      <c r="E66" s="8">
-        <v>9.15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="7">
-        <v>29.41</v>
-      </c>
-      <c r="D67" s="7">
-        <v>71.02</v>
-      </c>
-      <c r="E67" s="8">
-        <v>41.61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="7">
-        <v>-28.34</v>
-      </c>
-      <c r="D68" s="7">
-        <v>-7.19</v>
-      </c>
-      <c r="E68" s="8">
-        <v>21.15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="7">
-        <v>-10.51</v>
-      </c>
-      <c r="D69" s="7">
-        <v>-53.66</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-43.15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="7">
-        <v>10.11</v>
-      </c>
-      <c r="D70" s="7">
-        <v>41.04</v>
-      </c>
-      <c r="E70" s="8">
-        <v>30.93</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="7">
-        <v>-54.35</v>
-      </c>
-      <c r="D71" s="7">
-        <v>13.96</v>
-      </c>
-      <c r="E71" s="8">
-        <v>68.31</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="7">
-        <v>-69.75</v>
-      </c>
-      <c r="D72" s="7">
-        <v>-61.96</v>
-      </c>
-      <c r="E72" s="8">
-        <v>7.79</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="7">
-        <v>21.55</v>
-      </c>
-      <c r="D73" s="7">
+      <c r="C70" s="5">
         <v>-8.44</v>
       </c>
-      <c r="E73" s="9">
-        <v>-29.99</v>
+      <c r="D70" s="5">
+        <v>42.97</v>
+      </c>
+      <c r="E70" s="7">
+        <v>51.41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3251,60 +3093,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>80</v>
+      <c r="B1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>56.44</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="12">
-        <v>47.4</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>45.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
-        <v>-2.8</v>
-      </c>
-      <c r="G2" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>-3.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="H2" s="10">
         <v>56.1</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>50</v>
       </c>
     </row>
@@ -3406,55 +3248,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="15">
-        <v>0.2907</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1954</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.175</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1681</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1359</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0733</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.2443</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.3078</v>
+      <c r="A2" s="13">
+        <v>0.2819</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1892</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1788</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1651</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1388</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0709</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2461</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.3055</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,7 +175,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>46.1 → 52.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>46.1</t>
+  </si>
+  <si>
+    <t>52.5</t>
+  </si>
+  <si>
+    <t>47.1 → 51.5</t>
+  </si>
+  <si>
+    <t>47.1</t>
+  </si>
+  <si>
+    <t>51.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -261,14 +297,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -301,13 +337,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,14 +413,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -758,8 +795,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -899,10 +937,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>396.95</v>
+        <v>400</v>
       </c>
       <c r="D2">
-        <v>-1.56</v>
+        <v>0.77</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -911,46 +949,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-6.53</v>
+        <v>-5.82</v>
       </c>
       <c r="H2">
-        <v>42.33</v>
+        <v>43.42</v>
       </c>
       <c r="I2">
-        <v>0.63</v>
+        <v>0.74</v>
       </c>
       <c r="J2">
-        <v>-2.65</v>
+        <v>-1.76</v>
       </c>
       <c r="K2">
-        <v>15.83</v>
+        <v>18.84</v>
       </c>
       <c r="L2">
-        <v>43.02</v>
+        <v>42.3</v>
       </c>
       <c r="M2">
-        <v>28.19</v>
+        <v>28.47</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P2">
-        <v>400.83</v>
+        <v>401.42</v>
       </c>
       <c r="Q2">
-        <v>404.78</v>
+        <v>404.24</v>
       </c>
       <c r="R2">
-        <v>404</v>
+        <v>404.14</v>
       </c>
       <c r="S2">
-        <v>361.43</v>
+        <v>361.8</v>
       </c>
       <c r="T2">
-        <v>9.83</v>
+        <v>10.56</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -965,34 +1003,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>44.66</v>
+        <v>47.23</v>
       </c>
       <c r="Z2">
-        <v>-0.65</v>
+        <v>-0.85</v>
       </c>
       <c r="AA2">
-        <v>0.67</v>
+        <v>0.37</v>
       </c>
       <c r="AB2">
-        <v>-1.32</v>
+        <v>-1.21</v>
       </c>
       <c r="AC2">
-        <v>41.89</v>
+        <v>33.85</v>
       </c>
       <c r="AD2">
-        <v>44.04</v>
+        <v>42.21</v>
       </c>
       <c r="AE2">
-        <v>9.220000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="AF2">
-        <v>16.7</v>
+        <v>-29.68</v>
       </c>
       <c r="AG2">
-        <v>416.79</v>
+        <v>416.06</v>
       </c>
       <c r="AH2">
-        <v>392.77</v>
+        <v>392.41</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1001,7 +1039,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>23.23</v>
+        <v>22.98</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1012,10 +1050,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>52.24</v>
+        <v>51.33</v>
       </c>
       <c r="D3">
-        <v>-1.82</v>
+        <v>-1.74</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1024,25 +1062,25 @@
         <v>50.41</v>
       </c>
       <c r="G3">
-        <v>-44.12</v>
+        <v>-45.09</v>
       </c>
       <c r="H3">
-        <v>3.63</v>
+        <v>1.83</v>
       </c>
       <c r="I3">
-        <v>2.23</v>
+        <v>1.7</v>
       </c>
       <c r="J3">
-        <v>-14.42</v>
+        <v>-12.45</v>
       </c>
       <c r="K3">
-        <v>-11.1</v>
+        <v>-11.86</v>
       </c>
       <c r="L3">
-        <v>-36.97</v>
+        <v>-40.26</v>
       </c>
       <c r="M3">
-        <v>-24.61</v>
+        <v>-24.87</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1051,19 +1089,19 @@
         <v>8</v>
       </c>
       <c r="P3">
-        <v>51.86</v>
+        <v>52.03</v>
       </c>
       <c r="Q3">
-        <v>53.8</v>
+        <v>53.51</v>
       </c>
       <c r="R3">
-        <v>57.2</v>
+        <v>57.05</v>
       </c>
       <c r="S3">
-        <v>64.47</v>
+        <v>64.34</v>
       </c>
       <c r="T3">
-        <v>-18.97</v>
+        <v>-20.23</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1078,34 +1116,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.59</v>
+        <v>35.58</v>
       </c>
       <c r="Z3">
-        <v>-1.71</v>
+        <v>-1.7</v>
       </c>
       <c r="AA3">
         <v>-1.72</v>
       </c>
       <c r="AB3">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AC3">
-        <v>93.16</v>
+        <v>80.48</v>
       </c>
       <c r="AD3">
-        <v>64.39</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AE3">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AF3">
-        <v>-57.92</v>
+        <v>-55.8</v>
       </c>
       <c r="AG3">
-        <v>57.67</v>
+        <v>57.19</v>
       </c>
       <c r="AH3">
-        <v>49.92</v>
+        <v>49.82</v>
       </c>
       <c r="AI3">
         <v>55.66</v>
@@ -1114,7 +1152,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>42.13</v>
+        <v>36.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1125,10 +1163,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3306.8</v>
+        <v>3300</v>
       </c>
       <c r="D4">
-        <v>0.13</v>
+        <v>-0.21</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1137,25 +1175,25 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.18</v>
+        <v>-2.38</v>
       </c>
       <c r="H4">
-        <v>30.65</v>
+        <v>30.38</v>
       </c>
       <c r="I4">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="J4">
-        <v>-2.18</v>
+        <v>-0.67</v>
       </c>
       <c r="K4">
-        <v>7.67</v>
+        <v>6.81</v>
       </c>
       <c r="L4">
         <v>17.69</v>
       </c>
       <c r="M4">
-        <v>16.51</v>
+        <v>16.15</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1164,19 +1202,19 @@
         <v>67</v>
       </c>
       <c r="P4">
-        <v>3307.22</v>
+        <v>3308.24</v>
       </c>
       <c r="Q4">
-        <v>3292.91</v>
+        <v>3292.52</v>
       </c>
       <c r="R4">
-        <v>3218.53</v>
+        <v>3221.72</v>
       </c>
       <c r="S4">
-        <v>2942.4</v>
+        <v>2945.23</v>
       </c>
       <c r="T4">
-        <v>12.38</v>
+        <v>12.05</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1191,34 +1229,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>54.57</v>
+        <v>53.59</v>
       </c>
       <c r="Z4">
-        <v>26.91</v>
+        <v>24.78</v>
       </c>
       <c r="AA4">
-        <v>31.31</v>
+        <v>30</v>
       </c>
       <c r="AB4">
-        <v>-4.39</v>
+        <v>-5.22</v>
       </c>
       <c r="AC4">
-        <v>26.05</v>
+        <v>16.89</v>
       </c>
       <c r="AD4">
-        <v>27.66</v>
+        <v>23.87</v>
       </c>
       <c r="AE4">
-        <v>66.5</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AF4">
-        <v>-31.38</v>
+        <v>-28.82</v>
       </c>
       <c r="AG4">
-        <v>3349.58</v>
+        <v>3348.86</v>
       </c>
       <c r="AH4">
-        <v>3236.25</v>
+        <v>3236.19</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1227,7 +1265,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>17.36</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1238,10 +1276,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1009</v>
+        <v>1026.9</v>
       </c>
       <c r="D5">
-        <v>0.3</v>
+        <v>1.77</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1250,46 +1288,46 @@
         <v>738.75</v>
       </c>
       <c r="G5">
-        <v>-12.24</v>
+        <v>-10.68</v>
       </c>
       <c r="H5">
-        <v>36.58</v>
+        <v>39.01</v>
       </c>
       <c r="I5">
-        <v>-0.53</v>
+        <v>1.7</v>
       </c>
       <c r="J5">
-        <v>-4.27</v>
+        <v>-2.12</v>
       </c>
       <c r="K5">
-        <v>-2.92</v>
+        <v>0.25</v>
       </c>
       <c r="L5">
-        <v>36.53</v>
+        <v>38.06</v>
       </c>
       <c r="M5">
-        <v>17.88</v>
+        <v>17.92</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P5">
-        <v>1009.14</v>
+        <v>1012.58</v>
       </c>
       <c r="Q5">
-        <v>1032.4</v>
+        <v>1029.82</v>
       </c>
       <c r="R5">
-        <v>998.49</v>
+        <v>1000.23</v>
       </c>
       <c r="S5">
-        <v>967.78</v>
+        <v>969.02</v>
       </c>
       <c r="T5">
-        <v>4.26</v>
+        <v>5.97</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1304,34 +1342,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>46.09</v>
+        <v>52.53</v>
       </c>
       <c r="Z5">
-        <v>-0.65</v>
+        <v>0.03</v>
       </c>
       <c r="AA5">
-        <v>5.06</v>
+        <v>4.05</v>
       </c>
       <c r="AB5">
-        <v>-5.71</v>
+        <v>-4.02</v>
       </c>
       <c r="AC5">
-        <v>3.49</v>
+        <v>18.65</v>
       </c>
       <c r="AD5">
-        <v>1.99</v>
+        <v>7.79</v>
       </c>
       <c r="AE5">
-        <v>22.27</v>
+        <v>22.35</v>
       </c>
       <c r="AF5">
-        <v>-14.86</v>
+        <v>-5.52</v>
       </c>
       <c r="AG5">
-        <v>1072.53</v>
+        <v>1063.6</v>
       </c>
       <c r="AH5">
-        <v>992.28</v>
+        <v>996.04</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1340,7 +1378,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>20.9</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1351,58 +1389,58 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>15.42</v>
+        <v>15.52</v>
       </c>
       <c r="D6">
-        <v>-1.15</v>
+        <v>0.65</v>
       </c>
       <c r="E6">
         <v>15.6</v>
       </c>
       <c r="F6">
-        <v>7.23</v>
+        <v>7.27</v>
       </c>
       <c r="G6">
-        <v>-1.15</v>
+        <v>-0.51</v>
       </c>
       <c r="H6">
-        <v>113.28</v>
+        <v>113.48</v>
       </c>
       <c r="I6">
-        <v>9.67</v>
+        <v>6.81</v>
       </c>
       <c r="J6">
-        <v>19.35</v>
+        <v>20.4</v>
       </c>
       <c r="K6">
-        <v>11.1</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="L6">
-        <v>133.28</v>
+        <v>114.66</v>
       </c>
       <c r="M6">
-        <v>13.88</v>
+        <v>13.07</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P6">
-        <v>15.01</v>
+        <v>15.21</v>
       </c>
       <c r="Q6">
-        <v>14.42</v>
+        <v>14.52</v>
       </c>
       <c r="R6">
-        <v>13.85</v>
+        <v>13.87</v>
       </c>
       <c r="S6">
-        <v>11.95</v>
+        <v>11.98</v>
       </c>
       <c r="T6">
-        <v>29.06</v>
+        <v>29.6</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1417,43 +1455,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>65.15000000000001</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="Z6">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="AA6">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="AB6">
         <v>0.1</v>
       </c>
       <c r="AC6">
-        <v>65.98999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="AD6">
-        <v>51.7</v>
+        <v>63.24</v>
       </c>
       <c r="AE6">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="AF6">
-        <v>-31.02</v>
+        <v>5.02</v>
       </c>
       <c r="AG6">
-        <v>15.66</v>
+        <v>15.77</v>
       </c>
       <c r="AH6">
-        <v>13.18</v>
+        <v>13.27</v>
       </c>
       <c r="AI6">
-        <v>13.98</v>
+        <v>14.01</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>38.21</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1464,10 +1502,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.33</v>
+        <v>11.55</v>
       </c>
       <c r="D7">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1476,25 +1514,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-18.61</v>
+        <v>-17.03</v>
       </c>
       <c r="H7">
-        <v>141.58</v>
+        <v>146.27</v>
       </c>
       <c r="I7">
-        <v>2.07</v>
+        <v>2.48</v>
       </c>
       <c r="J7">
-        <v>-10.08</v>
+        <v>-6.48</v>
       </c>
       <c r="K7">
-        <v>4.23</v>
+        <v>10.42</v>
       </c>
       <c r="L7">
-        <v>113.37</v>
+        <v>117.51</v>
       </c>
       <c r="M7">
-        <v>-30.55</v>
+        <v>-30.51</v>
       </c>
       <c r="N7">
         <v>87</v>
@@ -1503,19 +1541,19 @@
         <v>92</v>
       </c>
       <c r="P7">
-        <v>11.13</v>
+        <v>11.19</v>
       </c>
       <c r="Q7">
-        <v>11.41</v>
+        <v>11.39</v>
       </c>
       <c r="R7">
-        <v>11.53</v>
+        <v>11.54</v>
       </c>
       <c r="S7">
-        <v>10.38</v>
+        <v>10.42</v>
       </c>
       <c r="T7">
-        <v>9.109999999999999</v>
+        <v>10.89</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1530,34 +1568,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>47.14</v>
+        <v>51.5</v>
       </c>
       <c r="Z7">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AA7">
         <v>-0.18</v>
       </c>
       <c r="AB7">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AC7">
-        <v>51.97</v>
+        <v>85.3</v>
       </c>
       <c r="AD7">
-        <v>31.6</v>
+        <v>53.49</v>
       </c>
       <c r="AE7">
         <v>0.25</v>
       </c>
       <c r="AF7">
-        <v>-40.3</v>
+        <v>19.69</v>
       </c>
       <c r="AG7">
-        <v>12.1</v>
+        <v>11.99</v>
       </c>
       <c r="AH7">
-        <v>10.73</v>
+        <v>10.78</v>
       </c>
       <c r="AI7">
         <v>11.75</v>
@@ -1566,7 +1604,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>28.17</v>
+        <v>27.15</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1577,58 +1615,58 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4261.7</v>
+        <v>4109.8</v>
       </c>
       <c r="D8">
-        <v>-0.86</v>
+        <v>-3.56</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
       </c>
       <c r="F8">
-        <v>4155.1</v>
+        <v>4109.8</v>
       </c>
       <c r="G8">
-        <v>-26.64</v>
+        <v>-29.26</v>
       </c>
       <c r="H8">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-2.1</v>
+        <v>-4.98</v>
       </c>
       <c r="J8">
+        <v>-6.39</v>
+      </c>
+      <c r="K8">
         <v>-2.35</v>
       </c>
-      <c r="K8">
-        <v>0.31</v>
-      </c>
       <c r="L8">
-        <v>-16.56</v>
+        <v>-19.82</v>
       </c>
       <c r="M8">
-        <v>18.92</v>
+        <v>17.48</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="P8">
-        <v>4312.74</v>
+        <v>4269.7</v>
       </c>
       <c r="Q8">
-        <v>4377.03</v>
+        <v>4364.27</v>
       </c>
       <c r="R8">
-        <v>4368.89</v>
+        <v>4363.04</v>
       </c>
       <c r="S8">
-        <v>4619.02</v>
+        <v>4613.21</v>
       </c>
       <c r="T8">
-        <v>-7.74</v>
+        <v>-10.91</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1643,43 +1681,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>40.04</v>
+        <v>30.38</v>
       </c>
       <c r="Z8">
-        <v>-19.46</v>
+        <v>-36.11</v>
       </c>
       <c r="AA8">
-        <v>-7.4</v>
+        <v>-13.14</v>
       </c>
       <c r="AB8">
-        <v>-12.06</v>
+        <v>-22.97</v>
       </c>
       <c r="AC8">
-        <v>8.6</v>
+        <v>0.91</v>
       </c>
       <c r="AD8">
-        <v>14.77</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AE8">
-        <v>89.84</v>
+        <v>103.61</v>
       </c>
       <c r="AF8">
-        <v>-53.26</v>
+        <v>717.89</v>
       </c>
       <c r="AG8">
-        <v>4538.91</v>
+        <v>4565.57</v>
       </c>
       <c r="AH8">
-        <v>4215.16</v>
+        <v>4162.98</v>
       </c>
       <c r="AI8">
-        <v>4558.89</v>
+        <v>4473.44</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>20.36</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1690,10 +1728,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11009</v>
+        <v>10900</v>
       </c>
       <c r="D9">
-        <v>-1.49</v>
+        <v>-0.99</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1702,25 +1740,25 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-15.65</v>
+        <v>-16.49</v>
       </c>
       <c r="H9">
-        <v>6.24</v>
+        <v>5.19</v>
       </c>
       <c r="I9">
-        <v>-3.43</v>
+        <v>-4.33</v>
       </c>
       <c r="J9">
-        <v>-8.550000000000001</v>
+        <v>-7.47</v>
       </c>
       <c r="K9">
-        <v>1.32</v>
+        <v>0.65</v>
       </c>
       <c r="L9">
-        <v>-12.98</v>
+        <v>-13.5</v>
       </c>
       <c r="M9">
-        <v>7.09</v>
+        <v>7.02</v>
       </c>
       <c r="N9">
         <v>38</v>
@@ -1729,19 +1767,19 @@
         <v>39</v>
       </c>
       <c r="P9">
-        <v>11252</v>
+        <v>11153.4</v>
       </c>
       <c r="Q9">
-        <v>11505.3</v>
+        <v>11455.75</v>
       </c>
       <c r="R9">
-        <v>11692.34</v>
+        <v>11681.22</v>
       </c>
       <c r="S9">
-        <v>11760.24</v>
+        <v>11756.1</v>
       </c>
       <c r="T9">
-        <v>-6.39</v>
+        <v>-7.28</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1756,43 +1794,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>31.13</v>
+        <v>28.86</v>
       </c>
       <c r="Z9">
-        <v>-146.66</v>
+        <v>-174.07</v>
       </c>
       <c r="AA9">
-        <v>-94.84999999999999</v>
+        <v>-110.69</v>
       </c>
       <c r="AB9">
-        <v>-51.81</v>
+        <v>-63.38</v>
       </c>
       <c r="AC9">
-        <v>14.76</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>15.39</v>
+        <v>9.84</v>
       </c>
       <c r="AE9">
-        <v>191.86</v>
+        <v>188.8</v>
       </c>
       <c r="AF9">
-        <v>42.97</v>
+        <v>32.25</v>
       </c>
       <c r="AG9">
-        <v>11907.81</v>
+        <v>11900.15</v>
       </c>
       <c r="AH9">
-        <v>11102.79</v>
+        <v>11011.35</v>
       </c>
       <c r="AI9">
-        <v>11680.57</v>
+        <v>11495.39</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>35.39</v>
+        <v>39.62</v>
       </c>
     </row>
   </sheetData>
@@ -1953,1127 +1991,1165 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>56</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-1.18</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-2.65</v>
       </c>
-      <c r="E7" s="6">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-1.76</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-15.98</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-14.42</v>
       </c>
-      <c r="E8" s="7">
+      <c r="D9" s="6">
+        <v>-12.45</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-2.18</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-0.67</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-4.27</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-2.12</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>19.35</v>
+      </c>
+      <c r="D12" s="6">
+        <v>20.4</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-10.08</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-6.48</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-2.35</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-6.39</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-4.04</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-7.47</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.63</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.74</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2.23</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1.7</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-0.53</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1.7</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>9.67</v>
+      </c>
+      <c r="D20" s="6">
+        <v>6.81</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2.07</v>
+      </c>
+      <c r="D21" s="6">
+        <v>2.48</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-2.1</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-4.98</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-2.88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-3.43</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-4.33</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>43.02</v>
+      </c>
+      <c r="D24" s="6">
+        <v>42.3</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-36.97</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-40.26</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-3.29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>36.53</v>
+      </c>
+      <c r="D26" s="6">
+        <v>38.06</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>133.28</v>
+      </c>
+      <c r="D27" s="6">
+        <v>114.66</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-18.62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>113.37</v>
+      </c>
+      <c r="D28" s="6">
+        <v>117.51</v>
+      </c>
+      <c r="E28" s="7">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-16.56</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-19.82</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-12.98</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-13.5</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>15.83</v>
+      </c>
+      <c r="D31" s="6">
+        <v>18.84</v>
+      </c>
+      <c r="E31" s="7">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-11.1</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-11.86</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>7.67</v>
+      </c>
+      <c r="D33" s="6">
+        <v>6.81</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-2.92</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="E34" s="7">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>11.1</v>
+      </c>
+      <c r="D35" s="6">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>4.23</v>
+      </c>
+      <c r="D36" s="6">
+        <v>10.42</v>
+      </c>
+      <c r="E36" s="7">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.31</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-2.35</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>1.32</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0.65</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-6.53</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-5.82</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-44.12</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-45.09</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-2.18</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-2.38</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-12.24</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-10.68</v>
+      </c>
+      <c r="E42" s="7">
         <v>1.56</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-0.62</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-2.18</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-5.06</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-4.27</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>22.55</v>
-      </c>
-      <c r="D11" s="5">
-        <v>19.35</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-1.15</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-0.51</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-12.79</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-10.08</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-1.65</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-2.35</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-7.68</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-8.550000000000001</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-1.5</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>2.13</v>
-      </c>
-      <c r="D16" s="5">
-        <v>2.23</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-2.04</v>
-      </c>
-      <c r="D17" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.09</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-0.93</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.53</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="D19" s="5">
-        <v>9.67</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="D20" s="5">
-        <v>2.07</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-1.26</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-2.1</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-2.4</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-3.43</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>44.4</v>
-      </c>
-      <c r="D23" s="5">
-        <v>43.02</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-34.64</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-36.97</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-2.33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>18.73</v>
-      </c>
-      <c r="D25" s="5">
-        <v>17.69</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>35.41</v>
-      </c>
-      <c r="D26" s="5">
-        <v>36.53</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>137.44</v>
-      </c>
-      <c r="D27" s="5">
-        <v>133.28</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-4.16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>109.62</v>
-      </c>
-      <c r="D28" s="5">
-        <v>113.37</v>
-      </c>
-      <c r="E28" s="7">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-16.86</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-16.56</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-12.24</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-12.98</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>14.77</v>
-      </c>
-      <c r="D31" s="5">
-        <v>15.83</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-11.98</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-11.1</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>6.68</v>
-      </c>
-      <c r="D33" s="5">
-        <v>7.67</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-6.57</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-2.92</v>
-      </c>
-      <c r="E34" s="7">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>10.33</v>
-      </c>
-      <c r="D35" s="5">
-        <v>11.1</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2.4</v>
-      </c>
-      <c r="D36" s="5">
-        <v>4.23</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>1.9</v>
-      </c>
-      <c r="D37" s="5">
-        <v>0.31</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>2.42</v>
-      </c>
-      <c r="D38" s="5">
-        <v>1.32</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="5">
-        <v>-5.05</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-6.53</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-43.08</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-44.12</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-2.31</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-2.18</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-12.5</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-12.24</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>0</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-1.15</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-20.19</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C44" s="6">
         <v>-18.61</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-17.03</v>
       </c>
       <c r="E44" s="7">
         <v>1.58</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C45" s="5">
-        <v>-26.01</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="C45" s="6">
         <v>-26.64</v>
       </c>
-      <c r="E45" s="6">
-        <v>-0.63</v>
+      <c r="D45" s="6">
+        <v>-29.26</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C46" s="5">
-        <v>-14.38</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C46" s="6">
         <v>-15.65</v>
       </c>
-      <c r="E46" s="6">
-        <v>-1.27</v>
+      <c r="D46" s="6">
+        <v>-16.49</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="5">
-        <v>403.25</v>
-      </c>
-      <c r="D47" s="5">
+      <c r="C47" s="6">
         <v>396.95</v>
       </c>
-      <c r="E47" s="6">
-        <v>-6.3</v>
+      <c r="D47" s="6">
+        <v>400</v>
+      </c>
+      <c r="E47" s="7">
+        <v>3.05</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C48" s="5">
-        <v>53.21</v>
-      </c>
-      <c r="D48" s="5">
+      <c r="C48" s="6">
         <v>52.24</v>
       </c>
-      <c r="E48" s="6">
-        <v>-0.97</v>
+      <c r="D48" s="6">
+        <v>51.33</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C49" s="5">
-        <v>3302.4</v>
-      </c>
-      <c r="D49" s="5">
+      <c r="C49" s="6">
         <v>3306.8</v>
       </c>
-      <c r="E49" s="7">
-        <v>4.4</v>
+      <c r="D49" s="6">
+        <v>3300</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-6.8</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="5">
-        <v>1006</v>
-      </c>
-      <c r="D50" s="5">
+      <c r="C50" s="6">
         <v>1009</v>
       </c>
+      <c r="D50" s="6">
+        <v>1026.9</v>
+      </c>
       <c r="E50" s="7">
-        <v>3</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C51" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D51" s="5">
+      <c r="C51" s="6">
         <v>15.42</v>
       </c>
-      <c r="E51" s="6">
-        <v>-0.18</v>
+      <c r="D51" s="6">
+        <v>15.52</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.1</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C52" s="5">
-        <v>11.11</v>
-      </c>
-      <c r="D52" s="5">
+      <c r="C52" s="6">
         <v>11.33</v>
+      </c>
+      <c r="D52" s="6">
+        <v>11.55</v>
       </c>
       <c r="E52" s="7">
         <v>0.22</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="5">
-        <v>4298.7</v>
-      </c>
-      <c r="D53" s="5">
+      <c r="C53" s="6">
         <v>4261.7</v>
       </c>
-      <c r="E53" s="6">
-        <v>-37</v>
+      <c r="D53" s="6">
+        <v>4109.8</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-151.9</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="5">
-        <v>11175</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C54" s="6">
         <v>11009</v>
       </c>
-      <c r="E54" s="6">
-        <v>-166</v>
+      <c r="D54" s="6">
+        <v>10900</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-109</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="5">
-        <v>49.26</v>
-      </c>
-      <c r="D55" s="5">
+      <c r="C55" s="6">
         <v>44.66</v>
       </c>
-      <c r="E55" s="6">
-        <v>-4.6</v>
+      <c r="D55" s="6">
+        <v>47.23</v>
+      </c>
+      <c r="E55" s="7">
+        <v>2.57</v>
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="5">
-        <v>42.11</v>
-      </c>
-      <c r="D56" s="5">
+      <c r="C56" s="6">
         <v>38.59</v>
       </c>
-      <c r="E56" s="6">
-        <v>-3.52</v>
+      <c r="D56" s="6">
+        <v>35.58</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-3.01</v>
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C57" s="5">
-        <v>54.07</v>
-      </c>
-      <c r="D57" s="5">
+      <c r="C57" s="6">
         <v>54.57</v>
       </c>
-      <c r="E57" s="7">
-        <v>0.5</v>
+      <c r="D57" s="6">
+        <v>53.59</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C58" s="5">
-        <v>44.92</v>
-      </c>
-      <c r="D58" s="5">
+      <c r="C58" s="6">
         <v>46.09</v>
       </c>
+      <c r="D58" s="6">
+        <v>52.53</v>
+      </c>
       <c r="E58" s="7">
-        <v>1.17</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C59" s="5">
-        <v>68.25</v>
-      </c>
-      <c r="D59" s="5">
+      <c r="C59" s="6">
         <v>65.15000000000001</v>
       </c>
-      <c r="E59" s="6">
-        <v>-3.1</v>
+      <c r="D59" s="6">
+        <v>66.06999999999999</v>
+      </c>
+      <c r="E59" s="7">
+        <v>0.92</v>
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="5">
-        <v>42.33</v>
-      </c>
-      <c r="D60" s="5">
+      <c r="C60" s="6">
         <v>47.14</v>
       </c>
+      <c r="D60" s="6">
+        <v>51.5</v>
+      </c>
       <c r="E60" s="7">
-        <v>4.81</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C61" s="5">
-        <v>43.14</v>
-      </c>
-      <c r="D61" s="5">
+      <c r="C61" s="6">
         <v>40.04</v>
       </c>
-      <c r="E61" s="6">
-        <v>-3.1</v>
+      <c r="D61" s="6">
+        <v>30.38</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-9.66</v>
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C62" s="5">
-        <v>35.03</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C62" s="6">
         <v>31.13</v>
       </c>
-      <c r="E62" s="6">
-        <v>-3.9</v>
+      <c r="D62" s="6">
+        <v>28.86</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="5">
-        <v>-20.84</v>
-      </c>
-      <c r="D63" s="5">
+      <c r="C63" s="6">
         <v>16.7</v>
       </c>
-      <c r="E63" s="7">
-        <v>37.54</v>
+      <c r="D63" s="6">
+        <v>-29.68</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-46.38</v>
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C64" s="5">
-        <v>71.02</v>
-      </c>
-      <c r="D64" s="5">
+      <c r="C64" s="6">
         <v>-57.92</v>
       </c>
-      <c r="E64" s="6">
-        <v>-128.94</v>
+      <c r="D64" s="6">
+        <v>-55.8</v>
+      </c>
+      <c r="E64" s="7">
+        <v>2.12</v>
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C65" s="5">
-        <v>-7.19</v>
-      </c>
-      <c r="D65" s="5">
+      <c r="C65" s="6">
         <v>-31.38</v>
       </c>
-      <c r="E65" s="6">
-        <v>-24.19</v>
+      <c r="D65" s="6">
+        <v>-28.82</v>
+      </c>
+      <c r="E65" s="7">
+        <v>2.56</v>
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C66" s="5">
-        <v>-53.66</v>
-      </c>
-      <c r="D66" s="5">
+      <c r="C66" s="6">
         <v>-14.86</v>
       </c>
+      <c r="D66" s="6">
+        <v>-5.52</v>
+      </c>
       <c r="E66" s="7">
-        <v>38.8</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C67" s="5">
-        <v>41.04</v>
-      </c>
-      <c r="D67" s="5">
+      <c r="C67" s="6">
         <v>-31.02</v>
       </c>
-      <c r="E67" s="6">
-        <v>-72.06</v>
+      <c r="D67" s="6">
+        <v>5.02</v>
+      </c>
+      <c r="E67" s="7">
+        <v>36.04</v>
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C68" s="5">
-        <v>13.96</v>
-      </c>
-      <c r="D68" s="5">
+      <c r="C68" s="6">
         <v>-40.3</v>
       </c>
-      <c r="E68" s="6">
-        <v>-54.26</v>
+      <c r="D68" s="6">
+        <v>19.69</v>
+      </c>
+      <c r="E68" s="7">
+        <v>59.99</v>
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C69" s="5">
-        <v>-61.96</v>
-      </c>
-      <c r="D69" s="5">
+      <c r="C69" s="6">
         <v>-53.26</v>
       </c>
+      <c r="D69" s="6">
+        <v>717.89</v>
+      </c>
       <c r="E69" s="7">
-        <v>8.699999999999999</v>
+        <v>771.15</v>
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C70" s="5">
-        <v>-8.44</v>
-      </c>
-      <c r="D70" s="5">
+      <c r="C70" s="6">
         <v>42.97</v>
       </c>
-      <c r="E70" s="7">
-        <v>51.41</v>
+      <c r="D70" s="6">
+        <v>32.25</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-10.72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3093,60 +3169,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="11">
+        <v>56.44</v>
+      </c>
+      <c r="C2" s="12">
+        <v>8</v>
+      </c>
+      <c r="D2" s="11">
+        <v>45.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.44</v>
-      </c>
-      <c r="C2" s="11">
-        <v>8</v>
-      </c>
-      <c r="D2" s="10">
-        <v>45.9</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-3.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>3.3</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-2.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>4</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>50</v>
       </c>
     </row>
@@ -3248,55 +3324,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.2819</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1892</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1788</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1651</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1388</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0709</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2461</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.3055</v>
+      <c r="A2" s="14">
+        <v>0.2847</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1792</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1748</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1615</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1307</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0702</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2487</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.3051</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="91">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,12 +160,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>UP</t>
   </si>
   <si>
@@ -190,28 +190,70 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.4% → -1.8%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.4%</t>
+  </si>
+  <si>
+    <t>-1.8%</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.9 → 32.7</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.9</t>
+  </si>
+  <si>
+    <t>32.7</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-0.5% → -4.5%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-0.5%</t>
+  </si>
+  <si>
+    <t>-4.5%</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>46.1 → 52.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>46.1</t>
+    <t>52.5 → 48.1</t>
   </si>
   <si>
     <t>52.5</t>
   </si>
   <si>
-    <t>47.1 → 51.5</t>
-  </si>
-  <si>
-    <t>47.1</t>
-  </si>
-  <si>
-    <t>51.5</t>
+    <t>48.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -263,7 +305,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,13 +346,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,6 +387,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -421,14 +476,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -437,7 +494,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -795,9 +852,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -940,7 +996,7 @@
         <v>400</v>
       </c>
       <c r="D2">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -955,82 +1011,82 @@
         <v>43.42</v>
       </c>
       <c r="I2">
-        <v>0.74</v>
+        <v>-0.5</v>
       </c>
       <c r="J2">
-        <v>-1.76</v>
+        <v>-2.66</v>
       </c>
       <c r="K2">
-        <v>18.84</v>
+        <v>11.7</v>
       </c>
       <c r="L2">
-        <v>42.3</v>
+        <v>38.46</v>
       </c>
       <c r="M2">
-        <v>28.47</v>
+        <v>28.79</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>401.42</v>
+        <v>401.02</v>
       </c>
       <c r="Q2">
-        <v>404.24</v>
+        <v>403.85</v>
       </c>
       <c r="R2">
-        <v>404.14</v>
+        <v>404.28</v>
       </c>
       <c r="S2">
-        <v>361.8</v>
+        <v>362.14</v>
       </c>
       <c r="T2">
-        <v>10.56</v>
+        <v>10.45</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
       </c>
       <c r="V2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
         <v>46</v>
       </c>
       <c r="X2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2">
         <v>47.23</v>
       </c>
       <c r="Z2">
-        <v>-0.85</v>
+        <v>-0.99</v>
       </c>
       <c r="AA2">
-        <v>0.37</v>
+        <v>0.09</v>
       </c>
       <c r="AB2">
-        <v>-1.21</v>
+        <v>-1.09</v>
       </c>
       <c r="AC2">
-        <v>33.85</v>
+        <v>28.97</v>
       </c>
       <c r="AD2">
-        <v>42.21</v>
+        <v>34.9</v>
       </c>
       <c r="AE2">
-        <v>9.17</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AF2">
-        <v>-29.68</v>
+        <v>-52.8</v>
       </c>
       <c r="AG2">
-        <v>416.06</v>
+        <v>415.7</v>
       </c>
       <c r="AH2">
-        <v>392.41</v>
+        <v>392</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1039,7 +1095,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>22.98</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1050,10 +1106,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>51.33</v>
+        <v>50.89</v>
       </c>
       <c r="D3">
-        <v>-1.74</v>
+        <v>-0.86</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1062,88 +1118,88 @@
         <v>50.41</v>
       </c>
       <c r="G3">
-        <v>-45.09</v>
+        <v>-45.56</v>
       </c>
       <c r="H3">
-        <v>1.83</v>
+        <v>0.95</v>
       </c>
       <c r="I3">
-        <v>1.7</v>
+        <v>0.95</v>
       </c>
       <c r="J3">
-        <v>-12.45</v>
+        <v>-10.97</v>
       </c>
       <c r="K3">
-        <v>-11.86</v>
+        <v>-15.04</v>
       </c>
       <c r="L3">
-        <v>-40.26</v>
+        <v>-42.73</v>
       </c>
       <c r="M3">
-        <v>-24.87</v>
+        <v>-25.14</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P3">
-        <v>52.03</v>
+        <v>52.13</v>
       </c>
       <c r="Q3">
-        <v>53.51</v>
+        <v>53.22</v>
       </c>
       <c r="R3">
-        <v>57.05</v>
+        <v>56.83</v>
       </c>
       <c r="S3">
-        <v>64.34</v>
+        <v>64.22</v>
       </c>
       <c r="T3">
-        <v>-20.23</v>
+        <v>-20.76</v>
       </c>
       <c r="U3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="X3">
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>35.58</v>
+        <v>34.19</v>
       </c>
       <c r="Z3">
-        <v>-1.7</v>
+        <v>-1.72</v>
       </c>
       <c r="AA3">
         <v>-1.72</v>
       </c>
       <c r="AB3">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AC3">
-        <v>80.48</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AD3">
-        <v>80.09999999999999</v>
+        <v>79.58</v>
       </c>
       <c r="AE3">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AF3">
-        <v>-55.8</v>
+        <v>-40.2</v>
       </c>
       <c r="AG3">
-        <v>57.19</v>
+        <v>56.75</v>
       </c>
       <c r="AH3">
-        <v>49.82</v>
+        <v>49.68</v>
       </c>
       <c r="AI3">
         <v>55.66</v>
@@ -1152,7 +1208,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>36.66</v>
+        <v>33.05</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1163,10 +1219,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3300</v>
+        <v>3319</v>
       </c>
       <c r="D4">
-        <v>-0.21</v>
+        <v>0.58</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1175,88 +1231,88 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.38</v>
+        <v>-1.82</v>
       </c>
       <c r="H4">
-        <v>30.38</v>
+        <v>31.13</v>
       </c>
       <c r="I4">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="J4">
-        <v>-0.67</v>
+        <v>0.34</v>
       </c>
       <c r="K4">
-        <v>6.81</v>
+        <v>6.87</v>
       </c>
       <c r="L4">
-        <v>17.69</v>
+        <v>18.36</v>
       </c>
       <c r="M4">
-        <v>16.15</v>
+        <v>16.19</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>3308.24</v>
+        <v>3310.04</v>
       </c>
       <c r="Q4">
-        <v>3292.52</v>
+        <v>3295.62</v>
       </c>
       <c r="R4">
-        <v>3221.72</v>
+        <v>3224.72</v>
       </c>
       <c r="S4">
-        <v>2945.23</v>
+        <v>2948.38</v>
       </c>
       <c r="T4">
-        <v>12.05</v>
+        <v>12.57</v>
       </c>
       <c r="U4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X4">
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>53.59</v>
+        <v>55.96</v>
       </c>
       <c r="Z4">
-        <v>24.78</v>
+        <v>24.35</v>
       </c>
       <c r="AA4">
-        <v>30</v>
+        <v>28.87</v>
       </c>
       <c r="AB4">
-        <v>-5.22</v>
+        <v>-4.52</v>
       </c>
       <c r="AC4">
-        <v>16.89</v>
+        <v>22.56</v>
       </c>
       <c r="AD4">
-        <v>23.87</v>
+        <v>21.83</v>
       </c>
       <c r="AE4">
-        <v>64.68000000000001</v>
+        <v>63.24</v>
       </c>
       <c r="AF4">
-        <v>-28.82</v>
+        <v>-11.97</v>
       </c>
       <c r="AG4">
-        <v>3348.86</v>
+        <v>3350.54</v>
       </c>
       <c r="AH4">
-        <v>3236.19</v>
+        <v>3240.71</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1265,7 +1321,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>15.79</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1276,37 +1332,37 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1026.9</v>
+        <v>1014</v>
       </c>
       <c r="D5">
-        <v>1.77</v>
+        <v>-1.26</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>738.75</v>
+        <v>741.05</v>
       </c>
       <c r="G5">
-        <v>-10.68</v>
+        <v>-11.8</v>
       </c>
       <c r="H5">
-        <v>39.01</v>
+        <v>36.83</v>
       </c>
       <c r="I5">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J5">
-        <v>-2.12</v>
+        <v>-5.98</v>
       </c>
       <c r="K5">
-        <v>0.25</v>
+        <v>-0.74</v>
       </c>
       <c r="L5">
-        <v>38.06</v>
+        <v>37.26</v>
       </c>
       <c r="M5">
-        <v>17.92</v>
+        <v>16.91</v>
       </c>
       <c r="N5">
         <v>62</v>
@@ -1315,61 +1371,61 @@
         <v>74</v>
       </c>
       <c r="P5">
-        <v>1012.58</v>
+        <v>1013.38</v>
       </c>
       <c r="Q5">
-        <v>1029.82</v>
+        <v>1028.21</v>
       </c>
       <c r="R5">
-        <v>1000.23</v>
+        <v>1001.53</v>
       </c>
       <c r="S5">
-        <v>969.02</v>
+        <v>970.22</v>
       </c>
       <c r="T5">
-        <v>5.97</v>
+        <v>4.51</v>
       </c>
       <c r="U5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X5">
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>52.53</v>
+        <v>48.07</v>
       </c>
       <c r="Z5">
-        <v>0.03</v>
+        <v>-0.46</v>
       </c>
       <c r="AA5">
-        <v>4.05</v>
+        <v>3.15</v>
       </c>
       <c r="AB5">
-        <v>-4.02</v>
+        <v>-3.61</v>
       </c>
       <c r="AC5">
-        <v>18.65</v>
+        <v>25.34</v>
       </c>
       <c r="AD5">
-        <v>7.79</v>
+        <v>15.82</v>
       </c>
       <c r="AE5">
-        <v>22.35</v>
+        <v>22.31</v>
       </c>
       <c r="AF5">
-        <v>-5.52</v>
+        <v>-35.54</v>
       </c>
       <c r="AG5">
-        <v>1063.6</v>
+        <v>1061.77</v>
       </c>
       <c r="AH5">
-        <v>996.04</v>
+        <v>994.65</v>
       </c>
       <c r="AI5">
         <v>999.73</v>
@@ -1378,7 +1434,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>19.25</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1389,10 +1445,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>15.52</v>
+        <v>14.9</v>
       </c>
       <c r="D6">
-        <v>0.65</v>
+        <v>-3.99</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1401,88 +1457,88 @@
         <v>7.27</v>
       </c>
       <c r="G6">
-        <v>-0.51</v>
+        <v>-4.49</v>
       </c>
       <c r="H6">
-        <v>113.48</v>
+        <v>104.95</v>
       </c>
       <c r="I6">
-        <v>6.81</v>
+        <v>2.9</v>
       </c>
       <c r="J6">
-        <v>20.4</v>
+        <v>10.37</v>
       </c>
       <c r="K6">
-        <v>9.529999999999999</v>
+        <v>-0</v>
       </c>
       <c r="L6">
-        <v>114.66</v>
+        <v>104.39</v>
       </c>
       <c r="M6">
-        <v>13.07</v>
+        <v>13.41</v>
       </c>
       <c r="N6">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="O6">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P6">
-        <v>15.21</v>
+        <v>15.29</v>
       </c>
       <c r="Q6">
-        <v>14.52</v>
+        <v>14.59</v>
       </c>
       <c r="R6">
-        <v>13.87</v>
+        <v>13.88</v>
       </c>
       <c r="S6">
-        <v>11.98</v>
+        <v>12</v>
       </c>
       <c r="T6">
-        <v>29.6</v>
+        <v>24.16</v>
       </c>
       <c r="U6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X6">
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>66.06999999999999</v>
+        <v>56.14</v>
       </c>
       <c r="Z6">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AA6">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="AB6">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="AC6">
-        <v>70.83</v>
+        <v>51.91</v>
       </c>
       <c r="AD6">
-        <v>63.24</v>
+        <v>62.91</v>
       </c>
       <c r="AE6">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="AF6">
-        <v>5.02</v>
+        <v>74.97</v>
       </c>
       <c r="AG6">
-        <v>15.77</v>
+        <v>15.76</v>
       </c>
       <c r="AH6">
-        <v>13.27</v>
+        <v>13.42</v>
       </c>
       <c r="AI6">
         <v>14.01</v>
@@ -1491,7 +1547,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>40.05</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1502,10 +1558,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.55</v>
+        <v>11.78</v>
       </c>
       <c r="D7">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1514,97 +1570,97 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-17.03</v>
+        <v>-15.37</v>
       </c>
       <c r="H7">
-        <v>146.27</v>
+        <v>151.17</v>
       </c>
       <c r="I7">
-        <v>2.48</v>
+        <v>6.61</v>
       </c>
       <c r="J7">
-        <v>-6.48</v>
+        <v>-2.73</v>
       </c>
       <c r="K7">
-        <v>10.42</v>
+        <v>7.29</v>
       </c>
       <c r="L7">
-        <v>117.51</v>
+        <v>118.55</v>
       </c>
       <c r="M7">
-        <v>-30.51</v>
+        <v>-30.74</v>
       </c>
       <c r="N7">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="O7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P7">
-        <v>11.19</v>
+        <v>11.33</v>
       </c>
       <c r="Q7">
-        <v>11.39</v>
+        <v>11.38</v>
       </c>
       <c r="R7">
-        <v>11.54</v>
+        <v>11.56</v>
       </c>
       <c r="S7">
-        <v>10.42</v>
+        <v>10.45</v>
       </c>
       <c r="T7">
-        <v>10.89</v>
+        <v>12.74</v>
       </c>
       <c r="U7" t="s">
+        <v>46</v>
+      </c>
+      <c r="V7" t="s">
         <v>47</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>46</v>
-      </c>
-      <c r="W7" t="s">
-        <v>47</v>
       </c>
       <c r="X7">
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>51.5</v>
+        <v>55.61</v>
       </c>
       <c r="Z7">
-        <v>-0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="AA7">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="AB7">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="AC7">
-        <v>85.3</v>
+        <v>100</v>
       </c>
       <c r="AD7">
-        <v>53.49</v>
+        <v>79.09</v>
       </c>
       <c r="AE7">
         <v>0.25</v>
       </c>
       <c r="AF7">
-        <v>19.69</v>
+        <v>54.9</v>
       </c>
       <c r="AG7">
-        <v>11.99</v>
+        <v>11.98</v>
       </c>
       <c r="AH7">
-        <v>10.78</v>
+        <v>10.79</v>
       </c>
       <c r="AI7">
-        <v>11.75</v>
+        <v>11.03</v>
       </c>
       <c r="AJ7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK7">
-        <v>27.15</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1615,10 +1671,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4109.8</v>
+        <v>4235.8</v>
       </c>
       <c r="D8">
-        <v>-3.56</v>
+        <v>3.07</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1627,88 +1683,88 @@
         <v>4109.8</v>
       </c>
       <c r="G8">
-        <v>-29.26</v>
+        <v>-27.09</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="I8">
-        <v>-4.98</v>
+        <v>-2.73</v>
       </c>
       <c r="J8">
-        <v>-6.39</v>
+        <v>-2.96</v>
       </c>
       <c r="K8">
-        <v>-2.35</v>
+        <v>-1.22</v>
       </c>
       <c r="L8">
-        <v>-19.82</v>
+        <v>-17.73</v>
       </c>
       <c r="M8">
-        <v>17.48</v>
+        <v>18.02</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="P8">
-        <v>4269.7</v>
+        <v>4245.96</v>
       </c>
       <c r="Q8">
-        <v>4364.27</v>
+        <v>4349.39</v>
       </c>
       <c r="R8">
-        <v>4363.04</v>
+        <v>4359.02</v>
       </c>
       <c r="S8">
-        <v>4613.21</v>
+        <v>4608.37</v>
       </c>
       <c r="T8">
-        <v>-10.91</v>
+        <v>-8.08</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
       </c>
       <c r="V8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>30.38</v>
+        <v>42.72</v>
       </c>
       <c r="Z8">
-        <v>-36.11</v>
+        <v>-38.69</v>
       </c>
       <c r="AA8">
-        <v>-13.14</v>
+        <v>-18.25</v>
       </c>
       <c r="AB8">
-        <v>-22.97</v>
+        <v>-20.44</v>
       </c>
       <c r="AC8">
-        <v>0.91</v>
+        <v>17.62</v>
       </c>
       <c r="AD8">
-        <v>8.699999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AE8">
-        <v>103.61</v>
+        <v>109.28</v>
       </c>
       <c r="AF8">
-        <v>717.89</v>
+        <v>-10.49</v>
       </c>
       <c r="AG8">
-        <v>4565.57</v>
+        <v>4541.83</v>
       </c>
       <c r="AH8">
-        <v>4162.98</v>
+        <v>4156.95</v>
       </c>
       <c r="AI8">
         <v>4473.44</v>
@@ -1717,7 +1773,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>26.83</v>
+        <v>32.44</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1728,10 +1784,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10900</v>
+        <v>10979</v>
       </c>
       <c r="D9">
-        <v>-0.99</v>
+        <v>0.72</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1740,25 +1796,25 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-16.49</v>
+        <v>-15.88</v>
       </c>
       <c r="H9">
-        <v>5.19</v>
+        <v>5.95</v>
       </c>
       <c r="I9">
-        <v>-4.33</v>
+        <v>-2.63</v>
       </c>
       <c r="J9">
-        <v>-7.47</v>
+        <v>-7.67</v>
       </c>
       <c r="K9">
-        <v>0.65</v>
+        <v>-1.24</v>
       </c>
       <c r="L9">
-        <v>-13.5</v>
+        <v>-13.31</v>
       </c>
       <c r="M9">
-        <v>7.02</v>
+        <v>7.18</v>
       </c>
       <c r="N9">
         <v>38</v>
@@ -1767,70 +1823,70 @@
         <v>39</v>
       </c>
       <c r="P9">
-        <v>11153.4</v>
+        <v>11094.2</v>
       </c>
       <c r="Q9">
-        <v>11455.75</v>
+        <v>11419.4</v>
       </c>
       <c r="R9">
-        <v>11681.22</v>
+        <v>11670.08</v>
       </c>
       <c r="S9">
-        <v>11756.1</v>
+        <v>11753.07</v>
       </c>
       <c r="T9">
-        <v>-7.28</v>
+        <v>-6.59</v>
       </c>
       <c r="U9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="X9">
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>28.86</v>
+        <v>32.69</v>
       </c>
       <c r="Z9">
-        <v>-174.07</v>
+        <v>-187.26</v>
       </c>
       <c r="AA9">
-        <v>-110.69</v>
+        <v>-126.01</v>
       </c>
       <c r="AB9">
-        <v>-63.38</v>
+        <v>-61.25</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="AD9">
-        <v>9.84</v>
+        <v>6.91</v>
       </c>
       <c r="AE9">
-        <v>188.8</v>
+        <v>183.95</v>
       </c>
       <c r="AF9">
-        <v>32.25</v>
+        <v>7.15</v>
       </c>
       <c r="AG9">
-        <v>11900.15</v>
+        <v>11895.42</v>
       </c>
       <c r="AH9">
-        <v>11011.35</v>
+        <v>10943.38</v>
       </c>
       <c r="AI9">
-        <v>11495.39</v>
+        <v>11470.36</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>39.62</v>
+        <v>43.31</v>
       </c>
     </row>
   </sheetData>
@@ -1971,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2011,7 +2067,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2031,1125 +2087,1225 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="8">
+        <v>-1.76</v>
+      </c>
+      <c r="D13" s="8">
+        <v>-2.66</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="8">
+        <v>-12.45</v>
+      </c>
+      <c r="D14" s="8">
+        <v>-10.97</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="8">
+        <v>-0.67</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="8">
+        <v>-2.12</v>
+      </c>
+      <c r="D16" s="8">
+        <v>-5.98</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-3.86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="8">
+        <v>20.4</v>
+      </c>
+      <c r="D17" s="8">
+        <v>10.37</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-10.03</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="8">
+        <v>-6.48</v>
+      </c>
+      <c r="D18" s="8">
+        <v>-2.73</v>
+      </c>
+      <c r="E18" s="10">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="8">
+        <v>-6.39</v>
+      </c>
+      <c r="D19" s="8">
+        <v>-2.96</v>
+      </c>
+      <c r="E19" s="10">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="8">
+        <v>-7.47</v>
+      </c>
+      <c r="D20" s="8">
+        <v>-7.67</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-2.65</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-1.76</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0.74</v>
+      </c>
+      <c r="D21" s="8">
+        <v>-0.5</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-14.42</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-12.45</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-2.18</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-0.67</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0.27</v>
+      </c>
+      <c r="E23" s="10">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-4.27</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-2.12</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>19.35</v>
-      </c>
-      <c r="D12" s="6">
-        <v>20.4</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="8">
+        <v>6.81</v>
+      </c>
+      <c r="D25" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-3.91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-10.08</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-6.48</v>
-      </c>
-      <c r="E13" s="7">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="8">
+        <v>2.48</v>
+      </c>
+      <c r="D26" s="8">
+        <v>6.61</v>
+      </c>
+      <c r="E26" s="10">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
+      <c r="B27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="8">
+        <v>-4.98</v>
+      </c>
+      <c r="D27" s="8">
+        <v>-2.73</v>
+      </c>
+      <c r="E27" s="10">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="8">
+        <v>-4.33</v>
+      </c>
+      <c r="D28" s="8">
+        <v>-2.63</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="8">
+        <v>42.3</v>
+      </c>
+      <c r="D29" s="8">
+        <v>38.46</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-3.84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="8">
+        <v>-40.26</v>
+      </c>
+      <c r="D30" s="8">
+        <v>-42.73</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="8">
+        <v>17.69</v>
+      </c>
+      <c r="D31" s="8">
+        <v>18.36</v>
+      </c>
+      <c r="E31" s="10">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="8">
+        <v>38.06</v>
+      </c>
+      <c r="D32" s="8">
+        <v>37.26</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="8">
+        <v>114.66</v>
+      </c>
+      <c r="D33" s="8">
+        <v>104.39</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-10.27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="8">
+        <v>117.51</v>
+      </c>
+      <c r="D34" s="8">
+        <v>118.55</v>
+      </c>
+      <c r="E34" s="10">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="8">
+        <v>-19.82</v>
+      </c>
+      <c r="D35" s="8">
+        <v>-17.73</v>
+      </c>
+      <c r="E35" s="10">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-13.5</v>
+      </c>
+      <c r="D36" s="8">
+        <v>-13.31</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="8">
+        <v>18.84</v>
+      </c>
+      <c r="D37" s="8">
+        <v>11.7</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-7.14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="8">
+        <v>-11.86</v>
+      </c>
+      <c r="D38" s="8">
+        <v>-15.04</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-3.18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="8">
+        <v>6.81</v>
+      </c>
+      <c r="D39" s="8">
+        <v>6.87</v>
+      </c>
+      <c r="E39" s="10">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="D40" s="8">
+        <v>-0.74</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="8">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="D41" s="8">
+        <v>-0</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-9.529999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="8">
+        <v>10.42</v>
+      </c>
+      <c r="D42" s="8">
+        <v>7.29</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-3.13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="8">
         <v>-2.35</v>
       </c>
-      <c r="D14" s="6">
-        <v>-6.39</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-4.04</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D43" s="8">
+        <v>-1.22</v>
+      </c>
+      <c r="E43" s="10">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-8.550000000000001</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-7.47</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B44" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="D44" s="8">
+        <v>-1.24</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="8">
+        <v>-45.09</v>
+      </c>
+      <c r="D45" s="8">
+        <v>-45.56</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="8">
+        <v>-2.38</v>
+      </c>
+      <c r="D46" s="8">
+        <v>-1.82</v>
+      </c>
+      <c r="E46" s="10">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="8">
+        <v>-10.68</v>
+      </c>
+      <c r="D47" s="8">
+        <v>-11.8</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="8">
+        <v>-0.51</v>
+      </c>
+      <c r="D48" s="8">
+        <v>-4.49</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-3.98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="8">
+        <v>-17.03</v>
+      </c>
+      <c r="D49" s="8">
+        <v>-15.37</v>
+      </c>
+      <c r="E49" s="10">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="8">
+        <v>-29.26</v>
+      </c>
+      <c r="D50" s="8">
+        <v>-27.09</v>
+      </c>
+      <c r="E50" s="10">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="8">
+        <v>-16.49</v>
+      </c>
+      <c r="D51" s="8">
+        <v>-15.88</v>
+      </c>
+      <c r="E51" s="10">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="8">
+        <v>51.33</v>
+      </c>
+      <c r="D52" s="8">
+        <v>50.89</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="8">
+        <v>3300</v>
+      </c>
+      <c r="D53" s="8">
+        <v>3319</v>
+      </c>
+      <c r="E53" s="10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="8">
+        <v>1026.9</v>
+      </c>
+      <c r="D54" s="8">
+        <v>1014</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-12.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="8">
+        <v>15.52</v>
+      </c>
+      <c r="D55" s="8">
+        <v>14.9</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="8">
+        <v>11.55</v>
+      </c>
+      <c r="D56" s="8">
+        <v>11.78</v>
+      </c>
+      <c r="E56" s="10">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="8">
+        <v>4109.8</v>
+      </c>
+      <c r="D57" s="8">
+        <v>4235.8</v>
+      </c>
+      <c r="E57" s="10">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="8">
+        <v>10900</v>
+      </c>
+      <c r="D58" s="8">
+        <v>10979</v>
+      </c>
+      <c r="E58" s="10">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="8">
+        <v>99</v>
+      </c>
+      <c r="D59" s="8">
+        <v>87</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="8">
+        <v>87</v>
+      </c>
+      <c r="D60" s="8">
+        <v>99</v>
+      </c>
+      <c r="E60" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="8">
+        <v>35.58</v>
+      </c>
+      <c r="D61" s="8">
+        <v>34.19</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="8">
+        <v>53.59</v>
+      </c>
+      <c r="D62" s="8">
+        <v>55.96</v>
+      </c>
+      <c r="E62" s="10">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="8">
+        <v>52.53</v>
+      </c>
+      <c r="D63" s="8">
+        <v>48.07</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-4.46</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="8">
+        <v>66.06999999999999</v>
+      </c>
+      <c r="D64" s="8">
+        <v>56.14</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-9.93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="8">
+        <v>51.5</v>
+      </c>
+      <c r="D65" s="8">
+        <v>55.61</v>
+      </c>
+      <c r="E65" s="10">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="8">
+        <v>30.38</v>
+      </c>
+      <c r="D66" s="8">
+        <v>42.72</v>
+      </c>
+      <c r="E66" s="10">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="8">
+        <v>28.86</v>
+      </c>
+      <c r="D67" s="8">
+        <v>32.69</v>
+      </c>
+      <c r="E67" s="10">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.63</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.74</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B68" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="8">
+        <v>-29.68</v>
+      </c>
+      <c r="D68" s="8">
+        <v>-52.8</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-23.12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>2.23</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B69" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="8">
+        <v>-55.8</v>
+      </c>
+      <c r="D69" s="8">
+        <v>-40.2</v>
+      </c>
+      <c r="E69" s="10">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0.15</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B70" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="8">
+        <v>-28.82</v>
+      </c>
+      <c r="D70" s="8">
+        <v>-11.97</v>
+      </c>
+      <c r="E70" s="10">
+        <v>16.85</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-0.53</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B71" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="8">
+        <v>-5.52</v>
+      </c>
+      <c r="D71" s="8">
+        <v>-35.54</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-30.02</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>9.67</v>
-      </c>
-      <c r="D20" s="6">
-        <v>6.81</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-2.86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B72" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="8">
+        <v>5.02</v>
+      </c>
+      <c r="D72" s="8">
+        <v>74.97</v>
+      </c>
+      <c r="E72" s="10">
+        <v>69.95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>2.07</v>
-      </c>
-      <c r="D21" s="6">
-        <v>2.48</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B73" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="8">
+        <v>19.69</v>
+      </c>
+      <c r="D73" s="8">
+        <v>54.9</v>
+      </c>
+      <c r="E73" s="10">
+        <v>35.21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-2.1</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-4.98</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B74" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="8">
+        <v>717.89</v>
+      </c>
+      <c r="D74" s="8">
+        <v>-10.49</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-728.38</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-3.43</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-4.33</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>43.02</v>
-      </c>
-      <c r="D24" s="6">
-        <v>42.3</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-36.97</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-40.26</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-3.29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>36.53</v>
-      </c>
-      <c r="D26" s="6">
-        <v>38.06</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>133.28</v>
-      </c>
-      <c r="D27" s="6">
-        <v>114.66</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-18.62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>113.37</v>
-      </c>
-      <c r="D28" s="6">
-        <v>117.51</v>
-      </c>
-      <c r="E28" s="7">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-16.56</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-19.82</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-12.98</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-13.5</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>15.83</v>
-      </c>
-      <c r="D31" s="6">
-        <v>18.84</v>
-      </c>
-      <c r="E31" s="7">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-11.1</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-11.86</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>7.67</v>
-      </c>
-      <c r="D33" s="6">
-        <v>6.81</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-2.92</v>
-      </c>
-      <c r="D34" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="E34" s="7">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>11.1</v>
-      </c>
-      <c r="D35" s="6">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>4.23</v>
-      </c>
-      <c r="D36" s="6">
-        <v>10.42</v>
-      </c>
-      <c r="E36" s="7">
-        <v>6.19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>0.31</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-2.35</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>1.32</v>
-      </c>
-      <c r="D38" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-6.53</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-5.82</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-44.12</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-45.09</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-2.18</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-2.38</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-12.24</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-10.68</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-1.15</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-0.51</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-18.61</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-17.03</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-26.64</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-29.26</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-2.62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-15.65</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-16.49</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>396.95</v>
-      </c>
-      <c r="D47" s="6">
-        <v>400</v>
-      </c>
-      <c r="E47" s="7">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>52.24</v>
-      </c>
-      <c r="D48" s="6">
-        <v>51.33</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>3306.8</v>
-      </c>
-      <c r="D49" s="6">
-        <v>3300</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-6.8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>1009</v>
-      </c>
-      <c r="D50" s="6">
-        <v>1026.9</v>
-      </c>
-      <c r="E50" s="7">
-        <v>17.9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>15.42</v>
-      </c>
-      <c r="D51" s="6">
-        <v>15.52</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>11.33</v>
-      </c>
-      <c r="D52" s="6">
-        <v>11.55</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>4261.7</v>
-      </c>
-      <c r="D53" s="6">
-        <v>4109.8</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-151.9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>11009</v>
-      </c>
-      <c r="D54" s="6">
-        <v>10900</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-109</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>44.66</v>
-      </c>
-      <c r="D55" s="6">
-        <v>47.23</v>
-      </c>
-      <c r="E55" s="7">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>38.59</v>
-      </c>
-      <c r="D56" s="6">
-        <v>35.58</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-3.01</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>54.57</v>
-      </c>
-      <c r="D57" s="6">
-        <v>53.59</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>46.09</v>
-      </c>
-      <c r="D58" s="6">
-        <v>52.53</v>
-      </c>
-      <c r="E58" s="7">
-        <v>6.44</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>65.15000000000001</v>
-      </c>
-      <c r="D59" s="6">
-        <v>66.06999999999999</v>
-      </c>
-      <c r="E59" s="7">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>47.14</v>
-      </c>
-      <c r="D60" s="6">
-        <v>51.5</v>
-      </c>
-      <c r="E60" s="7">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>40.04</v>
-      </c>
-      <c r="D61" s="6">
-        <v>30.38</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-9.66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>31.13</v>
-      </c>
-      <c r="D62" s="6">
-        <v>28.86</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
+      <c r="B75" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="6">
-        <v>16.7</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-29.68</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-46.38</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-57.92</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-55.8</v>
-      </c>
-      <c r="E64" s="7">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>-31.38</v>
-      </c>
-      <c r="D65" s="6">
-        <v>-28.82</v>
-      </c>
-      <c r="E65" s="7">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>-14.86</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-5.52</v>
-      </c>
-      <c r="E66" s="7">
-        <v>9.34</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>-31.02</v>
-      </c>
-      <c r="D67" s="6">
-        <v>5.02</v>
-      </c>
-      <c r="E67" s="7">
-        <v>36.04</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>-40.3</v>
-      </c>
-      <c r="D68" s="6">
-        <v>19.69</v>
-      </c>
-      <c r="E68" s="7">
-        <v>59.99</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>-53.26</v>
-      </c>
-      <c r="D69" s="6">
-        <v>717.89</v>
-      </c>
-      <c r="E69" s="7">
-        <v>771.15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>42.97</v>
-      </c>
-      <c r="D70" s="6">
+      <c r="C75" s="8">
         <v>32.25</v>
       </c>
-      <c r="E70" s="8">
-        <v>-10.72</v>
+      <c r="D75" s="8">
+        <v>7.15</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-25.1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3169,61 +3325,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>76</v>
+      <c r="B1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="13">
         <v>56.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="14">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>45.7</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="13">
+        <v>46.6</v>
+      </c>
+      <c r="E2" s="13">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-2.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="13">
+        <v>-2.8</v>
+      </c>
+      <c r="G2" s="13">
+        <v>1</v>
+      </c>
+      <c r="H2" s="13">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
-        <v>50</v>
+      <c r="I2" s="13">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3324,55 +3480,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="15" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.2847</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1792</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1748</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1615</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1307</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0702</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2487</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.3051</v>
+      <c r="A2" s="16">
+        <v>0.2879</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.1802</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.1691</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.1619</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.1341</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.0718</v>
+      </c>
+      <c r="G2" s="16">
+        <v>-0.2514</v>
+      </c>
+      <c r="H2" s="16">
+        <v>-0.3074</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,70 +190,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.4% → -1.8%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.4%</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.8% → -2.9%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>-1.8%</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.9 → 32.7</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>28.9</t>
-  </si>
-  <si>
-    <t>32.7</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-0.5% → -4.5%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-0.5%</t>
-  </si>
-  <si>
-    <t>-4.5%</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>52.5 → 48.1</t>
-  </si>
-  <si>
-    <t>52.5</t>
-  </si>
-  <si>
-    <t>48.1</t>
+    <t>-2.9%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -339,13 +288,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -354,6 +296,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -386,12 +335,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -399,6 +342,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -468,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -476,12 +425,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -852,8 +799,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -993,10 +940,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -1005,46 +952,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-5.82</v>
+        <v>-6.99</v>
       </c>
       <c r="H2">
-        <v>43.42</v>
+        <v>41.63</v>
       </c>
       <c r="I2">
-        <v>-0.5</v>
+        <v>-2.45</v>
       </c>
       <c r="J2">
-        <v>-2.66</v>
+        <v>-3.12</v>
       </c>
       <c r="K2">
-        <v>11.7</v>
+        <v>7.28</v>
       </c>
       <c r="L2">
-        <v>38.46</v>
+        <v>36.35</v>
       </c>
       <c r="M2">
-        <v>28.79</v>
+        <v>28.45</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P2">
-        <v>401.02</v>
+        <v>399.04</v>
       </c>
       <c r="Q2">
-        <v>403.85</v>
+        <v>403.55</v>
       </c>
       <c r="R2">
-        <v>404.28</v>
+        <v>404.15</v>
       </c>
       <c r="S2">
-        <v>362.14</v>
+        <v>362.39</v>
       </c>
       <c r="T2">
-        <v>10.45</v>
+        <v>9</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1059,34 +1006,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>47.23</v>
+        <v>43.4</v>
       </c>
       <c r="Z2">
-        <v>-0.99</v>
+        <v>-1.49</v>
       </c>
       <c r="AA2">
-        <v>0.09</v>
+        <v>-0.22</v>
       </c>
       <c r="AB2">
-        <v>-1.09</v>
+        <v>-1.27</v>
       </c>
       <c r="AC2">
-        <v>28.97</v>
+        <v>26.21</v>
       </c>
       <c r="AD2">
-        <v>34.9</v>
+        <v>29.68</v>
       </c>
       <c r="AE2">
-        <v>8.949999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AF2">
-        <v>-52.8</v>
+        <v>-44</v>
       </c>
       <c r="AG2">
-        <v>415.7</v>
+        <v>415.99</v>
       </c>
       <c r="AH2">
-        <v>392</v>
+        <v>391.11</v>
       </c>
       <c r="AI2">
         <v>389.09</v>
@@ -1095,7 +1042,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>22.75</v>
+        <v>24.53</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1106,10 +1053,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>50.89</v>
+        <v>50.44</v>
       </c>
       <c r="D3">
-        <v>-0.86</v>
+        <v>-0.88</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1118,46 +1065,46 @@
         <v>50.41</v>
       </c>
       <c r="G3">
-        <v>-45.56</v>
+        <v>-46.04</v>
       </c>
       <c r="H3">
-        <v>0.95</v>
+        <v>0.06</v>
       </c>
       <c r="I3">
-        <v>0.95</v>
+        <v>-4.78</v>
       </c>
       <c r="J3">
-        <v>-10.97</v>
+        <v>-11.09</v>
       </c>
       <c r="K3">
-        <v>-15.04</v>
+        <v>-17.37</v>
       </c>
       <c r="L3">
-        <v>-42.73</v>
+        <v>-44.62</v>
       </c>
       <c r="M3">
-        <v>-25.14</v>
+        <v>-25.26</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P3">
-        <v>52.13</v>
+        <v>51.62</v>
       </c>
       <c r="Q3">
-        <v>53.22</v>
+        <v>52.94</v>
       </c>
       <c r="R3">
-        <v>56.83</v>
+        <v>56.59</v>
       </c>
       <c r="S3">
-        <v>64.22</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="T3">
-        <v>-20.76</v>
+        <v>-21.31</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1172,43 +1119,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>34.19</v>
+        <v>32.79</v>
       </c>
       <c r="Z3">
-        <v>-1.72</v>
+        <v>-1.74</v>
       </c>
       <c r="AA3">
         <v>-1.72</v>
       </c>
       <c r="AB3">
-        <v>-0</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>65.09999999999999</v>
+        <v>53.84</v>
       </c>
       <c r="AD3">
-        <v>79.58</v>
+        <v>66.47</v>
       </c>
       <c r="AE3">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AF3">
-        <v>-40.2</v>
+        <v>0.36</v>
       </c>
       <c r="AG3">
-        <v>56.75</v>
+        <v>56.42</v>
       </c>
       <c r="AH3">
-        <v>49.68</v>
+        <v>49.45</v>
       </c>
       <c r="AI3">
-        <v>55.66</v>
+        <v>55.1</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>33.05</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1219,10 +1166,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3319</v>
+        <v>3281.9</v>
       </c>
       <c r="D4">
-        <v>0.58</v>
+        <v>-1.12</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1231,46 +1178,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-1.82</v>
+        <v>-2.92</v>
       </c>
       <c r="H4">
-        <v>31.13</v>
+        <v>29.66</v>
       </c>
       <c r="I4">
-        <v>0.27</v>
+        <v>-1.21</v>
       </c>
       <c r="J4">
-        <v>0.34</v>
+        <v>0.76</v>
       </c>
       <c r="K4">
-        <v>6.87</v>
+        <v>3.71</v>
       </c>
       <c r="L4">
-        <v>18.36</v>
+        <v>17.38</v>
       </c>
       <c r="M4">
-        <v>16.19</v>
+        <v>15.92</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>3310.04</v>
+        <v>3302.02</v>
       </c>
       <c r="Q4">
-        <v>3295.62</v>
+        <v>3297.28</v>
       </c>
       <c r="R4">
-        <v>3224.72</v>
+        <v>3226.74</v>
       </c>
       <c r="S4">
-        <v>2948.38</v>
+        <v>2951.36</v>
       </c>
       <c r="T4">
-        <v>12.57</v>
+        <v>11.2</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1285,34 +1232,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>55.96</v>
+        <v>50.53</v>
       </c>
       <c r="Z4">
-        <v>24.35</v>
+        <v>20.77</v>
       </c>
       <c r="AA4">
-        <v>28.87</v>
+        <v>27.25</v>
       </c>
       <c r="AB4">
-        <v>-4.52</v>
+        <v>-6.48</v>
       </c>
       <c r="AC4">
-        <v>22.56</v>
+        <v>15.45</v>
       </c>
       <c r="AD4">
-        <v>21.83</v>
+        <v>18.3</v>
       </c>
       <c r="AE4">
-        <v>63.24</v>
+        <v>62.44</v>
       </c>
       <c r="AF4">
-        <v>-11.97</v>
+        <v>-54.75</v>
       </c>
       <c r="AG4">
-        <v>3350.54</v>
+        <v>3348.08</v>
       </c>
       <c r="AH4">
-        <v>3240.71</v>
+        <v>3246.49</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1321,7 +1268,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>14.85</v>
+        <v>13.18</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1332,10 +1279,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1014</v>
+        <v>981.5</v>
       </c>
       <c r="D5">
-        <v>-1.26</v>
+        <v>-3.21</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1344,46 +1291,46 @@
         <v>741.05</v>
       </c>
       <c r="G5">
-        <v>-11.8</v>
+        <v>-14.63</v>
       </c>
       <c r="H5">
-        <v>36.83</v>
+        <v>32.45</v>
       </c>
       <c r="I5">
-        <v>0.4</v>
+        <v>-2.92</v>
       </c>
       <c r="J5">
-        <v>-5.98</v>
+        <v>-6.19</v>
       </c>
       <c r="K5">
-        <v>-0.74</v>
+        <v>-3.2</v>
       </c>
       <c r="L5">
-        <v>37.26</v>
+        <v>32.12</v>
       </c>
       <c r="M5">
-        <v>16.91</v>
+        <v>16.14</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P5">
-        <v>1013.38</v>
+        <v>1007.48</v>
       </c>
       <c r="Q5">
-        <v>1028.21</v>
+        <v>1025.81</v>
       </c>
       <c r="R5">
-        <v>1001.53</v>
+        <v>1002.09</v>
       </c>
       <c r="S5">
-        <v>970.22</v>
+        <v>971.1799999999999</v>
       </c>
       <c r="T5">
-        <v>4.51</v>
+        <v>1.06</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1398,43 +1345,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>48.07</v>
+        <v>39.07</v>
       </c>
       <c r="Z5">
-        <v>-0.46</v>
+        <v>-3.43</v>
       </c>
       <c r="AA5">
-        <v>3.15</v>
+        <v>1.83</v>
       </c>
       <c r="AB5">
-        <v>-3.61</v>
+        <v>-5.27</v>
       </c>
       <c r="AC5">
-        <v>25.34</v>
+        <v>22.87</v>
       </c>
       <c r="AD5">
-        <v>15.82</v>
+        <v>22.28</v>
       </c>
       <c r="AE5">
-        <v>22.31</v>
+        <v>23.63</v>
       </c>
       <c r="AF5">
-        <v>-35.54</v>
+        <v>55.57</v>
       </c>
       <c r="AG5">
-        <v>1061.77</v>
+        <v>1065.32</v>
       </c>
       <c r="AH5">
-        <v>994.65</v>
+        <v>986.3</v>
       </c>
       <c r="AI5">
-        <v>999.73</v>
+        <v>1053.85</v>
       </c>
       <c r="AJ5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK5">
-        <v>17.1</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1445,37 +1392,37 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.9</v>
+        <v>14.97</v>
       </c>
       <c r="D6">
-        <v>-3.99</v>
+        <v>0.47</v>
       </c>
       <c r="E6">
         <v>15.6</v>
       </c>
       <c r="F6">
-        <v>7.27</v>
+        <v>7.32</v>
       </c>
       <c r="G6">
-        <v>-4.49</v>
+        <v>-4.04</v>
       </c>
       <c r="H6">
-        <v>104.95</v>
+        <v>104.51</v>
       </c>
       <c r="I6">
-        <v>2.9</v>
+        <v>-0.33</v>
       </c>
       <c r="J6">
-        <v>10.37</v>
+        <v>10.81</v>
       </c>
       <c r="K6">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="L6">
-        <v>104.39</v>
+        <v>105.91</v>
       </c>
       <c r="M6">
-        <v>13.41</v>
+        <v>13.51</v>
       </c>
       <c r="N6">
         <v>87</v>
@@ -1484,19 +1431,19 @@
         <v>92</v>
       </c>
       <c r="P6">
-        <v>15.29</v>
+        <v>15.28</v>
       </c>
       <c r="Q6">
-        <v>14.59</v>
+        <v>14.63</v>
       </c>
       <c r="R6">
-        <v>13.88</v>
+        <v>13.89</v>
       </c>
       <c r="S6">
-        <v>12</v>
+        <v>12.02</v>
       </c>
       <c r="T6">
-        <v>24.16</v>
+        <v>24.49</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1511,34 +1458,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>56.14</v>
+        <v>56.93</v>
       </c>
       <c r="Z6">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="AA6">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="AB6">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="AC6">
-        <v>51.91</v>
+        <v>39.08</v>
       </c>
       <c r="AD6">
-        <v>62.91</v>
+        <v>53.94</v>
       </c>
       <c r="AE6">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="AF6">
-        <v>74.97</v>
+        <v>6.72</v>
       </c>
       <c r="AG6">
-        <v>15.76</v>
+        <v>15.79</v>
       </c>
       <c r="AH6">
-        <v>13.42</v>
+        <v>13.48</v>
       </c>
       <c r="AI6">
         <v>14.01</v>
@@ -1547,7 +1494,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>37.49</v>
+        <v>35.27</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1558,10 +1505,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.78</v>
+        <v>12.01</v>
       </c>
       <c r="D7">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1570,25 +1517,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-15.37</v>
+        <v>-13.72</v>
       </c>
       <c r="H7">
-        <v>151.17</v>
+        <v>156.08</v>
       </c>
       <c r="I7">
-        <v>6.61</v>
+        <v>10.18</v>
       </c>
       <c r="J7">
-        <v>-2.73</v>
+        <v>1.18</v>
       </c>
       <c r="K7">
-        <v>7.29</v>
+        <v>4.25</v>
       </c>
       <c r="L7">
-        <v>118.55</v>
+        <v>128.33</v>
       </c>
       <c r="M7">
-        <v>-30.74</v>
+        <v>-30.46</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1597,19 +1544,19 @@
         <v>94</v>
       </c>
       <c r="P7">
-        <v>11.33</v>
+        <v>11.56</v>
       </c>
       <c r="Q7">
-        <v>11.38</v>
+        <v>11.4</v>
       </c>
       <c r="R7">
-        <v>11.56</v>
+        <v>11.58</v>
       </c>
       <c r="S7">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
       <c r="T7">
-        <v>12.74</v>
+        <v>14.57</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1624,43 +1571,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>55.61</v>
+        <v>59.33</v>
       </c>
       <c r="Z7">
-        <v>-0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="AA7">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="AB7">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="AC7">
         <v>100</v>
       </c>
       <c r="AD7">
-        <v>79.09</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AE7">
         <v>0.25</v>
       </c>
       <c r="AF7">
-        <v>54.9</v>
+        <v>336.55</v>
       </c>
       <c r="AG7">
-        <v>11.98</v>
+        <v>12.04</v>
       </c>
       <c r="AH7">
-        <v>10.79</v>
+        <v>10.75</v>
       </c>
       <c r="AI7">
-        <v>11.03</v>
+        <v>11.26</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>28.24</v>
+        <v>30.71</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1671,10 +1618,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4235.8</v>
+        <v>4191.6</v>
       </c>
       <c r="D8">
-        <v>3.07</v>
+        <v>-1.04</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1683,46 +1630,46 @@
         <v>4109.8</v>
       </c>
       <c r="G8">
-        <v>-27.09</v>
+        <v>-27.85</v>
       </c>
       <c r="H8">
-        <v>3.07</v>
+        <v>1.99</v>
       </c>
       <c r="I8">
-        <v>-2.73</v>
+        <v>-3.06</v>
       </c>
       <c r="J8">
-        <v>-2.96</v>
+        <v>-7.54</v>
       </c>
       <c r="K8">
-        <v>-1.22</v>
+        <v>-4.31</v>
       </c>
       <c r="L8">
-        <v>-17.73</v>
+        <v>-19.34</v>
       </c>
       <c r="M8">
-        <v>18.02</v>
+        <v>17.76</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P8">
-        <v>4245.96</v>
+        <v>4219.52</v>
       </c>
       <c r="Q8">
-        <v>4349.39</v>
+        <v>4331.62</v>
       </c>
       <c r="R8">
-        <v>4359.02</v>
+        <v>4354.54</v>
       </c>
       <c r="S8">
-        <v>4608.37</v>
+        <v>4603.73</v>
       </c>
       <c r="T8">
-        <v>-8.08</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1737,34 +1684,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>42.72</v>
+        <v>40.04</v>
       </c>
       <c r="Z8">
-        <v>-38.69</v>
+        <v>-43.8</v>
       </c>
       <c r="AA8">
-        <v>-18.25</v>
+        <v>-23.36</v>
       </c>
       <c r="AB8">
         <v>-20.44</v>
       </c>
       <c r="AC8">
-        <v>17.62</v>
+        <v>31.41</v>
       </c>
       <c r="AD8">
-        <v>9.039999999999999</v>
+        <v>16.65</v>
       </c>
       <c r="AE8">
-        <v>109.28</v>
+        <v>108.81</v>
       </c>
       <c r="AF8">
-        <v>-10.49</v>
+        <v>-50.6</v>
       </c>
       <c r="AG8">
-        <v>4541.83</v>
+        <v>4512.52</v>
       </c>
       <c r="AH8">
-        <v>4156.95</v>
+        <v>4150.72</v>
       </c>
       <c r="AI8">
         <v>4473.44</v>
@@ -1773,7 +1720,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>32.44</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1784,10 +1731,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10979</v>
+        <v>11000</v>
       </c>
       <c r="D9">
-        <v>0.72</v>
+        <v>0.19</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1796,46 +1743,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-15.88</v>
+        <v>-15.72</v>
       </c>
       <c r="H9">
-        <v>5.95</v>
+        <v>6.16</v>
       </c>
       <c r="I9">
-        <v>-2.63</v>
+        <v>-3.58</v>
       </c>
       <c r="J9">
-        <v>-7.67</v>
+        <v>-6.03</v>
       </c>
       <c r="K9">
-        <v>-1.24</v>
+        <v>-4.06</v>
       </c>
       <c r="L9">
-        <v>-13.31</v>
+        <v>-12.5</v>
       </c>
       <c r="M9">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P9">
-        <v>11094.2</v>
+        <v>11012.6</v>
       </c>
       <c r="Q9">
-        <v>11419.4</v>
+        <v>11388.45</v>
       </c>
       <c r="R9">
-        <v>11670.08</v>
+        <v>11655.62</v>
       </c>
       <c r="S9">
-        <v>11753.07</v>
+        <v>11750.17</v>
       </c>
       <c r="T9">
-        <v>-6.59</v>
+        <v>-6.38</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1850,34 +1797,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>32.69</v>
+        <v>33.71</v>
       </c>
       <c r="Z9">
-        <v>-187.26</v>
+        <v>-193.78</v>
       </c>
       <c r="AA9">
-        <v>-126.01</v>
+        <v>-139.56</v>
       </c>
       <c r="AB9">
-        <v>-61.25</v>
+        <v>-54.22</v>
       </c>
       <c r="AC9">
-        <v>5.96</v>
+        <v>13.51</v>
       </c>
       <c r="AD9">
-        <v>6.91</v>
+        <v>6.49</v>
       </c>
       <c r="AE9">
-        <v>183.95</v>
+        <v>190.1</v>
       </c>
       <c r="AF9">
-        <v>7.15</v>
+        <v>-10.72</v>
       </c>
       <c r="AG9">
-        <v>11895.42</v>
+        <v>11889.65</v>
       </c>
       <c r="AH9">
-        <v>10943.38</v>
+        <v>10887.25</v>
       </c>
       <c r="AI9">
         <v>11470.36</v>
@@ -1886,7 +1833,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>43.31</v>
+        <v>43.78</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +1974,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2085,1227 +2032,1124 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-2.66</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-3.12</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-10.97</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-11.09</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.34</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.76</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-5.98</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-6.19</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>10.37</v>
+      </c>
+      <c r="D11" s="6">
+        <v>10.81</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-2.73</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1.18</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-2.96</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-7.54</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-4.58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-7.67</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-6.03</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-2.45</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-4.78</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-5.73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.27</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-1.21</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-2.92</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-3.32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-0.33</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-3.23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>6.61</v>
+      </c>
+      <c r="D20" s="6">
+        <v>10.18</v>
+      </c>
+      <c r="E20" s="8">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-2.73</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-3.06</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-2.63</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-3.58</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>38.46</v>
+      </c>
+      <c r="D23" s="6">
+        <v>36.35</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-42.73</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-44.62</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>18.36</v>
+      </c>
+      <c r="D25" s="6">
+        <v>17.38</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>37.26</v>
+      </c>
+      <c r="D26" s="6">
+        <v>32.12</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-5.14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>104.39</v>
+      </c>
+      <c r="D27" s="6">
+        <v>105.91</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>118.55</v>
+      </c>
+      <c r="D28" s="6">
+        <v>128.33</v>
+      </c>
+      <c r="E28" s="8">
+        <v>9.779999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-17.73</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-19.34</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-13.31</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-12.5</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>11.7</v>
+      </c>
+      <c r="D31" s="6">
+        <v>7.28</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-4.42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-15.04</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-17.37</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>6.87</v>
+      </c>
+      <c r="D33" s="6">
+        <v>3.71</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-3.16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-0.74</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-3.2</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-2.46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-0</v>
+      </c>
+      <c r="D35" s="6">
+        <v>0.13</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>7.29</v>
+      </c>
+      <c r="D36" s="6">
+        <v>4.25</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-1.22</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-4.31</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-1.24</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-4.06</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-2.82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>-1.76</v>
-      </c>
-      <c r="D13" s="8">
-        <v>-2.66</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-5.82</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-6.99</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>-12.45</v>
-      </c>
-      <c r="D14" s="8">
-        <v>-10.97</v>
-      </c>
-      <c r="E14" s="10">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-45.56</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-46.04</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>-0.67</v>
-      </c>
-      <c r="D15" s="8">
-        <v>0.34</v>
-      </c>
-      <c r="E15" s="10">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-1.82</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-2.92</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8">
-        <v>-2.12</v>
-      </c>
-      <c r="D16" s="8">
-        <v>-5.98</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-3.86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-11.8</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-14.63</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-2.83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="8">
-        <v>20.4</v>
-      </c>
-      <c r="D17" s="8">
-        <v>10.37</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-10.03</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-4.49</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-4.04</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="8">
-        <v>-6.48</v>
-      </c>
-      <c r="D18" s="8">
-        <v>-2.73</v>
-      </c>
-      <c r="E18" s="10">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-15.37</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-13.72</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-6.39</v>
-      </c>
-      <c r="D19" s="8">
-        <v>-2.96</v>
-      </c>
-      <c r="E19" s="10">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-27.09</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-27.85</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="8">
-        <v>-7.47</v>
-      </c>
-      <c r="D20" s="8">
-        <v>-7.67</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-15.88</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-15.72</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="8">
-        <v>0.74</v>
-      </c>
-      <c r="D21" s="8">
-        <v>-0.5</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>400</v>
+      </c>
+      <c r="D47" s="6">
+        <v>395</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>1.7</v>
-      </c>
-      <c r="D22" s="8">
-        <v>0.95</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>50.89</v>
+      </c>
+      <c r="D48" s="6">
+        <v>50.44</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="D23" s="8">
-        <v>0.27</v>
-      </c>
-      <c r="E23" s="10">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>3319</v>
+      </c>
+      <c r="D49" s="6">
+        <v>3281.9</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-37.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="8">
-        <v>1.7</v>
-      </c>
-      <c r="D24" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>1014</v>
+      </c>
+      <c r="D50" s="6">
+        <v>981.5</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-32.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="8">
-        <v>6.81</v>
-      </c>
-      <c r="D25" s="8">
-        <v>2.9</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-3.91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>14.9</v>
+      </c>
+      <c r="D51" s="6">
+        <v>14.97</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="8">
-        <v>2.48</v>
-      </c>
-      <c r="D26" s="8">
-        <v>6.61</v>
-      </c>
-      <c r="E26" s="10">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>11.78</v>
+      </c>
+      <c r="D52" s="6">
+        <v>12.01</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="8">
-        <v>-4.98</v>
-      </c>
-      <c r="D27" s="8">
-        <v>-2.73</v>
-      </c>
-      <c r="E27" s="10">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>4235.8</v>
+      </c>
+      <c r="D53" s="6">
+        <v>4191.6</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-44.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="8">
-        <v>-4.33</v>
-      </c>
-      <c r="D28" s="8">
-        <v>-2.63</v>
-      </c>
-      <c r="E28" s="10">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>10979</v>
+      </c>
+      <c r="D54" s="6">
+        <v>11000</v>
+      </c>
+      <c r="E54" s="8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="8">
-        <v>42.3</v>
-      </c>
-      <c r="D29" s="8">
-        <v>38.46</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-3.84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>47.23</v>
+      </c>
+      <c r="D55" s="6">
+        <v>43.4</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-3.83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="8">
-        <v>-40.26</v>
-      </c>
-      <c r="D30" s="8">
-        <v>-42.73</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-2.47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>34.19</v>
+      </c>
+      <c r="D56" s="6">
+        <v>32.79</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="8">
-        <v>17.69</v>
-      </c>
-      <c r="D31" s="8">
-        <v>18.36</v>
-      </c>
-      <c r="E31" s="10">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>55.96</v>
+      </c>
+      <c r="D57" s="6">
+        <v>50.53</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-5.43</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="8">
-        <v>38.06</v>
-      </c>
-      <c r="D32" s="8">
-        <v>37.26</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>48.07</v>
+      </c>
+      <c r="D58" s="6">
+        <v>39.07</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="8">
-        <v>114.66</v>
-      </c>
-      <c r="D33" s="8">
-        <v>104.39</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-10.27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>56.14</v>
+      </c>
+      <c r="D59" s="6">
+        <v>56.93</v>
+      </c>
+      <c r="E59" s="8">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="8">
-        <v>117.51</v>
-      </c>
-      <c r="D34" s="8">
-        <v>118.55</v>
-      </c>
-      <c r="E34" s="10">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>55.61</v>
+      </c>
+      <c r="D60" s="6">
+        <v>59.33</v>
+      </c>
+      <c r="E60" s="8">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="8">
-        <v>-19.82</v>
-      </c>
-      <c r="D35" s="8">
-        <v>-17.73</v>
-      </c>
-      <c r="E35" s="10">
-        <v>2.09</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>42.72</v>
+      </c>
+      <c r="D61" s="6">
+        <v>40.04</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-2.68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="8">
-        <v>-13.5</v>
-      </c>
-      <c r="D36" s="8">
-        <v>-13.31</v>
-      </c>
-      <c r="E36" s="10">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>32.69</v>
+      </c>
+      <c r="D62" s="6">
+        <v>33.71</v>
+      </c>
+      <c r="E62" s="8">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="8">
-        <v>18.84</v>
-      </c>
-      <c r="D37" s="8">
-        <v>11.7</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-7.14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-52.8</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-44</v>
+      </c>
+      <c r="E63" s="8">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="8">
-        <v>-11.86</v>
-      </c>
-      <c r="D38" s="8">
-        <v>-15.04</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-3.18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-40.2</v>
+      </c>
+      <c r="D64" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="E64" s="8">
+        <v>40.56</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="8">
-        <v>6.81</v>
-      </c>
-      <c r="D39" s="8">
-        <v>6.87</v>
-      </c>
-      <c r="E39" s="10">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>-11.97</v>
+      </c>
+      <c r="D65" s="6">
+        <v>-54.75</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-42.78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="D40" s="8">
-        <v>-0.74</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>-35.54</v>
+      </c>
+      <c r="D66" s="6">
+        <v>55.57</v>
+      </c>
+      <c r="E66" s="8">
+        <v>91.11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="8">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="D41" s="8">
-        <v>-0</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-9.529999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>74.97</v>
+      </c>
+      <c r="D67" s="6">
+        <v>6.72</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-68.25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="8">
-        <v>10.42</v>
-      </c>
-      <c r="D42" s="8">
-        <v>7.29</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-3.13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>54.9</v>
+      </c>
+      <c r="D68" s="6">
+        <v>336.55</v>
+      </c>
+      <c r="E68" s="8">
+        <v>281.65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="8">
-        <v>-2.35</v>
-      </c>
-      <c r="D43" s="8">
-        <v>-1.22</v>
-      </c>
-      <c r="E43" s="10">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>-10.49</v>
+      </c>
+      <c r="D69" s="6">
+        <v>-50.6</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-40.11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="D44" s="8">
-        <v>-1.24</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="8">
-        <v>-45.09</v>
-      </c>
-      <c r="D45" s="8">
-        <v>-45.56</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="8">
-        <v>-2.38</v>
-      </c>
-      <c r="D46" s="8">
-        <v>-1.82</v>
-      </c>
-      <c r="E46" s="10">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="8">
-        <v>-10.68</v>
-      </c>
-      <c r="D47" s="8">
-        <v>-11.8</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="8">
-        <v>-0.51</v>
-      </c>
-      <c r="D48" s="8">
-        <v>-4.49</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-3.98</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="8">
-        <v>-17.03</v>
-      </c>
-      <c r="D49" s="8">
-        <v>-15.37</v>
-      </c>
-      <c r="E49" s="10">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="8">
-        <v>-29.26</v>
-      </c>
-      <c r="D50" s="8">
-        <v>-27.09</v>
-      </c>
-      <c r="E50" s="10">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="8">
-        <v>-16.49</v>
-      </c>
-      <c r="D51" s="8">
-        <v>-15.88</v>
-      </c>
-      <c r="E51" s="10">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="8">
-        <v>51.33</v>
-      </c>
-      <c r="D52" s="8">
-        <v>50.89</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="8">
-        <v>3300</v>
-      </c>
-      <c r="D53" s="8">
-        <v>3319</v>
-      </c>
-      <c r="E53" s="10">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="8">
-        <v>1026.9</v>
-      </c>
-      <c r="D54" s="8">
-        <v>1014</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-12.9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="8">
-        <v>15.52</v>
-      </c>
-      <c r="D55" s="8">
-        <v>14.9</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="8">
-        <v>11.55</v>
-      </c>
-      <c r="D56" s="8">
-        <v>11.78</v>
-      </c>
-      <c r="E56" s="10">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="8">
-        <v>4109.8</v>
-      </c>
-      <c r="D57" s="8">
-        <v>4235.8</v>
-      </c>
-      <c r="E57" s="10">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="8">
-        <v>10900</v>
-      </c>
-      <c r="D58" s="8">
-        <v>10979</v>
-      </c>
-      <c r="E58" s="10">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="8">
-        <v>99</v>
-      </c>
-      <c r="D59" s="8">
-        <v>87</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="8">
-        <v>87</v>
-      </c>
-      <c r="D60" s="8">
-        <v>99</v>
-      </c>
-      <c r="E60" s="10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="8">
-        <v>35.58</v>
-      </c>
-      <c r="D61" s="8">
-        <v>34.19</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="8">
-        <v>53.59</v>
-      </c>
-      <c r="D62" s="8">
-        <v>55.96</v>
-      </c>
-      <c r="E62" s="10">
-        <v>2.37</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="8">
-        <v>52.53</v>
-      </c>
-      <c r="D63" s="8">
-        <v>48.07</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-4.46</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="8">
-        <v>66.06999999999999</v>
-      </c>
-      <c r="D64" s="8">
-        <v>56.14</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-9.93</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="8">
-        <v>51.5</v>
-      </c>
-      <c r="D65" s="8">
-        <v>55.61</v>
-      </c>
-      <c r="E65" s="10">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="8">
-        <v>30.38</v>
-      </c>
-      <c r="D66" s="8">
-        <v>42.72</v>
-      </c>
-      <c r="E66" s="10">
-        <v>12.34</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="8">
-        <v>28.86</v>
-      </c>
-      <c r="D67" s="8">
-        <v>32.69</v>
-      </c>
-      <c r="E67" s="10">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B68" s="7" t="s">
+      <c r="B70" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C68" s="8">
-        <v>-29.68</v>
-      </c>
-      <c r="D68" s="8">
-        <v>-52.8</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-23.12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="8">
-        <v>-55.8</v>
-      </c>
-      <c r="D69" s="8">
-        <v>-40.2</v>
-      </c>
-      <c r="E69" s="10">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="8">
-        <v>-28.82</v>
-      </c>
-      <c r="D70" s="8">
-        <v>-11.97</v>
-      </c>
-      <c r="E70" s="10">
-        <v>16.85</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="8">
-        <v>-5.52</v>
-      </c>
-      <c r="D71" s="8">
-        <v>-35.54</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-30.02</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="8">
-        <v>5.02</v>
-      </c>
-      <c r="D72" s="8">
-        <v>74.97</v>
-      </c>
-      <c r="E72" s="10">
-        <v>69.95</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="8">
-        <v>19.69</v>
-      </c>
-      <c r="D73" s="8">
-        <v>54.9</v>
-      </c>
-      <c r="E73" s="10">
-        <v>35.21</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="8">
-        <v>717.89</v>
-      </c>
-      <c r="D74" s="8">
-        <v>-10.49</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-728.38</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="8">
-        <v>32.25</v>
-      </c>
-      <c r="D75" s="8">
+      <c r="C70" s="6">
         <v>7.15</v>
       </c>
-      <c r="E75" s="9">
-        <v>-25.1</v>
+      <c r="D70" s="6">
+        <v>-10.72</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-17.87</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3325,60 +3169,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>90</v>
+      <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="11">
         <v>56.44</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="12">
         <v>8</v>
       </c>
-      <c r="D2" s="13">
-        <v>46.6</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="D2" s="11">
+        <v>44.5</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F2" s="13">
-        <v>-2.8</v>
-      </c>
-      <c r="G2" s="13">
-        <v>1</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="F2" s="11">
+        <v>-2.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-1.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -3480,55 +3324,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="16">
-        <v>0.2879</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.1802</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.1691</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.1619</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.1341</v>
-      </c>
-      <c r="F2" s="16">
-        <v>0.0718</v>
-      </c>
-      <c r="G2" s="16">
-        <v>-0.2514</v>
-      </c>
-      <c r="H2" s="16">
-        <v>-0.3074</v>
+      <c r="A2" s="14">
+        <v>0.2845</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1776</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1614</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1592</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1351</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0722</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2526</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.3046</v>
       </c>
     </row>
   </sheetData>
